--- a/Treinamento/GestaoReclamacao.xlsx
+++ b/Treinamento/GestaoReclamacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6F12C2-421F-452D-9FC1-AD9D4556FD62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6773543-A9D8-4A03-87CF-3595DFB12D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B1A77FD5-2AD3-4458-ACB3-7F19D1A3340A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="163">
   <si>
     <t>Id HugMe</t>
   </si>
@@ -122,13 +122,13 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>93977606</t>
-  </si>
-  <si>
-    <t>237026743</t>
-  </si>
-  <si>
-    <t>08/01/2026 10:20</t>
+    <t>94057666</t>
+  </si>
+  <si>
+    <t>237140591</t>
+  </si>
+  <si>
+    <t>09/01/2026 09:32</t>
   </si>
   <si>
     <t>Não respondido</t>
@@ -137,7 +137,7 @@
     <t>Não</t>
   </si>
   <si>
-    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; 1 Segurado ; OUV ; Sim ; 1 Ctt Sem Sucesso ; Ouv/Procon</t>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; Reclamante em nome do Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
     <t>Allianz</t>
@@ -155,406 +155,657 @@
     <t>Guincho</t>
   </si>
   <si>
+    <t>Reclamante em nome do Segurado</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>1 Ctt Sem Sucesso</t>
+  </si>
+  <si>
+    <t>Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131467908_x000D_
+</t>
+  </si>
+  <si>
+    <t>No dia 31/12/2025, meu veículo apresentou problemas mecânicos. No dia seguinte, 01/01/2026, acionei a seguradora, que prontamente enviou um guincho para rebocar o veículo  até então, tudo ocorreu corretamente._x000D_
+_x000D_
+_x000D_
+Ainda no dia seguinte, foi disponibilizado um táxi para que eu e minha família retornássemos para casa, visto que estávamos longe_x000D_
+_x000D_
+_x000D_
+A seguradora informou que o veículo seria entregue na oficina mecânica indicada por mim até o dia 05/01/2026 às 18h.  (trajeto de Cascavel/PR até Blumenau/SC)._x000D_
+_x000D_
+_x000D_
+O carro não chegou na segunda-feira (05/01). Ao entrar em contato, fui informado de que houve um atraso e que a entrega ocorreria no dia 06/01._x000D_
+_x000D_
+_x000D_
+Diante da situação, acionei meu corretor de seguros para auxiliar no caso. No entanto, no dia 07/01 o veículo novamente não foi entregue. Às 15h, a seguradora informou que o carro estaria a aproximadamente 1h30 de Blumenau, mas mesmo assim não houve entrega._x000D_
+_x000D_
+_x000D_
+No dia seguinte (08/01), garantiram que o veículo chegaria até o meio-dia na mecânica, o que não aconteceu. Posteriormente, informaram que o carro estaria em Joinville e que a entrega ocorreria até o final do dia  novamente, não ocorreu._x000D_
+_x000D_
+_x000D_
+Hoje, 09/01, sigo sem qualquer informação concreta sobre onde está o meu veículo. A seguradora se recusa a liberar carro reserva enquanto o veículo não chega, porém eu preciso trabalhar, estou sendo prejudicado profissionalmente e ninguém sabe informar a real localização do carro, nem mesmo se ele ainda está sob posse da empresa responsável pelo transporte._x000D_
+_x000D_
+_x000D_
+Considero a situação extremamente grave, com falha clara de comunicação, logística e suporte ao cliente.</t>
+  </si>
+  <si>
+    <t>94062582</t>
+  </si>
+  <si>
+    <t>237152735</t>
+  </si>
+  <si>
+    <t>09/01/2026 10:55</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Residência</t>
+  </si>
+  <si>
+    <t>Assistência Residencial</t>
+  </si>
+  <si>
     <t>1 Segurado</t>
   </si>
   <si>
-    <t>OUV</t>
-  </si>
-  <si>
-    <t>Sim</t>
-  </si>
-  <si>
-    <t>1 Ctt Sem Sucesso</t>
-  </si>
-  <si>
-    <t>Ouv/Procon</t>
+    <t xml:space="preserve">134531315_x000D_
+</t>
+  </si>
+  <si>
+    <t>Pacote de serviços da Allianz não funciona. Marcam, não comparecem  e nem dão satisfação. Me sinto enganada._x000D_
+_x000D_
+Marcado em novembro para dia 27/12, fiz novo agendamento para 7/12 e nada.</t>
+  </si>
+  <si>
+    <t>94069199</t>
+  </si>
+  <si>
+    <t>237169481</t>
+  </si>
+  <si>
+    <t>09/01/2026 12:53</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Sinistro</t>
+  </si>
+  <si>
+    <t>Análise Sinistro</t>
   </si>
   <si>
     <t>Andreza</t>
   </si>
   <si>
-    <t xml:space="preserve">134430872_x000D_
+    <t xml:space="preserve">303412830_x000D_
 </t>
   </si>
   <si>
-    <t>Precisei do serviço de guincho para meu carro e desde domingo na parte da manhã dia 04/01/2025, o guincho retirou meu carro e não me entregaram o veículo até hoje dia 08/01/2025. Estou em Goiânia esperando para resolver o defeito do carro na oficina e o não tenho nenhuma informação clara sobre o carro. É um absurdo demorar tanto para entregar o carro e o pior é o atendimento da ouvidoria dessa seguradora. (não estão dispostos a ouvir). Atendimento somente com um robô, mas para vender seguro e emitir boletos estão com vários humanos disponíveis. O serviço de táxi também foi péssimo, combinamos de sair as 05:00 horas e o motorista só chegou as 05:45 depois de eu avisar que a partir das 06:00 eu não iria esperar mais. Ele chegou ás 05:45 depois passou na casa dele para pegar seu pertences. (já nos deixou estressado no início de uma viajem longa).  Pagando pelo seguro por longos 16 anos, não esperava serviços tão ruins.</t>
-  </si>
-  <si>
-    <t>93982273</t>
-  </si>
-  <si>
-    <t>237037417</t>
-  </si>
-  <si>
-    <t>08/01/2026 11:23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132377449_x000D_
+    <t>Sofri um acidente dia 03/12/25, no qual levou a minha moto ter perda total, no dia 12/02/2025 foi aberto o sinistro, enviei todas a documentação necessária, juntamente com a carta e boleto de quitação, eles não pagaram o mesmo depois, quando o boleto expirou, pediram outro após alguns dias, me levando a perda do valor da moto, estou aguardando o pagamento até hoje, 09/01/2026! Allianz segurado não tem a menor preocupação por seus clientes!</t>
+  </si>
+  <si>
+    <t>94070814</t>
+  </si>
+  <si>
+    <t>237173479</t>
+  </si>
+  <si>
+    <t>09/01/2026 13:24</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Pagamento ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso</t>
+  </si>
+  <si>
+    <t>Pagamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135133758_x000D_
 </t>
   </si>
   <si>
-    <t>Eu, Monica Pancera Berthi, sou cliente desta seguradora através da apólice 5177202535310880074, seguro que iniciou em 02/05/2025 originalmente com veículo Nissan Kicks S Mec 2020, placas BEH3I22. No dia 23/12/2025 pela manhã esse veiculo foi abalroado por outra pessoa que tem seguro e ele acionou para pagar os prejuízos ao meu Kicks. Decidi passar o seguro do Kicks para uma S10 no mesmo dia pela tarde para que a gente não ficasse sem carro para andar no fim do ano enquanto eram feitos processos de vistoria e outras burocracias por parte da seguradora do rapaz que causou o acidente. _x000D_
-_x000D_
-No entanto, 2 ou 3 dias depois, ao ligar na central de assistência 24h e pedir guincho para que o Kicks batido fosse levado para a oficina, já diziam que não encontravam nada de Kicks no sistema, aparecia apenas a S10. E a mesma coisa agora que estou solicitando os 07 dias de carro reserva por ser terceira em sinistro de outra seguradora. Meu corretor não consegue nem abrir reclamado no SAC pois o atendente insiste que não tem Kicks no sistema. Ouvidoria não dá retorno._x000D_
-_x000D_
-Reitero: desejo as assistências para o veículo Kicks placas BEH3I22 que teve sinistro como terceiro em outra seguradora dia 23/12, e a apólice teve alteração para outro veículo ao fim do mesmo dia.</t>
-  </si>
-  <si>
-    <t>93995989</t>
-  </si>
-  <si>
-    <t>237072163</t>
-  </si>
-  <si>
-    <t>08/01/2026 15:22</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Residência</t>
-  </si>
-  <si>
-    <t>Assistência Residencial</t>
-  </si>
-  <si>
-    <t>Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133210895_x000D_
+    <t>Fiz o cancelamento da minha apólice, 03.01.2026, mas quando fiz o cancelamento o atendente me disse, que eu nao devia nenhuma parcela do seguro. Portanto verifiquei na fatura do meu cartão de crédito o lançamento da parcela do seguro de R$ 106,99.</t>
+  </si>
+  <si>
+    <t>94075531</t>
+  </si>
+  <si>
+    <t>237185817</t>
+  </si>
+  <si>
+    <t>09/01/2026 14:56</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Repasse Time MindBe</t>
+  </si>
+  <si>
+    <t>Micaele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131716973_x000D_
 </t>
   </si>
   <si>
-    <t>tenho seguro allianz e solicitei o servico de encanador para o dia 08/01 das 13h as 18h. _x000D_
-_x000D_
-a minha esposa o recebeu e pedimos para trocar os registros dos banheiros, ele comecou a reclamar , que disse que teria que fechar o registro da caixa dagua e que era responsabilidade minha fechar o registro, _x000D_
-_x000D_
-o tecnico chegou as 12:30h. com pressa, e disse que nao tinha como trocar os registros sem peca,_x000D_
-_x000D_
-pedi para ele verificar qual o modelo do registro e ele disse que era para eu solicitar uma nova assistencia para troca de pecas. _x000D_
-_x000D_
-1 - como vou comprar a peca para trocar se nem ele desmontou e nao sabe qual modelo de peca é?_x000D_
-_x000D_
-2 - como vou remarcar e deixar a caixa fechada e ele nao sabe qual o problema. _x000D_
-_x000D_
-_x000D_
-eu tinha seguro da porto seguro e os tecnicos da porto seguro , nao ficavam colocando dificuldades, e reclamando do servico, _x000D_
-_x000D_
-_x000D_
-se a allianz paga pouco para o tecnico fazer o servico, e ficar reclamando com o cliente, que nao passem o servico para eles, e contratem quem quer trabalhar, ao inves de resolver o meu  problema , ele criou outro e muito mais insatisfeito com o atendimento da allianz. _x000D_
-_x000D_
-atendimento n. 51089194</t>
-  </si>
-  <si>
-    <t>93997387</t>
-  </si>
-  <si>
-    <t>237075085</t>
-  </si>
-  <si>
-    <t>08/01/2026 15:45</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; 1 Segurado ; Não ; Sim ; Sem Resposta - Dentro SLA ; 1 Ctt Sem Sucesso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132153531_x000D_
+    <t xml:space="preserve">No dia 19/11/2025, registrei o protocolo n 50669443 para acionar o serviço de consulta pet, contudo até o momento não recebi o reembolso por motivos diversos:_x000D_
+_x000D_
+1 - atendente não seguiu o procedimento correto para a solicitação do reembolso, me enviou um link para preenchimento dos dados, quando o correto seria o envio de um formulário para preenchimento. Desta forma, foi negado porque o meio de envio estava errado;_x000D_
+_x000D_
+2 - enviado o formulário correto, foi autorizado o pagamento para 10/12/2025, como não aconteceu entrei em contato para saber o motivo e fui informada de que os dados bancários estavam errados, neste caso, erro meu;_x000D_
+_x000D_
+3 - Em 19/12/2025 me enviaram um e-mail para confirmação de dados, o que foi respondido no mesmo dia e mais uma vez fiquei sem retorno e sem reembolso;_x000D_
+_x000D_
+4 - No dia 05/01/2026, pediram para que eu enviasse toda a documentação novamente, o que foi feito, e me informaram que em 48h o problema seria resolvido. No mesmo dia, responderam meu e-mail falando que iriam reprocessar a data de pagamento e até o momento nada._x000D_
+_x000D_
+Perdi a conta de quantas vezes liguei para solicitar informações e esclarecimentos. A única coisa que fazem é alegar que estão passando o caso para revisão e que darão prioridade e nada fazem._x000D_
+_x000D_
+Estou acionando esse canal para talvez conseguir um retorno efetivo e uma consideração, mediante tanto descaso._x000D_
+_x000D_
+Ressalto que meu seguro Residencial sempre foi Allianz e que nunca tive problemas com esse tipo de serviço, somente com os prestadores de serviços que eles enviam e que sempre arrumam desculpas para dificultar e não fazer o serviço e ainda assim receber pela visita._x000D_
+_x000D_
 </t>
   </si>
   <si>
-    <t>Prezados, abrimos um chamado de reembolso de consulta veterinária e também cremação para o PET  em 09/12 e até agora ninguém respondeu, um desleixo com o segurado. _x000D_
-_x000D_
-Protocolo Assistência: Protocolo 50572981</t>
-  </si>
-  <si>
-    <t>94001160</t>
-  </si>
-  <si>
-    <t>237081605</t>
-  </si>
-  <si>
-    <t>08/01/2026 16:32</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Residência ; Sinistro ; Indenização ; 1 Segurado ; OUV ; Sim ; 1 Ctt Sem Sucesso ; Ouv/Procon</t>
-  </si>
-  <si>
-    <t>Sinistro</t>
-  </si>
-  <si>
-    <t>Indenização</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302602022_x000D_
+    <t>94075734</t>
+  </si>
+  <si>
+    <t>237186305</t>
+  </si>
+  <si>
+    <t>09/01/2026 14:59</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Guincho ; Reclamante em nome do Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131182521_x000D_
 </t>
   </si>
   <si>
-    <t>Contratei o seguro Allianz Residência e estou no segundo ano de vigência. Em 21 de novembro de 2025, uma árvore da via pública caiu e atingiu diretamente a frente do meu imóvel, causando dano material direto, comprovado por fotos e documentos._x000D_
-_x000D_
-_x000D_
-A Allianz negou a indenização por duas vezes. Na primeira negativa, alegou inexistência de vendaval (54 km/h), com base em dados do INMET  Mirante de Santana. Solicitei reavaliação esclarecendo que o pedido não se baseava em vendaval, mas no dano direto causado pela queda da árvore, destacando que o Manual do Segurado não exclui expressamente cobertura para esse tipo de evento._x000D_
-_x000D_
-_x000D_
-Mesmo assim, a seguradora negou a reavaliação e manteve a resposta anterior, repetindo o mesmo argumento, sem analisar o novo enquadramento solicitado e sem indicar cláusula contratual que exclua a cobertura._x000D_
-_x000D_
-_x000D_
-Ressalto que, conforme o Código de Defesa do Consumidor, exclusões e limitações de cobertura devem ser claras e expressas no contrato, o que não ocorre neste caso. Negar a indenização apenas alegando ausência de vendaval não supre a obrigação de informação clara ao consumidor._x000D_
-_x000D_
-_x000D_
-Já registrei reclamações no consumidor.gov, SUSEP e Procon. Solicito a reavaliação correta do sinistro e o pagamento da indenização devida, ou a indicação clara da cláusula contratual que exclua esse evento._x000D_
-_x000D_
-Eu esperava algo melhor desse seguro, tomem cuidade, estou preso a uma informação mal fornecida, e utilizam a mesma para negar o pagamento do sinistro. Tenho doxcumentos da conversa e sua negativa, solicitação de reavaliação do sinistro e sua negativa, fotografias da destruição causada pela queda da árvore e que passou por vistoria da seguradora após a queda da árvore.</t>
-  </si>
-  <si>
-    <t>94011833</t>
-  </si>
-  <si>
-    <t>237094719</t>
-  </si>
-  <si>
-    <t>08/01/2026 18:17</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Gestão de Oficina ; 2 Terceiro do Sinistro ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Gestão de Oficina</t>
+    <t>No dia 07/01/2025 (quarta-feira), por volta das 14h, o veículo RZL9C59 apresentou falha grave e ficou completamente inoperante durante uma viagem, a aproximadamente 340 km de Recife. Eu estava com meu marido, duas filhas menores, um cachorro (PET) e várias bagagens._x000D_
+_x000D_
+_x000D_
+Acionamos imediatamente a Assistência 24h da Allianz, solicitando inicialmente um mecânico e, em seguida, guincho para remoção do veículo até nossa oficina de confiança em Recife, além de transporte para minha família._x000D_
+_x000D_
+_x000D_
+O guincho chegou apenas por volta das 15h30. Logo após, foi enviado um Fiat pequeno, totalmente incompatível com a quantidade de pessoas, malas e o PET. Desde o primeiro contato informamos claramente à Allianz que seria necessário um veículo grande e adequado, o que foi ignorado._x000D_
+_x000D_
+_x000D_
+Além de não comportar todos com segurança, o veículo estava em condições precárias, com pneu careca, o que nos colocaria em risco real em uma viagem de mais de 300 km. O transporte foi corretamente recusado por falta de segurança._x000D_
+_x000D_
+_x000D_
+A Allianz informou que enviaria outro veículo, porém nos manteve em espera das 15h30 até aproximadamente 18h, com duas crianças e um PET, em situação de total vulnerabilidade, em um restaurante simples de beira de estrada, apenas porque tivemos a sorte de o carro ter quebrado próximo a ele._x000D_
+_x000D_
+_x000D_
+Somente após mais de 5 horas de espera chegou um Volkswagen Virtus, que comportava as bagagens, porém obrigou nosso PET a viajar no colo, o que é ilegal e inseguro, mesmo a Allianz tendo sido informada desde o início sobre a presença do animal._x000D_
+_x000D_
+_x000D_
+A Allianz:_x000D_
+_x000D_
+Enviou veículo inadequado_x000D_
+_x000D_
+Ignorou informações essenciais_x000D_
+_x000D_
+Nos deixou abandonados por horas_x000D_
+_x000D_
+Colocou crianças e um animal em risco_x000D_
+_x000D_
+E ainda nos expôs a uma situação ilegal e insegura._x000D_
+_x000D_
+_x000D_
+Falha grave na prestação do serviço!_x000D_
+_x000D_
+_x000D_
+A conduta da Allianz configura:_x000D_
+_x000D_
+Descumprimento contratual_x000D_
+_x000D_
+Falha na prestação do serviço (art. 14 do CDC)_x000D_
+_x000D_
+Violação do dever de segurança_x000D_
+_x000D_
+Exposição indevida de crianças e animal a risco_x000D_
+_x000D_
+_x000D_
+A assistência 24h existe justamente para proteger o consumidor em situações de emergência, e a Allianz falhou completamente quando mais precisamos._x000D_
+_x000D_
+_x000D_
+Exijo:_x000D_
+_x000D_
+1.Indenização por danos morais sofridos por mim, minhas filhas e meu marido_x000D_
+_x000D_
+2.Ressarcimento integral de todos os prejuízos_x000D_
+_x000D_
+3.Resposta formal da Allianz explicando essa negligência_x000D_
+_x000D_
+_x000D_
+Possuo protocolos, registros de ligações, horários e localização e, caso não haja solução, levarei o caso ao Procon e ao Juizado Especial Cível.</t>
+  </si>
+  <si>
+    <t>94078876</t>
+  </si>
+  <si>
+    <t>237193509</t>
+  </si>
+  <si>
+    <t>09/01/2026 15:54</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Vidros - AutoGlass ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Vidros - AutoGlass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134286074_x000D_
+</t>
+  </si>
+  <si>
+    <t>Título da reclamação_x000D_
+_x000D_
+Cobrança indevida de franquia em duplicidade, prática abusiva e prejuízo ao trabalho  violação ao CDC_x000D_
+_x000D_
+Descrição da reclamação_x000D_
+_x000D_
+Sofri uma queda com minha motocicleta, ocasionando a quebra simultânea dos dois retrovisores, decorrente de um único evento, caracterizando apenas um fato gerador do sinistro._x000D_
+_x000D_
+Conforme consta em minha apólice da seguradora Allianz, há cobertura para retrovisores (no plural), com franquia no valor de R$ 65,00, sem qualquer distinção de lado (direito ou esquerdo) e sem previsão de cobrança por unidade. Em nenhum momento o contrato especifica franquia individualizada por retrovisor._x000D_
+_x000D_
+Enviei todas as fotos solicitadas, comprovando claramente que ambos os retrovisores foram danificados no mesmo acidente. Ainda assim, a seguradora informou que autorizaria apenas a troca do retrovisor do lado esquerdo. Ao acionar a ouvidoria da Allianz, fui informado de que deveria abrir um novo chamado para o retrovisor do lado direito e pagar outra franquia no valor de R$ 65,00, o que não encontra respaldo contratual._x000D_
+_x000D_
+Tal conduta configura cobrança indevida e prática abusiva, vedada pelo:_x000D_
+_x000D_
+Art. 39, inciso V, do Código de Defesa do Consumidor, que proíbe exigir vantagem manifestamente excessiva;_x000D_
+_x000D_
+Art. 51, inciso IV, do CDC, que considera nulas cláusulas que coloquem o consumidor em desvantagem exagerada;_x000D_
+_x000D_
+Art. 47 do CDC, que determina que as cláusulas contratuais devem ser interpretadas da maneira mais favorável ao consumidor;_x000D_
+_x000D_
+Art. 6, incisos III e VI, do CDC, que garantem o direito à informação clara e à reparação de danos;_x000D_
+_x000D_
+Art. 14 do CDC, que trata da responsabilidade objetiva do fornecedor pela falha na prestação do serviço._x000D_
+_x000D_
+Além da cobrança indevida, a situação vem me causando grave prejuízo financeiro, pois dependo da motocicleta para trabalhar. Ressalto ainda que retrovisor é item de segurança obrigatório, conforme a legislação de trânsito, e circular sem esse equipamento gera multa, pontos na CNH e retenção do veículo, o que me impede de exercer minha atividade profissional e me expõe a penalidades legais por falha que não foi causada por mim._x000D_
+_x000D_
+Portanto, a postura da seguradora não apenas descumpre o contrato e o CDC, como também agrava os prejuízos do consumidor, prolongando indevidamente a solução de um sinistro simples._x000D_
+_x000D_
+Diante do exposto, solicito:_x000D_
+_x000D_
+A autorização imediata da troca dos dois retrovisores, mediante o pagamento de uma única franquia, conforme previsto na apólice;_x000D_
+_x000D_
+A cessação da cobrança indevida em duplicidade;_x000D_
+_x000D_
+Um posicionamento formal e fundamentado, com base contratual e legal._x000D_
+_x000D_
+Caso não haja solução administrativa imediata, informo que buscarei meus direitos junto ao Procon, SUSEP e demais medidas judiciais cabíveis.</t>
+  </si>
+  <si>
+    <t>94080837</t>
+  </si>
+  <si>
+    <t>237198523</t>
+  </si>
+  <si>
+    <t>09/01/2026 16:35</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; 1 Segurado ; SAC Aberto ; Sim</t>
+  </si>
+  <si>
+    <t>SAC Aberto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134196079_x000D_
+</t>
+  </si>
+  <si>
+    <t>Benefício VIP - Seguradora Allianz insiste em gastar novo chamado de direito do cliente de um problema que não foi resolvido no primeiro chamado. A máquina de lavar roupas começou a bater forte, de forma anormal durante o processo de girar/centrifugar, quando vai retirando água da roupa. A Seguradora Allianz foi acionada pelo Benefício VIP desse tipo de eletrodoméstico que concede 2 (dois) chamados pelo ano de seguro. O técnico veio e solicitou comprar 4 (quatro) molas. Quando as molas compradas chegaram o técnico retornou e instalou. Mas no dia seguinte ao usar a máquina, o problema continuou. Avisei a Seguradora que reenviou o mesmo técnico. Esse mesmo técnico solicitou comprar então 4 (quatro) suspensões. Avisei a Seguradora, que por ser fim de ano, essas suspensões que foram compradas chegariam no início desse mês. Assim que essas peças chegaram avisei a Seguradora. Mas a Seguradora Allianz está informado que para o técnico vir dessa vez, estarei usando um novo chamado. Ora! O problema é o mesmo, o original. Se o técnico não foi capaz de solucionar, o cliente não tem culpa. Se a solução estava em molas+suspensão ou ainda QQ outra peça, o técnico tem que indicar já na primeira visita e solicitar a compra de todas as peças necessárias para consertar. Agora, se o técnico só indicou a compra de molas e vendo que não resolveram, solicita a compra de outras peças, o chamado é o mesmo, pois o problema é o mesmo e não foi resolvido desde então. Dessa forma, registro que a Seguradora Allianz para ser justa deverá considerar esse caso como um único chamado, solicitar que o técnico resolva o problema (se esse técnico não está conseguindo resolver, que o substituam) e não subtrair do cliente o direito de manter um segundo chamado para outra necessidade futura do cliente.</t>
+  </si>
+  <si>
+    <t>94087153</t>
+  </si>
+  <si>
+    <t>237217171</t>
+  </si>
+  <si>
+    <t>09/01/2026 19:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136187496_x000D_
+</t>
+  </si>
+  <si>
+    <t>Título_x000D_
+_x000D_
+Restrição indevida de assistência e indicação de prestador inadequado em seguro residencial._x000D_
+_x000D_
+_x000D_
+Relato_x000D_
+_x000D_
+Contratei seguro residencial da Allianz e solicitei assistência técnica para purificador de água da marca Latina, em razão de falhas de funcionamento que exigem troca de torneiras e substituição de filtros._x000D_
+_x000D_
+Ressalto que todas as peças já foram adquiridas por mim, são originais, compradas diretamente da fabricante. O pedido feito à seguradora refere-se exclusivamente à execução do serviço (mão de obra)._x000D_
+_x000D_
+A seguradora inicialmente negou integralmente o atendimento, alegando inexistência de vazamento. Após nova análise, passou a autorizar apenas parte da assistência (troca das torneiras), mantendo a restrição quanto aos filtros, sob a justificativa genérica de que se trataria de manutenção, sem apresentação de laudo técnico ou avaliação específica do equipamento._x000D_
+_x000D_
+Além disso, foi indicado prestador manifestamente inadequado ao serviço solicitado, um MEI de atuação genérica, sem comprovação de especialização técnica em purificadores de água, nem vínculo com o fabricante, o que considero incompatível com equipamento destinado ao consumo humano._x000D_
+_x000D_
+A restrição parcial da assistência, aliada à indicação de prestador tecnicamente inadequado, impõe interpretação excessivamente restritiva ao contrato, esvaziando a finalidade da cobertura assistencial do seguro residencial._x000D_
+_x000D_
+_x000D_
+Solução esperada_x000D_
+_x000D_
+_x000D_
+- Autorização para execução integral do serviço solicitado, inclusive substituição dos filtros, com as peças já fornecidas pela segurada;_x000D_
+_x000D_
+_x000D_
+- Indicação de prestador tecnicamente habilitado;_x000D_
+_x000D_
+_x000D_
+- Resposta formal, objetiva e devidamente fundamentada._x000D_
+_x000D_
+_x000D_
+Na ausência de solução adequada, o caso será encaminhado à SUSEP, para análise da conduta da seguradora.</t>
+  </si>
+  <si>
+    <t>94095883</t>
+  </si>
+  <si>
+    <t>237244871</t>
+  </si>
+  <si>
+    <t>10/01/2026 09:17</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Condomínio ; Apólice ; Pagamento ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Condomínio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134801540_x000D_
+</t>
+  </si>
+  <si>
+    <t>TENHO DOIS SEGUROS DE VEICULOS APÓLICES (TCROSS PLACA SOS4G47 E ARGO PLACA PLACA QYQ6H84), PARCELAS VENCENDO DIAS 23 E 31 DE CADA MÊS RESPECTIVAMENTE, COLOCADAS NO CARTÃO DE CRÉDITO VISA BLACK BB TERMINAÇÃO 5873. ACONTECE QUE AS COBRANÇAS SÃO FEITAS MUITO APÓS O VENCIMENTO E AS PARCELAS FICAM NO SISTEMA PENDENTES, TANTO É QUE A PARCELA 3, DO TCROS EU PAGUEI PELO APLICATIVO EM DEZEMBRO E SÓ AGORA ELA VEM CONSTANDO NO FATURA DO CARTÃO DE FEVEREIRO, OU SEJA ESSA FATURA VAI SER PAGA EM DUPLICIDADE. EU PAGUEI VIA PIX DIA 23 PELO APP E AGORA ELA ESTÁ NA FATURA DO CARTÃO.  A FATURA DO ARGO É A MESMA COISA E EU PRECISO URGENTE QUE SEJAM RETIRADAS DO CARTÃO E QUE EU POSSA CONTINUAR O PAGAMENTO PELO APP OU DÉBITO EM CONTA CORRENTE QUE EU FICO MAIS TRANQUILO._x000D_
+_x000D_
+PEÇO REVER ISSO E ME POSICIONAR, CASO CONTRÁRIO A RENOVAÇÃO NÃO SERA EFETUADA._x000D_
+_x000D_
+OBRIGADO</t>
+  </si>
+  <si>
+    <t>94102410</t>
+  </si>
+  <si>
+    <t>237265159</t>
+  </si>
+  <si>
+    <t>10/01/2026 13:27</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Atendimento Local ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Atendimento Local</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134655917_x000D_
+</t>
+  </si>
+  <si>
+    <t>Sofri um acidente grave de moto na argentina,fui socorrido e levado ao hospital nuestra senhora de lurdes,em Lujan,recebi os primeiros socorros,mas devido a gravidade das minhas fraturas precisaria ser levado ao Brasil para fazer o procedimento cirúrgico,meu advogado abriu o sinistro pela manha dia 02/02/2026 pedindo uma ambulância para me levar do hospital da argentina para o hospital no Brasil,nos pediram diversos documentos,nos quais todos foram encaminhados a seguradora,pediram inclusive minha alta medica pela manhã,dai para frente foram dezenas de ligações a seguradora,durante o dia 02/01/2026,medico no brasil agendado e leito hospitalar tambem,em todas as ligações era sempre a mesma resposta esta com o setor de analise,eu precisando de urgencia pois estou com 3 fraturas pelo corpo e necessito de cirurgia,fui tentando resolver com a seguradora ondia todo,no final do dia,a seguradora autorizou que eu chamasse um serviço de ambulância privado,que a seguradora se comprometeria em me fazer o reembolso desta despesa,pois se tratava de uma urgente e eles nao tinham uma precisão de liberação para me levar de um hospital,para outro e que entao se eu tivesse condições poderia arcar com o custo que seria pago pela seguradora,pois nao poderia mais esperar em um_x000D_
+_x000D_
+Local precario,inclusive antes de pegar o serviço particular da ambulância passei o valor ao atendente da seguradora,paguei o montante de 3900,000,00(tres milhões e novecentos mil,pesos argentinos,pois bem paguei a ambulância e voltei,a segunda parte do descaso veio agora na hora de pedir o reembolso esta acontecendo exatamente a mesma coisa que aconteceu quando estava atirado no hospital na argentina,todo quebrado e com dores,novamente para tentar o reembolso foram dezenas de ligações,mandei nota e toda documentação que me pediram no link de reembolso que mandaram via email e nada de retorno,quandro preenchi o formulário estava ali escrito que seria pago em ate 5 dias uteis,ja se passaram os dias nao tive resposta e muito menos o reembolso,uma hora ta com a celula vida da cia o meu caso,outra hora ta em analise,ou me mandam ligar para outro numero me jogam de um lado para o outro e nao resolvem de maneira alguma o meu problema,estou passando o mesmo descaso que passei quando estava mal no hospital eu so quero o meu reembolso que a mim foi prometido,pois a ambulância paguei caso contrário estaria ate agora tentando com a cia,ai gastei meu dinheiro e agora preciso para pagar as cirurgias que fiz para recuperar minhas fraturas.</t>
+  </si>
+  <si>
+    <t>94108787</t>
+  </si>
+  <si>
+    <t>237285465</t>
+  </si>
+  <si>
+    <t>10/01/2026 18:57</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; 1 Segurado ; Não ; Sim ; Sem Resposta - Dentro SLA ; 1 Ctt Sem Sucesso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135176972_x000D_
+</t>
+  </si>
+  <si>
+    <t>Venho por meio desta registrar minha profunda insatisfação e formalizar uma reclamação referente ao atendimento prestado pela Allianz Seguro em razão de um sinistro envolvendo minha motocicleta._x000D_
+_x000D_
+_x000D_
+O sinistro ocorreu na Argentina, a menos de 30 quilômetros da cidade de Salta, capital da província, região claramente coberta pelo meu plano de seguro, que prevê assistência em toda a América do Sul. Após acionar o seguro, permaneci mais de 4 horas exposto ao sol, sem qualquer retorno, orientação ou suporte efetivo por parte da seguradora._x000D_
+_x000D_
+_x000D_
+Diante da total ausência de contato e de soluções, fui obrigado a chamar um guincho por conta própria e levar a motocicleta até a cidade mais próxima. Somente após várias horas a Allianz entrou em contato, justificando a demora pelo fato de o sinistro ter ocorrido fora do Brasil  justificativa esta totalmente inaceitável, uma vez que a cobertura internacional consta expressamente no contrato._x000D_
+_x000D_
+_x000D_
+Além disso, também fui obrigado a realizar um reparo paliativo na motocicleta com recursos próprios, já que nenhum tipo de assistência foi oferecido naquele momento._x000D_
+_x000D_
+_x000D_
+Após retornar ao Brasil, ao chegar na cidade de Cascavel, a motocicleta voltou a apresentar problemas. Acreditei que, estando novamente em território nacional, o atendimento seria mais eficiente. No entanto, após duas horas de espera, o prestador de serviços chegou, constatou que a motocicleta deveria ser encaminhada para minha residência e, a partir daí, a situação tornou-se ainda mais absurda._x000D_
+_x000D_
+_x000D_
+O suporte da Allianz iniciou uma espécie de leilão com o prestador de serviços, discutindo valores de transporte, prolongando ainda mais a resolução do problema. Após essa negociação, o atendente ainda passou a verificar se eu retornaria de táxi ou de avião, mesmo depois de todo o tempo já transcorrido. Nesse momento, perdi a paciência, pois já estava há mais de 3 horas sob o sol, a poucos quilômetros de uma cidade, sem qualquer assistência adequada._x000D_
+_x000D_
+_x000D_
+Ressalto que há três anos pago o plano mais completo para minha motocicleta junto à Allianz, e, infelizmente, na primeira vez em que precisei do seguro, senti-me totalmente desamparado e desrespeitado, como se estivesse sendo enganado._x000D_
+_x000D_
+_x000D_
+Diante de todo o ocorrido, informo que buscarei meus direitos como consumidor, recorrendo aos órgãos competentes e às medidas legais cabíveis. Ademais, cancelarei o seguro e farei questão de relatar minha experiência negativa à comunidade de motociclistas e a amigos próximos, para que tenham ciência do tratamento recebido._x000D_
+_x000D_
+_x000D_
+Aguardo um posicionamento formal da Allianz, bem como as devidas explicações e providências sobre os fatos relatados._x000D_
+_x000D_
+_x000D_
+Atenciosamente,_x000D_
+_x000D_
+_x000D_
+Felipe Barbosa da Silva</t>
+  </si>
+  <si>
+    <t>94110641</t>
+  </si>
+  <si>
+    <t>237291223</t>
+  </si>
+  <si>
+    <t>10/01/2026 20:57</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133446931_x000D_
+</t>
+  </si>
+  <si>
+    <t>Sou segurado, nunca precisei usar, hoje na primeira fez, estou a mais de 4h parado na beira da rodovia castelo branco e a seguradora me diz que não consegue encontrar um guincho pra enviar. Uma vergonha!</t>
+  </si>
+  <si>
+    <t>94115924</t>
+  </si>
+  <si>
+    <t>237308267</t>
+  </si>
+  <si>
+    <t>11/01/2026 10:12</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Guincho ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135231744_x000D_
+</t>
+  </si>
+  <si>
+    <t>Meu veículo quebrou e fiz uma solicitação de assistência 24h. Para minha surpresa, fui informado que meu carro iria para um pátio e somente seria enviado no dia de amanhã porque a Allianz não faz remoções nos fins de semana. Quando contratei o seguro, mudando da Porto Seguro, no fim do ano passado, contratei guincho ilimitado e nada me foi informado a respeito disso. Não aceito que meu carro seja encaminhado para um pátio sem minha aquiescência e, principalmente, que somente seja enviado em úteis. Em contato com o atendente, ele me informou que essa ressalva consta no manual do segurado, que não recebi e, pior, somente pude ter acesso após a contratação da apólice. Eles omitiram descaradamente informação. Fica a pergunta, se o carro quebrar em um sábado de carnaval, somente receberei meu carro na quarta de cinzas?! Primeira vez que aciono esse seguro e já estou arrependido da contratação. Pior é que meus dois veículos estão segurados com eles. Avaliar se é melhor cancelar e procurar alguma seguradora que não omita informações relevantes para depois surpreender negativamente o cliente. Não voltarei a fazer seguro de nenhuma espécie com eles e não recomendo a ninguém.</t>
+  </si>
+  <si>
+    <t>94131187</t>
+  </si>
+  <si>
+    <t>237357045</t>
+  </si>
+  <si>
+    <t>12/01/2026 08:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134249142_x000D_
+</t>
+  </si>
+  <si>
+    <t>Tenho seguro residencial completo, precisei de 24 horas no final do ano, através de vários chamados é infelizmente não fui atendido, segundo a seguradora por falta de prestador de serviços._x000D_
+_x000D_
+No último chamado número 5101779, de 08/01/26, o técnico esteve na minha residência, fez um laudo e disse que ia passar para a seguradora e não mais retornou, nem a seguradora deu feedback. _x000D_
+_x000D_
+Lamentável , eu precisei fazer outros contatos com o 0800 para saber o que ocorreu com meu chamado, por fim, disseram que tinha cobertura apenas para recarga de gás, necessário, mas troca de tubulação não tem cobertura, que é para eu procurar serviço particular, e apenas 1 serviço eles não fazem._x000D_
+_x000D_
+Lamentável esta atitude da Seguradora. _x000D_
+_x000D_
+Pense bem antes de contratar.</t>
+  </si>
+  <si>
+    <t>94132446</t>
+  </si>
+  <si>
+    <t>237360505</t>
+  </si>
+  <si>
+    <t>12/01/2026 09:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133238927_x000D_
+</t>
+  </si>
+  <si>
+    <t>Bom dia,_x000D_
+_x000D_
+_x000D_
+No dia 11/01/2026, acionei a assistência 24 horas solicitando, com caráter de urgência, um desentupimento de vaso sanitário. Resido em um apartamento com apenas um banheiro, onde mora também uma idosa de 81 anos. Informei claramente que a água estava transbordando, o que tornava a situação inviável e emergencial._x000D_
+_x000D_
+_x000D_
+Fui informada de que um técnico chegaria à minha residência em até 01 hora, o que não ocorreu. Após o prazo, recebi contato informando que não havia prestador disponível e que o atendimento seria remarcado para o dia seguinte, o que é inaceitável diante da urgência relatada._x000D_
+_x000D_
+_x000D_
+O chamado permaneceu aberto até 20h, e mesmo após novo contato, fui novamente informada da inexistência de prestador, evidenciando total falha na prestação do serviço. Ressalto que o seguro está rigorosamente em dia e foi contratado justamente para atendimentos emergenciais, o que claramente não foi cumprido._x000D_
+_x000D_
+_x000D_
+Diante da omissão da seguradora, fui obrigada a contratar um prestador por conta própria, assumindo uma responsabilidade que deveria ser da empresa. Posteriormente, fui informada de que haveria apenas reembolso limitado a R$ 100,00, valor que não cobre o serviço contratado e não compensa o transtorno, o desgaste e a exposição a uma situação extremamente constrangedora._x000D_
+_x000D_
+_x000D_
+Não se trata apenas de reembolso. Trata-se de falta de respeito, quebra de compromisso contratual e descaso com o consumidor, especialmente diante de uma situação envolvendo uma pessoa idosa. Pagar o seguro e, no momento em que se precisa, não receber o atendimento prometido é inadmissível._x000D_
+_x000D_
+_x000D_
+Diante disso, aguardo posicionamento formal, solução adequada e providências imediatas, pois não aceito que essa situação seja tratada como algo normal ou resolvida apenas com um reembolso simbólico.</t>
+  </si>
+  <si>
+    <t>94134353</t>
+  </si>
+  <si>
+    <t>237365815</t>
+  </si>
+  <si>
+    <t>12/01/2026 09:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302758894_x000D_
+</t>
+  </si>
+  <si>
+    <t>O meu carro foi dado como perca total, a seguradora fez o pagamento do carro e descontou as duas últimas parcelas que faltava para finalizar o pagamento total do seguro. Porém, não retiraram as cobranças do cartão de crédito. No cartão de crédito estão me cobrando as duas faturas que já foram pagas.</t>
+  </si>
+  <si>
+    <t>94139582</t>
+  </si>
+  <si>
+    <t>237380731</t>
+  </si>
+  <si>
+    <t>12/01/2026 11:16</t>
+  </si>
+  <si>
+    <t>Allianz ; Automóvel ; Sinistro ; Sinistro ; Análise Sinistro ; 2 Terceiro do Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
     <t>2 Terceiro do Sinistro</t>
   </si>
   <si>
-    <t xml:space="preserve">296918341_x000D_
+    <t xml:space="preserve">302913696_x000D_
 </t>
   </si>
   <si>
-    <t>A SEGURADA DA ALLIANZ BATEU NA TRASEIRA DO MEU CARRO E APOS RESOLUCAO DAS BUROCLACIAS FUI ENCAMINGADO PELA SEGURADORA PARA A OFICINA JR GARCIA LOCALUZADA EM MARICA QUE APOS A ENTREGA DO VEICULO NO DIA 11 DE AGOSTO DE 2025 , OBSERVEI QUE O CARRO VINHA DISNIVELANDO O PORTA MALAS , RETORNEI UMA, DUAS, TRES, QUATRO VEZES E O PROBLEMA NAO FOI SOLUCIONADO . NA ULTIMA VEZ QUE VOLTEI O PROFISSOONAL QUE FVEIO AVALIAR AINDA INSUNUOU QUE PROVAVELMENRE O VEICULO TIMHA SOFRIDO UM NOVO ACIDENTE TRASEIRO , SENDO MUITO DESONESTO, POIS ELE SABIA QUE HAVIA VOLTADO COM O MESMO PROBLEMA . DESTA FORMA , ENVIO AS FOTOS DE COMO CONTINUA DINIivelada O PORTA MALAS E SOLICITO QUE SE POSSIVEL ME ENCAMINHE A UM OUTRO LOCAL QUE POSSA RESOLVER, POIS SE NAO FOR RESOLVIDO VOU ACIONAR A SEHURADA NA JUSTICA PARA QUE ELA ARQUE COM O CONSERTO .</t>
-  </si>
-  <si>
-    <t>94012094</t>
-  </si>
-  <si>
-    <t>237094945</t>
-  </si>
-  <si>
-    <t>08/01/2026 18:19</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Guincho ; Assistência Não Danos ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; 1 Segurado</t>
-  </si>
-  <si>
-    <t>Repasse Time MindBe</t>
-  </si>
-  <si>
-    <t>Micaele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131897096_x000D_
+    <t>No dia 26/11/2025, meu carro estava estacionado quando foi atingido por um caminhão. Colegas da minha empresa presenciaram o acidente e me chamaram. Falei com o motorista, que me direcionou ao supervisor, responsável pelo registro do Boletim de Ocorrência, e depois fui orientado a contatar a seguradora._x000D_
+_x000D_
+_x000D_
+Segui todas as instruções da empresa: levei o carro para uma oficina de minha confiança para orçamento e depois também a uma oficina credenciada pela seguradora. Solicitei explicitamente o conserto com peças novas e substituição do pneu danificado, conforme a extensão dos danos._x000D_
+_x000D_
+_x000D_
+No entanto, a seguradora ofereceu um valor ridiculamente baixo, menos de 1/3 do orçamento real, ignorando a necessidade de peças novas e a gravidade dos danos. A postura da empresa tem sido resistente e inflexível, sem qualquer disposição para negociação, mesmo sendo totalmente claro que não tive qualquer responsabilidade pelo acidente._x000D_
+_x000D_
+_x000D_
+É inaceitável que uma seguradora tão conhecida trate seus clientes com tamanho descaso, oferecendo um valor que torna impossível consertar o carro de maneira adequada e segura._x000D_
+_x000D_
+_x000D_
+Exijo uma resolução justa e imediata, com pagamento compatível com o orçamento real e a substituição de todas as peças danificadas por novas, como solicitado. O descaso até agora não reflete o compromisso que se espera da Allianz._x000D_
+_x000D_
+_x000D_
+Aguardo uma resposta concreta e resolução do caso.</t>
+  </si>
+  <si>
+    <t>94144031</t>
+  </si>
+  <si>
+    <t>237393517</t>
+  </si>
+  <si>
+    <t>12/01/2026 12:33</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 2 Terceiro do Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301083661_x000D_
 </t>
   </si>
   <si>
-    <t>Minha esposa fez a solicitação do guincho através do WhatsApp da seguradora as 19:40, o guincho só retirou o veículo as 22:40 do dia 07/01/2025, hoje é dia 08/01/2025 exatamente 18:13hs e não recebi meu veículo na oficina, fiz 05 ligações, durante o dia e nada do meu veículo! _x000D_
-_x000D_
-_x000D_
-Um seguro de mais de R$ 5.000,00, nunca usei e na primeira vez, a seguradora não devolve meu carro!_x000D_
-_x000D_
-Não sei aonde está, com quem está! _x000D_
-_x000D_
-O carro quebrou em Santos próximo a Santa casa e sou morador de Mongagua, estamos utilizando o veículo para visitas ao nosso filho que está internado, agora temos que pagar UBER para se locomover por conta da irresponsabilidade da seguradora! _x000D_
-_x000D_
-Zero comprometimento, zero assistência!</t>
-  </si>
-  <si>
-    <t>94014354</t>
-  </si>
-  <si>
-    <t>237097773</t>
-  </si>
-  <si>
-    <t>08/01/2026 18:45</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Análise Sinistro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302572541_x000D_
-</t>
-  </si>
-  <si>
-    <t>No dia 20/11 sofri um roubo e abri o sinistro n 302572541 junto à Allianz. Desde então, o processo segue em análise, sem uma definição clara, mesmo após várias interações._x000D_
-_x000D_
-_x000D_
-No dia 06/01, entrei em contato pelo chat da Allianz e fui informado de que haveria uma posição sobre a conclusão da análise no dia 08/01._x000D_
-_x000D_
-Hoje, 08/01, voltei a entrar em contato e fui informado apenas que o processo continua em análise, sem qualquer nova previsão concreta._x000D_
-_x000D_
-_x000D_
-Já se passaram quase 50 dias desde o roubo, e até o momento não tive uma solução nem um posicionamento definitivo. O que causa mais insatisfação é a falta de cumprimento dos prazos informados pelo próprio atendimento, gerando insegurança e desgaste._x000D_
-_x000D_
-_x000D_
-Peço apenas clareza, transparência e uma definição objetiva sobre a conclusão do sinistro, já que a situação vem se prolongando além do razoável._x000D_
-_x000D_
-_x000D_
-_x000D_
-Aguardo retorno.</t>
-  </si>
-  <si>
-    <t>94022300</t>
-  </si>
-  <si>
-    <t>237105997</t>
-  </si>
-  <si>
-    <t>08/01/2026 20:09</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Assistência Residencial ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134405009_x000D_
-</t>
-  </si>
-  <si>
     <t>Prezados,_x000D_
 _x000D_
 _x000D_
-Venho por meio desta registrar minha profunda insatisfação com o atendimento prestado pela Allianz Seguros referente ao acionamento do seguro de minha máquina de lavar, que se encontra sem funcionamento há um período excessivo e injustificável._x000D_
-_x000D_
-_x000D_
-No dia 27/11/2025, após abertura do chamado junto à seguradora, os técnicos compareceram à minha residência e retiraram peças da máquina para conserto. Desde então, o problema não foi solucionado, totalizando quase um mês e meio de espera, sem uma resolução definitiva._x000D_
-_x000D_
-_x000D_
-No dia de hoje, 08/01/2026, havia um agendamento confirmado por e-mail, conforme comunicações recebidas da colaboradora Andressa, para a entrega e instalação da peça. Em função disso, desmarquei compromissos pessoais e profissionais para aguardar o atendimento. No entanto, ninguém compareceu, tampouco houve qualquer aviso prévio ou justificativa._x000D_
-_x000D_
-_x000D_
-Somente por volta das 19h, recebi uma ligação do técnico Rhenan, informando que houve um problema e perguntando se eu poderia recebê-lo no dia 09/01 no período da manhã. Mesmo extremamente prejudicado pela situação, informei que aguardaria, pois a máquina está fazendo muita falta em minha rotina._x000D_
-_x000D_
-_x000D_
-Para minha surpresa, cerca de 20 minutos depois, recebi uma ligação da própria Allianz, informando que a entrega e instalação da peça só ocorrerão na segunda-feira, dia 12/01/2026, contrariando totalmente o que havia sido comunicado anteriormente._x000D_
-_x000D_
-_x000D_
-Diante do cenário, abri uma nova reclamação junto à Ouvidoria da Allianz, sob o protocolo n 2624243010, sendo atendido pela colaboradora Michele. Fui informado de que o prazo para resposta da ouvidoria pode chegar a 30 dias, o que considero totalmente desproporcional, considerando o tempo já decorrido e o desgaste acumulado._x000D_
-_x000D_
-_x000D_
-Ressalto que estou emocionalmente exausto, frustrado e me sentindo desrespeitado como cliente, diante da falta de comunicação, do descumprimento de prazos e da ausência de comprometimento com a resolução do problema._x000D_
-_x000D_
-_x000D_
-Diante de todo o ocorrido, solicito formalmente o cancelamento do plano de seguro, sem qualquer cobrança de multa ou fidelidade, uma vez que houve falha grave e recorrente na prestação do serviço._x000D_
-_x000D_
-_x000D_
-Aguardo um posicionamento urgente e uma solução definitiva para este caso._x000D_
+Conforme já informado anteriormente, toda a documentação exigida para a regulação do sinistro foi integralmente entregue, o acordo entre as partes foi formalmente concluído e o valor da indenização já se encontra definido._x000D_
+_x000D_
+_x000D_
+Ressalto que já se passaram 30 dias corridos desde a entrega completa dos documentos, prazo este previsto para conclusão e pagamento da indenização, não havendo, até o momento, solicitação de documentos adicionais que justificassem a prorrogação do prazo legal._x000D_
+_x000D_
+_x000D_
+Fui informado, de forma posterior, sobre a necessidade de mais 15 dias úteis para compensação do valor, prazo que não havia sido previamente comunicado e que gera impacto direto na minha subsistência, considerando que me encontro em processo de recuperação e sem condições de exercer minhas atividades normalmente._x000D_
+_x000D_
+_x000D_
+Diante disso, solicito a confirmação formal da data exata para o crédito da indenização, bem como a priorização do pagamento, evitando-se a adoção de medidas administrativas junto à Ouvidoria, SUSEP ou demais órgãos competentes._x000D_
+_x000D_
+_x000D_
+Fico no aguardo de um retorno objetivo com a data final para pagamento._x000D_
 _x000D_
 _x000D_
 Atenciosamente,_x000D_
 _x000D_
-Johnny Nogueira Rabello</t>
-  </si>
-  <si>
-    <t>94023659</t>
-  </si>
-  <si>
-    <t>237107301</t>
-  </si>
-  <si>
-    <t>08/01/2026 20:23</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Cancelamento ; 1 Segurado ; OUV ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Cancelamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133509734_x000D_
-</t>
-  </si>
-  <si>
-    <t>No dia 18/07/2025 adquiri na em uma concessionária Yamaha uma moto Factor DX modelo 2025, e a loja me indicou uma corretora da própria Yamaha para contratar um seguro. Foi contratado então a Allianz no valor de R$1.522,72 pago a vista via pix (segue em anexo o comprovante) por 12 meses de proteção. No mês de Dezembro de 2025 vendi a moto e entrei em contato com o SAC Yamaha para fazer o cancelamento do seguro, fui informado que seria abatido os 5 meses utilizados e receberia o valor referente aos 7 meses restantes. Para minha surpresa recebi no dia 23/12 um e-mail (segue em anexo o e-mail) do SAC Yamaha informando que os documento iriam para análise interna e a programação no valor de R$567,23 a ser devolvido. Não concordo com esse valor pois 5 meses de uso do seguro corresponde a R$634,45 e o valor a ser devolvido seria R$888,27 e o pior ainda é que passou o prazo de 15 dias úteis e até agora não recebi sequer um e-mail ou uma explicação._x000D_
-_x000D_
-_x000D_
-Solicito o reembolso do valor correto que seria R$888,27.</t>
-  </si>
-  <si>
-    <t>94027776</t>
-  </si>
-  <si>
-    <t>237111253</t>
-  </si>
-  <si>
-    <t>08/01/2026 21:07</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; Reclamante em nome do Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Reclamante em nome do Segurado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133883777_x000D_
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa noite,tive um problema com meu carro ,o carro quebrou no dia 31/12/2025,chamei o guincho no dia 01 ele chegou pra guinchar meu carro e levou para uma base na baixada mesmo , no dia 02 meu carro ficou em outra base em São paulo na speed truck, na central me falaram que o carro iria chegar no dia 05 porém não chegou foi uma semana de dor de cabeça ninguém sabia em qual base meu carro estava descobri que meu carro estava na speed trunck porque liguei e a atendente me informou que estava desde o dia 02 o carro não chegava em minha residência porque a allianz não tinha liberado e nem passado meu endereço pra speed truck e o carro ficou lá até a data do dia 07 me entregando as 16:30. Fiquei muito chateado com a falta de transparência do seguro.fica aqui meu descontentamento com essa seguradora. _x000D_
-_x000D_
-</t>
-  </si>
-  <si>
-    <t>94060736</t>
-  </si>
-  <si>
-    <t>237147963</t>
-  </si>
-  <si>
-    <t>09/01/2026 10:26</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303102378_x000D_
-</t>
-  </si>
-  <si>
-    <t>Bom dia!_x000D_
-_x000D_
-_x000D_
-Abri um sinistro no dia 05/12/2025 com a empresa, que demorou todo o processo até a vistoria não foi no dia informado pela atendente, fizeram a vistoria, meu mecanico de confiança passou o orçamento a eles, foi me solicitado o boletim de ocorrencia, enviei a eles. E no dia 23/12/2025 me solicitaram copia de laudo médido. Pra que isso eu não sei, uma vez que eu informei na abertura do acidente que não tinha como ir atras dos envolvidos porque eles evadiram do local e eu ia arcar com a franquia, informei por e-mail ao perito que me solicitou de nome Ricardo que não tinha acesso a isto, visto que fiquei em observação em uma cidade longe de onde residuo por se tratar de um acidente em uma BR, e o hospital so disponibiliza isso pessoalmente. Ai hoje no dia 09/01/2025, tive uma cobraça do boleto mensal que é feito via cartão de crédito que tentaram fazer o desconto no mesmo, e como não foi autorizado pelo cartão eles geraram um boleto, que não foi enviado no dia do vencimento, detalhe so soube da cobrança porque entrei no chat pra reclamar sobre o sinistro. E em contato com o financeiro deles por telefone, fui informada que o boleto poderia chegar no meu e-mail em até 24 horas. Ou seja eu teria que pagar o juros de um boleto que não tinha ciencia._x000D_
-_x000D_
-_x000D_
-Eu sou cliente deles a dois anos, e de verdade foi o ultimo ano, não renovo contrato com eles, é de muito pouco caso, informei varias vezes que faço o uso da moto para me locomover, estou indo pro trabalho de uber, e que fica muito caro por sinal</t>
-  </si>
-  <si>
-    <t>94065515</t>
-  </si>
-  <si>
-    <t>237160069</t>
-  </si>
-  <si>
-    <t>09/01/2026 11:43</t>
-  </si>
-  <si>
-    <t>Allianz ; Automóvel ; Sinistro ; Análise Sinistro ; 11 Não Cliente ; CPF/CNPJ ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>CPF/CNPJ</t>
-  </si>
-  <si>
-    <t>11 Não Cliente</t>
-  </si>
-  <si>
-    <t>10505403609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bom dia, venho por meio desta informar minha insatisfação de um veículo comprado no leilão da Copart da Allianz seguros, o veículo falta PRATICAMENTE TODAS AS PEÇAS DE FUNCIONAMENTO, a caixa de câmbio foi retirada e substituída por uma carcaça oca de um veículo de outra marca, o motor também está oco faltando todas as peças internas, além disso o setor de direção também foi trocado, faltando também peças externas do motor como alternador, motor de arranque, sistema direção hidráulica, compressor do ar condicionado, condensador, entre muitas outras. Por esse motivo torna-se inviável ficar com o veículo, quero realizar a devolução do bem. Aguardo contato para uma solução._x000D_
-_x000D_
-_x000D_
-</t>
+Caique Costa</t>
   </si>
 </sst>
 </file>
@@ -1006,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AA8803-373C-4E0C-ABA8-1F171C96DA02}">
-  <dimension ref="A1:AA22"/>
+  <dimension ref="A1:AA20"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="3" bestFit="1" customWidth="1" collapsed="1"/>
@@ -1160,25 +1411,25 @@
         <v>38</v>
       </c>
       <c r="M2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="W2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="Y2" s="3" t="s">
         <v>26</v>
@@ -1188,13 +1439,13 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>30</v>
@@ -1203,7 +1454,7 @@
         <v>31</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>33</v>
@@ -1212,37 +1463,37 @@
         <v>34</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="M3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="V3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="V3" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="W3" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Y3" s="3" t="s">
         <v>26</v>
@@ -1252,13 +1503,13 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>30</v>
@@ -1267,46 +1518,46 @@
         <v>31</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P4" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="V4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Y4" s="3" t="s">
         <v>26</v>
@@ -1316,13 +1567,13 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>30</v>
@@ -1331,7 +1582,7 @@
         <v>31</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>33</v>
@@ -1340,37 +1591,34 @@
         <v>34</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="V5" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="Y5" s="3" t="s">
         <v>26</v>
@@ -1380,13 +1628,13 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>30</v>
@@ -1395,46 +1643,46 @@
         <v>31</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="M6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="N6" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="O6" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="V6" s="3" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="Y6" s="3" t="s">
         <v>26</v>
@@ -1444,13 +1692,13 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>30</v>
@@ -1459,46 +1707,46 @@
         <v>31</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="P7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P7" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="V7" s="3" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y7" s="3" t="s">
         <v>26</v>
@@ -1508,13 +1756,13 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>30</v>
@@ -1523,7 +1771,7 @@
         <v>31</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>33</v>
@@ -1538,25 +1786,25 @@
         <v>36</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="W8" s="4" t="s">
         <v>89</v>
@@ -1593,34 +1841,28 @@
         <v>33</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="K9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M9" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="N9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="W9" s="4" t="s">
         <v>96</v>
@@ -1651,7 +1893,7 @@
         <v>31</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>33</v>
@@ -1660,34 +1902,37 @@
         <v>34</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P10" s="3" t="s">
         <v>41</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="W10" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="X10" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="X10" s="4" t="s">
-        <v>103</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>26</v>
@@ -1695,13 +1940,13 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>30</v>
@@ -1710,7 +1955,7 @@
         <v>31</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>33</v>
@@ -1719,37 +1964,37 @@
         <v>34</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>34</v>
       </c>
       <c r="K11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="W11" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="L11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="V11" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="W11" s="4" t="s">
+      <c r="X11" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="X11" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="Y11" s="3" t="s">
         <v>26</v>
@@ -1757,13 +2002,13 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>30</v>
@@ -1772,7 +2017,7 @@
         <v>31</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>33</v>
@@ -1787,31 +2032,31 @@
         <v>36</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="L12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="W12" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="W12" s="4" t="s">
+      <c r="X12" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="X12" s="4" t="s">
-        <v>117</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>26</v>
@@ -1819,13 +2064,13 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>30</v>
@@ -1834,46 +2079,46 @@
         <v>31</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O13" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="P13" s="3" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="W13" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="X13" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="X13" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="Y13" s="3" t="s">
         <v>26</v>
@@ -1881,13 +2126,13 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>30</v>
@@ -1896,79 +2141,422 @@
         <v>31</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>128</v>
+        <v>34</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>129</v>
+        <v>51</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="P14" s="3" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W15" s="4"/>
+      <c r="A15" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W15" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
+      <c r="A16" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="W16" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="X16" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y16" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="17" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="18" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W18" s="4"/>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="W18" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="19" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="W19" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="X19" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y19" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="20" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W20" s="4"/>
-      <c r="X20" s="4"/>
-    </row>
-    <row r="21" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W21" s="4"/>
-    </row>
-    <row r="22" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W22" s="4"/>
-      <c r="X22" s="4"/>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="W20" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="X20" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AN9" xr:uid="{D3AA8803-373C-4E0C-ABA8-1F171C96DA02}"/>

--- a/Treinamento/GestaoReclamacao.xlsx
+++ b/Treinamento/GestaoReclamacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6773543-A9D8-4A03-87CF-3595DFB12D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619F2D67-2816-4A64-8C57-9DA6E6F02657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B1A77FD5-2AD3-4458-ACB3-7F19D1A3340A}"/>
   </bookViews>
@@ -1257,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AA8803-373C-4E0C-ABA8-1F171C96DA02}">
-  <dimension ref="A1:AA20"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="3" bestFit="1" customWidth="1" collapsed="1"/>
@@ -2558,6 +2558,13 @@
         <v>26</v>
       </c>
     </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="W21" s="4"/>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="W22" s="4"/>
+      <c r="X22" s="4"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AN9" xr:uid="{D3AA8803-373C-4E0C-ABA8-1F171C96DA02}"/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Treinamento/GestaoReclamacao.xlsx
+++ b/Treinamento/GestaoReclamacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CB1166-FAF6-429D-BFBA-DE89322D81C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77B2BA6-129B-43B5-937D-9C9D8A342BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B1A77FD5-2AD3-4458-ACB3-7F19D1A3340A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="152">
   <si>
     <t>Id HugMe</t>
   </si>
@@ -122,13 +122,13 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>94131462</t>
-  </si>
-  <si>
-    <t>237357663</t>
-  </si>
-  <si>
-    <t>12/01/2026 08:42</t>
+    <t>94180125</t>
+  </si>
+  <si>
+    <t>237502235</t>
+  </si>
+  <si>
+    <t>13/01/2026 10:12</t>
   </si>
   <si>
     <t>Não respondido</t>
@@ -137,7 +137,7 @@
     <t>Não</t>
   </si>
   <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+    <t>Allianz ; Automóvel ; Sinistro ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
     <t>Allianz</t>
@@ -167,477 +167,588 @@
     <t>Eliana</t>
   </si>
   <si>
-    <t xml:space="preserve">303213944_x000D_
+    <t xml:space="preserve">303559435_x000D_
 </t>
   </si>
   <si>
-    <t>Sou segurado da Allianz, apólice n 517720253D312009092, com cobertura vigente de_x000D_
-_x000D_
-Responsabilidade Civil Facultativa  RCF. O acidente foi comunicado regularmente_x000D_
-_x000D_
-à seguradora, originando o Sinistro n 303213944._x000D_
-_x000D_
-_x000D_
-No dia 05/12, por volta das 21h30, envolvi-me em acidente de trânsito ao realizar_x000D_
-_x000D_
-manobra para acessar a faixa da direita, vindo a colidir com veículo de terceiro_x000D_
-_x000D_
-(VW Golf), que ingressava na via a partir de vaga de estacionamento. O sinistro_x000D_
-_x000D_
-foi comunicado com envio de relato completo e detalhado dos fatos, sem omissão_x000D_
-_x000D_
-de informações._x000D_
-_x000D_
-_x000D_
-Desde o primeiro contato, manifestei interesse exclusivo na cobertura dos danos_x000D_
-_x000D_
-causados ao terceiro, conforme expressamente previsto em minha apólice._x000D_
-_x000D_
-Entretanto, a seguradora insistiu que o acionamento fosse feito para ambos os_x000D_
-_x000D_
-veículos. Após o procedimento, a Allianz recusou a cobertura ao terceiro,_x000D_
-_x000D_
-alegando, de forma genérica, que o segurado deveria se atentar à faixa da direita_x000D_
-_x000D_
-e que o terceiro deveria observar o fluxo da via, imputando responsabilidade_x000D_
-_x000D_
-sem qualquer perícia técnica, sem decisão judicial e sem indicação de cláusula_x000D_
-_x000D_
-contratual de exclusão._x000D_
-_x000D_
-_x000D_
-Ressalto que:_x000D_
-_x000D_
-- A apólice prevê expressamente cobertura RCF  Danos Materiais no valor de_x000D_
-_x000D_
-  R$ 200.000,00;_x000D_
-_x000D_
-- As Condições Gerais do Seguro Allianz Auto não excluem acidentes de trânsito_x000D_
-_x000D_
-  decorrentes de erro de manobra;_x000D_
-_x000D_
-- Não houve dolo, fraude ou omissão de informações;_x000D_
-_x000D_
-- A seguradora não pode negar cobertura com base em interpretação subjetiva de_x000D_
-_x000D_
-  culpa, substituindo o Poder Judiciário._x000D_
-_x000D_
-_x000D_
-Destaco ainda que resido no município de Paiva/MG, enquanto o acidente ocorreu_x000D_
-_x000D_
-em Barbacena/MG, local de residência do terceiro envolvido. A negativa indevida_x000D_
-_x000D_
-da cobertura vem me obrigando a realizar sucessivos deslocamentos até_x000D_
-_x000D_
-Barbacena (aproximadamente 66 km por trecho, além de pedágio), para tratar de_x000D_
-_x000D_
-orçamentos, tratativas e solução de prejuízos que deveriam ser integralmente_x000D_
-_x000D_
-geridos pela seguradora._x000D_
-_x000D_
-_x000D_
-Essa situação está gerando despesas adicionais, consumo significativo de tempo_x000D_
-_x000D_
-e prejuízo à minha rotina pessoal e profissional, caracterizando falha grave na_x000D_
-_x000D_
-prestação do serviço e desvio produtivo do consumidor, decorrente da conduta da_x000D_
-_x000D_
-seguradora._x000D_
-_x000D_
-_x000D_
-Diante disso, solicito a revisão imediata da decisão, com o reconhecimento da_x000D_
-_x000D_
-obrigação de cobertura dos danos causados ao terceiro no âmbito do Sinistro_x000D_
-_x000D_
-n 303213944, bem como a orientação formal quanto ao ressarcimento dos valores_x000D_
-_x000D_
-que venham a ser desembolsados.</t>
-  </si>
-  <si>
-    <t>94138271</t>
-  </si>
-  <si>
-    <t>237376741</t>
-  </si>
-  <si>
-    <t>12/01/2026 10:54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302652703_x000D_
+    <t>A pior seguradora de todas ! Estou com uma bmw S1000rr 2026 parada desde o dia 12/12/2025, pagando seguro e pagando parcela sem a moto por conta da incompetência da seguradora._x000D_
+_x000D_
+Não queriam aprovar o orçamento na minha oficina de confiança, mesmo a oficina sendo cadastrada e sabendo que só receberia pelos serviços após emissão de Nf eles disseram que ela se recusou emitir Nf. (Um absurdo)_x000D_
+_x000D_
+Após mais de 15 dias com muito custo o orçamento foi aprovado, porém, com diversos itens do orçamento pendente. Sim, por conta própria removeram itens do orçamento feito pela oficina. Sem falar que ainda estão me cobrando diferença de mão de obra e diferença no orçamento das peças comparado a outras oficinas._x000D_
+_x000D_
+Ainda sem resolver ! Ainda pagando seguro sem moto ! Eles são os contratados e nós pagamos, mas parece que estamos pedindo favor.</t>
+  </si>
+  <si>
+    <t>94196920</t>
+  </si>
+  <si>
+    <t>237535257</t>
+  </si>
+  <si>
+    <t>13/01/2026 13:34</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Empresa ; Assistência Não Danos ; Assistencia Empresa ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Apólice</t>
+  </si>
+  <si>
+    <t>Empresa</t>
+  </si>
+  <si>
+    <t>Assistência Não Danos</t>
+  </si>
+  <si>
+    <t>Assistencia Empresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133680004_x000D_
 </t>
   </si>
   <si>
-    <t xml:space="preserve">VIM RECLAMAR MAIS UMA VEZ SOBRE A INSATISFAÇÃO DA SEGURADORA ALLIANZ SEGURO._x000D_
-_x000D_
-HOJE ESTÁ FAZENDO 49 DIAS QUE ESTAMOS SEM O NOSSO CARRO._x000D_
-_x000D_
-O CARRO FOI LEVADO PARA A OFICINA NO DIA 24 DE NOVEMBRO DE 2025, AS 09:30HRS..MAS O ACIDENTE ACONTECEU UM DIA ANTES, AS 08:30 HRS..ALÉM DE TEREM DEMORADO PARA CHEGAREM O GUINCHO, ESTÃO DEMORANDO PARA ENTREGAREM O MEU CARRO._x000D_
-_x000D_
-NOS GARANTIRAM QUE O CARRO FICARIA PRONTO ESTA SEMANA, AGORA A CONVERSA TA SENDO OUTRA, A OFICINA NOS INFORMOU, QUE AINDA ESTÁ FALTANDO UMA PEÇA PRA CHEGAR._x000D_
-_x000D_
-MEU DEUS, QUEM NOS AJUDAR NESSA HORA._x000D_
-_x000D_
-É MUITA HUMILHAÇÃO PARA UM SEGURADO. É MUITA MENTIRA, É MUITA ENROLAÇÃO, É MUITA FALTA DE RESPEITO, E É MUITA COVARDIA O QUE ESTÃO FAZENDO COM A GENTE._x000D_
-_x000D_
-O QUE TA ACONTECENDO ALLIANZ SEGURO, PORQUE ESTE ABANDONO COM NÓS?_x000D_
-_x000D_
+    <t>Sou segurada da Allianz Seguro Empresarial e no dia 13/01 solicitei assistência técnica para minha geladeira comercial, que parou de funcionar após quedas de energia causadas por forte chuva._x000D_
+_x000D_
+Trata-se de um equipamento essencial para a minha atividade comercial, pois trabalho com alimentos perecíveis. Após cerca de 2 horas, a Allianz entrou em contato informando que não há prestador disponível na minha região , e que os prestadores só teriam disponibilidade apenas em fevereiro._x000D_
+_x000D_
+Como solução, a seguradora informou que eu deveria providenciar o conserto de forma particular e depois solicitar reembolso, pois eles não conseguem cumprir a assistência contratada._x000D_
+_x000D_
+Ressalto que a falta de prestador não pode ser transferida ao consumidor, tampouco justificar a demora excessiva no atendimento, principalmente quando se trata de um equipamento indispensável para o funcionamento do negócio. A situação caracteriza falha na prestação do serviço, conforme o Código de Defesa do Consumidor._x000D_
+_x000D_
+Solicito:_x000D_
+_x000D_
+Confirmação formal da cobertura do sinistro;_x000D_
+_x000D_
+Autorização expressa de reembolso integral do conserto dentro do limite da apólice;_x000D_
+_x000D_
+Garantia de que não serei prejudicada financeiramente por um problema operacional da seguradora._x000D_
+_x000D_
+Caso não haja solução adequada, irei registrar reclamação junto à SUSEP, Procon e, se necessário, buscar o Juizado Especial Cível para reparação dos prejuízos causados._x000D_
+_x000D_
+Aguardo uma solução urgente.</t>
+  </si>
+  <si>
+    <t>94201938</t>
+  </si>
+  <si>
+    <t>237543773</t>
+  </si>
+  <si>
+    <t>13/01/2026 14:29</t>
+  </si>
+  <si>
+    <t>2 Terceiro do Sinistro ; Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>2 Terceiro do Sinistro</t>
+  </si>
+  <si>
+    <t>Andreza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301822991_x000D_
 </t>
   </si>
   <si>
-    <t>94141948</t>
-  </si>
-  <si>
-    <t>237387863</t>
-  </si>
-  <si>
-    <t>12/01/2026 11:57</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Vida / Acidentes Pessoais ; Apólice ; Pagamento ; 1 Segurado ; Não ; Sim ; Sem Resposta - Dentro SLA ; 1 Ctt Sem Sucesso</t>
-  </si>
-  <si>
-    <t>Apólice</t>
-  </si>
-  <si>
-    <t>Vida / Acidentes Pessoais</t>
+    <t>Sou terceiro!! O sinistro 301822991 está registrado desde 27/10/25 para um táxi no município do Rio de Janeiro, ficou impossibilitado de trabalhar desde então, só foi liberado em janeiro/26 e a proposta de R$ 5.000,00 para  o lucro cessante, quando o justo repercute mais de R$ 30.000,00. Surreal !!! E, simplesmente silenciam. Judicializar é a única opção? Gostaria de um acordo.</t>
+  </si>
+  <si>
+    <t>94202439</t>
+  </si>
+  <si>
+    <t>237544763</t>
+  </si>
+  <si>
+    <t>13/01/2026 14:36</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Residência</t>
+  </si>
+  <si>
+    <t>Assistência Residencial</t>
+  </si>
+  <si>
+    <t>No começo de dezembro pedi assistencia do meu fogão, o técnico foi e disse que ia ver se tinham as peças para conserto e me ligariam. Até janeiro não recebi retorno e liguei para seguro que informou que não tinha nada pendente com eles e estavam verificando o caso. Eu paguei mais caro para ter esse tipo de serviço no seguro e não recebi o serviço vou cancelar seguro e não usar mais essa seguradora.</t>
+  </si>
+  <si>
+    <t>94209140</t>
+  </si>
+  <si>
+    <t>237564263</t>
+  </si>
+  <si>
+    <t>13/01/2026 16:49</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Repasse Time MindBe</t>
+  </si>
+  <si>
+    <t>Micaele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132225039_x000D_
+</t>
+  </si>
+  <si>
+    <t>Dia 27/12/2025 solicitei uma troca de ventilador do teto.veio dia 05/01 técnico veio nao conseguiu instalar o ventilador ficou de agendar retorno até hoje estou aguardando retorno obs:hoje ja e dia 13/01/26.sao vários dias de muito calor esperando a conclusão do mesmo</t>
+  </si>
+  <si>
+    <t>94212348</t>
+  </si>
+  <si>
+    <t>237573865</t>
+  </si>
+  <si>
+    <t>13/01/2026 18:01</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 2 Terceiro do Sinistro ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303685646_x000D_
+</t>
+  </si>
+  <si>
+    <t>Sofri um sinistro em estacionamento de uso coletivo, trafegando em baixa velocidade pela via interna de circulação. O veículo à minha frente encontrava-se parado no meio da via, sem qualquer sinalização indicativa de conversão ou manobra. Reduzi a velocidade e aguardei por alguns segundos._x000D_
+_x000D_
+_x000D_
+Diante da permanência do veículo parado, iniciei a manobra de contorno para seguir em frente. No momento do contorno, a condutora avançou repentinamente à esquerda, sem sinalizar, colidindo com a lateral do meu automóvel e causando danos à porta do passageiro, o que é plenamente compatível com a dinâmica real do acidente._x000D_
+_x000D_
+_x000D_
+Ressalto que, quando um veículo permanece parado sem sinalização, ocupando faixa de rolamento, ele pode ser considerado obstáculo na prática, sendo plenamente possível e legítima a manobra de desvio, cabendo a quem o deixou nessa condição a avaliação de sua responsabilidade, seja em perícia técnica ou em ação judicial._x000D_
+_x000D_
+_x000D_
+Em muitos processos judiciais, inclusive, a análise da dinâmica do sinistro considera situações como esta, nas quais:_x000D_
+_x000D_
+ O veículo estava parado no meio da via interna sem sinalização, gerando obstáculo não previsto, e a manobra de desvio foi necessária e segura._x000D_
+_x000D_
+ A falta de sinalização e a condução negligente do outro condutor contribuíram diretamente para o sinistro._x000D_
+_x000D_
+_x000D_
+Ocorre que a segurada prestou versão divergente dos fatos, e a seguradora, com base apenas nessa narrativa unilateral, negou o reparo do meu veículo, desconsiderando as provas fotográficas e a coerência lógica dos danos apresentados._x000D_
+_x000D_
+_x000D_
+Apresentei dois recursos administrativos, detalhando novamente a dinâmica do acidente e encaminhando novas fotografias, porém ambos foram indeferidos sem análise técnica adequada, evidenciando falha na avaliação do sinistro._x000D_
+_x000D_
+_x000D_
+Diante disso, solicito a revisão imediata da negativa, com análise técnica imparcial e a devida responsabilização pelos danos causados, sob pena de adoção das medidas administrativas e judiciais cabíveis.</t>
+  </si>
+  <si>
+    <t>94212910</t>
+  </si>
+  <si>
+    <t>237575957</t>
+  </si>
+  <si>
+    <t>13/01/2026 18:18</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Sinistro ; Automóvel ; Análise Sinistro ; 2 Terceiro do Sinistro ; RA ; Sim ; Sem Resposta - Dentro SLA ; 1 Ctt Com Sucesso</t>
+  </si>
+  <si>
+    <t>RA</t>
+  </si>
+  <si>
+    <t>1 Ctt Com Sucesso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303437579_x000D_
+</t>
+  </si>
+  <si>
+    <t>_x000D_
+_x000D_
+_x000D_
+Oficina Giants visconde caravelas 55 Botafogo ,  me humilhou, recusou receber meu carro e me deixou há mais de 40 dias sem trabalhar_x000D_
+_x000D_
+_x000D_
+Sou Márcia Gomes, esposa do terceiro prejudicado José Antônio Costa Gomes, vítima de um acidente ocorrido em 11/12/2025. O veículo é de trabalho e está parado desde então._x000D_
+_x000D_
+_x000D_
+A seguradora Allianz indicou a oficina Giants para realizar o reparo. No dia 22/12/2025 o reparo foi autorizado, porém a própria oficina informou que não poderia receber o carro por falta de peças, e agendou a entrega para 12/01/2026._x000D_
+_x000D_
+_x000D_
+No dia 12/01, informei à oficina que havia sofrido um acidente no pé e não conseguiria levar o carro naquele dia. Então ficou combinado que eu levaria no dia 13/01, sem horário marcado, tendo eu apenas perguntado o horário de abertura, e me disseram que seria às 8h._x000D_
+_x000D_
+_x000D_
+No dia 13/01, cheguei à oficina às 10h12, dentro do horário comercial, e fui tratada de forma grosseira e humilhante, sendo informada que não iriam receber meu carro porque eu tinha que ter chegado às 8h  exigência que nunca foi comunicada._x000D_
+_x000D_
+_x000D_
+Ou seja, me fizeram ir até lá à toa, me trataram mal, me expuseram a constrangimento e ainda recusaram o recebimento do veículo, sem qualquer justificativa válida._x000D_
+_x000D_
+_x000D_
+Para piorar, a oficina ainda reagendou para 21/01, o que fará o carro ficar mais de 40 dias parado, enquanto eu fico sem poder trabalhar e sem renda._x000D_
+_x000D_
+_x000D_
+A oficina Giants demonstrou total desorganização, falta de respeito com o cliente e despreparo, além de ter quebrado completamente a minha confiança. Depois do que sofri lá, não tenho nenhuma segurança de que meu carro seria consertado corretamente ou que peças não seriam trocadas ou danificadas._x000D_
+_x000D_
+_x000D_
+Estou tendo prejuízo financeiro diário, além do abalo emocional causado pelo tratamento que recebi._x000D_
+_x000D_
+_x000D_
+Exijo uma solução imediata, a troca de oficina e que a Allianz tome providências contra essa oficina._x000D_
+_x000D_
+_x000D_
+Oficina Giants: atendimento abusivo, desorganização e desrespeito total ao consumidor.</t>
+  </si>
+  <si>
+    <t>94214166</t>
+  </si>
+  <si>
+    <t>237579885</t>
+  </si>
+  <si>
+    <t>13/01/2026 18:53</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Gestão de Oficina ; Sac Enc ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Reclamante em nome do Segurado</t>
+  </si>
+  <si>
+    <t>Gestão de Oficina</t>
+  </si>
+  <si>
+    <t>Reclamante em nome do Segurado</t>
+  </si>
+  <si>
+    <t>Sac Enc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300794366_x000D_
+</t>
+  </si>
+  <si>
+    <t>Dia 28/09/25 bati meu carro e acionei meu seguro. Recolheram o carro para vistoria e posterior conserto. No dia 10/10/25 o seguro autorizou o serviço, porém o mesmo levou mais 14 dias para encomendar as peças necessárias sendo esse dia, 24/10/25. E entrei em contato e o problema era somente a demora das peças. Início de janeiro entrei em contato com a oficina e foi me passado que ainda faltava o cinto de segurança então eles não tinham ainda nem mexido no carro. (Coisa que poderia ter sido feita já, dado a demora e prazo excedido.) Então me falaram que já que faltava apenas o cinto, eles iriam começar a arrumar mas não entregariam o carro em dezembro dado as férias coletivas. Pois bem, dia 05/01/26 entrei em contato e falaram que o tal cinto não tinha chegado ainda. No mesmo dia fizemos uma reclamação por telefone, então dia 07/01/26 o corretor entrou em contato e prometeu entregar o carro dia ou ate o dia 09, no mais tardar, meio da seana seguinte, que seria amanhã dia 14/01/26. Pois bem ontem dia 12/01/26 entrei em contato novamente e para saber do andamento ( afinal já se passaram mais de 3 meses e sem bem dos meus direitos) e avisaram que o carro estava pronto, mas precisava passar um scaner no carro (algo que foi avisado tbm no dia 07) e eles sabendo que precisava de agendamento para tal serviço, resolveram agendar somente ontem e a GWM só tem data para dia 26/01/26, nisso essa enrolação vai dar 4 meses já. Eu com filho pequeno, todo esse tempo sem carro por causa de tanta incompetência tanto da seguradora quanto da oficina. Ontem liguei novamente no sac e foi me passado que me responderam no dia 07/01/26 avisando que o serviço ia ficar prnto dentro de 10 dias. Mas não recebemos nenhum email. Pedi que enviassem novamente e então recebi. Porém esse prazo do dia 26, tbm extrapola o prazo dado pelo sac. Dado as circunstâncias, não indico essa seguradora para ninguém. Eles sabem o prazo que precisa ser entregue o carro mais do que ninguém e mesmo assim levam 27 dias para liberar um serviço e encomendar as peças.</t>
+  </si>
+  <si>
+    <t>94215627</t>
+  </si>
+  <si>
+    <t>237583819</t>
+  </si>
+  <si>
+    <t>13/01/2026 19:28</t>
+  </si>
+  <si>
+    <t>Sinistro ; Allianz ; Automóvel ; Sinistro ; Gestão de Oficina ; 2 Terceiro do Sinistro ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301515981_x000D_
+</t>
+  </si>
+  <si>
+    <t>Em outubro/2025 meu carro foi colidido na traseira, quando eu estava parado em um semáforo fechado; o motorista do outro veículo deu assistência, informou sobre seu seguro e até aí tudo bem._x000D_
+_x000D_
+Em contato com a corretora do seguro, representando a ALIANZ, me informou de oficinas onde meu carro deveria ser atendido. Minha preferência, lógico, seria na autorizada FIAT, pois meu carro é um ARGO com 3 anos incompletos._x000D_
+_x000D_
+Não houve acordo. O seguro não aceitou fazer na autorizada, depois de eu perceber que corria o risco de ficar com mais prejuízo ainda, aceitei fazer em outra oficina._x000D_
+_x000D_
+O atendimento na referida oficina foi "porco". Pintura mal feita, instalação da tampa traseira imperfeita que fica rossando no teto do carro quando é aberta, tanto que arranhou toda tinda da parte de trás, junção com a tampa traseira. Faltou o refletor do lado direito, e me deixaram sem os "plugs" de sustentação da tampa interna do bagageiro._x000D_
+_x000D_
+Tudo isso, sem dizer que demorou 2 meses para fazer uma droga de serviço._x000D_
+_x000D_
+Estou tentando contato com a oficina, que não responde; Tentei contato com a ouvidoria do seguro, e a atendente parecia retardada, não dava informações precisas e ficava me direcionando para ligar outros números, como se não quisesse me atender._x000D_
+_x000D_
+Não recomendo esse seguro. É de má qualidade, atendimento ruim, tem vínculo com oficinas de ponta de rua, ruins. Se quiser ter seu carro acabado, contrate esse seguro.</t>
+  </si>
+  <si>
+    <t>94220529</t>
+  </si>
+  <si>
+    <t>237599187</t>
+  </si>
+  <si>
+    <t>13/01/2026 22:14</t>
+  </si>
+  <si>
+    <t>Allianz ; Assistência Danos ; Apólice ; Automóvel ; Guincho ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Assistência Danos</t>
+  </si>
+  <si>
+    <t>Guincho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133936863_x000D_
+</t>
+  </si>
+  <si>
+    <t>O protetor de cárter do meu carro caiu e ficou pendurado, se arrastando no chão e me impedindo de me locomover com meu veículo. Precisava de uma ajuda simples, apenas para conseguir remover a peça para que eu voltasse para casa. Liguei para o seguro e eles se recusaram a prestar atendimento. Disseram que o guincho não poderia ser chamado porque o carro estava funcionando, e que a assistência por moto não poderia ser enviada porque não se tratava de pane elétrica. Mandaram eu solicitar um mecânico particular às 22h debaixo de uma tempestade para que ele pudesse me trazer uma chave Philips e assim liberar meu carro. Não solicitei nenhum reparo complexo, apenas uma ajuda pontual como ocorreria se tivesse acabado a bateria ou furado um pneu, nada que mecânico de moto não pudesse tentar me ajudar apenas para liberar o veículo até que eu pudesse levá-lo para um lugar seguro e solicitar o reparo no dia seguinte.</t>
+  </si>
+  <si>
+    <t>94221087</t>
+  </si>
+  <si>
+    <t>237601149</t>
+  </si>
+  <si>
+    <t>13/01/2026 22:42</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Guincho ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133920592_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No mês de novembro tive uma ocorrência onde dois pneus do veículo foram danificados impedindo de seguir viagem, com muita dificuldade consegui sinal de celular e fiz contato com a assistência para solicitar um reboque e remover o veículo para comprar pneus novos no dia seguinte, após análise a atendente perguntou se o veículo estava carregado disse que sim, me perguntou se caberia em um taxi falei que se fosse dois taxi ou talvez u. Grande caberia .. assim fui informado que não seria possível seguir para a solicitação pois os reboques não tra porta veículo carregado e que eu deveria solicitar por meios próprios seguir com solicitação de reembolso._x000D_
+_x000D_
+Desta forma seguir, com extrema dificuldade consegui um reboque o valor cobrado foi de R$10150,00._x000D_
+_x000D_
+conforme orientado entrei com a nota fiscal! Pasmem a ALLIANS me reembolso apenas R$ q_x000D_
+_x000D_
+150,00. Esse valor o motorista cabra e para um transporte local entre ruas vizinhas._x000D_
+_x000D_
+Todo o diálogo esta gravado e pode ser verificado!_x000D_
+_x000D_
+Meu sentimento foi de abandono jogado a minha sorte em um estado estranho, carro próximo de uma curva _x000D_
+_x000D_
+Sem moral alguma frente a ALLIANS e detalhe o veículo segurando é de carga._x000D_
+_x000D_
+Diante dos fatos solicito reembolso do valor pago e retração de todo transtorno causado que vai_x000D_
+_x000D_
+Muito além de mero aborrecimento dos tempos modernos._x000D_
+_x000D_
+</t>
+  </si>
+  <si>
+    <t>94230869</t>
+  </si>
+  <si>
+    <t>237626483</t>
+  </si>
+  <si>
+    <t>14/01/2026 09:54</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Gestão de Oficina ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303220434_x000D_
+</t>
+  </si>
+  <si>
+    <t>Abri um sinistro com a seguradora e tem mais de 30 dias,o perito foi na concessionária aonde está o carro 3 vezes.Até agora não liberaram para concessionária nada ,mas recebi email e notificação que está liberado!_x000D_
+_x000D_
+Não façam esse seguro jamais!_x000D_
+_x000D_
+Eles não respeitam seus clientes,façam com empresas renomadas!</t>
+  </si>
+  <si>
+    <t>94239760</t>
+  </si>
+  <si>
+    <t>237640569</t>
+  </si>
+  <si>
+    <t>14/01/2026 11:24</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Apólice ; Cancelamento ; Reclamante em nome do Segurado ; SAC Aberto ; Automóvel ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Cancelamento</t>
+  </si>
+  <si>
+    <t>SAC Aberto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131844250_x000D_
+</t>
+  </si>
+  <si>
+    <t>Prezado Sr. Fábio Ohara,_x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+Na qualidade de responsável pela Allianz Seguros, venho por meio desta formalizar reclamação e notificação, com o devido embasamento jurídico, acerca do cancelamento indevido da apólice n 131844250, referente ao veículo Mercedes-Benz C200 EQ Boost, segurado em nome de Erika Roberto Buccini  CPF 351.318.468-97._x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+Em 06/11, fomos vítimas de assalto, situação que nos obrigou a proceder ao bloqueio imediato dos cartões de crédito. (Betim de ocorrência já apresentado a vocês) Em razão disso, o débito automático das parcelas do seguro, que era realizado via cartão, acabou sendo impactado._x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+Ressalto que havia parcelas com vencimento em 22/11 e 22/12, contudo não houve qualquer comunicação prévia, aviso formal ou notificação por parte da seguradora acerca da inadimplência, tampouco sobre o risco de cancelamento da apólice, o que configura violação direta ao dever de informação, previsto no art. 6, inciso III, do Código de Defesa do Consumidor (Lei n 8.078/90)._x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+Somente em 13/01 fui surpreendido com a informação de que a apólice seria cancelada. Na tentativa de regularização, encontrei instabilidade no sistema de atendimento, sendo direcionado à Ouvidoria, que me orientou quanto ao procedimento para pagamento._x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+Seguindo fielmente as orientações recebidas, realizei o pagamento integral das parcelas em atraso via PIX, em data na qual a apólice ainda constava como ativa, conforme comprovantes anexos._x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+Todavia, mesmo com:_x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+o pagamento devidamente efetuado,_x000D_
+_x000D_
+a apropriação dos valores pela seguradora,_x000D_
+_x000D_
+e a inexistência de comunicação prévia válida de cancelamento,_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+fui informado em 14/01 de que a apólice teria sido cancelada de forma definitiva, o que afronta não apenas o princípio da boa-fé objetiva, previsto no art. 422 do Código Civil, como também configura prática abusiva, vedada pelo art. 39, inciso V, do CDC._x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+Adicionalmente, a manutenção do cancelamento após o recebimento do pagamento caracteriza, em tese, enriquecimento sem causa, nos termos do art. 884 do Código Civil, uma vez que a seguradora se apropriou de valores sem a correspondente contraprestação._x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+Cumpre destacar ainda que, conforme entendimento consolidado dos tribunais, o cancelamento unilateral de contrato de seguro exige comunicação prévia, clara e comprovável ao segurado, sob pena de nulidade do ato, especialmente quando há possibilidade de purgação da mora, como ocorreu no presente caso._x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+Para agravar a situação, o atendimento prestado pelo SAC da Allianz foi inadequado, sem esclarecimentos técnicos, com negativa de informações básicas e ausência de orientação objetiva sobre ressarcimento dos valores pagos, limitando-se a informar prazo genérico de 7 dias, conduta que contraria os princípios da transparência e eficiência nas relações de consumo._x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+Diante de todo o exposto, REQUER-SE._x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+A reativação da apólice n 131844250, considerando a regularização financeira realizada em tempo e no ato da minha ciência com apolice ativa._x000D_
+_x000D_
+Alternativamente, caso a Allianz entenda pela manutenção do cancelamento, apresentação de justificativa formal e fundamentada, com indicação expressa das cláusulas contratuais aplicáveis;_x000D_
+_x000D_
+Restituição imediata e integral dos valores pagos, com informação clara sobre prazos e forma de devolução;_x000D_
+_x000D_
+Registro formal desta manifestação e posicionamento oficial da seguradora._x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+Ressalto que a ausência de solução adequada ensejará a adoção das medidas administrativas e judiciais cabíveis, incluindo, mas não se limitando, à Ouvidoria, SUSEP e Poder Judiciário._x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+Aguardo retorno urgente, compatível com a gravidade da situação e com os princípios que regem os contratos de seguro._x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+Atenciosamente,_x000D_
+_x000D_
+_x000D_
+ _x000D_
+_x000D_
+_x000D_
+Fabio Quinze</t>
+  </si>
+  <si>
+    <t>94241425</t>
+  </si>
+  <si>
+    <t>237643831</t>
+  </si>
+  <si>
+    <t>14/01/2026 11:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133982815_x000D_
+</t>
+  </si>
+  <si>
+    <t>Péssimo atendimento. Na verdade, INEXISTENTE! Após várias tentativas no chat..não cheguei a lugar algum! Liguei no 0800 e os tempo estimado de 4mins..virou 10 e- surpresa! - caiu a chamada! Imagino se fosse problema de sinistro do carro na estrada! LAMENTÁVEL!  Além disso chamei um chaveiro para instalar uma chave tetra e o sujeito - muito, mas muito porco - deixou toda a serragem espalhada pela minha casa. Abriu vários pacotes do ML que não eram da conta dele..um absurdo! Reclamei e me disseram que "não viram nada de errado"..então são cegos. Allianz nunca mais! Além de prestadores de serviço PORCOS AINDA SE FAZEM DE CEGOS! e NÃO ATENDEM O TELEFONE!</t>
+  </si>
+  <si>
+    <t>94242452</t>
+  </si>
+  <si>
+    <t>237646823</t>
+  </si>
+  <si>
+    <t>14/01/2026 12:03</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; Reclamante em nome do Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301173413_x000D_
+</t>
+  </si>
+  <si>
+    <t>Acidente aconteceu no dia 09.12.2025 por volta das 18:00hrs na Av. Domingos Olímpio, 20 - Joaquim Távora. A minha irmã Adriana estava a caminho de casa, quando próximo ao endereço citado colidiu com um motoqueiro ao mudar de faixa, aonde o mesmo também fez o mesmo procedimento. Ao notar a presença do motoqueiro a mesma não conseguiu freiar a tempo e acabou batendo atrás do mesmo, derrubando e danificando a sua moto. Ela bateu atrás e o motoqueiro caiu junto com sua moto. A mesma acionou a seguradora no sinistro da modalidade para terceiros. Então levamos a moto do terceiro até uma oficina referenciada em Fortaleza Ceará, a seguradora pediu fotos, BO, croqui do acidente, uma carta de próprio punho e a documentação. O perito fez a perícia e a seguradora deu prazo até 31.12.2025 para dar uma resposta a autorização. Nesse meio termo enviou uma pessoa que presta serviços a seguradora para realizar uma entrevista, no qual já foi feita com a Adriana(segurada) e com o terceiro. E até momento, dia 14.01.2026 a seguradora não autoriza ou dar uma resposta. Mais de 30 dias aguardando e não resolvem. O terceiro usa sua moto para trabalho, é pai de família e está parado. A segurada está tendo que arcar com as diárias do terceiro parado sem o seu transporte, aonde tira seu ganha pão. Solicitamos uma solução urgente, pois o seguro está em dias e a seguradora já extrapolou todos os prazos possíveis.</t>
+  </si>
+  <si>
+    <t>94246203</t>
+  </si>
+  <si>
+    <t>237657495</t>
+  </si>
+  <si>
+    <t>14/01/2026 13:18</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Pagamento ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
     <t>Pagamento</t>
   </si>
   <si>
-    <t xml:space="preserve">126251864_x000D_
+    <t xml:space="preserve">135830165_x000D_
 </t>
   </si>
   <si>
-    <t>Fui acessar boletos dda e apareceu um boleto de cobrança da Allianz seguros sa, sendo que não possuo vínculos com essa seguradora. Solicito cancelamento desse boleto.</t>
-  </si>
-  <si>
-    <t>94158510</t>
-  </si>
-  <si>
-    <t>237436555</t>
-  </si>
-  <si>
-    <t>12/01/2026 17:04</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 2 Terceiro do Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>2 Terceiro do Sinistro</t>
-  </si>
-  <si>
-    <t>Repasse Time MindBe</t>
-  </si>
-  <si>
-    <t>Micaele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303800212_x000D_
-</t>
-  </si>
-  <si>
-    <t>No dia 19 de Dezembro uma senhora bateu meu carro DO NADA, eu tava na minha faixa direitinha, devagar pois estava chovendo demais e ela sem mais nem menos virou o voltante todo pro meu lado causando o afundamento da lateral esquerda do meu carro, tirou até tinta._x000D_
-_x000D_
-No dia 25 o segurador me mandou uma mensagem dizendo pra que no dia 26 eu aparecesse na loja._x000D_
-_x000D_
-Assim foi feito. Meu carro ficou mais de uma semana parado dentro da oficina esperando uma resposta desse empresa abençoada ALLIANZ._x000D_
-_x000D_
-Na sexta quando eu fudi buscar pra não continuar sem carro, por nem trabalhar eu não estava indo pq eu trabalho há quase 2 horas de distância de casa e não tem rota no meu endereço._x000D_
-_x000D_
-Na sexta mesmo a moça da oficina disse que o status do pedido estava como NÃO AUTORIZADO! _x000D_
-_x000D_
-UM ABSURDO! A pessoa me bate, meu carro fica todo lascado, feio, sem pintura e amassado e eu aiiiinda tenho que ficar sem carro esperando a boa vontade da empresa, sem nenhum prazo, sem nenhuma explicação, sem nada!</t>
-  </si>
-  <si>
-    <t>94158801</t>
-  </si>
-  <si>
-    <t>237437475</t>
-  </si>
-  <si>
-    <t>12/01/2026 17:10</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; OUV ; Sim ; 1 Ctt Sem Sucesso ; Ouv/Procon</t>
-  </si>
-  <si>
-    <t>OUV</t>
-  </si>
-  <si>
-    <t>Ouv/Procon</t>
-  </si>
-  <si>
-    <t>Andreza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304115610_x000D_
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prezados Senhores,_x000D_
-_x000D_
-_x000D_
-Sou BRUNO BATISTA SILVA, segurado da Allianz Seguros S/A, apólice n 5177202556312398639, referente ao veículo Kia Niro, placa TVB1A57._x000D_
-_x000D_
-_x000D_
-Venho, por meio deste, apresentar reclamação formal acerca da condução do sinistro n 304115610, em razão de falhas operacionais relevantes que resultaram em atraso injustificado na tramitação do processo, com prejuízos materiais e logísticos concretos ao segurado._x000D_
-_x000D_
-_x000D_
-A colisão ocorreu em 31/12/2025 e decorreu de responsabilidade exclusiva de terceiro, que ignorou o sinal semafórico vermelho, ocasionando o acidente. Na ocasião, foi acionado o serviço de guincho da Allianz, circunstância em que o registro do sinistro deveria ter sido realizado pelo atendente, ou, ao menos, o segurado deveria ter sido claramente informado de que tal registro ainda não havia sido efetivado._x000D_
-_x000D_
-_x000D_
-Todavia, o sinistro não foi registrado naquele momento, circunstância que somente foi percebida posteriormente, levando à abertura formal do processo apenas em 05/01/2026, ou seja, cinco dias após o evento. Tal atraso não decorreu de inércia do segurado, mas sim de falha no fluxo de atendimento, que acabou por postergar artificialmente todo o trâmite subsequente._x000D_
-_x000D_
-_x000D_
-O cenário se agrava ao se constatar que, mesmo após a abertura do sinistro em 05/01/2026, o processo permaneceu paralisado, sem qualquer encaminhamento efetivo por parte da seguradora, situação que somente foi alterada por provocação direta do segurado. Concessionária e perito informaram reiteradamente estar no aguardo de acionamento da Allianz, evidenciando que a mera abertura do sinistro, desacompanhada de atos concretos como o agendamento da vistoria, revelou-se um registro meramente formal, sem efeito prático  afinal, qual a utilidade de se abrir um sinistro se dele não decorre nenhuma providência efetiva?_x000D_
-_x000D_
-_x000D_
-Somente em 12/01/2026, após sucessivas tentativas de contato, recebi comunicação informando o agendamento da vistoria do veículo, a ser realizada em 13 ou 14 de janeiro de 2026. Até então, não havia qualquer definição sequer quanto à destinação do veículo, se por reparo ou indenização integral._x000D_
-_x000D_
-_x000D_
-Na prática, isso significa que:_x000D_
-_x000D_
-_x000D_
-transcorreram 12 a 14 dias (a depender da efetiva realização da vistoria em 13 ou 14/01) desde o sinistro sem avanço efetivo;_x000D_
-_x000D_
-_x000D_
-houve perda objetiva de tempo útil, seja para conserto, seja para indenização;_x000D_
-_x000D_
-_x000D_
-os prazos totais do processo foram ampliados sem causa atribuível ao segurado._x000D_
-_x000D_
-_x000D_
-Cumpre registrar, ainda, que as tentativas de contato pelos canais telefônicos (0800) revelaram-se ineficientes e inadequadas para a resolução do problema. As ligações apresentam qualidade lastimável, frequentemente são interrompidas, direcionam o atendimento para fluxos automáticos via WhatsApp, e exigem novas chamadas sucessivas, sem possibilidade de transferência ou resolução direta. Esse modelo de atendimento cria entraves operacionais e verdadeiros entreveros procedimentais, ampliando a demora e impondo obstáculos adicionais justamente no momento em que o segurado busca solução célere  cenário incompatível com os padrões atuais de atendimento eletrônico esperados de uma seguradora de grande porte._x000D_
-_x000D_
-_x000D_
-Ressalto que a relação securitária é regida pelos princípios da boa-fé objetiva, eficiência, transparência e razoável duração do procedimento, à luz do Código de Defesa do Consumidor, bem como das normas da SUSEP, que impõem à seguradora o dever de condução diligente e tempestiva dos sinistros._x000D_
-_x000D_
-_x000D_
-Registro, ainda, que sou cliente fiel da Allianz, com histórico de contratação de seguros veiculares e de motocicletas, o que torna ainda mais lamentável a situação ora enfrentada._x000D_
-_x000D_
-_x000D_
-Cumpre destacar, por fim, um aspecto prático e relevante: possuo duas filhas menores, ambas submetidas a sessões diárias de fisioterapia em razão de torcicolo congênito. A indisponibilidade do veículo tem gerado custos adicionais significativos de deslocamento, que já se aproximam, proporcionalmente, do próprio prêmio anual do seguro contratado._x000D_
-_x000D_
-_x000D_
-Diante desse contexto, requeiro:_x000D_
-_x000D_
-_x000D_
-Esclarecimento formal acerca da razão pela qual o sinistro não foi registrado no momento da solicitação do guincho;_x000D_
-_x000D_
-_x000D_
-Justificativa objetiva para a ausência de qualquer movimentação processual entre 05/01/2026 e 12/01/2026;_x000D_
-_x000D_
-_x000D_
-Prioridade na condução da vistoria e na definição da destinação do veículo;_x000D_
-_x000D_
-_x000D_
-Disponibilização do carro reserva a partir do momento da aprovação do conserto ou da indenização, com manutenção do benefício até a efetiva entrega do veículo reparado ao segurado ou, em caso de perda total, até a integral efetivação do pagamento da indenização, como medida mínima de mitigação dos prejuízos já suportados._x000D_
-_x000D_
-_x000D_
-O presente registro tem por objetivo viabilizar solução administrativa adequada, evitando a necessidade de desdobramentos adicionais, inclusive de natureza indenizatória, por danos materiais decorrentes de demora injustificada._x000D_
-_x000D_
-_x000D_
-Aguardo retorno formal, por escrito, com o devido número de protocolo._x000D_
-_x000D_
-_x000D_
-Atenciosamente,_x000D_
-_x000D_
-_x000D_
-_x000D_
-</t>
-  </si>
-  <si>
-    <t>94159869</t>
-  </si>
-  <si>
-    <t>237440819</t>
-  </si>
-  <si>
-    <t>12/01/2026 17:34</t>
-  </si>
-  <si>
-    <t>Allianz ; CPF/CNPJ ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; Sem Resposta - Dentro SLA ; 1 Ctt Sem Sucesso</t>
-  </si>
-  <si>
-    <t>CPF/CNPJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303584510_x000D_
-</t>
-  </si>
-  <si>
-    <t>Meu marido bateu com nosso carro, iriamos pagar a franquia. Mas a Allianz somente nos deu uma opção de ofina para consertar o carro. Não queremos fazer onde foi indicada, mas nos informaram que não podem trocar pois a oficina já comprou as peças. Só acho engraçado que não autorizei nada, fui na oficina indicada para fazer vistoria, não sabia que ali que seria feito o serviço. E onde indicaram não quero fazer._x000D_
-_x000D_
-Já solicitei ao corretor que risque a Allianz da lista de cotações para o próximo ano.</t>
-  </si>
-  <si>
-    <t>94160946</t>
-  </si>
-  <si>
-    <t>237443883</t>
-  </si>
-  <si>
-    <t>12/01/2026 17:57</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303665885_x000D_
-</t>
-  </si>
-  <si>
-    <t>Acionamos o seguro contra terceiros, porém a seguradora, sem nem realizar uma vistoria no carro, decretou que o valor do reparo seria 838 reais, enquanto os orçamentos que temos são na ordem de 1250 reais e agora não tem como resolver a situação._x000D_
-_x000D_
-_x000D_
-ESSA SEGURADORA NÃO É CONFIÁVEL NÃO FAÇAM SEGUROS, POIS NA HORA DE COBRAR SÃO MUITO BONS, MAS NA HORA DE PAGAR É ESSA ENROLAÇÃO.</t>
-  </si>
-  <si>
-    <t>94163003</t>
-  </si>
-  <si>
-    <t>237450005</t>
-  </si>
-  <si>
-    <t>12/01/2026 18:47</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Residência</t>
-  </si>
-  <si>
-    <t>Assistência Não Danos</t>
-  </si>
-  <si>
-    <t>Assistência Residencial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133194397_x000D_
-</t>
-  </si>
-  <si>
-    <t>É o segundo ano que contrato um seguro residencial pela empresa mas nunca havia utilizado. Hoje, precisei de um serviço de hidráulica pois parece que a torneira da pia da cozinha está com ar pois está saindo pouca água. Avisei que havia um aquecedor na torneira mas que estava desativado. A atendente marcou um atendimento emergencial para as 14h. Às 17:30h liguei na empresa e fui informada que o serviço tinha sido cancelado pois o técnico não vai sem antes saber se a tubulação da torneira é de cobre ou pvc. Não fui avisada em nenhum momento dessa exigência, perdemos nossa tarde e estamos com o problema. Já enviei mensagem para o meu corretor pedindo o cancelamento do seguro e a migração para a Porto Seguro. _x000D_
-_x000D_
-Minha mensagem é para alertá-los, não queira economizar na hora de fechar o seguro com essa empresa que muitas vezes é mais barata que a Porto,  pois o barato sairá caro. Minha filha chamou hoje o técnico da Porto para instalar ventiladores na casa dela , não teve burocracia nenhuma, ela teve que abrir outra Ordem de Serviço e o próprio técnico fez isso. _x000D_
-_x000D_
-Não economizem , a Porto não tem essa restrição! Fuja dessa empresa e de seus atendentes mal informados. Muito obrigado.</t>
-  </si>
-  <si>
-    <t>94169099</t>
-  </si>
-  <si>
-    <t>237469351</t>
-  </si>
-  <si>
-    <t>12/01/2026 21:57</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; 1 Segurado ; Não ; Sim ; 1 Ctt Com Sucesso ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>1 Ctt Com Sucesso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135574955_x000D_
-</t>
-  </si>
-  <si>
-    <t>Eu estou tentando resolver um problema de um serviço de assistência que instalou um surporte na minha parede que caiu. Quase quebrou minha TV. E não instalou o olho mágico que estava contratado tb._x000D_
-_x000D_
-Hoje, um rapaz foi reinstalar o suporte, mas deixou o rombo da instalação anterior. Muito feio. E não instalou o olho mágico. Ele me recomendou que eu abrisse um novo chamado pra isso. Eu entrei em contato com a Allianz e a mesma informa que a empresa ainda não disponibilizou o laudo da situação e que isso poderia ficar pronto somente 14/jan. Eu viajo de quinta pra sexta. O atendimento da assistência 24h desligou o chat na minha cara. Eles estão desrespeitando contrato. Isso não vai ficar assim. Eles querem que seja eu a resolver o problema do desleixo e desrespeito deles.</t>
-  </si>
-  <si>
-    <t>94174469</t>
-  </si>
-  <si>
-    <t>237485923</t>
-  </si>
-  <si>
-    <t>13/01/2026 07:58</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Guincho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134033038_x000D_
-</t>
-  </si>
-  <si>
-    <t>No dia 25/12 necessitei do serviço do seguro e só venho tendo dor de cabeça desde então. 1 quando solicitamos o guincho a informação de que precisa de táxi precisa fica clara para o consumidor. 2 a informação de onde vai ficar seu carro não é objetiva parece que o motorista que decide. Ia para minha casa, depois não foi no outro dia o motorista não queria levar para oficina. 3 o acesso pelo app é pessimo e carente de atualização. Não consegui fazer meu cadastro cm facilidade. Tive que pedir apoio da corretora meu CPF dava como inválido. Quando consegui nao tem nem minha carteirinha nem do meu contrato. 4 o atendimento telefônico tem que dar sorte alguns atendentes jogam com vc pq não sabem a informação. Liguei para saber onde estava meu carro e ninguém sabia. E pasmem varios me mandaram ligar na oficina. 5 quando voce liga pede para resolver por WhatsApp ou no app mas como se nada atualiza? Hoje mesmo estou tentado informação se liberou meu sinistro e só da erro na página. 6 quando vc esta numa urgência abrindo um sinistro vc quer agilidade comecei meu atendimento as 21h a atendente via WhatsApp foi me retornar as 23h. Esse é o padrão de atendimento de vcs? Sinto muito informar mas está pessimo</t>
-  </si>
-  <si>
-    <t>94178101</t>
-  </si>
-  <si>
-    <t>237496287</t>
-  </si>
-  <si>
-    <t>13/01/2026 09:35</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 2 Terceiro do Sinistro ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">301157511_x000D_
-</t>
-  </si>
-  <si>
-    <t>Na data de 08 de outubro de 2025, por volta das 18h, tive meu veículo abalroado pelo segurado desta empresa, conforme descrito a seguir: "Estava estacionado no logradouro do sinistro, com a porta  do veículo levemente aberta (cerca de 25 cm entre a lingueta e o pino metálico do chassi) com uma perna do lado de fora e com o corpo para o lado de dentro, debruçado no banco do passageiro procurando um objeto (a porta estava encostada na minha perna). Neste momento senti uma forte colisão recolhendo imediatamente a perna para não ser atingido. Foi quando notei que o veículo do segurado atingiu  a lingueta da porta que já estava levemente aberta por um tempo (sendo possível a visualização pelo condutor), oque resultou no sanfonamento da porta do carro e uma trinca no para-brisa. Em momento algum eu abri a porta repentinamente, deixei totalmente aberta ou desci do veículo, fatos estes que poderiam ter causado a colisão por minha culpa exclusiva. Esclareço que o veículo do segurado passou rente ao meu demonstrando falta de atenção do motorista ao não manter a distância de segurança necessária. Ele só não causou mais danos porque no primeiro impacto ele deslocou seu veículo para o lado oposto. Afirmo que de qualquer maneira ele abalroaria meu veículo que estava estacionado, atingindo no mínimo o retrovisor mesmo a porta estando trancada._x000D_
-_x000D_
-No dia 09 de outubro de 2025 recebi um telefonema da corretora de seguros representando o segurado. Fui informado que seu cliente assumiu que foi ele quem causou o acidente, responsabilizando-se pelo conserto do meu veículo. Inclusive, o segurado redigiu uma carta de próprio punho assumindo a responsabilidade de ter causado o sinistro, carta está que foi entregue a seguradora. A partir do dia 22 de outubro de 2025, data em que levei meu veículo para passar pela vistoria para constatar os danos, fui informado pela corretora que brevemente o conserto estaria autorizado. Frequentemente entrava em contato com a corretora e sempre me informavam que a liberação para o conserto estaria para ocorrer quando, para minha surpresa, no dia 09 de dezembro fui informado que a seguradora recusou o meu atendimento encerrando o sinistro sem indenização. _x000D_
-_x000D_
-O corretor afirmou que o encerramento do sinistro sem indenização por parte da seguradora foi embasado no artigo 49 do CTB (o condutor e os passageiros não deverão abrir a porta do veículo, deixá-la aberta ou descer do veículo sem antes se certificarem de que isso não constitui perigo para eles e para outros usuários da via). Disse o corretor que ele não concordava com a decisão da seguradora e que já havia aberto um protocolo de reclamação na central da seguradora e que tinha pedido uma ajuda para a gerencia da Allianz para uma nova análise do sinistro, reforçando que nem ele e nem seu cliente(segurado) concordavam com a decisão, pois, a culpa pelo acidente não era do terceiro (minha pessoa no caso)._x000D_
-_x000D_
-Fatos expostos peço que a seguradora reavalie o caso em questão (NEGATIVA ABUSIVA) não isentando o seu segurado da culpa pelo acidente pelo fato de que a porta não estava sendo aberta na trajetória do veículo conforme a interpretação da seguradora._x000D_
-_x000D_
-Sem mais para o momento, aguardo  decisão favorável para evitar maiores transtornos.</t>
-  </si>
-  <si>
-    <t>94180456</t>
-  </si>
-  <si>
-    <t>237503147</t>
-  </si>
-  <si>
-    <t>13/01/2026 10:17</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Residência ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302506839_x000D_
-</t>
-  </si>
-  <si>
-    <t>Abri um sinistro junto a seguradora, pois devido a um temporal que ocorreu na minha região, tivemos uma infiltração no teto gerando a queda do lustre de nossa sala. Antes do episódio desse temporal, nunca tinha passado por infiltração nessa parte da casa, inclusive, acionamos o síndico e eles fizeram a cobertura com manta na fissura. Ocorre que a seguradora recusou meu sinistro informado se tratar de uma fissura já existente. A questão é, se a fissura já existia, porque antes do temporal eu nunca tive problemas ?  Como a seguradora pode determinar se essa fissura já existia, se eles nem foram até o meu apartamento, subiram no telhado ou algo desse sentido? Porque eu pago um seguro se em um momento como esses não posso contar com a seguradora? Absurdo e descaso total, até a minha gerente do Sicredi que me vendeu o seguro utilizou o termo eles estão agindo com má fé, abre um sac.</t>
-  </si>
-  <si>
-    <t>94186048</t>
-  </si>
-  <si>
-    <t>237515913</t>
-  </si>
-  <si>
-    <t>13/01/2026 11:31</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; Sem Resposta - Dentro SLA ; 1 Ctt Sem Sucesso ; Sem Solução - Fora do Escopo de Atuação</t>
-  </si>
-  <si>
-    <t>Sem Solução - Fora do Escopo de Atuação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">298542657_x000D_
-</t>
-  </si>
-  <si>
-    <t>Fiz a revisão dos reparos do acontecimento a seguradora não me deu suporte dos reparos ainda cancelaram meu seguro sem nenhuma justificativa</t>
+    <t>Meu esposo ao realizar o pagamento do seguro do nosso carro, ao invés de pagar do mês referente a Janeiro, pagou do mês referente a setembro que seria a última parcela._x000D_
+_x000D_
+Quando dei conta, porque abri o aplicativo e constava em aberto o pagamento de Janeiro, estranhei e fui conferir, geralmente sou eu quem faz o pagamento por estar no meu nome já recebo notificação do nubank. _x000D_
+_x000D_
+Ao entrar em contato com a Allianz no primeiro contato precisava ligar em outro setor, na segunda tentativa a moça me informou que não era possível reverter o pagamento nem reembolso, ao tentar entrar em contato com a ouvidoria a atendente me disse que a Ouvidoria não tinha acesso e nem autorização para esse tipo de tratativa._x000D_
+_x000D_
+Eu entendo que o erro foi "nosso", mas não vi nenhum tentativa de procurar solucionar o problema, ou alguma alternativa. Geralmente outras empresas dão alternativas ou até mesmo o reembolso._x000D_
+_x000D_
+É a segunda vez que preciso da Allianz e não tenho cooperação e retorno._x000D_
+_x000D_
+Allianz Seguros para carro esta sendo decepcionante totalmente diferente do seguro imóvel que tive e não tive do que reclamar, tanto pra atendimento quanto pra solução de problemas. Parecem ser empresas totalmente distintas que só possuem o mesmo nome.</t>
   </si>
 </sst>
 </file>
@@ -1286,22 +1397,22 @@
         <v>31</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>37</v>
@@ -1322,10 +1433,10 @@
         <v>41</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="Y3" s="3" t="s">
         <v>26</v>
@@ -1335,13 +1446,13 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>30</v>
@@ -1350,25 +1461,25 @@
         <v>31</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>31</v>
@@ -1383,13 +1494,13 @@
         <v>40</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="Y4" s="3" t="s">
         <v>26</v>
@@ -1399,13 +1510,13 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>30</v>
@@ -1414,25 +1525,25 @@
         <v>31</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>31</v>
@@ -1441,19 +1552,17 @@
         <v>38</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="P5" s="3" t="s">
         <v>40</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>65</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="W5" s="4"/>
       <c r="X5" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Y5" s="3" t="s">
         <v>26</v>
@@ -1463,13 +1572,13 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>30</v>
@@ -1478,46 +1587,46 @@
         <v>31</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>37</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>38</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y6" s="3" t="s">
         <v>26</v>
@@ -1527,13 +1636,13 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>30</v>
@@ -1542,13 +1651,13 @@
         <v>31</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>35</v>
@@ -1560,7 +1669,7 @@
         <v>36</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>31</v>
@@ -1575,7 +1684,7 @@
         <v>40</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="W7" s="4" t="s">
         <v>81</v>
@@ -1624,28 +1733,28 @@
         <v>36</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>38</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>40</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>26</v>
@@ -1655,13 +1764,13 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>30</v>
@@ -1670,46 +1779,46 @@
         <v>31</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>95</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>38</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>40</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>26</v>
@@ -1719,13 +1828,13 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>30</v>
@@ -1734,25 +1843,25 @@
         <v>31</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>95</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>31</v>
@@ -1761,19 +1870,19 @@
         <v>38</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>40</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>26</v>
@@ -1781,13 +1890,13 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>30</v>
@@ -1796,22 +1905,22 @@
         <v>31</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>37</v>
@@ -1823,19 +1932,19 @@
         <v>38</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="P11" s="3" t="s">
         <v>40</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="W11" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Y11" s="3" t="s">
         <v>26</v>
@@ -1843,13 +1952,13 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>30</v>
@@ -1858,25 +1967,25 @@
         <v>31</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>31</v>
@@ -1885,19 +1994,19 @@
         <v>38</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>40</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>26</v>
@@ -1905,13 +2014,13 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>30</v>
@@ -1920,7 +2029,7 @@
         <v>31</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>33</v>
@@ -1929,13 +2038,13 @@
         <v>34</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>34</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>37</v>
@@ -1947,19 +2056,19 @@
         <v>38</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="P13" s="3" t="s">
         <v>40</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="X13" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="X13" s="4" t="s">
+        <v>125</v>
       </c>
       <c r="Y13" s="3" t="s">
         <v>26</v>
@@ -1967,13 +2076,13 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>30</v>
@@ -1982,80 +2091,252 @@
         <v>31</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>38</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="V14" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W15" s="4"/>
+      <c r="A15" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="W15" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
+      <c r="A16" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="W16" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="X16" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y16" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="17" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="18" spans="23:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="W18" s="4"/>
     </row>
-    <row r="19" spans="23:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
     </row>
-    <row r="20" spans="23:24" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="W20" s="4"/>
       <c r="X20" s="4"/>
     </row>
-    <row r="21" spans="23:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="W21" s="4"/>
     </row>
-    <row r="22" spans="23:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="W22" s="4"/>
       <c r="X22" s="4"/>
     </row>

--- a/Treinamento/GestaoReclamacao.xlsx
+++ b/Treinamento/GestaoReclamacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D378A09C-E073-4732-A821-5777F39DC246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635C64A2-2BD9-4804-8007-52D601B5E638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B1A77FD5-2AD3-4458-ACB3-7F19D1A3340A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="186">
   <si>
     <t>Id HugMe</t>
   </si>
@@ -119,16 +119,13 @@
     <t xml:space="preserve">Resultado </t>
   </si>
   <si>
-    <t>Processar</t>
-  </si>
-  <si>
-    <t>95102089</t>
-  </si>
-  <si>
-    <t>239823459</t>
-  </si>
-  <si>
-    <t>05/02/2026 01:08</t>
+    <t>95153266</t>
+  </si>
+  <si>
+    <t>239969525</t>
+  </si>
+  <si>
+    <t>06/02/2026 12:00</t>
   </si>
   <si>
     <t>Não respondido</t>
@@ -137,536 +134,737 @@
     <t>Não</t>
   </si>
   <si>
-    <t>Allianz ; Apólice ; Vida / Acidentes Pessoais ; Canal de Atendimento ; Corretor ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
     <t>Allianz</t>
   </si>
   <si>
+    <t>Sinistro</t>
+  </si>
+  <si>
+    <t>Automóvel</t>
+  </si>
+  <si>
+    <t>Análise Sinistro</t>
+  </si>
+  <si>
+    <t>1 Segurado</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>1 Ctt Sem Sucesso</t>
+  </si>
+  <si>
+    <t>Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Juliana</t>
+  </si>
+  <si>
+    <t>303814204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+Data: 06/02/2026_x000D_
+Texto: @303814204_x000D_
+Usuário: Andreza_x000D_
+</t>
+  </si>
+  <si>
+    <t>Sofri um sinistro em Dezembro/2025 e o carro foi constatado perda total. O carro foi recolhido pela seguradora e precisei fazer a transferência do CRV para a Allianz, no entanto, perdi meu CRV e estou tentando uma segunda vida visto que meu documento antigo não era digital. O DETRAN PE precisa fazer uma vistoria externa, ainda que o carro esteja em sucata, o mesmo precisa do endereço de onde esta o veículo para poder realizar essa vistoria. A Allianz informa que não tem como fazer vistoria uma vez que o carro deu perda total e pediu que procurasse um despachante. Fizemos isso, e mesmo com o despachante o DETRAN ainda informa que precisa fazer a vistoria externa. Precisamos do endereço de onde está o veículo para que essa vistoria possa ser efetuada, pois no sistema do DETRAN não há nenhuma informação da seguradora que o veículo em questão foi perda total.</t>
+  </si>
+  <si>
+    <t>95151563</t>
+  </si>
+  <si>
+    <t>239965057</t>
+  </si>
+  <si>
+    <t>06/02/2026 11:29</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; Reclamante em nome do Segurado ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA ; Sac Enc</t>
+  </si>
+  <si>
     <t>Apólice</t>
   </si>
   <si>
-    <t>Vida / Acidentes Pessoais</t>
-  </si>
-  <si>
-    <t>Canal de Atendimento</t>
-  </si>
-  <si>
-    <t>Corretor</t>
-  </si>
-  <si>
-    <t>1 Segurado</t>
-  </si>
-  <si>
-    <t>Sim</t>
-  </si>
-  <si>
-    <t>1 Ctt Sem Sucesso</t>
-  </si>
-  <si>
-    <t>Sem Resposta - Dentro SLA</t>
+    <t>Residência</t>
+  </si>
+  <si>
+    <t>Assistência Não Danos</t>
+  </si>
+  <si>
+    <t>Assistência Residencial</t>
+  </si>
+  <si>
+    <t>Reclamante em nome do Segurado</t>
+  </si>
+  <si>
+    <t>Sac Enc</t>
+  </si>
+  <si>
+    <t>133226972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+Data: 06/02/2026_x000D_
+Texto: @133226972_x000D_
+Usuário: Andreza_x000D_
+_x000D_
+Data: 06/02/2026_x000D_
+Texto: Tem SAC 26/0001756 SLA 08/02_x000D_
+Usuário: Andreza_x000D_
+</t>
+  </si>
+  <si>
+    <t>Tenho um seguro residencial pela ALLIANZ em nome da minha esposa. Precisei acionar um serviço emergencial que consta na minha apólice. Foi agendado o serviço mas no dia, ninguém apareceu. Fiz contato novamente com a central e me informaram que NÃO HAVIA PRESTRADOR para me atender. Contratei um prestador particular par posterior pedido de reembolso. Fiz o pagamento de R$ 160,00 reais pelo serviço, paguei e enviei a documentação para a seguradora no dia 20/01/2026. Até hoje, não me reembolsaram. Criam uma burocracia que só me cria aborrecimentos e perda de tempo.</t>
+  </si>
+  <si>
+    <t>95149954</t>
+  </si>
+  <si>
+    <t>239960375</t>
+  </si>
+  <si>
+    <t>06/02/2026 10:57</t>
+  </si>
+  <si>
+    <t>2 Terceiro do Sinistro ; Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>2 Terceiro do Sinistro</t>
+  </si>
+  <si>
+    <t>Repasse Time MindBe</t>
+  </si>
+  <si>
+    <t>Carla</t>
+  </si>
+  <si>
+    <t>303933828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+Data: 06/02/2026_x000D_
+Texto: @303933828_x000D_
+Usuário: Carla_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fomos envolvidos em um acidente no dia 27/12/2025 e o causador do sinistro é segurado da Allianz, por isso, a indenização foi paga pela seguradora a mim como terceiro envolvido._x000D_
+_x000D_
+_x000D_
+O que ocorre, é que a indenização foi caracterizada como total, com base na tabela FIPE de dez/2025, ainda que a  indenização tenha sido efetuada em Jan/2026. Porém, foi descontado o valor integral do IPVA referente à 2026._x000D_
+_x000D_
+_x000D_
+Dois pesos e duas medidas. Para a indenização, a base é 2025 (valor menor), mas para desconto do IPVA a base é 2026._x000D_
+_x000D_
+Não concordamos, pois o imposto é devido para a utilização do automóvel durante o ano de 2026 e não rodamos um dia sequer, visto que o carro ficou impossibilitado de uso desde 27/12, data do sinistro._x000D_
+_x000D_
+_x000D_
+Queremos a devolução integral do valor do IPVA 2026 e o proporcional do licenciamento, visto que a taxa foi paga no prazo e está vigente._x000D_
+_x000D_
+_x000D_
+Já tentamos contato e negociação com a Allianz por 3 vezes essa semana e não tivemos retorno favorável. _x000D_
+_x000D_
+</t>
+  </si>
+  <si>
+    <t>95137457</t>
+  </si>
+  <si>
+    <t>239925955</t>
+  </si>
+  <si>
+    <t>05/02/2026 22:04</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Sac Enc ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
     <t>Andreza</t>
   </si>
   <si>
-    <t>131090486</t>
-  </si>
-  <si>
-    <t>Nunca fiz um seguro nessa empresa mas eles me mandaram um boleto com meu nome não tenho seguro não entendo pq estão me cobrando esses bandidos._x000D_
-_x000D_
-Não sei se foi o banco q fez esse seguro mas eu nunca dei autorização não sei como conseguiram meu CPF. Criminosos</t>
-  </si>
-  <si>
-    <t>95099732</t>
-  </si>
-  <si>
-    <t>239816383</t>
-  </si>
-  <si>
-    <t>04/02/2026 22:27</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Residência</t>
-  </si>
-  <si>
-    <t>Assistência Não Danos</t>
-  </si>
-  <si>
-    <t>Assistência Residencial</t>
-  </si>
-  <si>
-    <t>131925179</t>
-  </si>
-  <si>
-    <t>Abri uma solicitação para barulho no ar condicionado e o prestador informou que precisaria voltar apos a liberação como retorno de manutenção, somente após eu ir atras do corretor fui informado da negativa pq oprestador preencheuo laudo como limpeza e não como manutenção e agora como ja tive um acionamento perdi o direito de receber a manutenção devido ao erro no preenchimento do laudo do prestador de serviço</t>
-  </si>
-  <si>
-    <t>95097239</t>
-  </si>
-  <si>
-    <t>239808691</t>
-  </si>
-  <si>
-    <t>04/02/2026 20:49</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; 2 Terceiro do Sinistro ; Análise Sinistro ; Repasse Time MindBe ; Não ; Sim ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Sinistro</t>
-  </si>
-  <si>
-    <t>Automóvel</t>
-  </si>
-  <si>
-    <t>Análise Sinistro</t>
-  </si>
-  <si>
-    <t>2 Terceiro do Sinistro</t>
-  </si>
-  <si>
-    <t>Repasse Time MindBe</t>
+    <t>302587058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+Data: 06/02/2026_x000D_
+Texto: @302587058_x000D_
+Usuário: Andreza_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cliente há 5 anos._x000D_
+_x000D_
+_x000D_
+Primeiro acidente leve da vida: roda dianteira direita quebrada, portas amassaram, e um retrovisor perdido, além de defeitos leves na lataria frontal._x000D_
+_x000D_
+_x000D_
+Gasto Total: 5 x 12 x R$300 = R$18.000 (seguro)_x000D_
+_x000D_
+_x000D_
+[ + 5xR$40 x 4 x 12 x 5 = R$60.000 (estacionamento) + 5 x R$4.000 = R$20.000 (revisões em concessionária Volkswagen) + Guincho 2x que paguei por 1) não atender e estar em local perigoso + 2) estrada ]_x000D_
+_x000D_
+_x000D_
+Primeira vez que necessitei acionar R$2.300 + Uber R$300 até Mooca (serviço level B, considerado bom). Nem pedi guincho na ida, fui só com um retrovisor, contente com o fato de estar bem amparado, até que_x000D_
+_x000D_
+_x000D_
+Resposta de sinistro acusou meu relato de mentiroso: teoricamente eu estava andando com as duas portas amassadas segundo ao colaborador da Allianz_x000D_
+_x000D_
+_x000D_
+SAC 1 (funcionário bom e ruim tem em toda empresa, poderia não ser culpa da Allianz, né?) _x000D_
+_x000D_
+_x000D_
+Mooca me liga: carro tá pronto_x000D_
+_x000D_
+_x000D_
+Cheguei lá, sem os dois retrovisores (teoricamente era brinde no contrato. A roda era o estepe que eu troquei. A lataria desamassaram mais ou menos. Trocaram peças baratas._x000D_
+_x000D_
+_x000D_
+Carro sem condições de andar, inclusive com um retrovisor que estava danificado mas tinha, sem. Resposta da Allianz: um advogado citando termos que eles adoram e ninguém entende defendendo o funcionário, que apenas negou sem justificar._x000D_
+_x000D_
+_x000D_
+A supervisão na Mooca, tinha até pena dos funcionários, centenas de carros. Mas nem pra olharem debaixo onde tbm tinha danos. E ainda me ligaram pra pegar antes. A Allianz estava avaliando, ou melhor, estavam aguardando o advogado pra falar com o cliente._x000D_
+_x000D_
+_x000D_
+O advogado nunca vi, nem viu o carro, nem viu nada. Uma empresa quebrando recorde de lucros e não cumpre nem a parte dela como seguradora e nem a parte de contratar bons funcionários e bons mecânicos._x000D_
+_x000D_
+_x000D_
+Mas advogado pra acusar minha descrição de mentirosa, eles tem. Nem respondi, nota dó. Eu contratei pensando que eram o que tinha melhor. Nunca vi serviço tão porco na minha vida. Nunca vi alguém me dar suporte._x000D_
+_x000D_
+_x000D_
+Exceto 1x por ano, pra renovar. Dia 28 agora termina o contrato, alguma sugestão ou todas trabalham com burocratização e trade-off lucrativo?_x000D_
+_x000D_
+_x000D_
+Existe seguradora séria?  Que assegura, no caso. _x000D_
+_x000D_
+_x000D_
+Invistam em ações da Allianz pq ela nunca vai perder. Quem perde é o cliente bobo que nem eu, que acredita._x000D_
+_x000D_
+_x000D_
+Para quem dirige bem e não mora em local de roubo comum, não vale a pena. Guardem o dim. Seguro estás Allianz, lucrando sem trabalhar._x000D_
+_x000D_
+_x000D_
+Se valesse a pena ter seguro eles teriam algum prejuízo, nunca tem. Ou seja, para poucos pode ser que vale a pena. _x000D_
+_x000D_
+_x000D_
+De vez em quando eles fingem que asseguram._x000D_
+_x000D_
+_x000D_
+PT, roubo, e retrovisor de plástico._x000D_
+_x000D_
+_x000D_
+Aliás nesse sinistro a conta do retrovisor er R$2.400!_x000D_
+_x000D_
+_x000D_
+De 0 para R$2.400! E o mecânico amanhã me cobrará R$450 pelos 3 dias que estava trabalhando e não pude pegar o carro._x000D_
+_x000D_
+_x000D_
+Isso pq levaram 1 mês pra fazer quase nada._x000D_
+_x000D_
+_x000D_
+Brasil, um país de tolos. Nós somos trouxas._x000D_
+_x000D_
+_x000D_
+</t>
+  </si>
+  <si>
+    <t>95136040</t>
+  </si>
+  <si>
+    <t>239921635</t>
+  </si>
+  <si>
+    <t>05/02/2026 21:08</t>
+  </si>
+  <si>
+    <t>1 Segurado ; Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Não ; Sim</t>
+  </si>
+  <si>
+    <t>Guincho</t>
+  </si>
+  <si>
+    <t>135968772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+Data: 06/02/2026_x000D_
+Texto: @135968772_x000D_
+Usuário: Carla_x000D_
+_x000D_
+Data: 06/02/2026_x000D_
+Texto: E-mail enviado_x000D_
+Usuário: Juliana_x000D_
+</t>
+  </si>
+  <si>
+    <t>Solicitação de guincho com carro de apoio para retirada do veículo no 2 subsolo. Solicitação às 16:36,  o guincho chegou sem o reboque para retirada do carro, as 19:13 da noite previsão de chegada em 40 minutos._x000D_
+_x000D_
+Desrespeito total com o consumidor, mais de 4 horas para enviar um guincho com reboque._x000D_
+_x000D_
+Nunca mais fecho que esse seguro, vergonha, falta de respeito.</t>
+  </si>
+  <si>
+    <t>95135718</t>
+  </si>
+  <si>
+    <t>239920585</t>
+  </si>
+  <si>
+    <t>05/02/2026 20:56</t>
+  </si>
+  <si>
+    <t>2 Terceiro do Sinistro ; Allianz ; Sinistro ; Sinistro ; Automóvel ; Análise Sinistro ; Sem Resposta - Dentro SLA ; Repasse Time MindBe ; Não ; Sim</t>
   </si>
   <si>
     <t>Mari</t>
   </si>
   <si>
-    <t>304961933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contestação de Reparo e Pleito de Indenização Integral_x000D_
-_x000D_
-À Allianz _x000D_
-_x000D_
-Ref.: Sinistro n 304961933_x000D_
-_x000D_
-Veículo: FIAT/ NOVO UNO/ EWS2426_x000D_
-_x000D_
-Na qualidade de terceiro prejudicado no evento ocorrido em23/01/2026 , venho formalizar minha discordância quanto à proposta de reparo do veículo acima identificado, pelos fundamentos expostos:_x000D_
-_x000D_
-Da Natureza do Dano Estrutural: O orçamento prévio aponta dano na longarina do veículo. Conforme as normas técnicas de engenharia mecânica e padrões de segurança veicular, a longarina é o componente estrutural primário do chassi. Qualquer intervenção (solda, estiramento ou aquecimento) compromete a integridade da peça e a segurança dos ocupantes em colisões futuras._x000D_
-_x000D_
-Da Desvalorização de Mercado (Vício Oculto e Cautelar): Um veículo com histórico de reparo em longarina sofre rejeição imediata no mercado. O apontamento em laudo de Vistoria Cautelar deprecia o bem em patamares de 20% a 40%, conforme a prática comercial. O conserto, portanto, não restabelece o status quo ante, violando o Art. 944 do Código Civil, que prevê que a indenização mede-se pela extensão do dano._x000D_
-_x000D_
-Do Direito à Reparação Integral: Conforme o Art. 186 e Art. 927 do Código Civil, aquele que comete ato ilícito fica obrigado a reparar o dano. Se o reparo técnico é incapaz de devolver o valor de mercado original do bem, a seguradora (por solidariedade) e seu segurado devem arcar com a Indenização Integral (Tabela FIPE 100%)._x000D_
-_x000D_
-Do Requerimento:_x000D_
-_x000D_
-Diante do exposto, solicito a reclassificação do dano para Perda Total, com o consequente pagamento da indenização integral. _x000D_
-_x000D_
-Aguardo retorno em até [48 horas] antes de acionar as vias judiciais e registrar reclamação junto à SUSEP._x000D_
-_x000D_
-Atenciosamente,_x000D_
-_x000D_
-Elisana Roberta Carvalho do Nascimento _x000D_
-_x000D_
+    <t>304170744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+Data: 06/02/2026_x000D_
+Texto: @304170744_x000D_
+Usuário: Carla_x000D_
 </t>
   </si>
   <si>
-    <t>95095999</t>
-  </si>
-  <si>
-    <t>239804907</t>
-  </si>
-  <si>
-    <t>04/02/2026 20:09</t>
-  </si>
-  <si>
-    <t>Automóvel ; 1 Segurado ; Análise Sinistro ; Sinistro ; Sinistro ; Allianz ; Repasse Time MindBe ; Não ; Sem Resposta - Dentro SLA ; Sim</t>
+    <t>Levei meu carro em 15/01/2026 para troca da porta do porta-malas após um sinistro causado por terceiro. O serviço foi realizado a oficina Flabel em Belo Horizonte onde fui muito bem atendida e o reparo feito de forma impecável. Inclusive fiz um serviço particular complementar no mesmo carro com a oficina de tanto que gostei dos serviços prestados e super indico. Pois bem, com relação ao reparo do porta-malas, ele estava com funcionamento perfeito das alças ou amortecedores que o sustentam abertos e suspensos. A seguradora não autorizou o reparo ou troca pela oficina alegando que tal ocorrido se deu pelo desgaste desses amortecedores. Mas esse desgaste ocasionou o não funcionamento somente no momento da troca do porta-malas? Eles estavam funcionando normalmente quando meu carro entrou para o reparo e tenho fotos que comprovam. Preciso que a seguradora Allianz reveja essa questão pois tenho direito do serviço completo. Meu carro precisa ser entregue com todas as funções que existiam antes do sinistro e antes do reparo. Caso venham a insistir nisso, acionarmos os meios legais.</t>
+  </si>
+  <si>
+    <t>95134629</t>
+  </si>
+  <si>
+    <t>239917393</t>
+  </si>
+  <si>
+    <t>05/02/2026 20:18</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; Reclamante em nome do Segurado ; SAC Aberto ; 1 Ctt Sem Sucesso ; Sim ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>SAC Aberto</t>
+  </si>
+  <si>
+    <t>136082709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+Data: 06/02/2026_x000D_
+Texto: @136082709_x000D_
+Usuário: Andreza_x000D_
+_x000D_
+Data: 06/02/2026_x000D_
+Texto: SAC 26/0002015 SLA 12/02_x000D_
+Usuário: Andreza_x000D_
+</t>
+  </si>
+  <si>
+    <t>Solicitei serviço de Encanador com urgência,  pois o cano de água estourou às 14:19h, porém até o momento,  20:20h não tive retorno, ninguém apareceu e nem meu problema resolvido.  Estou sem água na casa, desde às 14:19h, pois tive que fechar o registro para parar o "alagamento" dentro de casa.</t>
+  </si>
+  <si>
+    <t>95132585</t>
+  </si>
+  <si>
+    <t>239911265</t>
+  </si>
+  <si>
+    <t>05/02/2026 19:14</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Fornecimento de Peças ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Fornecimento de Peças</t>
   </si>
   <si>
     <t>Eliana</t>
   </si>
   <si>
-    <t>303210850</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meu carro foi sinistrado dia 06/12/25 e até hoje, dia  04/02/26 o veículo se encontra na oficina . O processo está muito lento e para minha surpresa, na última vistoria a seguradora se  negou a aprovar a substituição de  um par de estribos laterais ,  que foram danificados no sinistro . _x000D_
-_x000D_
-Número do sinistro :303210850_x000D_
-_x000D_
+    <t>303426921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+Data: 06/02/2026_x000D_
+Texto: @303426921_x000D_
+Usuário: Andreza_x000D_
 </t>
   </si>
   <si>
-    <t>95094931</t>
-  </si>
-  <si>
-    <t>239801795</t>
-  </si>
-  <si>
-    <t>04/02/2026 19:36</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Canal de Atendimento ; Atendimento do Analista ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Atendimento do Analista</t>
-  </si>
-  <si>
-    <t>134504137</t>
-  </si>
-  <si>
-    <t>Liguei pra saber porque ficam enviando cobranças dizendo que estou com o seguro atrasado, sendo que o boleto vem em DDA ai eu cadastro pro pagamento que esta no boleto que aparece no aplicativo do meu banco, ai passei os dados pra atendente ,e simplesmente ela si recusou a me dizer, ficou falando que meu nome estava incorreto, ficou repetindo isso ate eu sair do sério e falar palavrões</t>
-  </si>
-  <si>
-    <t>95082503</t>
-  </si>
-  <si>
-    <t>239784519</t>
-  </si>
-  <si>
-    <t>04/02/2026 16:57</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Emissão ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Emissão</t>
-  </si>
-  <si>
-    <t>131018027</t>
-  </si>
-  <si>
-    <t>sou cliente da seguradora allianz a mais de  2 anos o pagamento era feito em debito em conta certo dia nao foi debitado o valor em minha conta e nao fui notificado por isso se passaram 3 meses meu seguro estava cancelado eu nao sabia so tomei conhecimento por quer tentei acessar o app pra tenta fazer uma cotacao para outro veiculo meu nao conseguir acesso e descobrir que nao estava mais asegurado dai tentei recuperar e nao tive sucesso tentei refazer e me cobraram um valor 3x mais me sentir lesado e fiquei com meu veiculo sem seguro.</t>
-  </si>
-  <si>
-    <t>95082315</t>
-  </si>
-  <si>
-    <t>239784189</t>
-  </si>
-  <si>
-    <t>04/02/2026 16:55</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Não ; Sim</t>
-  </si>
-  <si>
-    <t>301576762</t>
-  </si>
-  <si>
-    <t>Em 10/2025 sofri um sinistro com meu veículo Renault Sandero 2019, segurado pela Allianz. Após o acidente, fui encaminhado pela própria seguradora para uma oficina credenciada, onde o veículo permaneceu para reparos, mediante o pagamento da franquia. O carro foi devolvido como estando em condições normais de uso, sem qualquer ressalva sobre danos estruturais ou possíveis impactos futuros._x000D_
-_x000D_
-_x000D_
-No entanto, por não me sentir seguro com o resultado inicial do serviço, fui obrigado a retornar à oficina uma segunda vez, pois o reparo não havia ficado adequado na primeira entrega. Ainda assim, em nenhum momento fui informado de que a estrutura do veículo havia sido comprometida ou que teria ocorrido reparo em peças estruturais._x000D_
-_x000D_
-_x000D_
-Posteriormente, solicitei um laudo cautelar apenas para verificar a qualidade e a regularidade do conserto realizado, e fui surpreendido com a reprovação do veículo por constar reparo nas longarinas dianteiras esquerda e direita, conforme apontado no laudo. Esse tipo de intervenção é considerado grave, pois as longarinas fazem parte da estrutura de absorção de impacto do veículo, comprometendo a segurança e a originalidade da carroceria._x000D_
-_x000D_
-_x000D_
-A seguradora, como responsável técnica pelo processo de regulação do sinistro, tinha o dever de me informar com total transparência sobre a real extensão dos danos e sobre as consequências desse tipo de reparo. Caso eu tivesse sido devidamente esclarecido, poderia ter avaliado outras soluções, inclusive a caracterização de perda total técnica ou comercial._x000D_
-_x000D_
-_x000D_
-Hoje me encontro com um veículo que, embora aparentemente esteja &amp;#39;&amp;#39;consertado&amp;#39;&amp;#39;, possui restrição estrutural grave em laudo cautelar, resultado direto do reparo autorizado pela seguradora e executado por sua oficina credenciada. Diante disso, solicito a reanálise do caso e uma solução justa para o prejuízo sofrido, seja por meio de indenização pela desvalorização do veículo, recompra ou outro acordo compatível. Caso não haja solução administrativa, buscarei meus direitos pelas vias legais.</t>
-  </si>
-  <si>
-    <t>95077525</t>
-  </si>
-  <si>
-    <t>239775909</t>
-  </si>
-  <si>
-    <t>04/02/2026 15:49</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; Repasse Time MindBe ; Não ; Sim ; 2 Terceiro do Sinistro ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>304926476</t>
-  </si>
-  <si>
-    <t>No dia 24/01/2026 o proprietário de um veículo assegurado por esta seguradora a Allianz acabou colidindo em minha moto me levando ao chão e destruindo quase que totalmente o meu veículo,  no mesmo dia o assegurado abriu o sinistro liguei para seguradora e marquei a data com a seguradora para que o perito fizesse a avaliação no meu veículo, levei a moto a uma oficina de confiança assim como fui instruído pela pesuradora, oficina que seria a SAMELL motos, a avaliação no meu veículo foi feita dia 27/01, até este momento estava correndo tudo OK com a seguradora, o perito que fez avaliação do meu veículo assegurou para o responsável da mecânica da SAMELL  que o meu veículo não teria conserto, pois o valor que sairia para reparos não compensaria pois o veículo também é muito antigo, veículo em questão é uma CB 300 2013, o valor do conserto sairia R$ 10.258,13. Mas a seguradora me mandou uma proposta para que eu me virasse e arrumasse a moto por meios próprios o veículo, e quer me dar um valor de R$ 7.000 e eue virar para arrumar, aí deixo eu minha pergunta para vocês Allianz seguros como eu vou consertar um veículo que o orçamento saiu R$ 10.258,13 com R$ 7000 ?</t>
-  </si>
-  <si>
-    <t>95077238</t>
-  </si>
-  <si>
-    <t>239775025</t>
-  </si>
-  <si>
-    <t>04/02/2026 15:43</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; 1 Segurado ; Sac Enc ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Guincho</t>
-  </si>
-  <si>
-    <t>Sac Enc</t>
-  </si>
-  <si>
-    <t>133546053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No dia 30/11/2025 por volta das 22h sai da cidade de Bertioga sentido minha residência em São Paulo pela rodovia Rio x Santos , após 20km de viagem o meu veículo apresentou pane mecânica e fiquei parado no acostamento da rodovia com minha esposa e filho, liguei imediatamente para seguradora Allianz solicitando socorro guincho mais um taxi, deram um prazo de 80min, a princípio logo retornaram informando que o taxi estava a caminho, esperei o tempo informado e ninguém apareceu liguei o novamente informou que o taxista havia cancelado que era para aguardar que estavam verificando outro prestador e o guincho não tinham previsão de chegada, pois bem ninguém apareceu para nos socorrer por parte da seguradora, tive que chamar o guincho da concessionária da rodovia CNL que nos foi socorrer por volta das 01:30 da madrugada, ou seja fiquei das 22:30hs até 01:30 parado no acostamento em uma rodovia totalmente escura só mato dos lados e correndo todos os tipos de riscos, quando o guincho da CNL chegou me rebocaram de volta para a cidade de origem Bertioga e não me deixou na residência que minha mãe possui no local, deixaram o meu carro na rua eu tive que ir a pé até a residência da minha mãe pegar o carro dela para ir até o meu carro quebrado pegar as bagagens, meu carro ficou na rua para que só no outro dia eu ir atrás de mecânico para fazer o reparo._x000D_
-_x000D_
-_x000D_
-Resumindo Não tive nenhum socorro por parte da seguradora Allianz, liguei alguns dias depois para registrar minha reclamação através do protocolo 25/0015525 e a resposta que tive foi que iriam dar uma advertência para o taxista que recusou o corrida e que iriam reforçar os os prestadores da região. E eu como consumidor o constrangimento o risco de assalto e danos emocionais que essa empresa me causou para mim e minha família ?? _x000D_
-_x000D_
-Abri protocolo no consumidor.gov e informaram que realmente não haviam prestadores para atendimento na região onde eu estava e simplesmente ficou por isso mesmo sem nenhum ressarcimento nada se não fosse o serviço de guincho da  concessionaria da rodovia eu estaria lá até hoje esperando o socorro da Allianz , agora eu pergunto pegar um seguro que te deixa na mão quando precisa?, estão nem ai para o consumidor foi a primeira vez para nunca mais, fujam dessa seguradora. _x000D_
-_x000D_
-_x000D_
-Protocolo  50763388  Alianz  dia 30/11 /25_x000D_
-_x000D_
-PROTOCOLO: 2025.12/00012870660 consumidor gov _x000D_
+    <t xml:space="preserve">Acionei seguro em 15/12/2025 por acidente que ocorreu no dia 12/12/2025. Sinistro aprovado em 19/12/2025, porém ATÉ HOJE 05/02/2026 (48 dias após aprovação), Allianz NÃO forneceu peças para reparo. Veículo funciona mas está AVARIADO E COMPROMETIDO há 1,5 mês  circulo com carro danificado, inseguro e desvalorizado. 48 DIAS DE ATRASO INACEITÁVEL!_x000D_
+_x000D_
+_x000D_
+Pagamos CARO em seguro que nos deixa na mão! Allianz ignora prazos legais e direitos do consumidor!_x000D_
+_x000D_
+_x000D_
+Gostaria de uma explicação formal do descaso._x000D_
 _x000D_
 </t>
   </si>
   <si>
-    <t>95072852</t>
-  </si>
-  <si>
-    <t>239762307</t>
-  </si>
-  <si>
-    <t>04/02/2026 14:13</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Sim ; Não ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>304983039</t>
-  </si>
-  <si>
-    <t>Tenho um veiculo assegurado com a empresa acima , tive um problema que meu parabrisa quebrou e a empresa esta negando fazer a manutençao na concessionária, e uma porsche ano 2024 ( ainda na garantia , esta especificado no manual , que qualquer peca colocada fora da concessionária eu estaria abrindo mao da garantia) sendo que eu extendi a garantia ate 2027 do veiculo , nao posso fazer a troca na auto glass como eles querem , pelo codigo de defesa do consumidor , se o veiculo ainda estiver na garantia , eles sao obrigados a fazer o reparo na concessionária, ja estou os notificando judicialmente , apenas estou relatando , pros futuros donos de carros premium nunca fazer seguro com eles ! ( e ainda estao me negando , enviar a negativa por email , pois eles sabem que estou no meu direito ) _x000D_
-_x000D_
-Anexei a foto onde no manual e mencionado a questao da garantia !</t>
-  </si>
-  <si>
-    <t>95065345</t>
-  </si>
-  <si>
-    <t>239747231</t>
-  </si>
-  <si>
-    <t>04/02/2026 12:18</t>
-  </si>
-  <si>
-    <t>Allianz ; CPF/CNPJ ; Residência ; Apólice ; Condições Gerais ; 11 Não Cliente ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+    <t>95129405</t>
+  </si>
+  <si>
+    <t>239901987</t>
+  </si>
+  <si>
+    <t>05/02/2026 17:46</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 2 Terceiro do Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>300703921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+Data: 06/02/2026_x000D_
+Texto: @300703921_x000D_
+Usuário: Carla_x000D_
+</t>
+  </si>
+  <si>
+    <t>Boa  tarde!_x000D_
+_x000D_
+_x000D_
+Estou com problema com o Seguro Allianz, pra receber o seguro cessante do sinistro que ouve , me fizeram uma proposta de R$70,00 a diária, sendo que minha diária é R$160,00 dia,mandei todas as documentações solicitadas sendo que não estão aceitando o Extrado mensal dos últimos três meses antes do acidente, pois o aplicativo não fornece o Extrado via aplicativo (download) somente prints  ( carteira digital)da tela do aplicativo, me fizeram uma proposta de R$70,00 pra poder encerrar, sendo que se eu não aceitasse a proposta teria que enviar todas as documentações e seria ainda descontato 40% de manutenção e gasolina no tempo que a moto ficou parada, sem lógica esse desconto de 40% moto tava parada. Entrei em contato fazendo uma contra proposta e enviaram um e-mail não aceitando a contraposta. Tô vendo que terei que entrar com uma ação judicial contra eles.</t>
+  </si>
+  <si>
+    <t>95124715</t>
+  </si>
+  <si>
+    <t>239888683</t>
+  </si>
+  <si>
+    <t>05/02/2026 15:53</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 2 Terceiro do Sinistro ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>302356572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+Data: 06/02/2026_x000D_
+Texto: @302356572_x000D_
+Usuário: Andreza_x000D_
+</t>
+  </si>
+  <si>
+    <t>Um caminhão em movimento com a porta do baú aberta, bateu no meu veículo parado. O motorista do caminhão disse que tinha seguradora e que podíamos ficar tranquilos. Porém, depois de acionado a seguradora, a mesma anda pisando na bola! Onde eu moro não há oficina, levei na cidade mais próxima a mim para fazer o credenciamento da mesma, após isso, agendaram para fazer vistoria no veículo, 2 dias com o carro parado lá a disposição da seguradora e o perito simplesmente não apareceu na oficina credenciada. Alegou para a companhia que foi até a oficina e que o carro não estava lá, e passou nomes de funcionários que conversou no local, sem ter esses funcionários na oficina. Entrei em contato com o corretor, agendaram novamente 2 dias para vistoria do veículo, e no 4 dia pela manhã encaminharam um e-mail para oficina dizendo novamente que foram até o local (no 3 dia) e o carro não está lá, dando o lote como encerrado, e mencionando mais uma vez o nome do funcionário que não existe na oficina. Por este e-mail enviado podemos concluir que o mesmo estava indo em endereço errado ao da oficina, ou nem estava indo Entrei novamente em contato com o corretor, encaminhei a ele o endereço pelo qual o vistoriador alegava estar indo e pedi para atualizar o endereço da oficina, o mesmo me informou que o endereço estava certo e atualizado no sistema e não estava entendendo o motivo pelo qual o vistoriador estava indo no lugar errado. Agendaram novamente mais 2 dias pra vistoria, e novamente ninguém apareceu! Uma falta de respeito total, perdi 6 dias de trabalho pra poder deixar o carro a disposição da seguradora, tenho crianças pequenas que dependem do carro para ir e vir da escola, estamos com períodos de fortes chuvas no estado de SP e, simplesmente me fizerem de palhaço. Ninguém vai me ressarcir desses 6 dias com o carro parado, nem pagar meu combustível de ter que ficar indo e vindo da oficina, que como já mencionei fica numa cidade vizinha, a 1hs de distância da onde eu moro._x000D_
+_x000D_
+Allianz seguros caiu nos meus conceitos!!!</t>
+  </si>
+  <si>
+    <t>95124054</t>
+  </si>
+  <si>
+    <t>239886707</t>
+  </si>
+  <si>
+    <t>05/02/2026 15:37</t>
+  </si>
+  <si>
+    <t>6 Corretor ; Allianz ; Sinistro ; Automóvel ; Apólice ; Pagamento ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Pagamento</t>
+  </si>
+  <si>
+    <t>6 Corretor</t>
+  </si>
+  <si>
+    <t>136493976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+Data: 06/02/2026_x000D_
+Texto: @136493976_x000D_
+Usuário: Andreza_x000D_
+_x000D_
+Data: 06/02/2026_x000D_
+Texto: Em 06/02 - Andreza, orientação MindBe: _x000D_
+Abrir Nota Go 535 e anexar a reclamação em PDF do hugme;_x000D_
+Usuário: Andreza_x000D_
+</t>
+  </si>
+  <si>
+    <t>Sou corretora e estou enfrentando um problema grave com a Allianz. Foram debitadas 6 vezes a mesma parcela do seguro no cartão do meu cliente, de forma totalmente indevida._x000D_
+_x000D_
+_x000D_
+Já tentamos resolver pelo chat da Allianz, que informou prazo de até 15 dias para retirada das cobranças, porém o fechamento do cartão é na próxima semana, o que obrigará o cliente a pagar valores que não são devidos._x000D_
+_x000D_
+_x000D_
+Também procurei o banco, que informou que somente a Allianz pode remover essas parcelas._x000D_
+_x000D_
+_x000D_
+Solicito urgência na regularização, estorno imediato das cobranças indevidas e confirmação formal da correção, pois o erro está causando prejuízo financeiro e transtornos ao cliente.</t>
+  </si>
+  <si>
+    <t>95123084</t>
+  </si>
+  <si>
+    <t>239883989</t>
+  </si>
+  <si>
+    <t>05/02/2026 15:16</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Não ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Sim ; 1 Segurado ; Central de Atendimento ; Assistência Não Danos</t>
+  </si>
+  <si>
+    <t>Central de Atendimento</t>
+  </si>
+  <si>
+    <t>131917994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+Data: 05/02/2026_x000D_
+Texto: @131917994_x000D_
+Usuário: Carla_x000D_
+_x000D_
+Data: 05/02/2026_x000D_
+Texto: Aberta Nota go ao cliente_x000D_
+Usuário: Carla_x000D_
+</t>
+  </si>
+  <si>
+    <t>Precisei de atendimento e disseram que era mais rápido pelo whatsapp, passei todas as informações e disseram que iriam entrar em contato com um atendente, demoraram 20 minutos para me mandar a mensagem, eu ja não estava com o celular em mãos mas demorei apenas 5 minutos para ver a mensagem e já haviam encerrado apenas 3 minutos após enviarem a mensagem, o atendimento, um atendimento que tinha tudo para ser melhor para ambos feito via whatsapp mas após todo o tempo perdido preenchendo informações foi todo perdido, me obrigando a ligar novamente e fazer tudo pelo telefone ou preencher tudo de novo e ficar ali com a conversa deles aberta 20 minutos esperando a mensagem chegar? Ai fica a questão estão disponibilizando esse serviço pelo whatsapp apenas para falar que tem? Porque não tem a intenção de resolver né senão me ligariam ou esperariam pelo menos um pouco para encerrar onde ja se viu..</t>
+  </si>
+  <si>
+    <t>95116986</t>
+  </si>
+  <si>
+    <t>239866131</t>
+  </si>
+  <si>
+    <t>05/02/2026 12:55</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; 1 Segurado ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; RA ; Sim</t>
+  </si>
+  <si>
+    <t>RA</t>
+  </si>
+  <si>
+    <t>132225039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+Data: 06/02/2026_x000D_
+Texto: @132225039_x000D_
+Usuário: Carla_x000D_
+_x000D_
+Data: 06/02/2026_x000D_
+Texto: Cliente já abriu uma RA 237564263 em 13/01, já avaliado em nota 09 e disse que já havia resolvido._x000D_
+Não moderar por duplicidade para não perder a Nota!!!!!!_x000D_
+_x000D_
+_x000D_
+@132225039_x000D_
+Prot 26/0000661_x000D_
+Ass 50998481_x000D_
+PROCESSO SUSEP: 15414.100898/2004-62_x000D_
+Usuário: Carla_x000D_
+</t>
+  </si>
+  <si>
+    <t>Dese o 17/12/25 pra instalar um ventilador de teto onde ja existia era só trocar.fiz reclamação aqui essa semana depois de muito tempo me ligaram dizendo que iria resolver.falei que ia chamar um eletricista de confiança pra resolver. Eles se propuseram o reembolso. Hoje entrei em contato e o reembolso proposto foi de 80,00 que nao paga nem o transtorno e o prejuízo que o técnico deles me deu.ligou fio invertido queimou as teclas da tomada do ventilador.sem contar que ele abriu o outro ventilador da sala para ver como ta ligado e danificou a tecla do outro ventilador também</t>
+  </si>
+  <si>
+    <t>95110689</t>
+  </si>
+  <si>
+    <t>239848903</t>
+  </si>
+  <si>
+    <t>05/02/2026 10:49</t>
+  </si>
+  <si>
+    <t>Allianz ; CPF/CNPJ ; Automóvel ; Assistência Não Danos ; Central de Atendimento ; 11 Não Cliente ; Não ; Sim ; 1 Ctt Sem Sucesso ; Com Resposta - Dentro SLA - Analista</t>
   </si>
   <si>
     <t>CPF/CNPJ</t>
   </si>
   <si>
-    <t>Condições Gerais</t>
-  </si>
-  <si>
     <t>11 Não Cliente</t>
   </si>
   <si>
-    <t>27884281</t>
-  </si>
-  <si>
-    <t>Estou contratando um seguro residencial para minha casa e não estamos conseguindo clareza e certeza de algumas coberturas_x000D_
-_x000D_
-_x000D_
-_x000D_
-No fundo da minha casa tem um muro de arrimo de aproximadamente 3 metros de altura , no qual acima tem uma construção de meu vizinho. Nesse período chuvoso ficou preocupado e gostaria de fazer um seguro para me resguardar. Mas antes preciso da certeza que eu contratando a cobertura extra de desmoronamento eu terei cobertura e indenizado . Duas informações importantes_x000D_
-_x000D_
-_x000D_
-_x000D_
-1 - Se cobre esse muro de arrimo em um desmoronamento sendo que sou a parte de baixo_x000D_
-_x000D_
-_x000D_
-_x000D_
-2- em minha cidade 99% dos imóveis não tem habite-se, alvará de obra nem nada, tudo na raça. Se isso implica na indenização. Que no meu caso não tem tambem_x000D_
-_x000D_
-_x000D_
-_x000D_
-Tenho escritura e documentação da casa original.</t>
-  </si>
-  <si>
-    <t>95057802</t>
-  </si>
-  <si>
-    <t>239733145</t>
-  </si>
-  <si>
-    <t>04/02/2026 10:43</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Assistência Danos ; Vidros - AutoGlass ; 1 Segurado ; SAC Aberto ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Assistência Danos</t>
+    <t>Com Resposta - Dentro SLA - Analista</t>
+  </si>
+  <si>
+    <t>45500119800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+Data: 06/02/2026_x000D_
+Texto: @45500119800_x000D_
+Usuário: Andreza_x000D_
+_x000D_
+Data: 06/02/2026_x000D_
+Texto: Avisar Eli - Oportunidade_x000D_
+Data de agendamento: 09/02/2026_x000D_
+Usuário: Andreza_x000D_
+</t>
+  </si>
+  <si>
+    <t>Bom dia, tudo bem?_x000D_
+_x000D_
+_x000D_
+Me chamo André, e venho por meio desta mensagem pedir informações para conseguir ser prestador de serviço no seguimento assistência 24HRS como Táxi. Sou MEI e estou situado na cidade de Registro-SP, atuo na área de transporte particular, com minha agência MS Transfer, faço viagens de médias e longas distância, e tenho interesse em atuar como prestador de serviço para vocês nessa área. Estou entrando em contato por aqui pois não achei nenhum meio de comunicação de vocês para esse fim._x000D_
+_x000D_
+_x000D_
+_x000D_
+Cnpj: 61.424.367/0001-27_x000D_
+_x000D_
+_x000D_
+Contato: mstransferexec@gmail.com_x000D_
+_x000D_
+_x000D_
+_x000D_
+Fico no aguardo de informações para poder enviar a documentação e podermos ser parceiros. Desde já agradeço</t>
+  </si>
+  <si>
+    <t>95106330</t>
+  </si>
+  <si>
+    <t>239836339</t>
+  </si>
+  <si>
+    <t>05/02/2026 09:14</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>305156511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+Data: 05/02/2026_x000D_
+Texto: @305156511_x000D_
+Usuário: Carla_x000D_
+</t>
+  </si>
+  <si>
+    <t>Bom dia!_x000D_
+_x000D_
+No dia 09/01/26 por volta das 9:00h, solicitei socorro devido a pane elétrica em meu veículo, estava no litoral de Santa Catarina, aguardei o socorro por uma hora, contudo o socorro não foi enviado e mandaram mensagem informando que tinha reagendado o socorro para o período da noite. _x000D_
+_x000D_
+Entrei em contato com a seguradora e disseram que não tinham conseguido nenhuma empresa parceira na região, para me socorrer. Informei que estava longe de casa, com minha esposa passando mal e com duas crianças. Então a atendente informou que eu poderia fazer o serviço de forma particular, e que depois era só eu solicitar o reembolso, e enviaram o formulário de reembolso em meu e-mail. _x000D_
+_x000D_
+Diante a situação, contratei o serviço de uma auto-eletrica que me socorreu e resolveu meu problema, e cobrou o valor de 180,00._x000D_
+_x000D_
+No dia 15/01 enviei o formulário com os documentos solicitados para o reembolso. Aí iniciou outra dor de cabeça maior ainda, cheio de descaso e enrolação. Quando enviei o formulário e os documentos, recebi e-mail automático informando que em dois dias úteis seria analisado e reembolsado o valor._x000D_
+_x000D_
+Desde então tenho ligado e enviado e-mail a cada dois dias, contudo não tenho retorno da seguradora._x000D_
+_x000D_
+No dia 02/02 liguei e fui informado que no dia 03 seria feito o reembolso, porém até agora nada (dia 05 às 8:30min). Acabei de ligar novamente, e fui informado que foi feito o reembolso na minha conta no dia 03 e foi enviado o comprovante no meu e-mail.  Porém NÃO recebi o valor do reembolso e NÃO enviaram e-mail com o recibo do pagamento._x000D_
+_x000D_
+Estou fazendo essa reclamação aqui, para alertar outras pessoas sobre o péssimo atendimento e descaso da seguradora com seus clientes. _x000D_
+_x000D_
+Não recebi o socorro na hora que mais precisei e para receber o reembolso de um valor irrisório, fazem de tudo para não pagar. _x000D_
+_x000D_
+Já contratei outras seguradoras anteriormente e nunca tive problemas, mas com a Allianz estou passando raiva e perdendo meu tempo. _x000D_
+_x000D_
+Tenho dois veículos assegurados com a Allianz, mas definitivamente Allianz NUNCA MAIS. _x000D_
+_x000D_
+Fica meu relato e desabafo para aqueles que não conhecem a empresa,"FUJAM" pois, quando mais precisei não recebi o socorro e agora não consigo receber o valor do reembolso de um serviço que eles deveriam ter prestado, conforme previsto quando contatrei essa seguradora.</t>
+  </si>
+  <si>
+    <t>95106110</t>
+  </si>
+  <si>
+    <t>239835613</t>
+  </si>
+  <si>
+    <t>05/02/2026 09:08</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Residência ; 1 Segurado ; Não ; Sem Resposta - Dentro SLA ; Sim ; Assistência Não Danos ; Assistência Residencial ; Repasse Time MindBe</t>
+  </si>
+  <si>
+    <t>136363786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+Data: 06/02/2026_x000D_
+Texto: @136363786_x000D_
+Usuário: Carla_x000D_
+_x000D_
+Data: 06/02/2026_x000D_
+Texto: E-mail enviado_x000D_
+Usuário: Juliana_x000D_
+</t>
+  </si>
+  <si>
+    <t>O seguro de vocês querem pagar uma ninharia sendo que tenho provas de tudo oque aconteceu minhas coisas que queimaram por pane elétrica oque meu seguro cobre mesmo com o laudo vocês não estão querendo pagar isso é um absurdo, tenho o protocolo da Eletropaulo sobre as quedas de luz e os curtos nos postes e mesmo assim vocês ainda se acham no direito de querer me dar menos de 3 mil reais pra que eu pago vocês, o dinheiro que eu gasto todo mês com vocês é mais fácil eu guardar pra uma eventualidade já que o seguro de vocês não nos da suporte em nada e se acham no direito de nos pagar oque vocês acham não estamos querendo nada a mais só oque é meu por direito, código Eletropaulo 925242520</t>
+  </si>
+  <si>
+    <t>95105728</t>
+  </si>
+  <si>
+    <t>239834457</t>
+  </si>
+  <si>
+    <t>05/02/2026 08:56</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Vidros - AutoGlass ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
     <t>Vidros - AutoGlass</t>
   </si>
   <si>
-    <t>SAC Aberto</t>
-  </si>
-  <si>
-    <t>135456675</t>
-  </si>
-  <si>
-    <t>Contratei seguro automotivo da Allianz, por meio do Santander AutoCompara, cuja apólice inclui expressamente a cobertura Assistência a Vidros, Lanternas, Faróis e Retrovisores  Plano 1, constando de forma clara no documento contratual entregue ao consumidor._x000D_
-_x000D_
-_x000D_
-Ao tentar acionar a cobertura para troca de lanterna traseira, fui surpreendida com a negativa do atendimento, sob a alegação genérica de que meu seguro não cobre faróis, lanternas e retrovisores._x000D_
-_x000D_
-_x000D_
-Ressalto que em nenhum momento da contratação, tampouco na apólice, há informação clara, destacada ou inequívoca acerca de exclusão, limitação ou impossibilidade de uso dessa cobertura. A simples negativa baseada em critérios internos da seguradora não pode se sobrepor ao contrato firmado._x000D_
-_x000D_
-_x000D_
-Tal conduta viola frontalmente o Código de Defesa do Consumidor, especialmente:_x000D_
-_x000D_
-_x000D_
- Art. 6, III  direito à informação clara e adequada;_x000D_
-_x000D_
- Art. 30  a oferta vincula o fornecedor;_x000D_
-_x000D_
- Art. 46  cláusulas restritivas só têm validade se forem redigidas com destaque;_x000D_
-_x000D_
- Art. 47  interpretação contratual mais favorável ao consumidor;_x000D_
-_x000D_
- Art. 51, IV e 1  nulidade de cláusulas abusivas ou incompatíveis com a boa-fé._x000D_
-_x000D_
-_x000D_
-O consumidor não pode ser surpreendido com negativa de cobertura expressamente contratada, sobretudo quando não houve qualquer transparência prévia sobre exclusões._x000D_
-_x000D_
-_x000D_
-Diante disso, requeiro a reanálise imediata da negativa, com autorização da cobertura prevista em apólice._x000D_
-_x000D_
-_x000D_
-Informo, ainda, que caso a cobertura continue sendo indevidamente negada, adotarei as medidas judiciais cabíveis, inclusive com pedido de indenização por danos materiais e morais, além da comunicação aos órgãos de fiscalização competentes._x000D_
-_x000D_
-_x000D_
-Aguardo solução administrativa dentro do prazo legal.</t>
-  </si>
-  <si>
-    <t>95056591</t>
-  </si>
-  <si>
-    <t>239729573</t>
-  </si>
-  <si>
-    <t>04/02/2026 10:19</t>
-  </si>
-  <si>
-    <t>Allianz ; Automóvel ; Sinistro ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>305342331</t>
-  </si>
-  <si>
-    <t>Tinha um sinistro aberto em janeiro de 2025 o primeiro prestador não trabalhava mais com a companhia, o segundo foi autorizado e nunca podia fazer, ai qd eu reclamo a Allianz diz que encerrou o sinistro, porém não fizeram o reparo, o corretor tentou porém foi negado, agora mudei de seguradora e não querem mesmo arrumar, mas o sinistro foi aberto exijo reparação em um fornecedor procedente e em vinhedo, louveira ou americana. Não consigo acompanhar pelo site. O prestador não tinha disponibilidade e eles encerram sem fazer o reparo!! Solicito que façam o reparo conforme vigente no contrato e a abertura foi realizada durante a vigência. Note que ate prestadores param de trabalhar com eles e eles indicavam eles. Protocolo negado 19744372</t>
-  </si>
-  <si>
-    <t>95056406</t>
-  </si>
-  <si>
-    <t>239729053</t>
-  </si>
-  <si>
-    <t>04/02/2026 10:15</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; Reclamante em nome do Segurado ; RA ; Sim ; Sem Resposta - Dentro SLA ; Sem Ctt Duplicidade</t>
-  </si>
-  <si>
-    <t>Reclamante em nome do Segurado</t>
-  </si>
-  <si>
-    <t>RA</t>
-  </si>
-  <si>
-    <t>Sem Ctt Duplicidade</t>
-  </si>
-  <si>
-    <t>134428507</t>
-  </si>
-  <si>
-    <t>Na data de 17/01/2026, entrei em contato via WhatsApp com a seguradora e solicitei a opção de visita de um mecânico, às 14h02._x000D_
-_x000D_
-_x000D_
-Após uma hora de espera, recebi uma ligação de um atendente da Allianz informando que não seria possível o guincho chegar ao local, e que o resgate deveria ser feito pela Ecovias, para nos levar do km 60 ao km 62. Essa informação foi passada apenas às 15h02, o que considero inaceitável, pois ficamos uma hora aguardando sem qualquer orientação correta._x000D_
-_x000D_
-_x000D_
-Ressalto que estávamos em três mulheres, paradas em uma rodovia perigosa, expostas a riscos._x000D_
-_x000D_
-_x000D_
-O atendente Murilo nos passou essa informação e forneceu um novo número da assistência 24h. Ligamos novamente solicitando um mecânico_x000D_
-_x000D_
-_x000D_
-Posteriormente, recebemos um SMS e o atendente Vitor entrou em contato informando que o mecânico chegaria em aproximadamente 40 minutos. No entanto, essa ligação ocorreu às 15h54, ou seja, mais de 30 minutos após a confirmação, apenas para informar um novo prazo, o que demonstra total falta de agilidade e organização._x000D_
-_x000D_
-_x000D_
-Às 16h20, chegou um carro de guincho, conduzido pelo motorista Leandro, que informou que não era mecânico, vindo apenas com equipamento para recarga de bateria. Ressalto que solicitamos um mecânico, e ele sequer avaliou o veículo._x000D_
-_x000D_
-_x000D_
-Diante da situação e do horário avançado (quase 17h), questionamos a possibilidade de sermos guinchadas. Ele informou que não poderia realizar o serviço, pois precisaria de autorização da seguradora, e simplesmente foi embora, sem prestar qualquer atendimento._x000D_
-_x000D_
-_x000D_
-Entrei novamente em contato com a Central 24h, expliquei toda a situação e solicitei um guincho. Após quase 30 minutos aguardando, recebi uma ligação da atendente Fabiana, informando que estava iniciando a solicitação do guincho. Como assim iniciando, se eu já havia feito todo o processo anteriormente?_x000D_
-_x000D_
-_x000D_
-Reforço que estávamos sozinhas, em situação de risco,pois tinha homens nos rodeando .Felizmente, a Ecovias passou pelo local, percebeu a situação e nos conduziu até o estacionamento de um posto com conveniência. Tenho registros de tudo._x000D_
-_x000D_
-_x000D_
-Durante a ligação com a Fabiana, que durou cerca de 45 minutos (quase Até as 18h), ela informou que o guincho demoraria mais de 40 minutos para chegar e sugeriu que fizéssemos o serviço particular, com reembolso integral pela Allianz. Para isso, precisou entrar em contato com um supervisor para autorização, o que consumiu ainda mais tempo._x000D_
-_x000D_
-_x000D_
-Iniciei a solicitação às 14h02 e, após mais de 4 horas, nenhuma solução foi efetivamente prestada. As informações eram desencontradas, os serviços solicitados nunca eram atendidos, e o tempo todo ficávamos em situação de insegurança._x000D_
-_x000D_
-_x000D_
-Diante disso, e por ser inviável aguardar mais 50 a 60 minutos de incerteza, realizamos o guincho de forma particular, com indicação de pessoas solidárias que estavam no local._x000D_
-_x000D_
-_x000D_
-Ressalto ainda que, em razão da demora excessiva, da falta de informações claras e da não prestação do serviço solicitado dentro de um prazo razoável, fui impedida de comparecer a um compromisso previamente agendado em São Paulo, já integralmente pago, no valor de R$ 300,00._x000D_
-_x000D_
-_x000D_
-Embora compreenda que a seguradora não tenha controle direto sobre meus compromissos pessoais, é importante destacar que o impedimento ocorreu exclusivamente em decorrência da falha na prestação do serviço contratado, uma vez que entrei em contato com a assistência às 14h02 e, se houvesse uma resolução adequada até aproximadamente 16h, eu ainda conseguiria chegar ao evento._x000D_
-_x000D_
-_x000D_
-O prejuízo financeiro, portanto, não decorreu de um imprevisto isolado, mas sim da série de atrasos, informações divergentes e tentativas frustradas de atendimento, que se estenderam por mais de quatro horas._x000D_
-_x000D_
-_x000D_
-Dessa forma, solicito que o valor de R$ 300,00 referente ao compromisso perdido seja analisado para reembolso, considerando que o dano financeiro foi consequência direta da ineficiência e do descumprimento do serviço de assistência, caracterizando prejuízo material._x000D_
-_x000D_
-_x000D_
-Espero não ficar no prejuízo tanto do valor do guincho quanto do compromisso perdido, e solicito o reembolso integral._x000D_
-_x000D_
-_x000D_
-Possuo todos os registros:_x000D_
-_x000D_
-  Primeiro contato via WhatsApp às 14h02_x000D_
-_x000D_
-  Fotos do local e da situação de risco_x000D_
-_x000D_
-  Ligações e gravações da central_x000D_
-_x000D_
-  Nomes dos atendentes e horários_x000D_
-_x000D_
-  Foto do motorista Leandro, que compareceu e não prestou o serviço_x000D_
-_x000D_
-_x000D_
-O ocorrido foi um descaso total e uma experiência extremamente negativa._x000D_
-_x000D_
-_x000D_
-E Em razão da demora excessiva, permanecemos cerca de 4 horas aguardando atendimento, o que gerou gastos adicionais com bebidas e alimentos. Durante esse período, ficamos expostos em uma área de mato, resultando em diversas picadas de mosquitos, causando grande desconforto. Ressaltamos ainda que uma das passageiras, minha esposa, é hipertensa, o que tornou a situação ainda mais delicada e preocupante.</t>
-  </si>
-  <si>
-    <t>95055702</t>
-  </si>
-  <si>
-    <t>239727095</t>
-  </si>
-  <si>
-    <t>04/02/2026 10:02</t>
-  </si>
-  <si>
-    <t>135117501</t>
-  </si>
-  <si>
-    <t>Sou segurada da allianz seguros, seguro residencial. Fiz uma solicitação de assistência da minha máquina de lavar e fui informada que já havia atingido o limite de utilização da apólice em novembro de 2025, por conta da solicitação de assistência com minha geladeira. Acontece que a assistência da geladeira não veio um técnico na minha casa. A seguradora me pagou na modalidade de reembolso, porque na ocasião não tinha profissional disponível. No dia 09/01 recebi uma ligação do número 01127633800 dizendo ser uma pessoa da Allianz. Ela me explicou que a modalidade de reembolso não seria computada como utilização e que eu poderia novamente solicitar a assistência para a minha máquina de lavar e que seria atendida. _x000D_
-_x000D_
-É um absurdo esse desencontro de informações. Como consumidora preciso de transparência e eficiência nas solicitações.</t>
+    <t>131609845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+Data: 06/02/2026_x000D_
+Texto: @131609845_x000D_
+Usuário: Andreza_x000D_
+_x000D_
+Data: 06/02/2026_x000D_
+Texto: Em 06/02 - Andreza, orientação MindBe: _x000D_
+- Enviar e-mail para Vidros - Importante: colocar o chassi e placa do do veículo no e-mail;_x000D_
+Usuário: Andreza_x000D_
+</t>
+  </si>
+  <si>
+    <t>A seguradora não cumpre o que estabelece a apólice,  péssimo atendimento. NÃO RECOMENDO,  CUIDADO!!!!!!</t>
+  </si>
+  <si>
+    <t>95103080</t>
+  </si>
+  <si>
+    <t>239826417</t>
+  </si>
+  <si>
+    <t>05/02/2026 06:09</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Pagamento ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>134354449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+Data: 05/02/2026_x000D_
+Texto: @134354449_x000D_
+Usuário: Juliana_x000D_
+</t>
+  </si>
+  <si>
+    <t>Eu fiz um pagamento do meu Seguro automóvel no cartão de crédito porque eu vi que a parcela não tinha sido debitada. E aí ocorreu o pagamento no cartão de crédito, depois eu Verifiquei que a parcela tinha sido debitada na minha conta bancária, então foi paga em duplicidade. Meu corretor entrou em contato e abriu chamado para o estorno, porém a Allianz informa que não  houve a duplicidade, porém eu tenho os dois comprovantes. Solicito a devolução do pagamento em duplicidade.</t>
   </si>
 </sst>
 </file>
@@ -1118,7 +1316,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AA8803-373C-4E0C-ABA8-1F171C96DA02}">
-  <dimension ref="A1:AA16"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="3" bestFit="1" customWidth="1" collapsed="1"/>
@@ -1236,92 +1434,92 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="E2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="M2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="W2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="X2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="Y2" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="Z2"/>
       <c r="AA2"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>49</v>
@@ -1333,83 +1531,83 @@
         <v>51</v>
       </c>
       <c r="L3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="V3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="W3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="Z3"/>
       <c r="AA3"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="I4" s="3" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>61</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>62</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="V4" s="3" t="s">
         <v>63</v>
@@ -1420,764 +1618,950 @@
       <c r="X4" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="Y4" s="3" t="s">
-        <v>26</v>
+      <c r="Y4" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="Z4"/>
       <c r="AA4"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="L5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="V5" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y5" s="3" t="s">
-        <v>26</v>
+        <v>73</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="Z5"/>
       <c r="AA5"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="J6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="M6" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="P6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="V6" s="3" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y6" s="3" t="s">
-        <v>26</v>
+        <v>81</v>
+      </c>
+      <c r="Y6" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="Z6"/>
       <c r="AA6"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="P7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="V7" s="3" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="Z7"/>
       <c r="AA7"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="L8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N8" s="3" t="s">
+      <c r="P8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="V8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="Y8" s="3" t="s">
-        <v>26</v>
+        <v>98</v>
       </c>
       <c r="Z8"/>
       <c r="AA8"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="I9" s="3" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="V9" s="3" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y9" s="3" t="s">
-        <v>26</v>
+        <v>106</v>
+      </c>
+      <c r="Y9" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="Z9"/>
       <c r="AA9"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="N10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="P10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="V10" s="3" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y10" s="3" t="s">
-        <v>26</v>
+        <v>113</v>
+      </c>
+      <c r="Y10" s="4" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="I11" s="3" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="L11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N11" s="3" t="s">
+      <c r="P11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="V11" s="3" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="Y11" s="3" t="s">
-        <v>26</v>
+        <v>120</v>
+      </c>
+      <c r="Y11" s="4" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="I12" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="V12" s="3" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y12" s="3" t="s">
-        <v>26</v>
+        <v>129</v>
+      </c>
+      <c r="Y12" s="4" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>128</v>
+        <v>30</v>
       </c>
       <c r="N13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="P13" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="V13" s="3" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="X13" s="4" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="Y13" s="3" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>31</v>
+        <v>143</v>
       </c>
       <c r="N14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="P14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="V14" s="3" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="Y14" s="3" t="s">
-        <v>26</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>50</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>41</v>
+        <v>153</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y15" s="3" t="s">
-        <v>26</v>
+        <v>155</v>
+      </c>
+      <c r="Y15" s="4" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="W16" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="X16" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y16" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="3" t="s">
+      <c r="I17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J16" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L16" s="3" t="s">
+      <c r="K18" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N16" s="3" t="s">
+      <c r="P18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V16" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="W16" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="X16" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y16" s="3" t="s">
-        <v>26</v>
+      <c r="V18" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="W18" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="X18" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="W19" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="X19" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y19" s="3" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/Treinamento/GestaoReclamacao.xlsx
+++ b/Treinamento/GestaoReclamacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0760B76D-56A1-47EA-BD47-E4A8219E9399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E77EBAA-312F-4E74-8EC8-98C0F863532C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B1A77FD5-2AD3-4458-ACB3-7F19D1A3340A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="158">
   <si>
     <t>Id HugMe</t>
   </si>
@@ -1194,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AA8803-373C-4E0C-ABA8-1F171C96DA02}">
-  <dimension ref="A1:AA36"/>
+  <dimension ref="A1:AA17"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="3" bestFit="1" customWidth="1" collapsed="1"/>
@@ -1311,8 +1311,63 @@
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
+      <c r="A2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="Y2" s="3" t="s">
         <v>26</v>
       </c>
@@ -1320,7 +1375,63 @@
       <c r="AA2"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="X3" s="4"/>
+      <c r="A3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="Y3" s="3" t="s">
         <v>26</v>
       </c>
@@ -1328,8 +1439,63 @@
       <c r="AA3"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
+      <c r="A4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="Y4" s="3" t="s">
         <v>26</v>
       </c>
@@ -1337,8 +1503,63 @@
       <c r="AA4"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
+      <c r="A5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="Y5" s="3" t="s">
         <v>26</v>
       </c>
@@ -1346,8 +1567,63 @@
       <c r="AA5"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
+      <c r="A6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="X6" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="Y6" s="3" t="s">
         <v>26</v>
       </c>
@@ -1355,8 +1631,63 @@
       <c r="AA6"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
+      <c r="A7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="X7" s="4" t="s">
+        <v>88</v>
+      </c>
       <c r="Y7" s="3" t="s">
         <v>26</v>
       </c>
@@ -1364,8 +1695,63 @@
       <c r="AA7"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
+      <c r="A8" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="X8" s="4" t="s">
+        <v>94</v>
+      </c>
       <c r="Y8" s="3" t="s">
         <v>26</v>
       </c>
@@ -1373,8 +1759,63 @@
       <c r="AA8"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
+      <c r="A9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="X9" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="Y9" s="3" t="s">
         <v>26</v>
       </c>
@@ -1382,1065 +1823,498 @@
       <c r="AA9"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
+      <c r="A10" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="W10" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="X10" s="4" t="s">
+        <v>107</v>
+      </c>
       <c r="Y10" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="X11" s="4"/>
+      <c r="A11" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="X11" s="4" t="s">
+        <v>115</v>
+      </c>
       <c r="Y11" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="X12" s="4" t="s">
+        <v>121</v>
+      </c>
       <c r="Y12" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W13" s="4"/>
+      <c r="A13" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="W13" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="X13" s="4" t="s">
+        <v>129</v>
+      </c>
       <c r="Y13" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
+      <c r="A14" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W14" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="X14" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="Y14" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W15" s="4"/>
+      <c r="A15" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W15" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="X15" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="Y15" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
+      <c r="A16" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="W16" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="X16" s="4" t="s">
+        <v>149</v>
+      </c>
       <c r="Y16" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
+      <c r="A17" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>157</v>
+      </c>
       <c r="Y17" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="W18" s="4"/>
-      <c r="Y18" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="W20" s="4"/>
-      <c r="X20" s="4"/>
-      <c r="Y20" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="W21" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y21" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="W22" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="X22" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y23" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="W24" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="X24" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y24" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="P25" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V25" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="W25" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="X25" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y25" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="X26" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y26" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y27" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O28" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="P28" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V28" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="W28" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="X28" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y28" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="X29" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O30" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="P30" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="W30" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="X30" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y30" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P31" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V31" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="W31" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="X31" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y31" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="W32" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="X32" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y32" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="X33" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y33" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P34" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V34" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="W34" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="X34" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y34" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="X35" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y35" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="P36" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V36" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="W36" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="X36" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y36" s="3" t="s">
         <v>26</v>
       </c>
     </row>

--- a/Treinamento/GestaoReclamacao.xlsx
+++ b/Treinamento/GestaoReclamacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E77EBAA-312F-4E74-8EC8-98C0F863532C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2658FA21-1C1B-43CD-B3DF-F0255BF1AC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B1A77FD5-2AD3-4458-ACB3-7F19D1A3340A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="138">
   <si>
     <t>Id HugMe</t>
   </si>
@@ -122,13 +122,13 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>95321837</t>
-  </si>
-  <si>
-    <t>240193803</t>
-  </si>
-  <si>
-    <t>09/02/2026 12:19</t>
+    <t>95358064</t>
+  </si>
+  <si>
+    <t>240273213</t>
+  </si>
+  <si>
+    <t>09/02/2026 23:29</t>
   </si>
   <si>
     <t>Não respondido</t>
@@ -137,612 +137,522 @@
     <t>Não</t>
   </si>
   <si>
-    <t>Allianz ; Sinistro ; Sinistro ; Análise Sinistro ; 1 Segurado ; Automóvel ; Sem Resposta - Dentro SLA ; Sim ; Repasse Time MindBe ; OUV Antes do RA</t>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; Reclamante em nome do Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
     <t>Allianz</t>
   </si>
   <si>
+    <t>Apólice</t>
+  </si>
+  <si>
+    <t>Automóvel</t>
+  </si>
+  <si>
+    <t>Assistência Não Danos</t>
+  </si>
+  <si>
+    <t>Guincho</t>
+  </si>
+  <si>
+    <t>Reclamante em nome do Segurado</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Repasse Time MindBe</t>
+  </si>
+  <si>
+    <t>Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>132551160</t>
+  </si>
+  <si>
+    <t>Tive uma experiência pessima com essa seguradora! estava com o veiculo no shopping no dia 08/02 quando o mesmo deu pane elétrica e nao funcionou acionei o guincho pois era o meio mais pratico e seguro para resolver a situação! me mandaram msgs pedindo fotos do local videos e perguntando se estava no subsolo, eu respondi que nao porem estava numa vaga difícil que teria que ter cuidado ao tirar! o prestador de serviço terceiro chegou e disse eu nao consigo retirar o veiculo sem um apoio! vou embora e vou passar pra eles que tem que mandar guincho com apoio fiquei aguardando e mandando msgs por whats explicando o ocorrido e cobrando uma solução!! e pasmem pedi ajuda as 20:00 o prestador chegou as 20;45 e o que deveria vir de apoio estava dando 22;00 e nada resolvi cobrar insistentemente pois queria ir pra casa e me disseram que nao tinham guincho com patins para remover meu veiculo! e que estavam procurando as 00;00 entrei em contato e me deram de opção eu procurar um guincho pra remoção que ressarciam depois!!! me senti uma idiota pagando seguro e nao tendo respaldo na primeira vez de urgência que precisei!! nao vieram e disseram que se eu quisesse ficaria pro dia seguinte as 10:00 da manha!! eu cansada e ja sem forcas pedi que mandassem um taxi pra eu ir embora e atendente Paola me disse que eu so teria o taxi naquele momento se eu assumisse os custos do retorno ao shopping no dia seguinte!! fiquei indignada!! me obrigaram a dizer que eu concordava em assumir esse custo no dia seguinte para me liberarem o Uber as 01:40 mesmo ela sabendo que eu estava sozinha e exposta a risco de assalto ou a estupro naquele horário!! sou segurada Porto Seguro e nunca passei por isso na vida!descaso desrespeito e falta de profissionalismo</t>
+  </si>
+  <si>
+    <t>95351467</t>
+  </si>
+  <si>
+    <t>240252831</t>
+  </si>
+  <si>
+    <t>09/02/2026 19:28</t>
+  </si>
+  <si>
+    <t>Allianz ; Automóvel ; Assistência Não Danos ; Apólice ; Vidros - AutoGlass ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Vidros - AutoGlass</t>
+  </si>
+  <si>
+    <t>1 Segurado</t>
+  </si>
+  <si>
+    <t>Juliana</t>
+  </si>
+  <si>
+    <t>132779663</t>
+  </si>
+  <si>
+    <t>RECLAMAÇÃO FORMAL CONTRA A SEGURADORA ALLIANZ_x000D_
+_x000D_
+_x000D_
+Sou segurado da Allianz há mais de 5 anos, sempre mantendo meu contrato ativo e em dia. No meu seguro automotivo, contratei cobertura adicional para vidros, retrovisores, faróis e lanternas._x000D_
+_x000D_
+_x000D_
+Recentemente, envolvi-me em um sinistro de trânsito, no qual o terceiro responsável evadiu-se do local sem assumir os danos. Diante disso, acionei meu seguro para a substituição do farol dianteiro, que foi danificado._x000D_
+_x000D_
+_x000D_
+Ocorre que o farol do meu veículo é convencional, equipado com lâmpadas H7 e H11, e não é farol de LED ou Xenon. Inclusive, para o ano e modelo do meu carro, não existe versão original com farol de LED, apenas farol convencional de lâmpadas._x000D_
+_x000D_
+_x000D_
+Conforme consta claramente na minha apólice, a franquia para farol convencional é de R$ 415,00, enquanto a franquia para farol Xenon ou LED é de aproximadamente R$ 1.890,00 / R$ 1.990,00._x000D_
+_x000D_
+_x000D_
+Mesmo após o envio das fotos solicitadas, a seguradora afirmou de forma equivocada que o farol do meu veículo seria de LED e, com isso, tentou me impor uma franquia indevida de R$ 1.990,00, o que não condiz com a realidade do veículo nem com o que está previsto contratualmente._x000D_
+_x000D_
+_x000D_
+Já tentei resolver a situação pela ouvidoria da seguradora, porém não obtive qualquer solução. Solicitei ainda uma vistoria presencial, justamente para comprovar que o farol é convencional, mas esse pedido foi negado, sendo solicitadas apenas novas fotos, o que não resolve o problema e apenas prolonga o impasse._x000D_
+_x000D_
+_x000D_
+Ressalto que a própria franquia descrita na apólice é clara ao diferenciar:_x000D_
+_x000D_
+_x000D_
+Farol convencional: R$ 415,00_x000D_
+_x000D_
+_x000D_
+Farol Xenon ou LED: valor muito superior_x000D_
+_x000D_
+_x000D_
+_x000D_
+Portanto, considero a postura da seguradora abusiva, injusta e em desacordo com o contrato, além de gerar prejuízo financeiro indevido ao segurado._x000D_
+_x000D_
+_x000D_
+Diante do exposto, solicito:_x000D_
+_x000D_
+_x000D_
+1. O reconhecimento de que o farol do meu veículo é convencional;_x000D_
+_x000D_
+_x000D_
+_x000D_
+2. A aplicação correta da franquia prevista em apólice (R$ 415,00);_x000D_
+_x000D_
+_x000D_
+_x000D_
+3. Ou, alternativamente, a realização imediata de vistoria presencial para comprovação técnica;_x000D_
+_x000D_
+_x000D_
+_x000D_
+4. A regularização do sinistro sem novas exigências indevidas._x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+Caso não haja solução, reservo-me o direito de buscar meus direitos junto aos órgãos de defesa do consumidor (Procon, consumidor.gov.br) e demais medidas cabíveis.</t>
+  </si>
+  <si>
+    <t>95349784</t>
+  </si>
+  <si>
+    <t>240247605</t>
+  </si>
+  <si>
+    <t>09/02/2026 18:40</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; 1 Segurado ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Canal de Atendimento ; Corretor ; Não ; Condomínio</t>
+  </si>
+  <si>
+    <t>Condomínio</t>
+  </si>
+  <si>
+    <t>Canal de Atendimento</t>
+  </si>
+  <si>
+    <t>Corretor</t>
+  </si>
+  <si>
+    <t>302936078</t>
+  </si>
+  <si>
+    <t>Sou locadora da sala comercial segurada, bem como beneficiária do seguro. _x000D_
+_x000D_
+Tive um sinistro em novembro/25, acionei o seguro, fiz o trâmite, enviei todos os registros dos prejuizos do meu imovel e dos terceiros afetados, e agora, em fevereiro/26, recebo uma carta da Allianz,  negando a responsabilidade pelos danos, devido o corretor de seguros (parceiro Allianz) ter errado a sala segurada na apólice. Ao invés de colocar o endereço do imóvel do contrato de locação, conforme solicitado, ele colocou o endereço antigo que o locatário alugava, imóvel que não tem nada a ver comigo, e nem haveria motivo para que eu fosse beneficiaria._x000D_
+_x000D_
+Eu que não tenho nada a ver com a confusão, estou sendo penalizada. Peço urgentemente a solução. _x000D_
+_x000D_
+A Allianz tem responsabilidade solidária pelo erro do seu parceiro, e não pode se eximir da cobertura.</t>
+  </si>
+  <si>
+    <t>95348811</t>
+  </si>
+  <si>
+    <t>240244921</t>
+  </si>
+  <si>
+    <t>09/02/2026 18:16</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; Reclamante em nome do Segurado ; OUV Antes do RA ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>OUV Antes do RA</t>
+  </si>
+  <si>
+    <t>Carla</t>
+  </si>
+  <si>
+    <t>133618174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sou condutora principal da Allianz seguros para veículos, cujo cadastro está em nome do meu esposo, com contrato ativo e pagamentos em dia, e registro esta reclamação por falha grave na prestação do serviço de guincho, serviço essencial do seguro contratado._x000D_
+_x000D_
+No dia 08 de fevereiro de 2026, solicitei guincho pelo seguro. O serviço foi devidamente autorizado às 18:36h porém o guincho nunca foi enviado, mesmo após aguardar por longo período e tentar contato para solução._x000D_
+_x000D_
+Eu me encontrava em bairro de alto risco, Vila kosmos no Rio de Janeiro-RJ e havia ido ao local para assistir a uma missa. Permaneci do lado de fora da igreja aguardando o guincho, sem sequer conseguir entrar para assistir a missa, exposta à situação de insegurança e sob chuva, tentando resolver a situação. Ao final, por medo e falta de suporte, fui obrigada a abandonar meu veículo no local, deixando-o pernoitando longe de mim, e retornar para casa sem ele. Estava tendo alguns disparos de tiros nas redondezas._x000D_
+_x000D_
+Em razão da falha do serviço, meu esposo ainda precisou custear transporte por aplicativo (Uber) para que conseguíssemos voltar para casa, gerando gasto financeiro que não teria ocorrido se o serviço contratado tivesse sido prestado corretamente._x000D_
+_x000D_
+Chegando em casa tivemos que procurar o número da seguradora para ligar e avisar que já não estaríamos no local da ocorrência, pela demora excessiva da prestação de serviço e por segurança voltamos para casa e solicitamos um reagendamento para o dia seguinte._x000D_
+_x000D_
+Porém a situação me causou estresse excessivo, angústia, frustração, sensação de abandono e quebra total da expectativa de segurança que o seguro deveria oferecer, que inclusive se diz ser 24h em contrato. O ocorrido ultrapassa qualquer conceito de mero aborrecimento, tratando-se de exposição concreta ao risco, além de dano material e dano moral, chegamos todos molhados em casa, correndo risco de adoecer._x000D_
+_x000D_
+Em  09/02/2026 o agendamento do guincho estava para as 09h00. Não fui trabalhar para resolver a situação, e meu marido também foi prejudicado em seu trabalho. Houve atraso novamente. Diante da ausência do guincho, e incerteza se de fato o guincho viria, fomos obrigados a resolver o problema por conta própria, sob chuva, realizando esforços físicos e assumindo riscos, inclusive com auxílio de um terceiro, que apareceu oferecendo ajuda, para possibilitar a remoção do veículo. Ressalto que o guincho somente chegou às 10h50, quando o serviço já não era mais útil, pois o problema havia sido solucionado de forma improvisada por nós; isso porque já havíamos entrado em contato com os telefones disponíveis da seguradora para saber uma posição do guincho, se de fato viria, e o que estaria acontecendo, e a cada ligação algum atendente pedia paciência e que esperassemos 15, 25 minutos a mais._x000D_
+_x000D_
+O serviço de guincho não foi prestado de forma adequada, dentro do tempo razoável e com utilidade prática, mesmo assim a operadora me informou que é considerado como utilização válida da franquia anual, descontando o serviço. O que eu acho que me desrespeita ainda mais._x000D_
+_x000D_
+_x000D_
+Diante do exposto, solicito:_x000D_
+_x000D_
+esclarecimentos formais sobre a não prestação do serviço de guincho autorizado;_x000D_
+_x000D_
+reembolso do valor gasto com transporte por aplicativo,_x000D_
+_x000D_
+proposta de indenização por danos morais, compatível com a gravidade da situação vivenciada._x000D_
+_x000D_
+_x000D_
+</t>
+  </si>
+  <si>
+    <t>95346575</t>
+  </si>
+  <si>
+    <t>240238557</t>
+  </si>
+  <si>
+    <t>09/02/2026 17:24</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Emissão ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Emissão</t>
+  </si>
+  <si>
+    <t>135320137</t>
+  </si>
+  <si>
+    <t>Boa tarde!_x000D_
+_x000D_
+Em novembro de 2025, por ocasião da aquisição de um novo carro, contratei o  seguro de automóvel, da Allianz Seguros, por intermédio de uma corretora (da House Real Seguros), no valor de R$ 1.727,21. Ainda, importa dizer que, à época da contratação referenciada, eu morava no Estado do RS; todavia, esclareci que, brevemente, seria transferido para a cidade do Rio de Janeiro, RJ (tal mudança ocorreu, recentemente, em janeiro do presente ano (2026)). _x000D_
+_x000D_
+Neste seguimento, fui informado pela corretora que, ao ser transferido, era necessário tão somente comunicar a empresa, a fim de que fosse realizado o endosso por mudança de CEP. Todavia, hoje, ao tentar realizar tal endosso, fui comunicado por uma corretora da House Real Seguros que o CEP está fora da política de aceitação da Companhia. Em seguimento, ela me informou que eu devia cancelar a apólice pela Allianz e efetuar uma nova por uma outra Empresa. _x000D_
+_x000D_
+Por conseguinte, fiz contato com a Allianz (pelo SAC) e expliquei a situação mencionada; porém, fui comunicado que as negociações deveriam ser efetuadas por meio da corretora. Neste aspecto, retornei contato com a corretora e informei que já havia quitado o valor do seguro relacionado à Allianz, bem como solicitei um pedido formal (por e-mail) à Allianz, a fim de que a Empresa se manifestasse quanto à recusa do endosso._x000D_
+_x000D_
+A corretora informou que é uma prerrogativa da Empresa não aceitar o endosso e que não há documento a ser fornecido, por ser uma análise da Allianz, segundo padrões da SUSEPE. Ato contínuo, a corretora propôs o cancelamento do seguro, com a devolução de cerca de R$ 906,00 por parte da Empresa._x000D_
+_x000D_
+Dadas as circunstâncias, pedi para a corretora efetuar o cancelamento do seguro._x000D_
+_x000D_
+Isso posto, à luz das informações prestadas, estou insatisfeito com a Allianz Seguros e consulto a possibilidade de essa Empresa se manifestar quanto ao caso e ao valor da restituição, observada a regra da proporcionalidade referente ao prêmio não utilizado.</t>
+  </si>
+  <si>
+    <t>95346183</t>
+  </si>
+  <si>
+    <t>240237413</t>
+  </si>
+  <si>
+    <t>09/02/2026 17:15</t>
+  </si>
+  <si>
+    <t>Allianz ; CPF/CNPJ ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>CPF/CNPJ</t>
+  </si>
+  <si>
     <t>Sinistro</t>
   </si>
   <si>
-    <t>Automóvel</t>
-  </si>
-  <si>
     <t>Análise Sinistro</t>
   </si>
   <si>
-    <t>1 Segurado</t>
-  </si>
-  <si>
-    <t>OUV Antes do RA</t>
-  </si>
-  <si>
-    <t>Sim</t>
-  </si>
-  <si>
-    <t>Repasse Time MindBe</t>
-  </si>
-  <si>
-    <t>Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Juliana</t>
-  </si>
-  <si>
-    <t>303831473</t>
-  </si>
-  <si>
-    <t>eu estou muito decepcionado com essa empresa depois de ano pagando esse seguro na hora que eu precisei não fui atendido estou muito decepcionada até agora estou sem entender.</t>
-  </si>
-  <si>
-    <t>95319446</t>
-  </si>
-  <si>
-    <t>240189099</t>
-  </si>
-  <si>
-    <t>09/02/2026 11:48</t>
-  </si>
-  <si>
-    <t>Allianz ; Sem Resposta - Dentro SLA ; Não ; Sim ; Repasse Time MindBe ; 1 Segurado ; Automóvel ; Assistência Não Danos ; Vidros - AutoGlass ; Apólice</t>
-  </si>
-  <si>
-    <t>Apólice</t>
-  </si>
-  <si>
-    <t>Assistência Não Danos</t>
-  </si>
-  <si>
-    <t>Vidros - AutoGlass</t>
-  </si>
-  <si>
-    <t>134020482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allianz  NUNCA MAIS !!!_x000D_
-_x000D_
-_x000D_
-A simples troca de um retrovisor externo do meu carro, serviço contratado na apólice do seguro, se tornou uma novela !!!_x000D_
-_x000D_
-Mais de uma semana esperando e nada da seguradora, liberar o atendimento._x000D_
-_x000D_
-A prestadora do serviço,  AUTOGLASS, enrolando para não fazer o serviço. _x000D_
-_x000D_
-Cada hora, algo novo.._x000D_
-_x000D_
-Fotos, documentos, mais fotos, mais documentos e nada de fazer a troca.._x000D_
-_x000D_
-Agora, a historia é que no chassis do meu carro, não consta o retrovisor com pisca e a enrolação continua !!!!_x000D_
-_x000D_
-Mais de uma semana e nada !!!_x000D_
-_x000D_
-Somente enrolação  !!!!_x000D_
-_x000D_
-IMAGINA SE O SINISTRO FOSSE MAIOR ???_x000D_
-_x000D_
-QUANTO TEMPO LEVARIA ???_x000D_
-_x000D_
-Me arrependo muito  de ter trocado a Porto Seguro, por essa porcaria de seguradora !!!!_x000D_
-_x000D_
-ALLIANZ NUNCA MAIS !!!_x000D_
-_x000D_
+    <t>Andreza</t>
+  </si>
+  <si>
+    <t>78536316420</t>
+  </si>
+  <si>
+    <t>Comprei um veículo na Vip Leiloes da Allianz Seguros, e ela me enviou a documentacão incompleta para tranferência, faltando O CRLV 2025 e a CNH ou RG do assinante da procuração, Bernardo Doria Rawicz._x000D_
+_x000D_
+_x000D_
+Solicito cópia do CRLV e de CNH ou RG (pode ser a digital) de Bernardo Doria Rawicz para que eu consiga finalizar a transferência do veiculo para o meu nome._x000D_
+_x000D_
+_x000D_
+O Detran RN está solicitando para que eu consiga fazer a transferência do veiculo._x000D_
+_x000D_
+Tentei falar com Allianz e não consegui, mandei mensgem para Vip Leilões não responderam.</t>
+  </si>
+  <si>
+    <t>95338523</t>
+  </si>
+  <si>
+    <t>240222407</t>
+  </si>
+  <si>
+    <t>09/02/2026 15:32</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Vida / Acidentes Pessoais ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Canal de Atendimento ; Central de Atendimento</t>
+  </si>
+  <si>
+    <t>Vida / Acidentes Pessoais</t>
+  </si>
+  <si>
+    <t>Central de Atendimento</t>
+  </si>
+  <si>
+    <t>131181675</t>
+  </si>
+  <si>
+    <t>Apareceu no aplicativo do meu banco um boleto que vence amanhã dia 10/02, emitido pela ALLIANZ SEGUROS SA de cnpj 61.573.796/0001-66, porém, eu não possuo seguros nessa seguradora e também não solicitei NADA, nao autorizei nada, se quer tive contato e foi gerado de forma indevida, sem autorização. _x000D_
+_x000D_
+Quero que seja retirado e quero saber o pq estão gerando boletos no meu CPF, pois nunca tive em contato com essa seguradora! Preciso que resolvam logo</t>
+  </si>
+  <si>
+    <t>95335154</t>
+  </si>
+  <si>
+    <t>240217355</t>
+  </si>
+  <si>
+    <t>09/02/2026 14:58</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Fornecimento de Peças ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Fornecimento de Peças</t>
+  </si>
+  <si>
+    <t>301829961</t>
+  </si>
+  <si>
+    <t>Demora excessiva no conserto de veículo sinistrado  Allianz Seguros_x000D_
+_x000D_
+_x000D_
+Sou segurada da Allianz Seguros, e registro esta reclamação pela demora excessiva e injustificada no conserto do meu veículo._x000D_
+_x000D_
+_x000D_
+O sinistro ocorreu em 30/10/2025 e, desde essa mesma data, o meu veículo está na oficina credenciada, sem previsão de entrega até hoje. Em nenhum momento foi apresentado um prazo claro ou uma solução efetiva para a conclusão do reparo._x000D_
+_x000D_
+_x000D_
+Conforme previsto em apólice, foi disponibilizado carro reserva por 30 dias. Após esse período, mesmo com o meu veículo ainda impossibilitado de uso, a seguradora recusou a prorrogação, deixando-me completamente desassistida. _x000D_
+_x000D_
+_x000D_
+A justificativa apresentada pela Allianz é a falta de peças por parte da fabricante Nissan. No entanto, entendo que esse é um problema que deve ser resolvido entre a seguradora e a fabricante, não podendo o segurado ser penalizado por uma falha que não lhe cabe._x000D_
+_x000D_
+_x000D_
+O veículo é essencial para minha vida cotidiana. Dependo dele para trabalhar, para o deslocamento diário da minha mãe idosa, para levar meu filho menor à escola e a consultas médicas, além de atividades básicas como mercado, farmácia e demais compromissos indispensáveis. A negativa de manutenção do carro reserva, somada à longa espera, tem causado prejuízos concretos, transtornos constantes e grande impacto na minha rotina. _x000D_
+_x000D_
+_x000D_
+Sinto-me desrespeitada como consumidora. A situação demonstra falha na prestação do serviço e descumprimento do dever de boa-fé, colocando todo o ônus da demora sobre quem cumpre regularmente suas obrigações contratuais._x000D_
+_x000D_
+_x000D_
+Diante disso, solicito uma solução imediata, seja pela conclusão do reparo do veículo, seja pela manutenção de um carro reserva até a efetiva entrega do bem, evitando que os prejuízos continuem a se acumular.</t>
+  </si>
+  <si>
+    <t>95334756</t>
+  </si>
+  <si>
+    <t>240216989</t>
+  </si>
+  <si>
+    <t>09/02/2026 14:56</t>
+  </si>
+  <si>
+    <t>Allianz ; Automóvel ; Apólice ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Assistência Não Danos ; Guincho ; 1 Segurado ; SAC Aberto</t>
+  </si>
+  <si>
+    <t>SAC Aberto</t>
+  </si>
+  <si>
+    <t>134621783</t>
+  </si>
+  <si>
+    <t>Meu auto teve uma pane mecânica, solicitei em reboque para levar o veículo até uma oficina (protocolo 51365182). A Allianz levou 4 horas para chegar até o local do destino._x000D_
+_x000D_
+Isso pq, a pane foi ontem entre 21:30 e 22h, também fiz contato solicitando reboque, por 2 oportunidades (protocolos 51362729 e 51362922) e fui ignorado, me pediram para aguardar, não mandaram o reboque e não me deram retorno._x000D_
+_x000D_
+Por sorte eu estava perto da minha casa, consegui levar o carro até em casa, empurrando o veículo pelo meio da rua, as 23h da noite, sob forte chuva._x000D_
+_x000D_
+A Allianz descumpriu uma das obrigações contratuais ontem quando me deixou a minha própria sorte e hoje novamente quando, devido a uma 3 solicitação de reboque, apareceu após 4h de espera._x000D_
+_x000D_
+Desejo providencias ou irei acionar a justiça a fim de ser reparado._x000D_
+_x000D_
+Fico aguardando.</t>
+  </si>
+  <si>
+    <t>95331635</t>
+  </si>
+  <si>
+    <t>240212449</t>
+  </si>
+  <si>
+    <t>09/02/2026 14:26</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Sinistro ; Análise Sinistro ; Automóvel ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>305240574</t>
+  </si>
+  <si>
+    <t>Demora em fazer perícia_x000D_
+_x000D_
+_x000D_
+Estou tentando fazer a perícia do meu carro há 1 semana e até agora nada. O sistema da Allianz me indicou fazer a perícia em duas oficinas que se recusaram a prestar o serviço, pois se trata de um carro novo e na garantia. No meu caso, o mais indicado é fazer a perícia na própria concessionária (eu não sabia disso). No dia 05/02 deixei o carro na concessionária Geely Jorlan (Brasília), mas até agora (09/02) a perícia não foi realizada._x000D_
+_x000D_
+_x000D_
+Gostaria de uma resolução para meu caso, pois estou sem carro aguardando uma simples burocracia entre a concessionária e a seguradora.</t>
+  </si>
+  <si>
+    <t>95328268</t>
+  </si>
+  <si>
+    <t>240207209</t>
+  </si>
+  <si>
+    <t>09/02/2026 13:52</t>
+  </si>
+  <si>
+    <t>Allianz ; Automóvel ; CPF/CNPJ ; Apólice ; Pagamento ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Pagamento</t>
+  </si>
+  <si>
+    <t>5560636193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venho por meio deste formalizar a respeito do cancelamento da apólice de seguro n 0836.990.0244.719502 , realizado sem qualquer aviso prévio ou comunicação formal, o que considero indevido e ilegal, à luz da legislação consumerista e da jurisprudência do Superior Tribunal de Justiça._x000D_
+_x000D_
+_x000D_
+Esclareço que:_x000D_
+_x000D_
+_x000D_
+1. Houve contestação de uma cobrança que não reconheci, o que resultou no cancelamento do meu cartão de crédito;_x000D_
+_x000D_
+2. Assim que informada pela corretora sobre a tentativa de cobrança, agí de boa-fé, pedi desculpas pela confusão e forneci imediatamente os dados do novo cartão;_x000D_
+_x000D_
+3. Uma nova tentativa de cobrança foi realizada e recusada, sem que me fosse informado qualquer problema adicional ou risco de cancelamento;_x000D_
+_x000D_
+4. Não recebi qualquer notificação prévia informando atraso, prazo para regularização ou cancelamento da apólice;_x000D_
+_x000D_
+5. Apenas descobri que estava sem cobertura ao tentar utilizar o seguro._x000D_
+_x000D_
+_x000D_
+Diante disso, requeiro formalmente:_x000D_
+_x000D_
+_x000D_
+* a reativação imediata da apólice, mantendo-se a continuidade da cobertura;_x000D_
+_x000D_
+* o reconhecimento da validade da cobertura, uma vez que não houve comunicação prévia válida sobre o cancelamento;_x000D_
+_x000D_
+* o envio de nova forma de cobrança para regularização do valor eventualmente pendente._x000D_
 _x000D_
 </t>
   </si>
   <si>
-    <t>95308463</t>
-  </si>
-  <si>
-    <t>240165963</t>
-  </si>
-  <si>
-    <t>09/02/2026 09:21</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Vida / Acidentes Pessoais ; Corretor ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Canal de Atendimento</t>
-  </si>
-  <si>
-    <t>Vida / Acidentes Pessoais</t>
-  </si>
-  <si>
-    <t>Canal de Atendimento</t>
-  </si>
-  <si>
-    <t>Corretor</t>
-  </si>
-  <si>
-    <t>Andreza</t>
-  </si>
-  <si>
-    <t>136075773</t>
-  </si>
-  <si>
-    <t>Abri minha conta no nu Bank e tem um boleto pra pagar não tenho vínculo nenhum e não conheço essa empresa..</t>
-  </si>
-  <si>
-    <t>95307161</t>
-  </si>
-  <si>
-    <t>240163487</t>
-  </si>
-  <si>
-    <t>09/02/2026 09:00</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Fornecimento de Peças ; 1 Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Fornecimento de Peças</t>
-  </si>
-  <si>
-    <t>1 Ctt Sem Sucesso</t>
-  </si>
-  <si>
-    <t>304427359</t>
-  </si>
-  <si>
-    <t>Abri sinistro n 304427359 para conserto do veículono dia 12.01.2026 e até hoje, em 9.02.2026 nao forneceram as peças para realização do serviço. Em contato com a consercionária, fui atendida com muito descaso, informando q deveria aguardar mais. Localizei novo fornecedor q entrega em 24h e fiz a requisição de alteração de serviço, mas nem a Allianz me retorna. Descaso total enquanto fico 1 mês aguardando o serviço q infelizmente contratei com eles. Primeiro e ultimo ano como cliente deles. Porto seguro tem atendimento muito melhor</t>
-  </si>
-  <si>
-    <t>95306756</t>
-  </si>
-  <si>
-    <t>240162761</t>
-  </si>
-  <si>
-    <t>09/02/2026 08:53</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Condomínio ; Sinistro ; Indenização ; Reclamante em nome do Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Condomínio</t>
+    <t>95322602</t>
+  </si>
+  <si>
+    <t>240195335</t>
+  </si>
+  <si>
+    <t>09/02/2026 12:29</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Apólice ; Análise Sinistro ; 2 Terceiro do Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>2 Terceiro do Sinistro</t>
+  </si>
+  <si>
+    <t>300442217</t>
+  </si>
+  <si>
+    <t>Fui envolvido em acidente 16.09.2025 ao ser atingido na parte traseira de meu veículo por um veículo segurado pela Allianz Seguros. Após várias tentativas e apresentação de orçamento a seguradora se negou a reparar os danos causados em meu veículo devido ao ano modelo 1998 e infelizmente tive que entrar com processo judicial contra a pessoa que ocasionou o acidente. Visto que ela contratou uma seguradora contra acidente de terceiros e a empresa negou se a reparar os danos, até que ponto nós contratantes de seguros junto as Cia de Seguro estamos livre deste constrangimento. Atualmente tenho seguro junto a Allianz Seguros, porém não mais irei renovar seguros de veículos, pois caso venha me envolver em acidente que seja de minha responsabilidade, fica definitivamente dúvida se a seguradora irá ressarcir os danos causados.</t>
+  </si>
+  <si>
+    <t>95320855</t>
+  </si>
+  <si>
+    <t>240191769</t>
+  </si>
+  <si>
+    <t>09/02/2026 12:05</t>
+  </si>
+  <si>
+    <t>Linhas Corporativas ; Allianz ; 1 Segurado ; Repasse Time MindBe ; Não ; Sem Resposta - Dentro SLA ; Sim ; Sinistro ; Sinistro ; Indenização</t>
+  </si>
+  <si>
+    <t>Linhas Corporativas</t>
   </si>
   <si>
     <t>Indenização</t>
   </si>
   <si>
-    <t>Reclamante em nome do Segurado</t>
-  </si>
-  <si>
-    <t>Carla</t>
-  </si>
-  <si>
-    <t>294179384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia, durante os fortes ventos de Dezembro 2025, tivemos um incidente com uma das torres de iluminação da quadra de Tênis do nosso edífico, CNPJ: 19.857.870/0001-00, Razão Social: Edificio Le Marc - Vila Romana e _x000D_
-_x000D_
-Nome Fantasia: Edificio Le Marc._x000D_
-_x000D_
-Foi aberto um sinistro junto a seguradora, mas por duas vezes a mesma recusou a cobertura dos eventos, precisamos que a Segurado reavalie o ocorrido e verifique a possibilidade novamente para a cobertura do seguro e o reembolso dos danos causados para o reparo._x000D_
-_x000D_
-Sinistro S-294179384 - COND. LE MARC _x000D_
-_x000D_
-Obrigado_x000D_
+    <t>212766895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fui segurado da Allianz Seguros em contrato de seguro de responsabilidade civil profissional._x000D_
+_x000D_
+_x000D_
+Em 2017, fui demandado judicialmente em razão de suposto erro em procuração lavrada no Tabelionato de Notas e Protestos de Ituporanga/SC, do qual eu era titular à época._x000D_
+_x000D_
+Diante da natureza do risco coberto, denunciei a lide à seguradora, conforme autorizado pelo contrato de seguro, que previa expressamente a cobertura de despesas processuais, inclusive honorários advocatícios._x000D_
+_x000D_
+_x000D_
+A ação tramitou regularmente e, ao final, obtive êxito integral, não havendo qualquer condenação contra minha pessoa._x000D_
+_x000D_
+_x000D_
+Apesar disso, de forma absolutamente inesperada e juridicamente indevida, a advogada da seguradora ingressou com execução de honorários sucumbenciais contra mim, sob o argumento de que a denunciação da lide geraria obrigação de pagamento em favor da seguradora._x000D_
+_x000D_
+Mais grave: promoveu bloqueio de valores em minha conta bancária, em evidente abuso de direito._x000D_
+_x000D_
+_x000D_
+Tal conduta é incompatível com a natureza do contrato de seguro e com os princípios da boa-fé objetiva e da função social do contrato._x000D_
+_x000D_
+O seguro de responsabilidade civil existe justamente para transferir ao segurador os riscos econômicos do sinistro, inclusive custos de defesa e honorários. Não é juridicamente aceitável que o segurado, vencedor da ação, seja compelido a pagar honorários à própria seguradora, que atua como sua garantidora._x000D_
+_x000D_
+_x000D_
+Se assim fosse, o contrato de seguro se tornaria inútil e contraditório, pois o exercício regular do direito de denunciar a lide implicaria punição econômica ao segurado._x000D_
+_x000D_
+Eventual condenação em honorários  se existente  jamais poderia ser imputada ao segurado, mas, em tese, à própria seguradora ou simplesmente afastada, diante da inexistência de sucumbência material._x000D_
+_x000D_
+_x000D_
+Portanto, a execução promovida contra mim carece de fundamento jurídico, configura abuso processual e deve ser reconhecida como manifestamente inexigível, com imediato levantamento das constrições realizadas._x000D_
+_x000D_
 _x000D_
 </t>
-  </si>
-  <si>
-    <t>95288450</t>
-  </si>
-  <si>
-    <t>240138661</t>
-  </si>
-  <si>
-    <t>08/02/2026 19:24</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; 1 Segurado ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Não</t>
-  </si>
-  <si>
-    <t>Guincho</t>
-  </si>
-  <si>
-    <t>134232279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sou segurada e na última semana de janeiro de 2026 precisei usar o serviço de guincho e foi recusado. O atendente informou que pelo motivo que eu estava solicitando ( pneu furado) eu não tenho direito direito. O interessante é que isso não foi explicado na hora da venda do serviço. Fiz várias ligações para que alguém pudesse me esclarecer e ninguém responde a minha pergunta._x000D_
-_x000D_
-Total falta de respeito!_x000D_
-_x000D_
-</t>
-  </si>
-  <si>
-    <t>95287713</t>
-  </si>
-  <si>
-    <t>240137923</t>
-  </si>
-  <si>
-    <t>08/02/2026 19:09</t>
-  </si>
-  <si>
-    <t>Allianz ; Automóvel ; Sinistro ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>134955468</t>
-  </si>
-  <si>
-    <t>Tenho 3 motos asseguradas com a Alianzz , todas com seguro completo,  pela primeira vez precisei usar ,porque o pneu furou hj ( domingo) em lugar onde não  tinha borracheiro . Acionei o reboque , mais de uma hora esperando , fiz contato 3 vezes . O reboque chegou e o rapaz disse que não  ia levar em casa , depois fiz contato , falou que levaria , mas que não  poderia levar meu esposo e que não  tinha direito a táxi ( também não não  sei se o taxi iria onde a moto estava) , isso tudo a 25km de casa , fiquei me perguntando se fosse eu ( mulher) sozinha  a noite (porque o reboque só  cehgou a noite) como ia fazer para ir embora. Aí a pergunta: Como confiar em um seguro que não  resolve um problema tao simples ? Imagina um acidente ou um roubo , ou algo mais grave . Que bom que descobri a incompetência com um pneu furado . Da tempo de trocar e não  correr mais risco.  Muito insatisfeita e decepcionada .</t>
-  </si>
-  <si>
-    <t>95276627</t>
-  </si>
-  <si>
-    <t>240124707</t>
-  </si>
-  <si>
-    <t>08/02/2026 14:48</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Gestão de Oficina ; Reclamante em nome do Segurado ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Gestão de Oficina</t>
-  </si>
-  <si>
-    <t>302652319</t>
-  </si>
-  <si>
-    <t>No dia 24/11 registramos um sinistro junto à seguradora em razão de uma chuva de granizo severa que atingiu nossa cidade. Na ocasião, nosso veículo, que estava estacionado em via pública, foi atingido, resultando na quebra do para-brisa e em danos significativos na lataria._x000D_
-_x000D_
-_x000D_
-A vistoria inicial foi agendada para o dia 04/12, em uma oficina credenciada pela seguradora. Após a realização da vistoria, a oficina encaminhou o orçamento para os reparos. Em 08/12, recebemos o retorno da seguradora autorizando os serviços. Contudo, ao verificarmos os reparos que seriam executados, optamos por não prosseguir com essa oficina, pois não concordávamos com a forma como o serviço seria prestado._x000D_
-_x000D_
-_x000D_
-Diante disso, decidimos levar o veículo a uma concessionária autorizada, a fim de obter um novo orçamento. No dia 18/12, a concessionária realizou uma vistoria completa e encaminhou o orçamento à seguradora. Em 22/12, recebemos a informação de que os serviços não haviam sido autorizados. Alguns dias depois, a seguradora informou a aprovação de um valor correspondente a apenas 17% do orçamento apresentado pela concessionária, quantia insuficiente inclusive para cobrir a mão de obra da oficina._x000D_
-_x000D_
-_x000D_
-Não concordando com o valor aprovado, no dia 18/01 registramos uma comunicação no sistema da seguradora solicitando a revisão do orçamento. Como não obtivemos retorno, no dia 03/02 realizamos nova tentativa de contato, reiterando o pedido de reavaliação e anexando novamente o orçamento da concessionária devidamente assinado._x000D_
-_x000D_
-_x000D_
-No dia 06/02, recebemos a seguinte resposta da seguradora:_x000D_
-_x000D_
-Em contato com a oficina, informaram que está aguardando a chegada de peças. Por favor, entre em contato com a oficina para verificar o andamento, pois informaram que estão trabalhando no veículo. Trata-se de uma concessionária escolhida pelo cliente._x000D_
-_x000D_
-_x000D_
-Entretanto, essa resposta não esclarece nosso pedido de revisão dos valores, tampouco informa o motivo pelo qual as peças solicitadas pela concessionária não foram aprovadas pela seguradora._x000D_
-_x000D_
-_x000D_
-Ressalto ainda que, no dia 17/12, foi necessária a substituição do para-brisa, pois as rachaduras comprometiam seriamente a visibilidade. A troca foi realizada em uma oficina autorizada pela seguradora, porém o número do chassi não foi gravado no vidro. Dias depois, identificamos distorções onduladas e irregulares no para-brisa, que ficaram ainda mais evidentes após a aplicação da película solar. Em razão disso, fomos obrigados a retirar a película, acarretando a perda do valor investido._x000D_
-_x000D_
-_x000D_
-Ressaltamos ainda que, em razão dos danos sofridos, o teto solar também foi afetado e, sempre que ocorre chuva, há entrada de água no interior do veículo, o que vem ocasionando transtornos adicionais e agravando o estado de conservação do automóvel._x000D_
-_x000D_
-_x000D_
-Diante de todo o exposto, registramos nossa reclamação, uma vez que, além de o veículo permanecer visivelmente danificado, não recebemos esclarecimentos adequados por parte da seguradora quanto à não autorização dos serviços indicados pela concessionária autorizada pela seguradora. Aguardamos, com urgência, um retorno da seguradora para os devidos esclarecimentos e para a revisão do orçamento.</t>
-  </si>
-  <si>
-    <t>95249967</t>
-  </si>
-  <si>
-    <t>240097315</t>
-  </si>
-  <si>
-    <t>07/02/2026 23:01</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Sinistro ; Análise Sinistro ; Automóvel ; 1 Segurado ; Sem Resposta - Dentro SLA ; Repasse Time MindBe ; Não ; Sim</t>
-  </si>
-  <si>
-    <t>302680146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fui paciente até de mais, e já chegou ao meu limite, tô vendo a hora fazer o pior comigo mesmo. venho aqui mostra meu desespero e insatisfação com a seguradora, meu veículo um caminhão 3/4 teve um princípio de incêndio ocasionando um sinistro parcial do veículo, isso ocorreu no final de mês de novembro de 2025, e já se aproxima dos 3 meses e ainda não foi feito absolutamente nada no meu veículo, preciso do caminhão pra sustentar minha família._x000D_
-_x000D_
-eles ficam fazendo vistorias e mais vistorias ganhando tempo e sugando do resto do dinheiro que tenho, pois ainda estão cobrando as parcelas mensais que se aproxima dos 1000,00._x000D_
-_x000D_
-_x000D_
-isso é um pedido de socorro de um trabalhador honesto que não aguenta mais esperar, tô cheio de dívidas, sendo humilhado por conta da seguradora. _x000D_
-_x000D_
-_x000D_
-</t>
-  </si>
-  <si>
-    <t>95234020</t>
-  </si>
-  <si>
-    <t>240078811</t>
-  </si>
-  <si>
-    <t>07/02/2026 16:57</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Apólice ; 6 Corretor ; Pagamento ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA ; 1 Segurado</t>
-  </si>
-  <si>
-    <t>Pagamento</t>
-  </si>
-  <si>
-    <t>1 Segurado ; 6 Corretor</t>
-  </si>
-  <si>
-    <t>136560789</t>
-  </si>
-  <si>
-    <t>Cliente nao recebeu o estorno do cartao de credito da primeira proposta que foi cancelada , cliente esta me cobrando todos os dias._x000D_
-_x000D_
-Proposta- 136560789_x000D_
-_x000D_
-Segue anexo proposta em pdf</t>
-  </si>
-  <si>
-    <t>95170488</t>
-  </si>
-  <si>
-    <t>240015059</t>
-  </si>
-  <si>
-    <t>06/02/2026 18:43</t>
-  </si>
-  <si>
-    <t>OUV Antes do RA ; Allianz ; Automóvel ; 1 Segurado ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Apólice ; Assistência Não Danos ; Vidros - AutoGlass</t>
-  </si>
-  <si>
-    <t>136314573</t>
-  </si>
-  <si>
-    <t>Contratei um seguro de automóvel com a Allianz, incluindo cobertura adicional para pneus, rodas e suspensão, pela qual foi cobrado valor extra. O veículo passou por vistoria prévia, que foi aprovada sem qualquer ressalva, estando com as mesmas rodas e pneus até hoje, sem alterações posteriores._x000D_
-_x000D_
-_x000D_
-Ao sofrer um sinistro  furo de pneu ao passar por um sinalizador de pista  acionei o seguro e, para minha surpresa, a Allianz negou a cobertura, alegando que a roda seria maior que a original de fábrica. Esse argumento nunca foi apresentado na contratação, nem na vistoria, nem como exclusão contratual. Se fosse impeditivo, o seguro sequer deveria ter sido aprovado, muito menos vendido com cobertura adicional._x000D_
-_x000D_
-_x000D_
-Como a análise estava demorando excessivamente, a própria corretora orientou que eu realizasse a compra do pneu e a instalação, para não ficar com o veículo parado, e que posteriormente solicitasse o reembolso junto à seguradora._x000D_
-_x000D_
-_x000D_
-Segui exatamente essa orientação:_x000D_
-_x000D_
-_x000D_
-Comprei o pneu; Realizei a instalação; Paguei integralmente os valores; Enviei todas as notas fiscais; Preenchi os formulários exigidos pela Allianz._x000D_
-_x000D_
-_x000D_
-Mesmo assim, a seguradora negou também o pedido de reembolso, mantendo uma postura totalmente contraditória, abusiva e desrespeitosa com o consumidor._x000D_
-_x000D_
-_x000D_
-A Allianz:_x000D_
-_x000D_
-Aceitou o risco na vistoria;_x000D_
-_x000D_
-Cobrou pela cobertura adicional;_x000D_
-_x000D_
-Orientou, por meio da corretora Asserta SUSEP No: 202053026, a realização do reparo;_x000D_
-_x000D_
-E só depois negou tanto a cobertura quanto o reembolso._x000D_
-_x000D_
-_x000D_
-Solicito a revisão imediata da negativa e o reembolso integral dos valores pagos, além de uma posição coerente com o contrato firmado._x000D_
-_x000D_
-_x000D_
-Allianz Apólice Digital - 5177202675310145883 - Emissão:21/01/2026</t>
-  </si>
-  <si>
-    <t>95168423</t>
-  </si>
-  <si>
-    <t>240012569</t>
-  </si>
-  <si>
-    <t>06/02/2026 18:15</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Residência ; Sinistro ; Atraso na Análise ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Residência</t>
-  </si>
-  <si>
-    <t>Atraso na Análise</t>
-  </si>
-  <si>
-    <t>304990249</t>
-  </si>
-  <si>
-    <t>Segundo o técnico, em função de uma descarga elétrica a placa do meu microondas queimou!_x000D_
-_x000D_
-Abri um Sinistro para a seguradora Allianz que respondeu que o conserto NÃO está autorizado pois o valor de R$ 250 está abaixo do valor da franquia, que seria de R$ 600._x000D_
-_x000D_
-Porém, na apólice do meu seguro, está dizendo que NÃO é cobrado taxa de franquia para danos elétricos!_x000D_
-_x000D_
-Estou há mais de 10 dias sem meu microondas das e a Allianz não autoriza o reparo e não responde sobre o email enviado SEM SENTIDO!!</t>
-  </si>
-  <si>
-    <t>95166860</t>
-  </si>
-  <si>
-    <t>240008835</t>
-  </si>
-  <si>
-    <t>06/02/2026 17:38</t>
-  </si>
-  <si>
-    <t>Allianz ; Residência ; Reclamante em nome do Segurado ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; SAC Aberto ; Sim ; Assistência Não Danos ; Assistência Residencial ; Apólice</t>
-  </si>
-  <si>
-    <t>Assistência Residencial</t>
-  </si>
-  <si>
-    <t>SAC Aberto</t>
-  </si>
-  <si>
-    <t>136082709</t>
-  </si>
-  <si>
-    <t>Solicitei um encanador com urgência,  pois o cano estourou e alagou minha casa por dentro, às 14:19h. Tive que fechar todos os registros de entrada de água,  para que não piorasse a situação. Me informaram que o mesmo viria até às 18:40h, porém,  não veio. Me ligaram perguntando se poderia mandar outro, disse que sim. Nada! Detalhe: tenho uma mãe com 87 anos e requer alguns cuidados!_x000D_
-_x000D_
-No dia seguinte, bem cedo, entrei em contato novamente e me informaram que viriam até às 13h. E mais uma vez, nada! Fui obrigada a chamar alguém particular para resolver meu problema,  pois já estava ha 24h sem água,  tendo que pedir ajuda de vizinhos para encher baldes. Pago seguro para quando precisar e nesse caso, NÃO TIVE sequer retorno. O encanador do seguro só chegou em casa às 16:30h, mas aí já estava tudo resolvido. Achei uma falta de respeito com nós,  que pagamos seguro e não é barato e ainda mais, com minha mãe que é  a titular do mesmo.</t>
-  </si>
-  <si>
-    <t>95165543</t>
-  </si>
-  <si>
-    <t>240005093</t>
-  </si>
-  <si>
-    <t>06/02/2026 17:01</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>303742518</t>
-  </si>
-  <si>
-    <t>Sou segurada da Allianz e estou em processo de sinistro com perda total de veículo._x000D_
-_x000D_
-_x000D_
-Há vários dias venho tentando obter, junto à seguradora, uma informação simples e indispensável para dar andamento ao processo:_x000D_
-_x000D_
-o CPF da pessoa física (preposto) do despachante indicado pela Allianz para lavratura de procuração pública no Consulado do Brasil._x000D_
-_x000D_
-_x000D_
-A Allianz já me forneceu apenas o CNPJ do despachante, porém isso não é suficiente para o procedimento exigido._x000D_
-_x000D_
-_x000D_
-Informo que resido atualmente nos Estados Unidos, e por esse motivo: preciso lavrar procuração pública no Consulado do Brasil; o sistema consular exige obrigatoriamente os dados do outorgado pessoa física (CPF), mesmo quando se trata de empresa/despachante; empresas agem por meio de representantes pessoas físicas, o que é padrão jurídico e administrativo._x000D_
-_x000D_
-_x000D_
-Além disso, esclareço que:_x000D_
-_x000D_
-_x000D_
-houve extravio do CRV;_x000D_
-_x000D_
-_x000D_
-não é possível realizar transferência para pessoa jurídica (CNPJ) via ATPV-e;_x000D_
-_x000D_
-_x000D_
-o próprio atendimento da Allianz informou que o procedimento deve seguir por documentos físicos, com procuração pública consular + termo de extravio._x000D_
-_x000D_
-_x000D_
-Apesar de todas essas informações já terem sido repassadas diversas vezes, continuo sendo direcionada apenas para atendimento padrão, sem que a Allianz forneça o CPF do representante/preposto autorizado, o que impede totalmente a lavratura da procuração e paralisa o processo._x000D_
-_x000D_
-_x000D_
-Reforço que:_x000D_
-_x000D_
-_x000D_
-não estou solicitando exceção;_x000D_
-_x000D_
-_x000D_
-não estou solicitando alteração de procedimento;_x000D_
-_x000D_
-_x000D_
-estou apenas solicitando os dados completos da pessoa física que representará o despachante indicado pela própria Allianz, conforme exigido pelo Consulado do Brasil._x000D_
-_x000D_
-_x000D_
-Solicito, portanto, atendimento técnico e resolutivo, com o fornecimento:_x000D_
-_x000D_
-_x000D_
-do nome completo e CPF do preposto/representante autorizado do despachante indicado,_x000D_
-_x000D_
-ou_x000D_
-_x000D_
-_x000D_
-orientação formal alternativa viável e compatível com as exigências consulares._x000D_
-_x000D_
-_x000D_
-A ausência dessa informação tem causado atraso indevido na finalização do processo de sinistro, sem qualquer responsabilidade de minha parte._x000D_
-_x000D_
-_x000D_
-Aguardo retorno objetivo e solução.</t>
-  </si>
-  <si>
-    <t>95160072</t>
-  </si>
-  <si>
-    <t>239989003</t>
-  </si>
-  <si>
-    <t>06/02/2026 14:44</t>
-  </si>
-  <si>
-    <t>Allianz ; Não ; Sem Resposta - Dentro SLA ; Sim ; Repasse Time MindBe ; 1 Segurado ; Sinistro ; Residência ; Sinistro ; Atraso na Análise</t>
-  </si>
-  <si>
-    <t>304851054</t>
-  </si>
-  <si>
-    <t>Este é o segundo ano que pago o seguro residencial da ALLIANZ, dessa vez fechei o "Allianz Residência - Plano VIP" nunca tinha usado o Seguro, e como o Ar condicionado SPLIT parou de funcionar resolvi experimentar._x000D_
-_x000D_
-_x000D_
-Fizemos o Chamado de assistência N 51202162 do dia 20 de Janeiro de 2026_x000D_
-_x000D_
-_x000D_
-1 - Rapidamente mandaram técnico que constatou que houve problema em uma peça específica (compressor). A seguradora nos informou que a peça seria por nossa conta. Conseguimos providenciar a peça e informamos a seguradora. Daqui pra frente foi um sofrimento_x000D_
-_x000D_
-2 - Foi marcado dois agendamentos para a instalação que não deram certo, o segundo solicitou que tivéssemos GÁS e Solda como se isso fossem peças ( como eu poderia ir atrás desse tipo de peça que estão incluídas na mão de obra) Dessa forma foi cancelado novamente a troca da peça._x000D_
-_x000D_
-3 - Solicitamos através da agencia do SICREDI solução para o caso. O pessoal do SICREDI prontamente tentou resolver de maneira que eu contratasse o serviço e que a ALLIANZ reembolsasse o mesmo._x000D_
-_x000D_
-4 - Fornecemos o melhor orçamento que foi de 350 reais, mas eles aprovaram 150 reais o que é um grande absurdo._x000D_
-_x000D_
-_x000D_
-Conclusão, depois de 3 semanas, só incomodo e enrolação. Tornaram o serviço impossível ao solicitarem peças que estão incluídas na mão de obra, o trabalho de agendamento é péssimo e não respeita os horários combinados e o valor da mão de obra está fora da realidade de mercado._x000D_
-_x000D_
-Eu deveria ter concertado por conta mesmo, teria sofrido menos, o fato é que o seguro não funcionou para nós já na primeira tentativa._x000D_
-_x000D_
-Estou deixando minha experiência pública e dando uma última chance para resolverem ou cancelarei o seguro solicitando reembolso pelo procon.</t>
-  </si>
-  <si>
-    <t>95147330</t>
-  </si>
-  <si>
-    <t>239950001</t>
-  </si>
-  <si>
-    <t>06/02/2026 10:04</t>
-  </si>
-  <si>
-    <t>Allianz ; CPF/CNPJ ; Automóvel ; Canal de Atendimento ; Corretor ; 11 Não Cliente ; Não ; Sim ; 1 Ctt Sem Sucesso ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>CPF/CNPJ</t>
-  </si>
-  <si>
-    <t>11 Não Cliente</t>
-  </si>
-  <si>
-    <t>11760891452</t>
-  </si>
-  <si>
-    <t>Realizei uma cotação de seguro por meio do site da seguradora. Após o cadastro, meu número de telefone foi repassado a um consultor, que entrou em contato diretamente pelo meu WhatsApp pessoal informando que o seguro não havia sido aprovado e que retornaria por outro número._x000D_
-_x000D_
-_x000D_
-Posteriormente, esse mesmo consultor passou a me contatar de outro telefone oferecendo seguros de outras seguradoras, o que caracteriza possível desvio de finalidade no uso dos meus dados e abordagem comercial inadequada._x000D_
-_x000D_
-_x000D_
-Ao buscar esclarecimentos no chat oficial da Allianz, a atendente informou que não existia qualquer cotação vinculada ao meu CPF e que eventuais reclamações só poderiam ser registradas por meio do SAC, fornecendo apenas um número 0800, sem solução efetiva para o problema._x000D_
-_x000D_
-_x000D_
-Destaca-se ainda que, ao solicitar que a seguradora orientasse o consultor a cessar os contatos insistentes, fui informado de que ele seria apenas um parceiro e não colaborador. Contudo, a responsabilidade pela escolha, supervisão e conduta de parceiros comerciais é da própria seguradora, especialmente quanto ao tratamento de dados pessoais e à abordagem comercial realizada em seu nome._x000D_
-_x000D_
-_x000D_
-A situação evidencia:_x000D_
-_x000D_
-_x000D_
-Falha grave no atendimento desde a cotação até o suporte ao consumidor;_x000D_
-_x000D_
-Possível uso indevido de dados pessoais, em desacordo com a LGPD;_x000D_
-_x000D_
-Abordagem comercial insistente e oferta de produtos de terceiros após captação de dados em ambiente vinculado à seguradora;_x000D_
-_x000D_
-Ausência de canal eficaz para resolução do problema._x000D_
-_x000D_
-_x000D_
-Diante disso, solicito:_x000D_
-_x000D_
-_x000D_
-Apuração formal do ocorrido e identificação do responsável pelo contato;_x000D_
-_x000D_
-Cessação imediata de qualquer contato comercial não autorizado;_x000D_
-_x000D_
-Esclarecimento sobre o tratamento e compartilhamento dos meus dados pessoais;_x000D_
-_x000D_
-Providências para evitar novas ocorrências com outros consumidores._x000D_
-_x000D_
-_x000D_
-Aguardo retorno formal dentro do prazo legal.</t>
   </si>
 </sst>
 </file>
@@ -1194,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AA8803-373C-4E0C-ABA8-1F171C96DA02}">
-  <dimension ref="A1:AA17"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="3" bestFit="1" customWidth="1" collapsed="1"/>
@@ -1339,16 +1249,16 @@
         <v>35</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>39</v>
@@ -1397,19 +1307,19 @@
         <v>33</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>31</v>
@@ -1424,7 +1334,7 @@
         <v>41</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="W3" s="3" t="s">
         <v>52</v>
@@ -1461,7 +1371,7 @@
         <v>33</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>58</v>
@@ -1473,7 +1383,7 @@
         <v>60</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>31</v>
@@ -1488,13 +1398,13 @@
         <v>41</v>
       </c>
       <c r="V4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="W4" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="W4" s="4" t="s">
+      <c r="X4" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="X4" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="Y4" s="3" t="s">
         <v>26</v>
@@ -1504,13 +1414,13 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>30</v>
@@ -1519,7 +1429,7 @@
         <v>31</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>33</v>
@@ -1531,34 +1441,34 @@
         <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>39</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="P5" s="3" t="s">
         <v>41</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="W5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="X5" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="X5" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="Y5" s="3" t="s">
         <v>26</v>
@@ -1568,13 +1478,13 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>30</v>
@@ -1583,7 +1493,7 @@
         <v>31</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>33</v>
@@ -1592,16 +1502,16 @@
         <v>34</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>34</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>31</v>
@@ -1610,19 +1520,19 @@
         <v>39</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="P6" s="3" t="s">
         <v>41</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Y6" s="3" t="s">
         <v>26</v>
@@ -1632,13 +1542,13 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>30</v>
@@ -1647,25 +1557,25 @@
         <v>31</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>31</v>
@@ -1680,13 +1590,13 @@
         <v>41</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="W7" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="X7" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="X7" s="4" t="s">
-        <v>88</v>
       </c>
       <c r="Y7" s="3" t="s">
         <v>26</v>
@@ -1696,13 +1606,13 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>30</v>
@@ -1711,7 +1621,7 @@
         <v>31</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>33</v>
@@ -1720,16 +1630,16 @@
         <v>34</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>31</v>
@@ -1744,13 +1654,13 @@
         <v>41</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>26</v>
@@ -1760,13 +1670,13 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>30</v>
@@ -1775,25 +1685,25 @@
         <v>31</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>31</v>
@@ -1802,7 +1712,7 @@
         <v>39</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>41</v>
@@ -1811,10 +1721,10 @@
         <v>42</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>26</v>
@@ -1824,13 +1734,13 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>30</v>
@@ -1839,7 +1749,7 @@
         <v>31</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>33</v>
@@ -1851,16 +1761,16 @@
         <v>35</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>39</v>
@@ -1872,13 +1782,13 @@
         <v>41</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>26</v>
@@ -1886,13 +1796,13 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>30</v>
@@ -1901,25 +1811,25 @@
         <v>31</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>31</v>
@@ -1928,7 +1838,7 @@
         <v>39</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="P11" s="3" t="s">
         <v>41</v>
@@ -1969,22 +1879,22 @@
         <v>33</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="M12" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>39</v>
@@ -1996,13 +1906,13 @@
         <v>41</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="X12" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>26</v>
@@ -2010,13 +1920,13 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>30</v>
@@ -2025,25 +1935,25 @@
         <v>31</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>34</v>
       </c>
       <c r="K13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>31</v>
@@ -2058,12 +1968,12 @@
         <v>41</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="W13" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="X13" s="4" t="s">
+      <c r="X13" s="3" t="s">
         <v>129</v>
       </c>
       <c r="Y13" s="3" t="s">
@@ -2093,22 +2003,22 @@
         <v>33</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="J14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="M14" s="3" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>39</v>
@@ -2120,7 +2030,7 @@
         <v>41</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="W14" s="4" t="s">
         <v>136</v>
@@ -2133,190 +2043,33 @@
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="W15" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="X15" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y15" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="W15" s="4"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V16" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="W16" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="X16" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y16" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="W17" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="X17" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y17" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="W16" s="4"/>
+      <c r="X16" s="4"/>
+    </row>
+    <row r="17" spans="23:24" x14ac:dyDescent="0.2">
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+    </row>
+    <row r="18" spans="23:24" x14ac:dyDescent="0.2">
+      <c r="W18" s="4"/>
+    </row>
+    <row r="19" spans="23:24" x14ac:dyDescent="0.2">
+      <c r="W19" s="4"/>
+      <c r="X19" s="4"/>
+    </row>
+    <row r="20" spans="23:24" x14ac:dyDescent="0.2">
+      <c r="W20" s="4"/>
+      <c r="X20" s="4"/>
+    </row>
+    <row r="21" spans="23:24" x14ac:dyDescent="0.2">
+      <c r="W21" s="4"/>
+    </row>
+    <row r="22" spans="23:24" x14ac:dyDescent="0.2">
+      <c r="W22" s="4"/>
+      <c r="X22" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AN9" xr:uid="{D3AA8803-373C-4E0C-ABA8-1F171C96DA02}"/>

--- a/Treinamento/GestaoReclamacao.xlsx
+++ b/Treinamento/GestaoReclamacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72F8FDD-BFBA-4AED-98F3-AB2438669464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1F10E4-4B84-45F7-BC74-C4B7899A62ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B1A77FD5-2AD3-4458-ACB3-7F19D1A3340A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="141">
   <si>
     <t>Id HugMe</t>
   </si>
@@ -122,6 +122,460 @@
     <t>Processar</t>
   </si>
   <si>
+    <t>95438805</t>
+  </si>
+  <si>
+    <t>240504799</t>
+  </si>
+  <si>
+    <t>11/02/2026 22:05</t>
+  </si>
+  <si>
+    <t>Não respondido</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Pagamento ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Allianz</t>
+  </si>
+  <si>
+    <t>Apólice</t>
+  </si>
+  <si>
+    <t>Automóvel</t>
+  </si>
+  <si>
+    <t>Pagamento</t>
+  </si>
+  <si>
+    <t>1 Segurado</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Repasse Time MindBe</t>
+  </si>
+  <si>
+    <t>Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Juliana</t>
+  </si>
+  <si>
+    <t>133887801</t>
+  </si>
+  <si>
+    <t>Cobrança indevida dupla do mesmo boleto. Foi pago e deposi debitado automaticamente. _x000D_
+_x000D_
+Preciso do reembolso urgente</t>
+  </si>
+  <si>
+    <t>95437357</t>
+  </si>
+  <si>
+    <t>240500211</t>
+  </si>
+  <si>
+    <t>11/02/2026 21:06</t>
+  </si>
+  <si>
+    <t>Allianz ; Vida / Acidentes Pessoais ; Apólice ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Assistência Não Danos ; Assistencia Funeral</t>
+  </si>
+  <si>
+    <t>Vida / Acidentes Pessoais</t>
+  </si>
+  <si>
+    <t>Assistência Não Danos</t>
+  </si>
+  <si>
+    <t>Assistencia Funeral</t>
+  </si>
+  <si>
+    <t>127621229</t>
+  </si>
+  <si>
+    <t>No dia 21/12/2025 meu pai faleceu, neste sentido liguei na Allianz para solicitar os serviços de funerária cobertos pela prestadora de serviço que gerou o protocolo/Sinistro 50948352, como a minha irmã possui um plano funerário de atendimento com o grupo Serra ao qual a atendente da Allianz informou não possuir parceria, mas para seguir com os serviços necessarios para posterior reembolso, assim fizemos. Seguindo com o orientado através do atendimento do sinistro, preenchi o formulário e encaminhei toda a documentação necessária no dia 09/01/2026. Deste momento para a frente tive que ligar diversas vezes para cobrar o andamento do reembolso, que foi respondido por e-mail no dia 25/01/2026 que o documento nota fiscal do serviço funerário não fora aceito pois não continha o desmembramento dos serviços, algo que eu não tinha sido orientado pelo atendimento inicial e que não tenho ingerência no formato que a empresa emite sua nota fiscal. Sendo assim solicitei o documento ao grupo Serra o com a descriminação dos serviços, enviei no dia 26/01 juntamente com o comprovante de residência do falecido, meu pai, também solicitado. Contudo, até o momento não obtive retorno da Allianz, mesmo falando com uma atendente via telefone na semana do envio. O descaso com o atendimento está me deixando abalado emocionalmente, visto a situação da perda de um ente querido e também por não ser atendido de forma ágil e adequada para um serviço contratado que é para resolver e não para criar mais dificuldades.</t>
+  </si>
+  <si>
+    <t>95431392</t>
+  </si>
+  <si>
+    <t>240482077</t>
+  </si>
+  <si>
+    <t>11/02/2026 17:55</t>
+  </si>
+  <si>
+    <t>Allianz ; Automóvel ; Sinistro ; CPF/CNPJ ; Análise Sinistro ; 11 Não Cliente ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>CPF/CNPJ</t>
+  </si>
+  <si>
+    <t>Sinistro</t>
+  </si>
+  <si>
+    <t>Análise Sinistro</t>
+  </si>
+  <si>
+    <t>11 Não Cliente</t>
+  </si>
+  <si>
+    <t>19817161</t>
+  </si>
+  <si>
+    <t>Adquiri um veículo cruze na data de Leilão 23/12/2025 número de leilão: 9712 lote: 82  Ltz 2021/2022 pelo leiloeiro copart leilões, no edital informava que o IPVA seria por conta da comitente (Allianz Seguros) sendo pago até a data do vencimento. O prazo para pagamento venceu e o pagamento do IPVA ainda não foi realizado. Ao acionar o canal de pós-venda e sac sou orientado pela copart a aguardar, uma vez que já foi aberto um chamado. Estou sem documento sem como transferir, sem como andar no carro preciso urgentemente desse ipva pago!!!!</t>
+  </si>
+  <si>
+    <t>95431228</t>
+  </si>
+  <si>
+    <t>240481597</t>
+  </si>
+  <si>
+    <t>11/02/2026 17:50</t>
+  </si>
+  <si>
+    <t>Allianz ; CPF/CNPJ ; Automóvel ; Sinistro ; Análise Sinistro ; 11 Não Cliente ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>468540338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Em 2021 minha moto foi roubada, fiz boletim de ocorrência e recebi indenização por perda total pela seguradora Sua América._x000D_
+_x000D_
+Mesmo assim, anos depois apareceu um protesto indevido no meu nome referente ao IPVA do veículo, no valor de R$ 234, causando negativação no Serasa._x000D_
+_x000D_
+Essa cobrança é irregular, pois após a indenização a responsabilidade pelo veículo deixou de ser minha._x000D_
+_x000D_
+Solicito com urgência:_x000D_
+_x000D_
+1.Regularização da baixa do veículo junto ao DETRAN_x000D_
+_x000D_
+2.Cancelamento do débito de IPVA_x000D_
+_x000D_
+3.Retirada imediata do protesto no Serasa_x000D_
+_x000D_
+4.Comprovante formal da regularização_x000D_
+_x000D_
+Anexo documentos que comprovam roubo e indenização._x000D_
+_x000D_
+</t>
+  </si>
+  <si>
+    <t>95430389</t>
+  </si>
+  <si>
+    <t>240479279</t>
+  </si>
+  <si>
+    <t>11/02/2026 17:29</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Reclamante em nome do Segurado ; Análise Sinistro</t>
+  </si>
+  <si>
+    <t>Reclamante em nome do Segurado</t>
+  </si>
+  <si>
+    <t>303609456</t>
+  </si>
+  <si>
+    <t>Não consigo entrar em contato pelos canais  da seguradora. Foi indicado no sinistro do meu veiculo que será trocado duas longarinas do veiculo. O que me deixa recioso, primeiro por questões de segurança já que é um componente importante do veiculo que pode impactar diretamente na segurança,  a seguradora não consegue garantir que meu veiculo terá as mesmas condições de segurança de quando comprei, segundo porque a seguradora está deprenciando meu veiculo com essa alteração. Dado que a troca dessa peça desvaloriza o valor de mercado do veiculo. O que não faz sentido já que meu seguro é feito para proteger meus bens.</t>
+  </si>
+  <si>
+    <t>95428843</t>
+  </si>
+  <si>
+    <t>240474983</t>
+  </si>
+  <si>
+    <t>11/02/2026 16:53</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>305327919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prezados,_x000D_
+_x000D_
+_x000D_
+No dia 03 de fevereiro de 2026, fui vítima de furto da minha motocicleta. Na mesma data, registrei o Boletim de Ocorrência e entrei em contato com a seguradora para dar início ao processo de sinistro._x000D_
+_x000D_
+_x000D_
+Na ocasião, fui informado de que receberia um e-mail no prazo de 24 horas com as orientações necessárias. No entanto, o e-mail foi encaminhado apenas no dia 09 de fevereiro, ultrapassando o prazo informado._x000D_
+_x000D_
+_x000D_
+Após o recebimento das solicitações de documentação, encontrei dificuldades especialmente em relação ao ATPV, que tem sido meu maior contratempo até o momento. Tenho me deslocado diversas vezes, arcando com custos de transporte por aplicativo, para tentar resolver a situação. Contudo, conforme informado pelo Detran, não é possível emitir o ATPV devido à restrição de furto registrada no veículo._x000D_
+_x000D_
+_x000D_
+Além disso, em contato telefônico com a seguradora, a ligação foi interrompida no momento em que eu seria transferido ao setor responsável, impossibilitando a continuidade do atendimento._x000D_
+_x000D_
+_x000D_
+Diante de todos esses transtornos, solicito, com urgência, uma orientação clara e uma solução efetiva para o meu caso, a fim de que o processo seja resolvido o mais breve possível._x000D_
+_x000D_
+_x000D_
+Fico no aguardo de um retorno imediato._x000D_
+_x000D_
+_x000D_
+Atenciosamente,_x000D_
+_x000D_
+</t>
+  </si>
+  <si>
+    <t>95425563</t>
+  </si>
+  <si>
+    <t>240465431</t>
+  </si>
+  <si>
+    <t>11/02/2026 15:38</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Canal de Atendimento ; Corretor ; Reclamante em nome do Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Canal de Atendimento</t>
+  </si>
+  <si>
+    <t>Corretor</t>
+  </si>
+  <si>
+    <t>131443117</t>
+  </si>
+  <si>
+    <t>Venho por meio desta comunicar minha indignação com a allianz, sou cliente, e fui renovar o seguro com minha corretora e o preço aumentou, a tendência ao não usar o seguro é os anos se passarem é diminuir o valor, mas não o valor subiu, aí como continuaremos com a fidelidade se a allianz não fideliza o cliente, procuramos andar da melhor forma possível, pois sei que se usar o seguro no ano seguinte tud aumenta, mais mesmo com esses cuidados o seguro só aumenta e quando entro em contato com a allianz a única resposta que obtive é: cote em outros lugares pra ver se consegue um preço melhor, penso que reter o cliente é uma das formas de continuar no mercado, mas sendo assim vou sair e não indicarei pois já se preocupam em conseguir preços atrativos para quem já é cliente e se quer usou o seguro.</t>
+  </si>
+  <si>
+    <t>95424941</t>
+  </si>
+  <si>
+    <t>240463611</t>
+  </si>
+  <si>
+    <t>11/02/2026 15:24</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Reclamante em nome do Segurado</t>
+  </si>
+  <si>
+    <t>298810467</t>
+  </si>
+  <si>
+    <t>Terceiro já foi atendido no sinistro s298810467 referente aos danos da moto, entretanto o mesmo terceiro sofreu fraturas e solicita cobertura IPA, mesmo tendo atendido a moto, havendo culpa do motorista segurado no BO e havendo notícia da cidade com a van do segurado em cima da moto a seguradora não dá sequencia no sinistro, pois solicita novamente uma carta de culpabilidade do segurado. Todos os documentos do terceiro foram enviados em 30/09/2025 , mas sinistro está parado por seguradora solicitar uma nova declaração de culpabilidade do mesmo segurado que já atendeu a moto do mesmo terceiro no mesmo sinistro de mesmo número. Favor dar andamento nas tratativas dos danos corporais com urgencia e retornar ao procurador em e-mail da reclamação e procuração.</t>
+  </si>
+  <si>
+    <t>95424416</t>
+  </si>
+  <si>
+    <t>240462415</t>
+  </si>
+  <si>
+    <t>11/02/2026 15:15</t>
+  </si>
+  <si>
+    <t>Allianz ; Residência ; Sinistro ; Sinistro ; Análise Sinistro ; 1 Segurado ; OUV Antes do RA ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Residência</t>
+  </si>
+  <si>
+    <t>OUV Antes do RA</t>
+  </si>
+  <si>
+    <t>303511857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Título: Sinistro negado + falha na assistência 24h + prejuízo material  Apólice Allianz 5177202532140388993_x000D_
+_x000D_
+_x000D_
+Descrição da reclamação:_x000D_
+_x000D_
+_x000D_
+Venho registrar minha insatisfação formal com a Allianz Seguros referente à apólice abaixo:_x000D_
+_x000D_
+_x000D_
+INFORMAÇÕES DO SEGURO_x000D_
+_x000D_
+Endereço do local segurado: Avenida Vereador Carlito Cordeiro, 2315  Jardim Botânico  Uberlândia/MG  CEP 38410-665_x000D_
+_x000D_
+Produto | Ramo: 14  Residência Digital_x000D_
+_x000D_
+Tipo de residência: Casa Condomínio Habitual Alvenaria_x000D_
+_x000D_
+Tipo de contratação: Edifício + Conteúdo_x000D_
+_x000D_
+Limite Máximo de Garantia: R$ 1.500.000,00_x000D_
+_x000D_
+Proposta n: 134296787_x000D_
+_x000D_
+Apólice n: 5177202532140388993_x000D_
+_x000D_
+Versão da tabela: 43/42.05_x000D_
+_x000D_
+Condições gerais: 02/2025_x000D_
+_x000D_
+Vigência: 04/09/2025 a 04/09/2026_x000D_
+_x000D_
+_x000D_
+Número do Sinistro: 303511857_x000D_
+_x000D_
+Protocolo Assistência 24h: 51159748_x000D_
+_x000D_
+_x000D_
+_x000D_
+_x000D_
+No momento da contratação do seguro, deixei claras minhas necessidades, especialmente cobertura para problemas oriundos de chuva, incluindo danos ao gesso e infiltrações. Tenho evidências de que me foi assegurado que esse tipo de evento estaria coberto._x000D_
+_x000D_
+_x000D_
+Inclusive, eu estava fechando com o Santander, mas optei pela Allianz por recomendação da corretora, que afirmou que o produto seria superior e atenderia plenamente minhas necessidades._x000D_
+_x000D_
+_x000D_
+No dia 08/12, houve forte chuva com vento e granizo em Uberlândia, causando infiltração em minha residência. Ao acionar o seguro (sinistro n 303511857), tive a cobertura negada, com base em cláusula contratual restritiva apresentada somente no momento do sinistro._x000D_
+_x000D_
+_x000D_
+Na contratação a cobertura existia; quando precisei utilizar, surgiu uma cláusula limitadora que esvaziou a garantia prometida. Isso viola os princípios da boa-fé, transparência e equilíbrio contratual previstos no Código de Defesa do Consumidor._x000D_
+_x000D_
+_x000D_
+Além disso, enfrentei sérias falhas na assistência 24h (protocolo 51159748):_x000D_
+_x000D_
+Em 15/01, o prestador informou que não poderia atuar porque seria necessário quebrar;_x000D_
+_x000D_
+Em 20/01, outro profissional compareceu e disse não estar autorizado;_x000D_
+_x000D_
+Ocorreram sucessivos reagendamentos com não comparecimento;_x000D_
+_x000D_
+Apenas em 04/02, houve a quebra da calçada, mas o problema não foi solucionado, sob alegação de que seria responsabilidade do DMAE._x000D_
+_x000D_
+_x000D_
+O mais grave: quando o DMAE compareceu, informou que bastaria verificar que o relógio do hidrômetro não estava rodando para constatar que o problema era de responsabilidade da concessionária._x000D_
+_x000D_
+_x000D_
+Ou seja, houve erro de diagnóstico básico por parte do prestador da seguradora, que resultou na quebra da minha calçada de forma indevida, gerando prejuízo material direto, deixando o local danificado e sem reparo._x000D_
+_x000D_
+_x000D_
+Como consumidor, não tenho obrigação de conhecimento técnico para diferenciar responsabilidades entre seguradora e concessionária pública. Esperava que a Allianz prestasse serviço técnico adequado e evitasse danos desnecessários à minha propriedade._x000D_
+_x000D_
+_x000D_
+Diante de todo o ocorrido, exijo:_x000D_
+_x000D_
+1.Revisão imediata da negativa do sinistro referente à chuva e granizo;_x000D_
+_x000D_
+2.Posicionamento formal e técnico sobre a cobertura contratada;_x000D_
+_x000D_
+3.Ressarcimento do prejuízo causado pela quebra indevida da calçada;_x000D_
+_x000D_
+4.Solução definitiva da demanda aberta na assistência._x000D_
+_x000D_
+_x000D_
+Caso não haja solução adequada, buscarei meus direitos judicialmente, inclusive com pedido de reparação por danos materiais e morais, diante da falha na prestação do serviço e da frustração contratual._x000D_
+_x000D_
+_x000D_
+Possuo fotos, registros, protocolos e evidências da contratação e dos atendimentos realizados._x000D_
+_x000D_
+_x000D_
+Aguardo solução urgente._x000D_
+_x000D_
+</t>
+  </si>
+  <si>
+    <t>95416604</t>
+  </si>
+  <si>
+    <t>240441879</t>
+  </si>
+  <si>
+    <t>11/02/2026 12:36</t>
+  </si>
+  <si>
+    <t>Allianz ; Automóvel ; Sinistro ; Não ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Sim ; CPF/CNPJ ; 11 Não Cliente ; Fornecimento de Peças</t>
+  </si>
+  <si>
+    <t>Fornecimento de Peças</t>
+  </si>
+  <si>
+    <t>301949664</t>
+  </si>
+  <si>
+    <t>Sofri um sinistro no dia 01/11/2025 e já vai fazer 4 meses desde o início do sinistro e até hoje o carro segue na oficina, a oficina diz que está aguardando as peças chegarem, e que essas peças são fornecidas pela a seguradora, em resumo estou a 4 meses sem carro por conta de desorganização da seguradora.</t>
+  </si>
+  <si>
+    <t>95408109</t>
+  </si>
+  <si>
+    <t>240418963</t>
+  </si>
+  <si>
+    <t>11/02/2026 10:00</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Empresa ; Assistência Não Danos ; Assistencia Empresa ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Empresa</t>
+  </si>
+  <si>
+    <t>Assistencia Empresa</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>134703470</t>
+  </si>
+  <si>
+    <t>Tenho tentado contato incessantemente com a Allianz Seguradora, porém não estou obtendo qualquer retorno efetivo. Nenhum atendente consegue fornecer uma resposta concreta, e o atendimento se resume a um verdadeiro jogo de empurra._x000D_
+_x000D_
+_x000D_
+No chat, quando finalmente um atendente humano inicia o atendimento, a conversa simplesmente é interrompida sem qualquer conclusão._x000D_
+_x000D_
+_x000D_
+No dia 12/12/2025, durante o apagão ocorrido em São Paulo, um técnico da Allianz compareceu ao nosso estabelecimento (somos proprietárias de uma confeitaria). Na ocasião, suspeitávamos que uma de nossas geladeiras havia queimado, porém o técnico constatou que o problema era que apenas uma fase da nossa energia elétrica havia sido religada, sendo que nosso sistema é trifásico._x000D_
+_x000D_
+_x000D_
+O profissional foi extremamente atencioso, gentil e prestou todas as orientações necessárias para que pudéssemos tratar a situação junto a Enel. Entretanto, precisamos apenas do laudo que comprove a visita técnica e o diagnóstico realizado no local, documento este que não conseguimos obter._x000D_
+_x000D_
+_x000D_
+Já realizamos inúmeras ligações, tentativas de contato pelo chat, acessos a área do cliente, além de contato com a central de emergência 24h e outros telefones da Allianz, porém até o momento ninguém localiza o sinistro referente a visita técnica, tampouco apresenta qualquer solução._x000D_
+_x000D_
+_x000D_
+A falta de retorno e de organização no atendimento tem nos causado grande transtorno, especialmente considerando que dependemos desse laudo para apresentar a advogada._x000D_
+_x000D_
+_x000D_
+Aguardo um posicionamento urgente._x000D_
+_x000D_
+_x000D_
+Cristina</t>
+  </si>
+  <si>
+    <t>95406846</t>
+  </si>
+  <si>
+    <t>240415623</t>
+  </si>
+  <si>
+    <t>11/02/2026 09:36</t>
+  </si>
+  <si>
+    <t>Allianz ; Automóvel ; Apólice ; Carro Reserva ; Assistência Não Danos ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; 1 Segurado</t>
+  </si>
+  <si>
+    <t>Carro Reserva</t>
+  </si>
+  <si>
+    <t>135381358</t>
+  </si>
+  <si>
+    <t>Sou segurado allianz e me decepcionei com uma resposta obtida por telefone ontem. Acabei me envolvendo num incidente onde uma pessoa bateu no meu carro, ela acionou o seguro dela e agendamos o serviço entre os dia 24/02 e 27/02. Entrei em contato com minha segurado, pois necessito de um veículo para me deslocar para o trabalho, solicitando carro reserva. Fui informado que, devido ao valor do serviço ter ficado menor que minha franquia, eu não tinha direito a carro reserva. Achei a resposta absurda, qual a necessidade de eu ter um seguro? O que vale é o valor da franquia ou a necessidade do cliente?</t>
+  </si>
+  <si>
     <t>95405618</t>
   </si>
   <si>
@@ -131,43 +585,13 @@
     <t>11/02/2026 09:07</t>
   </si>
   <si>
-    <t>Não respondido</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
     <t>Allianz ; Sinistro ; Sinistro ; Automóvel ; Análise Sinistro ; 1 Segurado ; Repasse Time MindBe ; SAC Aberto ; Sim ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
-    <t>Allianz</t>
-  </si>
-  <si>
-    <t>Sinistro</t>
-  </si>
-  <si>
-    <t>Automóvel</t>
-  </si>
-  <si>
-    <t>Análise Sinistro</t>
-  </si>
-  <si>
-    <t>1 Segurado</t>
-  </si>
-  <si>
     <t>SAC Aberto</t>
   </si>
   <si>
-    <t>Sim</t>
-  </si>
-  <si>
-    <t>Repasse Time MindBe</t>
-  </si>
-  <si>
-    <t>Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Juliana</t>
+    <t>Andreza</t>
   </si>
   <si>
     <t>303478531</t>
@@ -176,517 +600,24 @@
     <t>Queria registrar uma reclamação, sobre essa seguradora. Houve um sinistro dia 14 de dezembro, meu carro foi entregue dia 16 de janeiro, rateando e com a luz do freio ABS ligada.  Segundo o proprietário da oficina, era a gasolina, portanto, coloquei a gasolina aditivada, e o carro permaneceu na garagem. Em fevereiro quando iniciou se o período de aulas, o carro continuou com o mesmo problema, perdendo força, meu marido viu que não havia líquido de arrefecimento,voltei na oficina, e colocaram o líquido,continuou com o problema, meu esposo viu q a mangueira de entrada de ar do motor estava rasgada( acreditamos q seja pela batida,ou por troca do peças) voltei na oficina, o dono da oficina passou FITA ISOLANTE, e o carro continua na garagem, sem poder andar. O seguro foi informado desde o dia 02 de fevereiro, dos diversos acontecimentos, pediu 48 horas venceu, pediu 24 horas venceu, agora pediu 7 dias. e nada da reabertura de vistoria. Meu carro chegou na oficina ANDANDO e saiu sem condições de andar, quase fundiu o motor por irresponsabilidade da oficina, e a seguradora não faz nada a respeito. Nem em contato comigo ela entrou. O valor foi pago de forma única e as parcelas do seguro continuam a ser descontadas, mas meu carro está parado sem condições de uso .. Um absurdo esse descaso.</t>
   </si>
   <si>
-    <t>95399798</t>
-  </si>
-  <si>
-    <t>240394811</t>
-  </si>
-  <si>
-    <t>10/02/2026 23:04</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; Reclamante em nome do Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Apólice</t>
-  </si>
-  <si>
-    <t>Assistência Não Danos</t>
-  </si>
-  <si>
-    <t>Guincho</t>
-  </si>
-  <si>
-    <t>Reclamante em nome do Segurado</t>
-  </si>
-  <si>
-    <t>130860520</t>
-  </si>
-  <si>
-    <t>Fiz uma solicitacao hoje 10/02 as 21/41 para allianz com uma atendente totalmente despreparada e mal educada. Vanessa o nome dela. Numero do protocolo 51385189_x000D_
-_x000D_
-Ela simplesmente acionou o guincho para sao paulo (capital) sendo que eu moro em_x000D_
-_x000D_
-Paulinia. O pessoal do guincho de sao paulo me ligou e eu disse q estava errado. Nao era o endereco de la e sim daqui de paulinia! Repeti mil vezes o cep e falei nao que nao era em_x000D_
-_x000D_
-Sp apos a vanessa me perguntar! Estou esperando um simples servico de recarga na bateria ate_x000D_
-_x000D_
-Agora 23:02. Um simples chamado pra um_x000D_
-_x000D_
-Caos desse, pq o pessoal_x000D_
-_x000D_
-De sao paulo perde tempo e eu tambem!</t>
-  </si>
-  <si>
-    <t>95398168</t>
-  </si>
-  <si>
-    <t>240389855</t>
-  </si>
-  <si>
-    <t>10/02/2026 21:55</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>132245637</t>
-  </si>
-  <si>
-    <t>Estou vindo aqui pelo descaso da seguradora @allianzbrasil , mais de duas horas de espera e não chegou o guincho e nem tão pouco o transporte, fiquei parado na beira da rodovia na chuva , fiz o contato com a seguradora e eles me disseram que não estavam conseguindo contato com nenhum prestador de serviço da seguradora, tive que solicitar um guincho particular para poder chegar até em casa, você paga o seguro para ser socorrido e quando precisa é a mesma coisa que nada  estou extremamente desapontado !!</t>
-  </si>
-  <si>
-    <t>95395786</t>
-  </si>
-  <si>
-    <t>240382337</t>
-  </si>
-  <si>
-    <t>10/02/2026 20:33</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 2 Terceiro do Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>2 Terceiro do Sinistro</t>
-  </si>
-  <si>
-    <t>301956038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sou terceiro vítima de sinistro causado por segurado da Allianz Seguros S.A., ocorrido em 14/10/2025, sinistro n 301956038._x000D_
-_x000D_
-Em razão da demora injustificada da seguradora na condução do sinistro (autorização dos reparos somente em 14/11/2025; conclusão dos reparos em 01/12/2025, mas a oficina somente liberou em 17/12/2025, pois a Allianz não autorizou a liberação do veículo),  permaneci privado do uso da minha motocicleta, sendo obrigado a alugar uma moto de forma particular para atuar em minha atividade profissional de promotor de merchandising, onde preciso frequentar várias lojas de varejo e atacado, por dia, em diferentes cidades para realizar o atendimento contratado._x000D_
-_x000D_
-O gasto total com o aluguel foi cerca de R$ 2.000,00, devidamente comprovado por contrato, comprovantes bancários e recibos assinados._x000D_
-_x000D_
-Entretanto, de forma unilateral e sem apresentar critério objetivo ou base contratual, a Allianz efetuou o reembolso de apenas R$ 1.000,00 em 10/02/2026, deixando saldo indevido de R$ 1.000,00, o que configura  apenas reparação parcial do dano._x000D_
-_x000D_
-Diante disso, requeiro o pagamento integral do valor restante de R$ 1.000,00, referente ao prejuízo suportado em razão da demora da seguradora, pois só pude usufruir da minha motocicleta depois de mais de dois meses após o sinistro. E isso ainda porque a oficina, diante da demora injustificada da seguradora, optou por liberar a motocicleta por decisão própria, o que evidencia falha na condução do sinistro e descaso por parte da Allianz._x000D_
-_x000D_
-_x000D_
-</t>
-  </si>
-  <si>
-    <t>95393940</t>
-  </si>
-  <si>
-    <t>240376813</t>
-  </si>
-  <si>
-    <t>10/02/2026 19:38</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Sim ; Repasse Time MindBe ; SAC Aberto ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>305334316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa noite,_x000D_
-_x000D_
-_x000D_
-Venho, por meio do Reclame Aqui, registrar formalmente minha insatisfação com todo o ocorrido envolvendo meu veículo e as sucessivas falhas no atendimento prestado pela Allianz Seguros._x000D_
-_x000D_
-_x000D_
-Abaixo, descrevo os fatos em ordem cronológica:_x000D_
-_x000D_
-_x000D_
-03/02/2026  Realizei o primeiro contato com a seguradora para solicitação de guincho, em razão de um acidente com o veículo. A solicitação foi feita via WhatsApp, conforme imagem anexada._x000D_
-_x000D_
-_x000D_
-04/02/2026  Abertura do sinistro pelo aplicativo, com o envio de todas as informações solicitadas e fotos do veículo._x000D_
-_x000D_
-_x000D_
-06/02/2026  Recebi um SMS informando que o veículo estava sendo encaminhado para a oficina parceira da seguradora. No entanto, identifiquei divergência na cidade informada: constava Itapevi, quando o correto sempre foi Carapicuíba, conforme informado desde o primeiro atendimento._x000D_
-_x000D_
-Entrei em contato com a seguradora e solicitei a correção do endereço, que foi realizada pela atendente. Em razão desse erro, o veículo constou como ausente na primeira tentativa de vistoria. Fui informada de que o veículo seria entregue corretamente no dia 09/02/2026, no endereço correto._x000D_
-_x000D_
-_x000D_
-09/02/2026  Recebi contato telefônico da seguradora informando que o veículo não seria entregue nesta data, mas que a entrega seria priorizada para o dia seguinte._x000D_
-_x000D_
-_x000D_
-10/02/2026  Entrei novamente em contato para confirmar a entrega do veículo. Fui informada de que a entrega ocorreria até o meio-dia. Pouco depois, recebi uma ligação informando que o guincho estava com meu carro no endereço correto, porém havia outro veículo sendo vistoriado antes do meu._x000D_
-_x000D_
-Neste momento, fui informada de que o guincho não poderia aguardar por muito tempo e que eu poderia ser cobrada pelo tempo de espera  mesmo se tratando de uma oficina parceira da própria Allianz, e não uma mecânica escolhida por mim. Após eu questionar essa informação, o discurso do atendente mudou, informando que aguardaria por se tratar de parceiro da Allianz._x000D_
-_x000D_
-_x000D_
-Ainda no mesmo dia, recebi novo contato da seguradora informando que o veículo havia sido recusado, sem qualquer explicação detalhada, sendo apenas orientada a entrar em contato com a central de atendimento. Ao fazê-lo, fui informada de que, normalmente, nesses casos, a recusa ocorre por perda total, mas que eu deveria confirmar junto à central de sinistros._x000D_
-_x000D_
-_x000D_
-Em novo contato com o setor de sinistros, fui informada de que o veículo novamente constou como ausente e que uma nova vistoria foi reagendada para o dia 11/02/2026, no mesmo local._x000D_
-_x000D_
-_x000D_
-Diante de todo esse desgaste, registrei a reclamação n 260002204, protocolo 2624491400, junto à Ouvidoria da Allianz._x000D_
-_x000D_
-_x000D_
-Diante disso, questiono:_x000D_
-_x000D_
-_x000D_
-Onde está o meu veículo?_x000D_
-_x000D_
-_x000D_
-Como o carro pode ser considerado ausente se está em posse da seguradora?_x000D_
-_x000D_
-_x000D_
-Qual a dificuldade em encaminhar corretamente o veículo para a vistoria?_x000D_
-_x000D_
-_x000D_
-Ressalto ainda que precisei solicitar carro reserva e dependo do laudo técnico para não ser posteriormente cobrada pelos custos desse serviço. Como é possível não ter a assistência adequada de um serviço que está contratado, pago e em dia?_x000D_
-_x000D_
-_x000D_
-Até quando meu processo continuará sendo atrasado?_x000D_
-_x000D_
-Quanto tempo mais terei que aguardar?_x000D_
-_x000D_
-_x000D_
-O que tenho enfrentado é excesso de burocracia, falhas operacionais e total falta de clareza nas informações prestadas._x000D_
-_x000D_
-_x000D_
-Aguardo retorno e uma solução efetiva com urgência._x000D_
-_x000D_
-</t>
-  </si>
-  <si>
-    <t>95393936</t>
-  </si>
-  <si>
-    <t>240376739</t>
-  </si>
-  <si>
-    <t>10/02/2026 19:37</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; 2 Terceiro do Sinistro</t>
-  </si>
-  <si>
-    <t>304935548</t>
-  </si>
-  <si>
-    <t>Sou Uber no dia 23/01/2026 estava em deslocamento com 3 passageiros para guarda do Embaú pela rua Aderbal Ramos da Silva , com meu veículo Logan ivy9c86 quando do nada invadiu a pista contraria o automóvel Onix jcr3b50 , após isto o Onix rodopiou e ainda acertou outro veículo uma spin ixa7b28 já no primeiro dia levei o carro para oficina através de guincho pois o mesmo não mais rodou pelo dano causado , entrou em contato com o segurado ao qual falou que já havia aberto o sinistro junto a Allianz , desde então eu Cristiano venho cobrando o concerto do carro ou pagamento do mesmo , (que no caso deu como perca total ) todo os dias ficam enrolando e pedindo documentos , e eu como trabalho de Uber estou sem trabalhar desde então , sem ao menos ter o direito ao lucros cessantes pois estou sem ainha fonte de renda , e as contas estão vencendo , venho por meio desta cobrar uma solução junto a Allianz, meu carro concertado ou o dinheiro do mesmo ou um carro para mim voltar a trabalhar ou os lucros cessantes para mim me manter</t>
-  </si>
-  <si>
-    <t>95393203</t>
-  </si>
-  <si>
-    <t>240374545</t>
-  </si>
-  <si>
-    <t>10/02/2026 19:15</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; 1 Segurado ; Sim ; Repasse Time MindBe ; Sac Enc ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Residência</t>
-  </si>
-  <si>
-    <t>Assistência Residencial</t>
-  </si>
-  <si>
-    <t>Sac Enc</t>
-  </si>
-  <si>
-    <t>134045965</t>
-  </si>
-  <si>
-    <t>Em 12.01.2026 realizei um chamado de assistência 24h para encanador junto à Allianz Seguros Residenciais e a corretora diz que o prestador esteve no local, porém não tentou um contato telefônico comigo._x000D_
-_x000D_
-_x000D_
-Fiquei aguardando mais de 1 hora quando resolvi ligar para mencionar o atraso e a Allianz informou que o prestador tinha ido no local e que, mesmo eu não tendo fornecido a *senha de acesso* ao serviço, o atendimento foi contabilizado como utilizado._x000D_
-_x000D_
-_x000D_
-Após receber essa informação, registrei uma reclamação no SAC da empresa neste mesmo dia com a promessa de resposta em *7 dias úteis no máximo*._x000D_
-_x000D_
-_x000D_
-Entrei em contato no dia 20.01.2026 através do protocolo 262.433.6480 sobre a resolução do caso, pois meu banheiro estava interditado e o tempo máximo para resposta havia se esgotado._x000D_
-_x000D_
-Somente responderam em 24.01.2026, 13 dias depois, confirmando que as utilizações na minha apólice foram esgotas._x000D_
-_x000D_
-_x000D_
-Depois desse longo tempo de espera, totalmente insatisfeita e sem a realização do serviço pela Allianz fui obrigada a contratar um prestador particular para resolver o caso._x000D_
-_x000D_
-_x000D_
-Se eu soubesse da incompetência dessa empresa, jamais teria contratado um seguro com vigência de um ano, que não se preocupa com a satisfação de seu cliente e já o teria resolvido em 12.01.2026._x000D_
-_x000D_
-_x000D_
-Diante disso, solicito a garantia de que este incidente não será contabilizado como uso do limite de assistências da minha apólice e o estorno de qualquer taxa de "visita improdutiva" que venha a ser gerada indevidamente._x000D_
-_x000D_
-_x000D_
-Resta-me a insatisfação e a impotência na resolução desse problema. Gostaria de enfatiza que nunca mais irei confiar nessa empresa e farei questão de divulgar sua ineficiência para toda a comunidade, para que outras pessoas não passem por este tipo de transtorno, pois para mim restou somente lamentar minha péssima escolha de contratação da Allianz Seguros.</t>
-  </si>
-  <si>
-    <t>95387266</t>
-  </si>
-  <si>
-    <t>240357025</t>
-  </si>
-  <si>
-    <t>10/02/2026 16:45</t>
-  </si>
-  <si>
-    <t>133484949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faz mais de 2 horas  que meu esposo está em Cubatão aguardando um guincho_x000D_
-_x000D_
-Para socorre!._x000D_
-_x000D_
-O meu esposo já solicitou o guincho colocou o endereço correto massss mandaram o guincho para outro endereço._x000D_
-_x000D_
-O meu esposo ligou reclamando e falaram que precisa abrir outro chamando! _x000D_
-_x000D_
-O meu esposo tem problema de pressão alta ! Por conta o stress precisou ser atendido no local!_x000D_
-_x000D_
-Vou deixar registrado aqui!_x000D_
-_x000D_
-</t>
-  </si>
-  <si>
-    <t>95386845</t>
-  </si>
-  <si>
-    <t>240355679</t>
-  </si>
-  <si>
-    <t>10/02/2026 16:34</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Carla</t>
-  </si>
-  <si>
-    <t>132486154</t>
-  </si>
-  <si>
-    <t>Tenho seguro residencial e no final de semana tive um curto na minha casa. Acionei a Allianz para um atendimento emergencial no final de semana. O retorno foi que eu já tinha atingido o limite (3) acionamentos. Questionei quais foram esses acionamentos e me responderam conforme print da conversa. No entanto, tive apenas UM acionamento e por ineficiência da seguradora contaram como 3. Segue o ocorrido:_x000D_
-_x000D_
-1) Acionei a seguradora pois estava com um problema de vazão da água da minha lava louça. Não concluía o serviço por falta de vazão da água. O prestador foi e informou que se tratava de um entupimento e me indicou abrir outra solicitação seguindo outro caminho;_x000D_
-_x000D_
-2) O segundo prestador foi até minha casa e disse que precisava ser um prestador que tivesse uma sonda e me orientou a novamente retornar à seguradora._x000D_
-_x000D_
-3) Por fim o terceiro veio fez o serviço de desentupimento (detalhe que resolveu somente nos primeiros dias e voltou o problema.)_x000D_
-_x000D_
-_x000D_
-Enfim, eu tive um problema e foi contado como 3. Ao tentar informar isso para atendente no whatsapp simplesmente me informou que não podia fazer nada e me desconectou. A obrigação de entender o meu problema e me direcionar para o prestador correto é da seguradora e não meu. Se eu não precisasse de ajuda para me assistir nos problemas da minha casa não precisaria de seguro. O que eu faço agora?</t>
-  </si>
-  <si>
-    <t>95383088</t>
-  </si>
-  <si>
-    <t>240345091</t>
-  </si>
-  <si>
-    <t>10/02/2026 15:18</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Carro Reserva ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Carro Reserva</t>
-  </si>
-  <si>
-    <t>134538263</t>
-  </si>
-  <si>
-    <t>Passei por um sinistro na estrada, meu carro teve o para brisa detonado por um coco arremessado por um caminhão. Após acionar o seguro, o carro foi levado para a base e fui transportado de táxi para a minha residência. Fui informado que o carro chegaria no outro dia e deveria levar no reparo conveniado. O carro não chegou, após entrar em contato com a assistência 24 horas, fui informado que o carro chegaria no próximo dia, o carro não chegou de novo. Após novo contato com a assistência 24 horas fui informado que o carro chega amanhã. Em todos os casos a justificativa foi que há um problema de demanda e logística. O carro não chega e não confio mais nos prazos informados. Ao tentar solicitar o carro reserva, descobri que deveria ter aberto um comunicado de sinistro, em  nenhum momento fui informado que deveria abrir um chamado de sinistro. Após um bom tempo na central de atendimento e sendo transferido entre setores (em cada vez tendo que informar todos os meus dados e navegar nas opções novamente) sou informado que o carro precisa passar por um perito. Tenho que agendar o perito, mas não tenho carro, pois a Allianz não me entrega. Os setores não se comunicam e a cada necessidade de algo, sou transferido e volta a novela da central de atendimento. O tempo passa e o carro não chega e não posso solicitar um carro reserva, pois a Allianz não me entrega o carro, pois tem problemas de demanda, logística, comunicação, eficiência na hora de vender o seguro a eficiência é maravilhosa, a comunicação é eficiente e não há problema de demanda e logística. Profundamente insatisfeito com essa seguradora!</t>
-  </si>
-  <si>
-    <t>95382707</t>
-  </si>
-  <si>
-    <t>240343965</t>
-  </si>
-  <si>
-    <t>10/02/2026 15:10</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Fornecimento de Peças ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Fornecimento de Peças</t>
-  </si>
-  <si>
-    <t>304039320</t>
-  </si>
-  <si>
-    <t>Estou aguardando peças para conserto do meu carro e cada vez que ligo para me informar me passam uma data diferente, tenho urgência, tenho problemas de mobilidade na perna esquerda, aqui não tem prestadoras de serviço como Uber, estou decepcionada com serviço de vcs, pois já estou esperando a mais de 40 dias, solicito urgência na entrega das peças.</t>
-  </si>
-  <si>
-    <t>95375751</t>
-  </si>
-  <si>
-    <t>240324429</t>
-  </si>
-  <si>
-    <t>10/02/2026 12:55</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Análise Sinistro</t>
-  </si>
-  <si>
-    <t>296243165</t>
-  </si>
-  <si>
-    <t>Estou esperando uma indenização já passou da data do prazo e ainda não recebi o valor.</t>
-  </si>
-  <si>
-    <t>95374794</t>
-  </si>
-  <si>
-    <t>240321489</t>
-  </si>
-  <si>
-    <t>10/02/2026 12:35</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Sinistro ; Análise Sinistro ; Automóvel ; 1 Segurado ; Sac Enc ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Andreza</t>
-  </si>
-  <si>
-    <t>304186883</t>
-  </si>
-  <si>
-    <t>Já havia feito uma reclamação dias atrás._x000D_
-_x000D_
-Meu veículo sofreu um sinistro (número 304186883)._x000D_
-_x000D_
-Após demorar quase 30 dias, deram retorno dando perda no veículo._x000D_
-_x000D_
-Agora estou aguardando desde o dia 05/02 retorno do valor a ser preenchido no dut do veículo._x000D_
-_x000D_
-Total descaso comigo._x000D_
-_x000D_
-Pessimo atendimento.</t>
-  </si>
-  <si>
-    <t>95371683</t>
-  </si>
-  <si>
-    <t>240312415</t>
-  </si>
-  <si>
-    <t>10/02/2026 11:34</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; 1 Segurado ; Canal de Atendimento ; Corretor</t>
-  </si>
-  <si>
-    <t>Canal de Atendimento</t>
-  </si>
-  <si>
-    <t>Corretor</t>
-  </si>
-  <si>
-    <t>129683714</t>
-  </si>
-  <si>
-    <t>Na data 06/02 o corretor da stellantis seguros me ofereceu um seguro Pela allianz Seguradora, na ligação infomei que meu CNPJ estava baixado (Inativo) e se era possível, corretor informou que sim, e que não teria nenhum problemas. _x000D_
-_x000D_
-até ai tudo bem, realizei a contratação e mesmo assim nada de chegar a minha apólice para conferi as coberturas. Dias depois chegou minha apolice na data de ontem 09/10/2026._x000D_
-_x000D_
-Passei meus dados e foi cobrado no meu cartão de credito o valor de 253,92._x000D_
-_x000D_
-No entanto, ao realizar algumas buscas com outros corretores me informaram que eu nao teria cobertura em caso de sinistro, pois meu CNPJ estava inativo e não se enquadrava nas normas da seguradora._x000D_
-_x000D_
-entrei em contato com a própria seguradora no prototoclo de N 2624489076 e tive a confirmação que não haveria as coberturas em caso de sinistro, pois meu CNPJ estava baixado._x000D_
-_x000D_
-Diante disso, realizei abertura de outra reclamação no sac, protocolo de N 260002190 para estorno do valor descontado do meu cartão de crédito._x000D_
-_x000D_
-Ressaltando que solicitei o cancelamento e estorno no dia seguinte após envio da minha Apolice ( menos de 24 horas) e quero de volta meu valor pago, pois não tive nenhuma cobertura do seguro e solicitei o cancelamento dentro do prazo de 7 dias corridos._x000D_
-_x000D_
-_x000D_
-Solicito apoio para devolução dos valores pago.</t>
-  </si>
-  <si>
-    <t>95366682</t>
-  </si>
-  <si>
-    <t>240298071</t>
-  </si>
-  <si>
-    <t>10/02/2026 10:08</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Apólice ; Pagamento ; 1 Segurado ; OUV Antes do RA ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Vida / Acidentes Pessoais</t>
-  </si>
-  <si>
-    <t>Vida / Acidentes Pessoais</t>
-  </si>
-  <si>
-    <t>Pagamento</t>
-  </si>
-  <si>
-    <t>OUV Antes do RA</t>
-  </si>
-  <si>
-    <t>122362411</t>
-  </si>
-  <si>
-    <t>Venho sendo  utilizado meu CPF  para fazer boletos falsos  em nome de vossa empresa  por falsários,  sendo que não  tenho nenhum  vínculo  com a empresa  Allianz Seguro, venho solicitar o broqueio desses  boletos  falsos.</t>
-  </si>
-  <si>
-    <t>95363115</t>
-  </si>
-  <si>
-    <t>240287861</t>
-  </si>
-  <si>
-    <t>10/02/2026 08:51</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Apólice ; Automóvel ; Pagamento ; 1 Segurado ; SAC Aberto ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>133367044</t>
-  </si>
-  <si>
-    <t>Pagamento em duplicidade realizado na parcela 7 e ainda não estornado. Devido não ter sido cobrado na data prevista (11/01) no cartão, realizei o pagamento da parcela por pix para nao ficar em atraso, mas aí na data de 13/01 foi cobrada novamente a mesma parcela. Amanhã já fecha os 30 dias que o CDC estabelece para prazo nestes casos e a questão ainda nao foi solucionada, mesmo fazendo contato diretamente com a empresa.</t>
-  </si>
-  <si>
-    <t>95360399</t>
-  </si>
-  <si>
-    <t>240280301</t>
-  </si>
-  <si>
-    <t>10/02/2026 06:51</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Residência ; Apólice ; Pagamento ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>133807081</t>
-  </si>
-  <si>
-    <t>Eu paguei em duplicidade o boleto mês passado e estou me cobrando desse mês, o Chat online não entende essa mensagem e nao consegui abrir chamado na Allianz porque o link de reclamação está indisponível.</t>
-  </si>
-  <si>
-    <t>95359444</t>
-  </si>
-  <si>
-    <t>240277305</t>
-  </si>
-  <si>
-    <t>10/02/2026 02:02</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Guincho ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Assistência Não Danos</t>
-  </si>
-  <si>
-    <t>134902349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liguei para o seguro as 23:57, me informaram que estavam buscando o guincho, já são 01:58 e não acharam ainda o prestador de serviço, estou parado na Fernão Dias na beira da rodovia com minha esposa e minha filha no carro sem nenhuma assistência e sem retorno, pergunto a eles de 30 em 30 minutos e sempre a mesma informação estamos buscando o prestador de serviço._x000D_
-_x000D_
-Como uma empresa pode assim com o consumidor._x000D_
-_x000D_
-_x000D_
-</t>
+    <t>95402527</t>
+  </si>
+  <si>
+    <t>240403109</t>
+  </si>
+  <si>
+    <t>11/02/2026 06:32</t>
+  </si>
+  <si>
+    <t>Allianz ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; 1 Segurado ; Pagamento ; Apólice ; Automóvel ; Apólice</t>
+  </si>
+  <si>
+    <t>132031718</t>
+  </si>
+  <si>
+    <t>Cobrança indevida, _x000D_
+_x000D_
+Recebi boleto no DDA do Nubank, vencimento 23/02/26 valor R$ 148,28, desconheço dívida favor posionar a que se refere. Não autorizo uso do cpf</t>
   </si>
 </sst>
 </file>
@@ -1138,7 +1069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AA8803-373C-4E0C-ABA8-1F171C96DA02}">
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="3" bestFit="1" customWidth="1" collapsed="1"/>
@@ -1292,25 +1223,25 @@
         <v>37</v>
       </c>
       <c r="M2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="W2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="Y2" s="3" t="s">
         <v>26</v>
@@ -1320,13 +1251,13 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>30</v>
@@ -1335,46 +1266,46 @@
         <v>31</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="W3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="X3" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="Y3" s="3" t="s">
         <v>26</v>
@@ -1384,13 +1315,13 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>30</v>
@@ -1399,46 +1330,46 @@
         <v>31</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="V4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="V4" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="W4" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Y4" s="3" t="s">
         <v>26</v>
@@ -1448,13 +1379,13 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>30</v>
@@ -1463,46 +1394,46 @@
         <v>31</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="V5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="V5" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="W5" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y5" s="3" t="s">
         <v>26</v>
@@ -1512,13 +1443,13 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>30</v>
@@ -1527,46 +1458,46 @@
         <v>31</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="M6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="O6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O6" s="3" t="s">
+      <c r="P6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P6" s="3" t="s">
+      <c r="V6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="V6" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="W6" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Y6" s="3" t="s">
         <v>26</v>
@@ -1576,13 +1507,13 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>30</v>
@@ -1591,46 +1522,46 @@
         <v>31</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="P7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P7" s="3" t="s">
+      <c r="V7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="V7" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="W7" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Y7" s="3" t="s">
         <v>26</v>
@@ -1640,13 +1571,13 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>30</v>
@@ -1655,46 +1586,46 @@
         <v>31</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="N8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O8" s="3" t="s">
+      <c r="P8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="V8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="W8" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>26</v>
@@ -1704,13 +1635,13 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>30</v>
@@ -1719,46 +1650,46 @@
         <v>31</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="P9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="V9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="W9" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>26</v>
@@ -1768,13 +1699,13 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>30</v>
@@ -1783,46 +1714,46 @@
         <v>31</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>37</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="N10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O10" s="3" t="s">
+      <c r="P10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P10" s="3" t="s">
+      <c r="V10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="W10" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>26</v>
@@ -1830,13 +1761,13 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>30</v>
@@ -1845,46 +1776,46 @@
         <v>31</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="3" t="s">
+      <c r="P11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P11" s="3" t="s">
+      <c r="V11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="V11" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="W11" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="Y11" s="3" t="s">
         <v>26</v>
@@ -1892,13 +1823,13 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>30</v>
@@ -1907,7 +1838,7 @@
         <v>31</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>33</v>
@@ -1916,13 +1847,13 @@
         <v>34</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>37</v>
@@ -1931,22 +1862,22 @@
         <v>31</v>
       </c>
       <c r="N12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O12" s="3" t="s">
+      <c r="P12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="V12" s="3" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
+      </c>
+      <c r="X12" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>26</v>
@@ -1954,13 +1885,13 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>30</v>
@@ -1969,7 +1900,7 @@
         <v>31</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>33</v>
@@ -1981,10 +1912,10 @@
         <v>35</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>37</v>
@@ -1993,22 +1924,22 @@
         <v>31</v>
       </c>
       <c r="N13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O13" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="3" t="s">
+      <c r="P13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P13" s="3" t="s">
+      <c r="V13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="V13" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="W13" s="4" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="Y13" s="3" t="s">
         <v>26</v>
@@ -2016,13 +1947,13 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>30</v>
@@ -2031,46 +1962,46 @@
         <v>31</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>37</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>86</v>
+        <v>131</v>
       </c>
       <c r="N14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="V14" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>26</v>
@@ -2078,13 +2009,13 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>30</v>
@@ -2093,22 +2024,22 @@
         <v>31</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>132</v>
+        <v>34</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>133</v>
+        <v>36</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>37</v>
@@ -2117,274 +2048,52 @@
         <v>31</v>
       </c>
       <c r="N15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="P15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="V15" s="3" t="s">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V16" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="W16" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="X16" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="Y16" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="W16" s="4"/>
+      <c r="X16" s="4"/>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="W17" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="X17" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y17" s="3" t="s">
-        <v>26</v>
-      </c>
+    <row r="17" spans="23:24" x14ac:dyDescent="0.2">
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="W18" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="X18" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y18" s="3" t="s">
-        <v>26</v>
-      </c>
+    <row r="18" spans="23:24" x14ac:dyDescent="0.2">
+      <c r="W18" s="4"/>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V19" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="W19" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="X19" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="Y19" s="3" t="s">
-        <v>26</v>
-      </c>
+    <row r="19" spans="23:24" x14ac:dyDescent="0.2">
+      <c r="W19" s="4"/>
+      <c r="X19" s="4"/>
+    </row>
+    <row r="20" spans="23:24" x14ac:dyDescent="0.2">
+      <c r="W20" s="4"/>
+      <c r="X20" s="4"/>
+    </row>
+    <row r="21" spans="23:24" x14ac:dyDescent="0.2">
+      <c r="W21" s="4"/>
+    </row>
+    <row r="22" spans="23:24" x14ac:dyDescent="0.2">
+      <c r="W22" s="4"/>
+      <c r="X22" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AN9" xr:uid="{D3AA8803-373C-4E0C-ABA8-1F171C96DA02}"/>

--- a/Treinamento/GestaoReclamacao.xlsx
+++ b/Treinamento/GestaoReclamacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1F10E4-4B84-45F7-BC74-C4B7899A62ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8944A7A4-CFBA-4CD8-8688-1305BE8B1C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B1A77FD5-2AD3-4458-ACB3-7F19D1A3340A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="148">
   <si>
     <t>Id HugMe</t>
   </si>
@@ -122,13 +122,13 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>95438805</t>
-  </si>
-  <si>
-    <t>240504799</t>
-  </si>
-  <si>
-    <t>11/02/2026 22:05</t>
+    <t>95488154</t>
+  </si>
+  <si>
+    <t>240643253</t>
+  </si>
+  <si>
+    <t>13/02/2026 10:53</t>
   </si>
   <si>
     <t>Não respondido</t>
@@ -137,487 +137,653 @@
     <t>Não</t>
   </si>
   <si>
+    <t>Allianz ; Apólice ; Condomínio ; Canal de Atendimento ; Corretor ; Reclamante em nome do Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Allianz</t>
+  </si>
+  <si>
+    <t>Apólice</t>
+  </si>
+  <si>
+    <t>Condomínio</t>
+  </si>
+  <si>
+    <t>Canal de Atendimento</t>
+  </si>
+  <si>
+    <t>Corretor</t>
+  </si>
+  <si>
+    <t>Reclamante em nome do Segurado</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Repasse Time MindBe</t>
+  </si>
+  <si>
+    <t>Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Juliana</t>
+  </si>
+  <si>
+    <t>131555284</t>
+  </si>
+  <si>
+    <t>Empresa Allianz não renovou apólice de seguro predial e respondeu: análise interna. PENSEM BEM ANTES DE CONTRATAR A ALLIANZ SEGURO PREDIAL.</t>
+  </si>
+  <si>
+    <t>95482591</t>
+  </si>
+  <si>
+    <t>240628165</t>
+  </si>
+  <si>
+    <t>13/02/2026 08:35</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Residência ; Sinistro ; 1 Segurado ; Indenização ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Sinistro</t>
+  </si>
+  <si>
+    <t>Residência</t>
+  </si>
+  <si>
+    <t>Indenização</t>
+  </si>
+  <si>
+    <t>1 Segurado</t>
+  </si>
+  <si>
+    <t>304930856</t>
+  </si>
+  <si>
+    <t>Abri sinistro residencial no dia 16/01/2026. Foi aprovado, teto da minha casa está caindo devido vendaval com chuvas fortes, indenização era para ter sido depositada no máximo 3 dias úteis e não foi, ao entrar em contato pediram mais dias para verificar o porquê._x000D_
+_x000D_
+Literalmente o teto da minha casa está caindo, preciso começar a obra e não tenho como por descaso da Allianz.</t>
+  </si>
+  <si>
+    <t>95482474</t>
+  </si>
+  <si>
+    <t>240627867</t>
+  </si>
+  <si>
+    <t>13/02/2026 08:31</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 2 Terceiro do Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Automóvel</t>
+  </si>
+  <si>
+    <t>Análise Sinistro</t>
+  </si>
+  <si>
+    <t>2 Terceiro do Sinistro</t>
+  </si>
+  <si>
+    <t>303982969</t>
+  </si>
+  <si>
+    <t>30 de dezembro um segurado da Allianz bateu contra o meu veiculo, desde então venho enfrentando dificuldade com a seguradora, sou motorista de app, inclusive no dia estava trabalhando, após o acidente entraram em contato comigo da corretora de seguros, esse por sua vez me ofereceu um acordo, acordo esse que me ressarciram o valor do reparo do veiculo, entretanto em momento algum me informaram que se houvesse acordo eu perderia direito aos lucros cessantes, segundo a corretora "estava escrito no contrato de acordo com a seguradora" contrato esse que eu nunca vi nem assinei, ou seja alguém assinou por mim e não ha qualquer evidência de envio de link ou demais formas digitais de assinatura, ou seja houve uma assinatura por parte de "alguém" junto a seguradora, gostaria de esclarecimentos pois liguei no dia 5 para pedir esclarecimentos e me passaram 7 dias para resposta sobre o ocorrido e nada.</t>
+  </si>
+  <si>
+    <t>95475511</t>
+  </si>
+  <si>
+    <t>240606643</t>
+  </si>
+  <si>
+    <t>12/02/2026 20:47</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Mídias ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Mídias</t>
+  </si>
+  <si>
+    <t>304061629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À ALLIANZ SEGUROS S.A._x000D_
+_x000D_
+CNPJ/MF: 61.573.796/0001-66_x000D_
+_x000D_
+Rua Eugenio de Medeiros, n 303, 1 andar-parte, 2 ao 9 andar,_x000D_
+_x000D_
+15 e 16 andar, Pinheiros, São Paulo  SP  CEP 05.425-000_x000D_
+_x000D_
+_x000D_
+Ref.: Apólice n 5177202521312154962_x000D_
+_x000D_
+Sinistro n 304061629_x000D_
+_x000D_
+Segurado: ROBERTO DE MATTOS QUARESMA_x000D_
+_x000D_
+CPF: 077.259.547-08_x000D_
+_x000D_
+Veículo: Hyundai HB20  Placa RJC4J22_x000D_
+_x000D_
+Data do Sinistro: 03 de janeiro de 2026_x000D_
+_x000D_
+_x000D_
+_x000D_
+NOTIFICAÇÃO EXTRAJUDICIAL COM PRAZO PERENTÓRIO_x000D_
+_x000D_
+_x000D_
+Prezados,_x000D_
+_x000D_
+_x000D_
+1. DOS FATOS E DO ATRASO ABUSIVO_x000D_
+_x000D_
+_x000D_
+No dia 03 de janeiro de 2026, o veículo acima qualificado envolveu-se em sinistro coberto pela apólice contratada. Imediatamente acionada, a seguradora determinou a remoção do automóvel para oficina credenciada A2 MOTORS SERVICOS AUTOMOTIVOS na Rua Artur Rios, 1463, Campo Grande  RJ, onde permanece até a presente data  12 de fevereiro de 2026  há mais de 30 (trinta) dias e dias atuais, sem qualquer solução ou pagamento._x000D_
+_x000D_
+_x000D_
+A seguradora insiste, injustificadamente, na realização de vistorias complementares, postergando a conclusão do processo, embora já seja inequívoca a condição de perda total do bem._x000D_
+_x000D_
+_x000D_
+2. DO DIREITO  VIOLAÇÃO DO PRAZO LEGAL E ABUSIVIDADE_x000D_
+_x000D_
+_x000D_
+O prazo máximo para a seguradora se manifestar e efetuar o pagamento da indenização é de 30 (trinta) dias, nos termos do art. 3, 3, da Resolução CNSP n 382/2020 e do art. 77, Parágrafo único da LEI N 15.040, DE 9 DE DEZEMBRO DE 2024 e Código de defesa do Consumidor. _x000D_
+_x000D_
+_x000D_
+Ultrapassado esse limite sem liquidação do sinistro, a conduta da Allianz:_x000D_
+_x000D_
+_x000D_
+ Viola o dever de boa-fé objetiva (art. 422 do Código Civil);_x000D_
+_x000D_
+ Configura nítida manobra protelatória;_x000D_
+_x000D_
+ Subtrai do segurado o direito de dispor do bem ou de receber a importância devida para aquisição de outro veículo._x000D_
+_x000D_
+_x000D_
+3. DO VALOR DEVIDO E DOS DANOS GERADOS_x000D_
+_x000D_
+_x000D_
+O veículo HB20, placa RJC4J22, na data do sinistro (03/01/2026), possuía valor médio de mercado R$ 78.726,00, conforme Tabela FIPE vigente Código Fipe: 015209-9._x000D_
+_x000D_
+._x000D_
+_x000D_
+_x000D_
+A seguradora NÃO pode mais postergar o pagamento desse montante. A retenção prolongada do automóvel e a recusa injustificada em indenizar já geram danos materiais e morais ao notificante, que:_x000D_
+_x000D_
+_x000D_
+ Está privado do uso do veículo;_x000D_
+_x000D_
+ Suporta despesas extras com locomoção;_x000D_
+_x000D_
+ Sofre desgaste emocional e transtornos incompatíveis com o pactuado._x000D_
+_x000D_
+_x000D_
+4. PEDIDO  PAGAMENTO EM 48 HORAS SOB PENA DE COBRANÇA JUDICIAL INTEGRAL_x000D_
+_x000D_
+_x000D_
+Notifico, pois, para que, no prazo improrrogável de 48 (quarenta e oito) horas a partir da data desta Notificação, a Allianz Seguros:_x000D_
+_x000D_
+_x000D_
+a) Efetue o pagamento integral da indenização com base no valor da Tabela FIPE de 03/01/2026 (R$ R$ 78.726,00), devidamente atualizado com juros e correções legais;_x000D_
+_x000D_
+_x000D_
+b) Comunique imediatamente o segurado sobre a liberação do veículo na oficina, encerrando a retenção abusiva._x000D_
+_x000D_
+_x000D_
+5. ADVERTÊNCIA EXPRESSA_x000D_
+_x000D_
+_x000D_
+Esgotado o prazo supra sem a efetiva liquidação, ficarão configurados, de forma inequívoca, os danos materiais e morais, que serão cobrados judicialmente, acrescidos de:_x000D_
+_x000D_
+_x000D_
+ Correção monetária plena (INPC/IGPM) desde 03/01/2026;_x000D_
+_x000D_
+ Juros de mora (1% ao mês);_x000D_
+_x000D_
+ Honorários advocatícios (20%);_x000D_
+_x000D_
+ Danos morais (valor não inferior a R$ 20.000,00);_x000D_
+_x000D_
+ Reembolso de todas as despesas com locomoção (Uber, táxi, aluguel de veículo)._x000D_
+_x000D_
+_x000D_
+A presente notificação serve como constituição em mora e prova da ciência inequívoca da seguradora acerca do ilícito contratual praticado._x000D_
+_x000D_
+_x000D_
+_x000D_
+Atenciosamente,_x000D_
+_x000D_
+_x000D_
+Rio, 12/02/2026_x000D_
+_x000D_
+_x000D_
+_x000D_
+Roberto de Mattos Quaresma  Segurado_x000D_
+_x000D_
+CPF:077.259.547-08_x000D_
+_x000D_
+Celular e Whatsapp: (21) 96894-0060_x000D_
+_x000D_
+E-mail: robertomattoscontador@hotmail.com_x000D_
+_x000D_
+E-mail: robertoquaresma10@gmail.com_x000D_
+_x000D_
+_x000D_
+</t>
+  </si>
+  <si>
+    <t>95475398</t>
+  </si>
+  <si>
+    <t>240606277</t>
+  </si>
+  <si>
+    <t>12/02/2026 20:42</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; OUV Antes do RA ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>OUV Antes do RA</t>
+  </si>
+  <si>
+    <t>303547892</t>
+  </si>
+  <si>
+    <t>Allianz Seguros S.A. _x000D_
+_x000D_
+_x000D_
+Ref.: Sinistro n 303547892_x000D_
+_x000D_
+Segurado: Laisla Regina  / Condutor principal: Samia Nunes _x000D_
+_x000D_
+Placa do veículo:TTT1.. - Tiggo 7 CAOA_x000D_
+_x000D_
+_x000D_
+Prezados,_x000D_
+_x000D_
+_x000D_
+Venho por meio deste solicitar providências urgentes quanto ao sinistro em referência._x000D_
+_x000D_
+_x000D_
+O veículo encontra-se em oficina referenciada há mais de 57 (cinquenta e sete) dias, sem que tenha sido apresentada previsão concreta para conclusão dos reparos, sendo informado apenas que há indisponibilidade de peças pela montadora._x000D_
+_x000D_
+_x000D_
+Ressalto que o carro reserva já foi encerrado, permanecendo o veículo segurado indisponível, situação que vem me causando prejuízos e transtornos significativos._x000D_
+_x000D_
+_x000D_
+Diante disso, REQUEIRO:_x000D_
+_x000D_
+_x000D_
+1. A prorrogação imediata do carro reserva até a efetiva conclusão dos reparos e disponibilização do veículo; _x000D_
+_x000D_
+ou, alternativamente, _x000D_
+_x000D_
+o custeio integral de transporte substitutivo enquanto perdurar a indisponibilidade;_x000D_
+_x000D_
+_x000D_
+2. A apresentação, por escrito, de prazo máximo e definitivo para conclusão do conserto;_x000D_
+_x000D_
+_x000D_
+3. Caso o reparo não seja viável em prazo razoável, que seja avaliada a conversão do sinistro em indenização integral, se for o caso._x000D_
+_x000D_
+_x000D_
+Destaco que a ausência de prazo definido e a manutenção da indisponibilidade do veículo por período excessivo configuram falha na prestação do serviço, nos termos do Código de Defesa do Consumidor._x000D_
+_x000D_
+_x000D_
+Aguardo resposta formal no prazo máximo de 5 (cinco) dias._x000D_
+_x000D_
+_x000D_
+Sem mais,_x000D_
+_x000D_
+_x000D_
+Laisla Regina _x000D_
+_x000D_
+Telefone: 21964_x000D_
+_x000D_
+E-mail: laislamenezes@_x000D_
+_x000D_
+Data: 12/02/2026.</t>
+  </si>
+  <si>
+    <t>95472723</t>
+  </si>
+  <si>
+    <t>240598309</t>
+  </si>
+  <si>
+    <t>12/02/2026 19:07</t>
+  </si>
+  <si>
+    <t>Allianz ; 2 Terceiro do Sinistro ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>304202716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abri sinistro como terceiro junto à Allianz referente a colisão traseira ocorrida em 19/12/2025. Enviei toda a documentação solicitada, incluindo contrato de locação digital da empresa Turbi, que possui validade jurídica conforme legislação brasileira._x000D_
+_x000D_
+_x000D_
+A seguradora passou a exigir contrato com firma reconhecida em cartório anterior ao sinistro  requisito incompatível com contratos eletrônicos de locadoras por aplicativo, que são formalizados exclusivamente de forma digital._x000D_
+_x000D_
+_x000D_
+Solicitei esclarecimento objetivo sobre qual elemento jurídico estaria insuficiente no documento apresentado, porém não obtive resposta dentro do prazo informado. O processo permanece parado sem justificativa formal._x000D_
+_x000D_
+_x000D_
+Solicito posicionamento técnico claro e fundamentado, bem como andamento imediato da análise._x000D_
+_x000D_
+</t>
+  </si>
+  <si>
+    <t>95467919</t>
+  </si>
+  <si>
+    <t>240584555</t>
+  </si>
+  <si>
+    <t>12/02/2026 16:49</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; 1 Segurado ; Sim ; Não ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Assistência Não Danos</t>
+  </si>
+  <si>
+    <t>Guincho</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>133213481</t>
+  </si>
+  <si>
+    <t>Na terça-feira dia 3 de fevereiro eu tive e as rodas do meu veículo furtadas após algum período que deixei o meu carro na rua ao retornar a primeira coisa que fiz foi acionar a central do seguro fiz a ligação por telefone porque precisaria explicar a situação. Foi aí que começou a minha dor de cabeça maior porque ao entrar em contato me deparei com um atendente totalmente inexperiente que ficava o tempo todo perguntando para outra pessoa de fundo como proceder naquela situação ao final dessa primeira ligação, eu expliquei que o meu veículo estava sem as duas rodas e no chão e que precisaria de um auxílio para rebocar o veículo, mas que não poderia ser um reboque simples. Devido o veículo está no chão. Falei que se tivesse um auxílio de algum reboque que pudesse levantar o veículo eu até poderia me dispor a arrumar caso um step a mais para colocar E já solucionar o caso momentaneamente ali pelo menos para que eu pudesse sair daquele local que não eram local seguro além do que estava chovendo. E começando a ficar tarde isso foi por volta das 21h horas. O atendente encerrou a ligação dizendo que eu aguardasse no local que Ou seja já estava a caminho por volta de 60 minutos era o tempo de espera. Aguardei porém o que ele me enviou foi um motoboy sem nenhum tipo de ferramenta para trocar um pneu sendo que eu expliquei tudo para ele o prestador de serviço ao chegar lá falou que não iria conseguir me ajudar em nada que eu teria que novamente ligar na central e fazer o pedido de um reboque especializado foi embora sem prestar nenhum tipo de auxílio eu novamente. Entrei em contato. Tive que explicar novamente o caso e mais uma vez, peguei outra pessoa que não tinha o mínimo de noção do que fazer. Ficou cerca de 15 a 20 minutos para poder falar para mim. Queria tentar me enviar um reboque especializado. Mesmo eu explicando a ela que se tivesse qualquer tipo de pessoa que tivesse um macaco hidráulico ou algum outro tipo de ferramenta que só me ajudasse a levantar o carro eu mesmo poderia colocar o step que eu consegui reserva. E ir embora. Mesmo assim ela insistia que teria que ser o reboque para poder levar até a borracharia. Eu falei Ok tudo bem. Me mande o reboque que já era para ter mandado há mais de uma hora atrás isso foi foi por volta das 22:30. Quando deu meia-noite eu não tinha nenhuma posição nenhum tipo de ligação nada retornei a central para ver o que estava acontecendo. E mais uma vez o atendente me informou que o meu pedido não tinha sido nem aceito pela terceirizada que eles não tinham achado profissional e que o tempo de espera só iria contar a partir do momento que algum profissional aceitasse meu pedido. Eu enganei na central porque a responsabilidade disso não seria minha a responsabilidade seria da seguradora em me fornecer o serviço que eu contratei. E a resposta que obtive é que ele não poderia fazer nada que eu teria que esperar. Enfim para resumir o caso eu tive que me virar de comprar uma carta hidráulico, eu tive que me virar de arrumar um step eu tive que me enviar de arrumar pessoas para poder levantar o carro para que eu pudesse sair do local, pois era um local perigoso só conseguir sair do local as duas e 30 da manhã. E nesse período todo não tive nenhum tipo de contato auxílio ou ligação por parte da seguradora. Fica aqui a minha indignação pelo péssimo serviço oferecido. Tenho certeza que jamais indicarei para ninguém a allianz .</t>
+  </si>
+  <si>
+    <t>95460711</t>
+  </si>
+  <si>
+    <t>240564533</t>
+  </si>
+  <si>
+    <t>12/02/2026 14:04</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Assistência Não Danos ; Residência ; OUV Antes do RA ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Assistência Residencial ; 1 Segurado</t>
+  </si>
+  <si>
+    <t>Assistência Residencial</t>
+  </si>
+  <si>
+    <t>133184900</t>
+  </si>
+  <si>
+    <t>Boa tarde_x000D_
+_x000D_
+Estou com um problema com a Allianz Seguros que está desde Novembro de 2025. Tenho um seguro residencial, solicitei um serviço de limpeza da caixa de água da minha casa, que só me deu prejuízo. O prestador de serviço deixou a bóia da caixa enroscada, vazando água por mais de 48 horas. E quando veio acertar a bóias o mesmo ainda me quebrou dua telhas de eternit. Total do prejuízo cerca de 800,00._x000D_
+_x000D_
+Já abri chamado, já encaminhei notas fiscal, recibo do prestador de serviço que trocou as telhas, faturas das contas de água para provar o valor que veio em minha conta._x000D_
+_x000D_
+Não estão nem respondendo mais minhas mensagens a mais de uma semana_x000D_
+_x000D_
+Nr chamdo da reclamação: Informações do Atendimento - 50520689 - Allianz_x000D_
+_x000D_
+_x000D_
+Solicito um contato da Seguradora.</t>
+  </si>
+  <si>
+    <t>95458921</t>
+  </si>
+  <si>
+    <t>240559313</t>
+  </si>
+  <si>
+    <t>12/02/2026 13:20</t>
+  </si>
+  <si>
     <t>Allianz ; Apólice ; Automóvel ; Apólice ; Pagamento ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
-    <t>Allianz</t>
-  </si>
-  <si>
-    <t>Apólice</t>
-  </si>
-  <si>
-    <t>Automóvel</t>
-  </si>
-  <si>
     <t>Pagamento</t>
   </si>
   <si>
-    <t>1 Segurado</t>
-  </si>
-  <si>
-    <t>Sim</t>
-  </si>
-  <si>
-    <t>Repasse Time MindBe</t>
-  </si>
-  <si>
-    <t>Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Juliana</t>
-  </si>
-  <si>
-    <t>133887801</t>
-  </si>
-  <si>
-    <t>Cobrança indevida dupla do mesmo boleto. Foi pago e deposi debitado automaticamente. _x000D_
-_x000D_
-Preciso do reembolso urgente</t>
-  </si>
-  <si>
-    <t>95437357</t>
-  </si>
-  <si>
-    <t>240500211</t>
-  </si>
-  <si>
-    <t>11/02/2026 21:06</t>
-  </si>
-  <si>
-    <t>Allianz ; Vida / Acidentes Pessoais ; Apólice ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Assistência Não Danos ; Assistencia Funeral</t>
-  </si>
-  <si>
-    <t>Vida / Acidentes Pessoais</t>
-  </si>
-  <si>
-    <t>Assistência Não Danos</t>
-  </si>
-  <si>
-    <t>Assistencia Funeral</t>
-  </si>
-  <si>
-    <t>127621229</t>
-  </si>
-  <si>
-    <t>No dia 21/12/2025 meu pai faleceu, neste sentido liguei na Allianz para solicitar os serviços de funerária cobertos pela prestadora de serviço que gerou o protocolo/Sinistro 50948352, como a minha irmã possui um plano funerário de atendimento com o grupo Serra ao qual a atendente da Allianz informou não possuir parceria, mas para seguir com os serviços necessarios para posterior reembolso, assim fizemos. Seguindo com o orientado através do atendimento do sinistro, preenchi o formulário e encaminhei toda a documentação necessária no dia 09/01/2026. Deste momento para a frente tive que ligar diversas vezes para cobrar o andamento do reembolso, que foi respondido por e-mail no dia 25/01/2026 que o documento nota fiscal do serviço funerário não fora aceito pois não continha o desmembramento dos serviços, algo que eu não tinha sido orientado pelo atendimento inicial e que não tenho ingerência no formato que a empresa emite sua nota fiscal. Sendo assim solicitei o documento ao grupo Serra o com a descriminação dos serviços, enviei no dia 26/01 juntamente com o comprovante de residência do falecido, meu pai, também solicitado. Contudo, até o momento não obtive retorno da Allianz, mesmo falando com uma atendente via telefone na semana do envio. O descaso com o atendimento está me deixando abalado emocionalmente, visto a situação da perda de um ente querido e também por não ser atendido de forma ágil e adequada para um serviço contratado que é para resolver e não para criar mais dificuldades.</t>
-  </si>
-  <si>
-    <t>95431392</t>
-  </si>
-  <si>
-    <t>240482077</t>
-  </si>
-  <si>
-    <t>11/02/2026 17:55</t>
-  </si>
-  <si>
-    <t>Allianz ; Automóvel ; Sinistro ; CPF/CNPJ ; Análise Sinistro ; 11 Não Cliente ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>CPF/CNPJ</t>
-  </si>
-  <si>
-    <t>Sinistro</t>
-  </si>
-  <si>
-    <t>Análise Sinistro</t>
-  </si>
-  <si>
-    <t>11 Não Cliente</t>
-  </si>
-  <si>
-    <t>19817161</t>
-  </si>
-  <si>
-    <t>Adquiri um veículo cruze na data de Leilão 23/12/2025 número de leilão: 9712 lote: 82  Ltz 2021/2022 pelo leiloeiro copart leilões, no edital informava que o IPVA seria por conta da comitente (Allianz Seguros) sendo pago até a data do vencimento. O prazo para pagamento venceu e o pagamento do IPVA ainda não foi realizado. Ao acionar o canal de pós-venda e sac sou orientado pela copart a aguardar, uma vez que já foi aberto um chamado. Estou sem documento sem como transferir, sem como andar no carro preciso urgentemente desse ipva pago!!!!</t>
-  </si>
-  <si>
-    <t>95431228</t>
-  </si>
-  <si>
-    <t>240481597</t>
-  </si>
-  <si>
-    <t>11/02/2026 17:50</t>
-  </si>
-  <si>
-    <t>Allianz ; CPF/CNPJ ; Automóvel ; Sinistro ; Análise Sinistro ; 11 Não Cliente ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>468540338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Em 2021 minha moto foi roubada, fiz boletim de ocorrência e recebi indenização por perda total pela seguradora Sua América._x000D_
-_x000D_
-Mesmo assim, anos depois apareceu um protesto indevido no meu nome referente ao IPVA do veículo, no valor de R$ 234, causando negativação no Serasa._x000D_
-_x000D_
-Essa cobrança é irregular, pois após a indenização a responsabilidade pelo veículo deixou de ser minha._x000D_
-_x000D_
-Solicito com urgência:_x000D_
-_x000D_
-1.Regularização da baixa do veículo junto ao DETRAN_x000D_
-_x000D_
-2.Cancelamento do débito de IPVA_x000D_
-_x000D_
-3.Retirada imediata do protesto no Serasa_x000D_
-_x000D_
-4.Comprovante formal da regularização_x000D_
-_x000D_
-Anexo documentos que comprovam roubo e indenização._x000D_
+    <t>136275779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiz renovacao de apólice de seguro conforme mensagem abaixo:_x000D_
+_x000D_
+RENOVAÇÃO SEGURO AUTO_x000D_
+_x000D_
+_x000D_
+Olá Fernanda,_x000D_
+_x000D_
+_x000D_
+A sua proposta de renovação foi contratada com sucesso e já está em análise com a seguradora._x000D_
+_x000D_
+_x000D_
+Veículo: TOYOTA COROLLA CROSS XRE 2.0 16V FLEX 4X2 AUT._x000D_
+_x000D_
+Ano Modelo: 2022_x000D_
+_x000D_
+Placa: RDL5B58_x000D_
+_x000D_
+_x000D_
+Plano: Personalizado_x000D_
+_x000D_
+Valor: 3.305,16 em 6 x de R$ 550,86 no DÉBITO EM CONTA_x000D_
+_x000D_
+_x000D_
+E depois de pagar, conforme anexo, recebi que minha apólice foi cancelada._x000D_
+_x000D_
+_x000D_
+ENDOSSO DE CANCELAMENTO_x000D_
+_x000D_
+_x000D_
+Olá Fernanda, tudo bem?_x000D_
+_x000D_
+_x000D_
+Vimos que sua apólice de seguro auto foi cancelada recentemente e gostaríamos de deixar aberto um convite: estamos à disposição para reativar sua proteção com condições diferenciadas._x000D_
+_x000D_
+_x000D_
+*Número da Apólice:*: 5177202651310106740_x000D_
+_x000D_
+*Seguradora*: ALLIANZ_x000D_
+_x000D_
+_x000D_
+Podemos ajustar a cobertura conforme sua necessidade atual, garantindo segurança e tranquilidade para você e seu automóvel._x000D_
+_x000D_
+_x000D_
+Estou sem seguro após ter pago. Vou processar essa seguradora. Que absurdo!_x000D_
+_x000D_
+_x000D_
+Paguei via Pix. Está pago fevereiro que nem venceu ainda..._x000D_
+_x000D_
 _x000D_
 </t>
   </si>
   <si>
-    <t>95430389</t>
-  </si>
-  <si>
-    <t>240479279</t>
-  </si>
-  <si>
-    <t>11/02/2026 17:29</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Reclamante em nome do Segurado ; Análise Sinistro</t>
-  </si>
-  <si>
-    <t>Reclamante em nome do Segurado</t>
-  </si>
-  <si>
-    <t>303609456</t>
-  </si>
-  <si>
-    <t>Não consigo entrar em contato pelos canais  da seguradora. Foi indicado no sinistro do meu veiculo que será trocado duas longarinas do veiculo. O que me deixa recioso, primeiro por questões de segurança já que é um componente importante do veiculo que pode impactar diretamente na segurança,  a seguradora não consegue garantir que meu veiculo terá as mesmas condições de segurança de quando comprei, segundo porque a seguradora está deprenciando meu veiculo com essa alteração. Dado que a troca dessa peça desvaloriza o valor de mercado do veiculo. O que não faz sentido já que meu seguro é feito para proteger meus bens.</t>
-  </si>
-  <si>
-    <t>95428843</t>
-  </si>
-  <si>
-    <t>240474983</t>
-  </si>
-  <si>
-    <t>11/02/2026 16:53</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>305327919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prezados,_x000D_
-_x000D_
-_x000D_
-No dia 03 de fevereiro de 2026, fui vítima de furto da minha motocicleta. Na mesma data, registrei o Boletim de Ocorrência e entrei em contato com a seguradora para dar início ao processo de sinistro._x000D_
-_x000D_
-_x000D_
-Na ocasião, fui informado de que receberia um e-mail no prazo de 24 horas com as orientações necessárias. No entanto, o e-mail foi encaminhado apenas no dia 09 de fevereiro, ultrapassando o prazo informado._x000D_
-_x000D_
-_x000D_
-Após o recebimento das solicitações de documentação, encontrei dificuldades especialmente em relação ao ATPV, que tem sido meu maior contratempo até o momento. Tenho me deslocado diversas vezes, arcando com custos de transporte por aplicativo, para tentar resolver a situação. Contudo, conforme informado pelo Detran, não é possível emitir o ATPV devido à restrição de furto registrada no veículo._x000D_
-_x000D_
-_x000D_
-Além disso, em contato telefônico com a seguradora, a ligação foi interrompida no momento em que eu seria transferido ao setor responsável, impossibilitando a continuidade do atendimento._x000D_
-_x000D_
-_x000D_
-Diante de todos esses transtornos, solicito, com urgência, uma orientação clara e uma solução efetiva para o meu caso, a fim de que o processo seja resolvido o mais breve possível._x000D_
-_x000D_
-_x000D_
-Fico no aguardo de um retorno imediato._x000D_
-_x000D_
-_x000D_
-Atenciosamente,_x000D_
-_x000D_
-</t>
-  </si>
-  <si>
-    <t>95425563</t>
-  </si>
-  <si>
-    <t>240465431</t>
-  </si>
-  <si>
-    <t>11/02/2026 15:38</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Canal de Atendimento ; Corretor ; Reclamante em nome do Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Canal de Atendimento</t>
-  </si>
-  <si>
-    <t>Corretor</t>
-  </si>
-  <si>
-    <t>131443117</t>
-  </si>
-  <si>
-    <t>Venho por meio desta comunicar minha indignação com a allianz, sou cliente, e fui renovar o seguro com minha corretora e o preço aumentou, a tendência ao não usar o seguro é os anos se passarem é diminuir o valor, mas não o valor subiu, aí como continuaremos com a fidelidade se a allianz não fideliza o cliente, procuramos andar da melhor forma possível, pois sei que se usar o seguro no ano seguinte tud aumenta, mais mesmo com esses cuidados o seguro só aumenta e quando entro em contato com a allianz a única resposta que obtive é: cote em outros lugares pra ver se consegue um preço melhor, penso que reter o cliente é uma das formas de continuar no mercado, mas sendo assim vou sair e não indicarei pois já se preocupam em conseguir preços atrativos para quem já é cliente e se quer usou o seguro.</t>
-  </si>
-  <si>
-    <t>95424941</t>
-  </si>
-  <si>
-    <t>240463611</t>
-  </si>
-  <si>
-    <t>11/02/2026 15:24</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Reclamante em nome do Segurado</t>
-  </si>
-  <si>
-    <t>298810467</t>
-  </si>
-  <si>
-    <t>Terceiro já foi atendido no sinistro s298810467 referente aos danos da moto, entretanto o mesmo terceiro sofreu fraturas e solicita cobertura IPA, mesmo tendo atendido a moto, havendo culpa do motorista segurado no BO e havendo notícia da cidade com a van do segurado em cima da moto a seguradora não dá sequencia no sinistro, pois solicita novamente uma carta de culpabilidade do segurado. Todos os documentos do terceiro foram enviados em 30/09/2025 , mas sinistro está parado por seguradora solicitar uma nova declaração de culpabilidade do mesmo segurado que já atendeu a moto do mesmo terceiro no mesmo sinistro de mesmo número. Favor dar andamento nas tratativas dos danos corporais com urgencia e retornar ao procurador em e-mail da reclamação e procuração.</t>
-  </si>
-  <si>
-    <t>95424416</t>
-  </si>
-  <si>
-    <t>240462415</t>
-  </si>
-  <si>
-    <t>11/02/2026 15:15</t>
-  </si>
-  <si>
-    <t>Allianz ; Residência ; Sinistro ; Sinistro ; Análise Sinistro ; 1 Segurado ; OUV Antes do RA ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Residência</t>
-  </si>
-  <si>
-    <t>OUV Antes do RA</t>
-  </si>
-  <si>
-    <t>303511857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Título: Sinistro negado + falha na assistência 24h + prejuízo material  Apólice Allianz 5177202532140388993_x000D_
-_x000D_
-_x000D_
-Descrição da reclamação:_x000D_
-_x000D_
-_x000D_
-Venho registrar minha insatisfação formal com a Allianz Seguros referente à apólice abaixo:_x000D_
-_x000D_
-_x000D_
-INFORMAÇÕES DO SEGURO_x000D_
-_x000D_
-Endereço do local segurado: Avenida Vereador Carlito Cordeiro, 2315  Jardim Botânico  Uberlândia/MG  CEP 38410-665_x000D_
-_x000D_
-Produto | Ramo: 14  Residência Digital_x000D_
-_x000D_
-Tipo de residência: Casa Condomínio Habitual Alvenaria_x000D_
-_x000D_
-Tipo de contratação: Edifício + Conteúdo_x000D_
-_x000D_
-Limite Máximo de Garantia: R$ 1.500.000,00_x000D_
-_x000D_
-Proposta n: 134296787_x000D_
-_x000D_
-Apólice n: 5177202532140388993_x000D_
-_x000D_
-Versão da tabela: 43/42.05_x000D_
-_x000D_
-Condições gerais: 02/2025_x000D_
-_x000D_
-Vigência: 04/09/2025 a 04/09/2026_x000D_
-_x000D_
-_x000D_
-Número do Sinistro: 303511857_x000D_
-_x000D_
-Protocolo Assistência 24h: 51159748_x000D_
-_x000D_
-_x000D_
-_x000D_
-_x000D_
-No momento da contratação do seguro, deixei claras minhas necessidades, especialmente cobertura para problemas oriundos de chuva, incluindo danos ao gesso e infiltrações. Tenho evidências de que me foi assegurado que esse tipo de evento estaria coberto._x000D_
-_x000D_
-_x000D_
-Inclusive, eu estava fechando com o Santander, mas optei pela Allianz por recomendação da corretora, que afirmou que o produto seria superior e atenderia plenamente minhas necessidades._x000D_
-_x000D_
-_x000D_
-No dia 08/12, houve forte chuva com vento e granizo em Uberlândia, causando infiltração em minha residência. Ao acionar o seguro (sinistro n 303511857), tive a cobertura negada, com base em cláusula contratual restritiva apresentada somente no momento do sinistro._x000D_
-_x000D_
-_x000D_
-Na contratação a cobertura existia; quando precisei utilizar, surgiu uma cláusula limitadora que esvaziou a garantia prometida. Isso viola os princípios da boa-fé, transparência e equilíbrio contratual previstos no Código de Defesa do Consumidor._x000D_
-_x000D_
-_x000D_
-Além disso, enfrentei sérias falhas na assistência 24h (protocolo 51159748):_x000D_
-_x000D_
-Em 15/01, o prestador informou que não poderia atuar porque seria necessário quebrar;_x000D_
-_x000D_
-Em 20/01, outro profissional compareceu e disse não estar autorizado;_x000D_
-_x000D_
-Ocorreram sucessivos reagendamentos com não comparecimento;_x000D_
-_x000D_
-Apenas em 04/02, houve a quebra da calçada, mas o problema não foi solucionado, sob alegação de que seria responsabilidade do DMAE._x000D_
-_x000D_
-_x000D_
-O mais grave: quando o DMAE compareceu, informou que bastaria verificar que o relógio do hidrômetro não estava rodando para constatar que o problema era de responsabilidade da concessionária._x000D_
-_x000D_
-_x000D_
-Ou seja, houve erro de diagnóstico básico por parte do prestador da seguradora, que resultou na quebra da minha calçada de forma indevida, gerando prejuízo material direto, deixando o local danificado e sem reparo._x000D_
-_x000D_
-_x000D_
-Como consumidor, não tenho obrigação de conhecimento técnico para diferenciar responsabilidades entre seguradora e concessionária pública. Esperava que a Allianz prestasse serviço técnico adequado e evitasse danos desnecessários à minha propriedade._x000D_
-_x000D_
-_x000D_
-Diante de todo o ocorrido, exijo:_x000D_
-_x000D_
-1.Revisão imediata da negativa do sinistro referente à chuva e granizo;_x000D_
-_x000D_
-2.Posicionamento formal e técnico sobre a cobertura contratada;_x000D_
-_x000D_
-3.Ressarcimento do prejuízo causado pela quebra indevida da calçada;_x000D_
-_x000D_
-4.Solução definitiva da demanda aberta na assistência._x000D_
-_x000D_
-_x000D_
-Caso não haja solução adequada, buscarei meus direitos judicialmente, inclusive com pedido de reparação por danos materiais e morais, diante da falha na prestação do serviço e da frustração contratual._x000D_
-_x000D_
-_x000D_
-Possuo fotos, registros, protocolos e evidências da contratação e dos atendimentos realizados._x000D_
-_x000D_
-_x000D_
-Aguardo solução urgente._x000D_
-_x000D_
-</t>
-  </si>
-  <si>
-    <t>95416604</t>
-  </si>
-  <si>
-    <t>240441879</t>
-  </si>
-  <si>
-    <t>11/02/2026 12:36</t>
-  </si>
-  <si>
-    <t>Allianz ; Automóvel ; Sinistro ; Não ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Sim ; CPF/CNPJ ; 11 Não Cliente ; Fornecimento de Peças</t>
-  </si>
-  <si>
-    <t>Fornecimento de Peças</t>
-  </si>
-  <si>
-    <t>301949664</t>
-  </si>
-  <si>
-    <t>Sofri um sinistro no dia 01/11/2025 e já vai fazer 4 meses desde o início do sinistro e até hoje o carro segue na oficina, a oficina diz que está aguardando as peças chegarem, e que essas peças são fornecidas pela a seguradora, em resumo estou a 4 meses sem carro por conta de desorganização da seguradora.</t>
-  </si>
-  <si>
-    <t>95408109</t>
-  </si>
-  <si>
-    <t>240418963</t>
-  </si>
-  <si>
-    <t>11/02/2026 10:00</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Empresa ; Assistência Não Danos ; Assistencia Empresa ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Empresa</t>
-  </si>
-  <si>
-    <t>Assistencia Empresa</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>134703470</t>
-  </si>
-  <si>
-    <t>Tenho tentado contato incessantemente com a Allianz Seguradora, porém não estou obtendo qualquer retorno efetivo. Nenhum atendente consegue fornecer uma resposta concreta, e o atendimento se resume a um verdadeiro jogo de empurra._x000D_
-_x000D_
-_x000D_
-No chat, quando finalmente um atendente humano inicia o atendimento, a conversa simplesmente é interrompida sem qualquer conclusão._x000D_
-_x000D_
-_x000D_
-No dia 12/12/2025, durante o apagão ocorrido em São Paulo, um técnico da Allianz compareceu ao nosso estabelecimento (somos proprietárias de uma confeitaria). Na ocasião, suspeitávamos que uma de nossas geladeiras havia queimado, porém o técnico constatou que o problema era que apenas uma fase da nossa energia elétrica havia sido religada, sendo que nosso sistema é trifásico._x000D_
-_x000D_
-_x000D_
-O profissional foi extremamente atencioso, gentil e prestou todas as orientações necessárias para que pudéssemos tratar a situação junto a Enel. Entretanto, precisamos apenas do laudo que comprove a visita técnica e o diagnóstico realizado no local, documento este que não conseguimos obter._x000D_
-_x000D_
-_x000D_
-Já realizamos inúmeras ligações, tentativas de contato pelo chat, acessos a área do cliente, além de contato com a central de emergência 24h e outros telefones da Allianz, porém até o momento ninguém localiza o sinistro referente a visita técnica, tampouco apresenta qualquer solução._x000D_
-_x000D_
-_x000D_
-A falta de retorno e de organização no atendimento tem nos causado grande transtorno, especialmente considerando que dependemos desse laudo para apresentar a advogada._x000D_
-_x000D_
-_x000D_
-Aguardo um posicionamento urgente._x000D_
-_x000D_
-_x000D_
-Cristina</t>
-  </si>
-  <si>
-    <t>95406846</t>
-  </si>
-  <si>
-    <t>240415623</t>
-  </si>
-  <si>
-    <t>11/02/2026 09:36</t>
-  </si>
-  <si>
-    <t>Allianz ; Automóvel ; Apólice ; Carro Reserva ; Assistência Não Danos ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; 1 Segurado</t>
-  </si>
-  <si>
-    <t>Carro Reserva</t>
-  </si>
-  <si>
-    <t>135381358</t>
-  </si>
-  <si>
-    <t>Sou segurado allianz e me decepcionei com uma resposta obtida por telefone ontem. Acabei me envolvendo num incidente onde uma pessoa bateu no meu carro, ela acionou o seguro dela e agendamos o serviço entre os dia 24/02 e 27/02. Entrei em contato com minha segurado, pois necessito de um veículo para me deslocar para o trabalho, solicitando carro reserva. Fui informado que, devido ao valor do serviço ter ficado menor que minha franquia, eu não tinha direito a carro reserva. Achei a resposta absurda, qual a necessidade de eu ter um seguro? O que vale é o valor da franquia ou a necessidade do cliente?</t>
-  </si>
-  <si>
-    <t>95405618</t>
-  </si>
-  <si>
-    <t>240412253</t>
-  </si>
-  <si>
-    <t>11/02/2026 09:07</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Sinistro ; Automóvel ; Análise Sinistro ; 1 Segurado ; Repasse Time MindBe ; SAC Aberto ; Sim ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>SAC Aberto</t>
+    <t>95458040</t>
+  </si>
+  <si>
+    <t>240556871</t>
+  </si>
+  <si>
+    <t>12/02/2026 12:59</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Sim ; Repasse Time MindBe ; OUV Antes do RA ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>303809783</t>
+  </si>
+  <si>
+    <t>Meu carro sofreu um acidente. Foi abalroado por trás e jogado contra a cancela do pedagio da Linha Amarela. Acionei o seguro que se manifestou dizendo que só pagaria os danos traseiros porque a "vistoria" achava que os danos dianteiros não tinham nada a ver com o acidente. Apesar das provas de imagens, testemunhas, detalhes desse acidente, a empresa não voltou atrás para reavaliar a primeira "avaliação" e simplesmente diz que não vai pagar esse conserto. Acionei a Ouvidoria que também se negou a fazer nova avaliação e se mostrou firme na decisão de NÃO PAGAR O DANO SOFRIDO NO CAPÔ DO MEU CARRO. UM VERDADEIRO ABSURDO. NUNCA MAIS FAREI QUALQUER NEGOCIO COM ESSA EMPRESA E RECOMENDO ISSO A TODOS.</t>
+  </si>
+  <si>
+    <t>95451904</t>
+  </si>
+  <si>
+    <t>240542623</t>
+  </si>
+  <si>
+    <t>12/02/2026 11:14</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>136547027</t>
+  </si>
+  <si>
+    <t>Chamei o serviço de Hidráulica emergencial da Allianz na minha residência por estava com vazamento nas duchas higiênicas dos meus 2 banheiros. Eu tinha direito a R$100 em peças. Não sabia o que precisaria trocar, por isso não tinha comprado nada antes. O prestador de serviço disse que teria que trocar a torneira, a ducha era nova. Eu disse que precisaria de tempo pra comprar, que ele voltasse depois pra fazer a troca. Ele disse que sairia pra comprar pra mim. Pedi que tirasse foto pra comprar uma torneira igual, ele disse que não era necessário, que sabia qual era o produto. Chegou aqui com um produto totalmente diferente, de péssima qualidade, que vinha com torneira e ducha, e que era incompatível com o buraco da minha parede. Já chegou abrindo o produto e instalando, ficou péssimo. Além disso, levou minhas torneiras antigas sem a minha autorização, sem sequer pedir, e fiquei até sem ter como comprar outra pois não sabia o modelo. Liguei, reclamei, o seguro disse que mandaria outra pessoa pra instalar uma torneira igual a que eu tinha e eu pagaria somente a diferença de valor. Porém, o sr. Tiago, responsável pela empresa Daniela ou Danielle Hidráulica me ligou exaltado, dizendo que acusei um prestador de serviço dele de roubo das minhas torneiras, que compraria outras torneiras e eu teria que pagar a difetença. Fiquei extremamente assustada, inclusive com medo. A Allianz é responsável pelas pessoas que coloca nas nossas casas, estou horrorizada com a forma como fui tratada. Esse Sr. chegou na porta da minha casa e obviamente não deixei que entrasse. Acionei o seguro, a Sra. Camille me atendeu e disse que o seguro não arcaria com o valor de R$100 a que tenho direito, que eu teria que ficar com o produto de péssima qualidade que instalaram na minha casa ou teria que pagar 100% do valor do produto adequado. Acabei de renovar meu seguro na Allianz pela Sicoob, mas estou totalmente arrependida, assustada e com medo de receber qualquer outro prestador enviado por eles para a minha residência! Um absurdo completo!!!</t>
+  </si>
+  <si>
+    <t>95450507</t>
+  </si>
+  <si>
+    <t>240538347</t>
+  </si>
+  <si>
+    <t>12/02/2026 10:44</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>133740768</t>
+  </si>
+  <si>
+    <t>Veio esclarecer minha indignação com relação ao seguro onde me gerou um constrangimento de esperar de atendimento liguei 3 vezes para a central abriu a solicitação para reboque ppr volta das 22.30 eu vim chegar em casa era mais de meia noite e detalhe ainda tive que escutar de uma atendente que não tinha reboque disponível por conta de Carnaval me senti um nada tive que voltar para casa de uber e e deixar a moto no local rezando para no outro dia está lá tudo certo um absurdo pago pelo serviço e ocorreu isso quero posicionamento as 23.30 não tinha nada de reboque sugeriu solicitar particular mas eu não sabia de nenhum ainda mais para eu pagar absurdo sem ter dinheiro mo momento a noite.  Solicito solução devido ao constrangimento pois pago todos os meses</t>
+  </si>
+  <si>
+    <t>95450326</t>
+  </si>
+  <si>
+    <t>240538003</t>
+  </si>
+  <si>
+    <t>12/02/2026 10:42</t>
+  </si>
+  <si>
+    <t>134073688</t>
+  </si>
+  <si>
+    <t>Meu seguro é 24h. Meu carro deu uma pane, nao ligava. Chamei o seguro, tive dificuldade p o contato. Era próximo de 24h do dia 4 de fevereiro. Ninguém veio e fui informada q somente no dia seguinte às 8h alguem poderia comparecer. Isso foi resolvido quase 2h da manha. Fiquei sozinha na rua e sem recurso. O carro nao trancava._x000D_
+_x000D_
+_x000D_
+Ninguem me ligou no dia seguinte e abri novo chamado. Gerou mto transtorno. Agendaram, me informando q iriam. Esperei cerca de 40mim e depois recebi um comunicado q so iriam cerca de 1h30 depois._x000D_
+_x000D_
+_x000D_
+Dispensei o serviço e resolvi particular. Péssimo atendimento! Infelizmente.</t>
+  </si>
+  <si>
+    <t>95450044</t>
+  </si>
+  <si>
+    <t>240537309</t>
+  </si>
+  <si>
+    <t>12/02/2026 10:37</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Canal de Atendimento ; Corretor ; 1 Segurado ; Não ; Sim ; Sem Resposta - Dentro SLA ; Repasse Time MindBe</t>
   </si>
   <si>
     <t>Andreza</t>
   </si>
   <si>
-    <t>303478531</t>
-  </si>
-  <si>
-    <t>Queria registrar uma reclamação, sobre essa seguradora. Houve um sinistro dia 14 de dezembro, meu carro foi entregue dia 16 de janeiro, rateando e com a luz do freio ABS ligada.  Segundo o proprietário da oficina, era a gasolina, portanto, coloquei a gasolina aditivada, e o carro permaneceu na garagem. Em fevereiro quando iniciou se o período de aulas, o carro continuou com o mesmo problema, perdendo força, meu marido viu que não havia líquido de arrefecimento,voltei na oficina, e colocaram o líquido,continuou com o problema, meu esposo viu q a mangueira de entrada de ar do motor estava rasgada( acreditamos q seja pela batida,ou por troca do peças) voltei na oficina, o dono da oficina passou FITA ISOLANTE, e o carro continua na garagem, sem poder andar. O seguro foi informado desde o dia 02 de fevereiro, dos diversos acontecimentos, pediu 48 horas venceu, pediu 24 horas venceu, agora pediu 7 dias. e nada da reabertura de vistoria. Meu carro chegou na oficina ANDANDO e saiu sem condições de andar, quase fundiu o motor por irresponsabilidade da oficina, e a seguradora não faz nada a respeito. Nem em contato comigo ela entrou. O valor foi pago de forma única e as parcelas do seguro continuam a ser descontadas, mas meu carro está parado sem condições de uso .. Um absurdo esse descaso.</t>
-  </si>
-  <si>
-    <t>95402527</t>
-  </si>
-  <si>
-    <t>240403109</t>
-  </si>
-  <si>
-    <t>11/02/2026 06:32</t>
-  </si>
-  <si>
-    <t>Allianz ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; 1 Segurado ; Pagamento ; Apólice ; Automóvel ; Apólice</t>
-  </si>
-  <si>
-    <t>132031718</t>
-  </si>
-  <si>
-    <t>Cobrança indevida, _x000D_
-_x000D_
-Recebi boleto no DDA do Nubank, vencimento 23/02/26 valor R$ 148,28, desconheço dívida favor posionar a que se refere. Não autorizo uso do cpf</t>
+    <t>132745868</t>
+  </si>
+  <si>
+    <t>Contratei a cobertura adicional de Pequenos Reparos no seguro da minha motocicleta, mediante pagamento adicional, acreditando tratar-se de cobertura para danos de pequena monta que não caracterizassem sinistro de grande valor._x000D_
+_x000D_
+_x000D_
+Ao acionar a cobertura, fui informada de que ela contempla exclusivamente mão de obra, não incluindo a substituição de peças  independentemente do valor._x000D_
+_x000D_
+_x000D_
+O problema é que essa limitação não é informada de forma clara e objetiva no momento da contratação. Para descobrir que a cobertura não inclui peças, o consumidor precisa acessar as Condições Gerais, um documento extenso (mais de 100 páginas), localizar a seção específica e identificar a exclusão dentro do conteúdo._x000D_
+_x000D_
+_x000D_
+A nomenclatura Pequenos Reparos leva naturalmente ao entendimento de que se trata de reparos de baixo custo, e não exclusivamente de serviços sem possibilidade de troca de peça._x000D_
+_x000D_
+_x000D_
+No meu caso, os danos ocorreram nas peças plásticas externas da motocicleta. Após avaliação realizada por profissional independente, fui informada de que não há viabilidade técnica de reparo adequado, sendo necessária a substituição das peças._x000D_
+_x000D_
+_x000D_
+O orçamento total é de R$ 1.322,74, sendo:_x000D_
+_x000D_
+R$ 972,74 em peças_x000D_
+_x000D_
+R$ 350,00 em mão de obra_x000D_
+_x000D_
+_x000D_
+Considerando que praticamente toda a parte externa da motocicleta é composta por plástico, a limitação imposta torna a cobertura contratada praticamente ineficaz para meu veículo._x000D_
+_x000D_
+_x000D_
+Já registrei reclamação diretamente com a seguradora, na Ouvidoria e no Consumidor.gov (atendimento n OUV_264_2026), sem solução efetiva._x000D_
+_x000D_
+_x000D_
+Solicito reavaliação do caso à luz do dever de informação clara e da boa-fé contratual, pois a cobertura contratada, na prática, não atende à finalidade esperada pelo consumidor.</t>
+  </si>
+  <si>
+    <t>95446308</t>
+  </si>
+  <si>
+    <t>240526963</t>
+  </si>
+  <si>
+    <t>12/02/2026 09:21</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Sinistro ; Sem Resposta - Dentro SLA ; Repasse Time MindBe ; 1 Segurado ; Automóvel ; Análise Sinistro ; Não ; Sim</t>
+  </si>
+  <si>
+    <t>304033519</t>
+  </si>
+  <si>
+    <t>Desde que abri meu sinistor por uma queda sofrida com minha moto tive algumas dificuldades, o perito não foi a vistroria na concessionaria onde a moto se encontrava dentro do prazo da seguradora e no sistema de aqcompanhamento marcou que a moto não se encontrava la sendo que ja estava la desde o dia seguinte a queda, apos 10 dias do inicio do sinistro e dois contatos com a Allianz o perito foi ao local e aprovou a manutenção e solicitação de peças._x000D_
+_x000D_
+No sistema de acompanhamento de sinistro da Allianz não recebi mais nenhuma notificação so sendo informado pela concessionaria das atualizações._x000D_
+_x000D_
+A um pouco mais de uma semana, na quinta feira 05/02 minha moto teve os reparos finalizados, foi efetuada uma tentativa de contato pela concessionaria para que a vistoria final fosse realizada porem não obtiveram resposta, na sexta 06/02 as 8h foi efetuado meu primeiro contato via whatsapp o sistema robotico me informou que não existiam sinistro na minha opolice de seguro, mesmo com o numero dela informado, o atendente que falou comigo apos o robo foi capaz de a encontrar, confirmou comigo duas vezes se a moto realmente ja estava pronta e agendou a vistoria para até a segunda dia 09/02._x000D_
+_x000D_
+No dia 09/02 não aconteceu a vistoria e apos contato via telefone a atendente fou que um novo agendamento foi reaizado para odia 10/02 e que minha solicitação foi escalonada para um supervisor, neste mesmo dia responderam o e-mai lde contato com a concessionaria onde informaram que tambem agendaram uma vistoria para o dia 10/02, quando a mesma não ocorreu novamente foi feito novo contato e novo agendamento para o dia 11/02, no periodo da tarde do dia 11/02 sem contato com o perito tentei novamente contato porem me informaram que como ainda tinha tempo não podiam fazer nada. Hoje 12/02 foi efetuado novo contato na parte da manhã onde me informaram que hoje mesmo seria feita a vistoria e que a supervisão foi notificada. _x000D_
+_x000D_
+Tentei contato com a ouvidoria tambem hoje mas fui informado que como não existem protocolos para os atendimentos nem um conflito a ser resolvido o problema não era com eles._x000D_
+_x000D_
+Como não sei mais a quem recorer aqui reclamo.</t>
+  </si>
+  <si>
+    <t>95445576</t>
+  </si>
+  <si>
+    <t>240524963</t>
+  </si>
+  <si>
+    <t>12/02/2026 09:03</t>
+  </si>
+  <si>
+    <t>135615380</t>
+  </si>
+  <si>
+    <t>Há aproximadamente 2 meses eu solicitei a assistência 24 para a minha lava louças. O técnico veio e pediu para levar a máquina para maiores análises. E, desde então, nunca mais tive um contato da seguradora ou do técnico. Eu já entrei em contato com a seguradora pelo whatsapp muitas vezes. Sempre dizem que vão verificar e nunca dão retorno. Há uns 15 dias finalmente alguém conseguiu me atender e disse que a máquina estava aguardando a aprovação do orçamento (que eu nunca recebi e não sabia de nada.. nunca entraram em contato comigo). _x000D_
+_x000D_
+Eu aprovei de imediato o orçamento de R$ 890 reais, mesmo sem nenhum descritivo formal do que tinha sido identificado.. apenas um "queimou uma placa". e agendei o retorno da máquina. No dia agendado, fiquei em casa esperando.. e nada. Nenhuma notícia da máquina. Depois disso voltei 3 vezes a procurar o atendimento. Sempre dizem que vão ter que consultar e que me enviarão um sms. Nunca recebi nada._x000D_
+_x000D_
+Hoje entrei em contato novamente e a assistente foi, pela primeira vez, indelicada e nem quis entender a demanda, apenas mandou a mesma mensagem padrão de depois continua num SMS._x000D_
+_x000D_
+Nunca recebi SMS, e agora ainda fui destratado pelo atendimento._x000D_
+_x000D_
+Quero minha maquina, pelo orçamento aprovado, e atenção digna por parte da seguradora, que NUNCA entra em contato e agora é indelicada. Não sei mais a quem recorrer. e fortemente ponho em dúvida se esta é a seguradora que eu deveria confiar.</t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1235,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AA8803-373C-4E0C-ABA8-1F171C96DA02}">
-  <dimension ref="A1:AA22"/>
+  <dimension ref="A1:AA17"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="3" bestFit="1" customWidth="1" collapsed="1"/>
@@ -1214,34 +1380,34 @@
         <v>35</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y2" s="3" t="s">
         <v>26</v>
@@ -1251,13 +1417,13 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>30</v>
@@ -1266,46 +1432,46 @@
         <v>31</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>49</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y3" s="3" t="s">
         <v>26</v>
@@ -1315,13 +1481,13 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>30</v>
@@ -1330,46 +1496,46 @@
         <v>31</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Y4" s="3" t="s">
         <v>26</v>
@@ -1379,13 +1545,13 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>30</v>
@@ -1394,46 +1560,46 @@
         <v>31</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Y5" s="3" t="s">
         <v>26</v>
@@ -1443,13 +1609,13 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>30</v>
@@ -1458,46 +1624,46 @@
         <v>31</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Y6" s="3" t="s">
         <v>26</v>
@@ -1507,13 +1673,13 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>30</v>
@@ -1522,46 +1688,46 @@
         <v>31</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Y7" s="3" t="s">
         <v>26</v>
@@ -1571,13 +1737,13 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>30</v>
@@ -1586,7 +1752,7 @@
         <v>31</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>33</v>
@@ -1595,37 +1761,37 @@
         <v>34</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>26</v>
@@ -1635,13 +1801,13 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>30</v>
@@ -1650,46 +1816,46 @@
         <v>31</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>26</v>
@@ -1699,13 +1865,13 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>30</v>
@@ -1714,46 +1880,46 @@
         <v>31</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>26</v>
@@ -1761,13 +1927,13 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>30</v>
@@ -1776,46 +1942,46 @@
         <v>31</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Y11" s="3" t="s">
         <v>26</v>
@@ -1823,13 +1989,13 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>30</v>
@@ -1838,7 +2004,7 @@
         <v>31</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>33</v>
@@ -1847,37 +2013,37 @@
         <v>34</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V12" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="W12" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="W12" s="3" t="s">
+      <c r="X12" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="X12" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>26</v>
@@ -1885,13 +2051,13 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>30</v>
@@ -1900,7 +2066,7 @@
         <v>31</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>33</v>
@@ -1909,37 +2075,37 @@
         <v>34</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="K13" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="W13" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="X13" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="V13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="W13" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="X13" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="Y13" s="3" t="s">
         <v>26</v>
@@ -1947,13 +2113,13 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>30</v>
@@ -1962,46 +2128,46 @@
         <v>31</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>131</v>
+        <v>31</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>26</v>
@@ -2009,13 +2175,13 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>30</v>
@@ -2024,7 +2190,7 @@
         <v>31</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>33</v>
@@ -2033,67 +2199,165 @@
         <v>34</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
+      <c r="A16" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="W16" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="X16" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y16" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="17" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
-    </row>
-    <row r="18" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W18" s="4"/>
-    </row>
-    <row r="19" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
-    </row>
-    <row r="20" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W20" s="4"/>
-      <c r="X20" s="4"/>
-    </row>
-    <row r="21" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W21" s="4"/>
-    </row>
-    <row r="22" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W22" s="4"/>
-      <c r="X22" s="4"/>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AN9" xr:uid="{D3AA8803-373C-4E0C-ABA8-1F171C96DA02}"/>

--- a/Treinamento/GestaoReclamacao.xlsx
+++ b/Treinamento/GestaoReclamacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86FB23B-5E90-4481-B380-F2C8EDCE3F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9E8668-D1BF-494D-B481-4BDDE8F7E3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B1A77FD5-2AD3-4458-ACB3-7F19D1A3340A}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="GestaoReclamacao" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GestaoReclamacao!$A$1:$AN$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GestaoReclamacao!$A$1:$AN$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="103">
   <si>
     <t>Id HugMe</t>
   </si>
@@ -119,161 +119,303 @@
     <t xml:space="preserve">Resultado </t>
   </si>
   <si>
+    <t>Processar</t>
+  </si>
+  <si>
+    <t>95591799</t>
+  </si>
+  <si>
+    <t>240942843</t>
+  </si>
+  <si>
+    <t>18/02/2026 09:01</t>
+  </si>
+  <si>
     <t>Não respondido</t>
   </si>
   <si>
     <t>Não</t>
   </si>
   <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Assistência Não Danos ; Vidros - AutoGlass ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; 1 Segurado ; Assistência Residencial ; SAC Aberto ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
     <t>Allianz</t>
   </si>
   <si>
+    <t>Apólice</t>
+  </si>
+  <si>
+    <t>Automóvel</t>
+  </si>
+  <si>
+    <t>Assistência Não Danos</t>
+  </si>
+  <si>
+    <t>Assistência Residencial</t>
+  </si>
+  <si>
+    <t>1 Segurado</t>
+  </si>
+  <si>
+    <t>SAC Aberto</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Repasse Time MindBe</t>
+  </si>
+  <si>
+    <t>Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Juliana</t>
+  </si>
+  <si>
+    <t>135166100</t>
+  </si>
+  <si>
+    <t>No dia 26/01 foi encaminhado documentação para análise reembolso, porém até a data de hoje, o setor de assistência não analisou a o documento a documentação e muito menos realizou o reembolso. Fazendo com que até o momento eu ficasse sem o valor que o desembolse por uma ineficiência no sistema de assistência da Allianz.</t>
+  </si>
+  <si>
+    <t>95590747</t>
+  </si>
+  <si>
+    <t>240939947</t>
+  </si>
+  <si>
+    <t>18/02/2026 08:20</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Residência ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Sinistro ; Análise Sinistro</t>
+  </si>
+  <si>
     <t>Sinistro</t>
   </si>
   <si>
-    <t>Automóvel</t>
-  </si>
-  <si>
-    <t>Assistência Não Danos</t>
-  </si>
-  <si>
-    <t>Vidros - AutoGlass</t>
-  </si>
-  <si>
-    <t>1 Segurado</t>
-  </si>
-  <si>
-    <t>Sim</t>
-  </si>
-  <si>
-    <t>Repasse Time MindBe</t>
-  </si>
-  <si>
-    <t>Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Juliana</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 2 Terceiro do Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+    <t>Residência</t>
   </si>
   <si>
     <t>Análise Sinistro</t>
   </si>
   <si>
+    <t>305042073</t>
+  </si>
+  <si>
+    <t>Abri um sinistro desde de o dia 13/01, envie todas as documentações e orçamento e ate agora não recebi._x000D_
+_x000D_
+Moro sozinha, estou sem motor do portão, sem as cameras._x000D_
+_x000D_
+Pagamos um seguro para ser RAPIDO, e ate agora não resolveram meu problema.</t>
+  </si>
+  <si>
+    <t>95589312</t>
+  </si>
+  <si>
+    <t>240935779</t>
+  </si>
+  <si>
+    <t>18/02/2026 03:32</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Canal de Atendimento ; Corretor ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Reclamante em nome do Segurado</t>
+  </si>
+  <si>
+    <t>Canal de Atendimento</t>
+  </si>
+  <si>
+    <t>Corretor</t>
+  </si>
+  <si>
+    <t>Reclamante em nome do Segurado</t>
+  </si>
+  <si>
+    <t>134774861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espirito Santo do Pinhal.  13/02/2026_x000D_
+_x000D_
+Tenho Um Fox 2009 Modelo 2010. Desde que o  comprei eu tenho seguro, com uma vendedora chamada Patrícia aqui de Espirito Santo do Pinhal-SP. Não sei se ela sempre trabalhou pela Seguradora Allianz, se trabalhava para outra seguradora, o fato é que meu Pai Honorato **** da Costa, CPF 040.***.***-08  sempre foi fiel a essa vendedora Patricia, desde que compramos o carro confiamos nela sobre o seguro do Fox. _x000D_
+_x000D_
+No dia 23/jan/2026 tivemos um incidente e batemos num carro, quebrando o retrovisor deste, o dono nos contatou, ligamos para a Patricia que trabalha para a  Allianz responsável pelo seguro do nosso Fox no dia 26/jan/2026 ela pediu todos os dados, o que aconteceu, pediu o documento do carro, as fotos do nosso carro e do carro do terceiro mandamos para ela. No dia 30 de Janeiro de 2026 ela diz que o sinistro foi aberto e esta tudo encaminhado. Ficamos sossegados. _x000D_
+_x000D_
+06/FEV/2026 ficamos sabendo pelo terceiro, que houve um problema na cobertura do seguro, um problema no pagamento lá em novembro de 2025, FICAMOS SABENDO PELO TERECEIRO QUE NOSSO CARRO ESTAVA DESCOBERTO DE SEGURO. Pelo que nosso advogado orientou o que aconteceu foi ilegal e abusivo, liguei para a Patricia ela disse que mandou mensagem no WhatsApp de fato ela mandou, mas não vimos a mensagem em MOMENTO ALGUM houve uma conversa que o SEGURO HAVIA SIDO CANCELADO. Que falta de respeito é essa que um assunto num nível tão serio foi conversado de maneira tão indiferente para ser enviado via WhastApp? Desde outrubro do ano passado minha família vem enfrentando problemas de saúde (PROBLEMA EXCLUSIVO NOSSO, NINGUEM TEM NADA A VER COM ISSO) mas se não houve resposta no aplicativo de conversa e não regularizamos o pagamento, Patricia não nos contatou, nem no telefone fixo, ela alegou que não tem nosso telefone fixo, como alguém que é responsável pelo seguro do nosso carro há mais de dez anos não tem nosso telefone fixo? Durante a ligação Patricia  foi rude, hostil, grossa, disse que não tem como saber qual cliente esta doente ou não, uma grosseria, e um total constrangimento a nós clientes a mais de uma década. O modo como ela tratou minha mãe Terezinha de F***  L**** Costa foi um tom alterado, rude, totalmente constrangedor.  esse comportamento vai contra o Codigo de Defesa do Consumidor: Vendedor que constrange, (..)  expõe cliente ao ridículo viola o Código de Defesa do Consumidor (art. 42). E foi exatamente isso que a Patricia e seguradora Allianz  fez: expos meu Pai, minha mãe ao ridículo, por sabermos somente pelo terceiro que houve falha no pagamento e o carro estava descoberto. Não houve nenhum contato direto da Vendedora de Seguros da Allianz, Patricia com ninguém dessa família. Um assunto tão serio que envolve seguro de carro não devia ser tratado como conversa de aplicativo, Leu a mensagem, leu. Não Leu Paciencia É essa a mensagem e imagem que a seguradora Allianz transmite? Um assunto tão serio como fofoca de aplicativo? Ao ser questionada por que não ligou no telefone fixo onde era certeza encontrar alguém e conversar diretamente a resposta de Patricia foi: Não tenho o telefone fixo de voces uma década sendo a responsável pelo seguro do carro com todos os nossos dados ela não tem o fixo e nunca pensou em acrescentar no nosso cadastro. _x000D_
+_x000D_
+Que TOTAL FALTA DE RESPEITO SEGURADORA ALLIANZ. _x000D_
+_x000D_
+Vocês violaram o código de defesa do consumidor, estava disposta a pagar o seguro até por boleto mesmo com juros altíssimos para termos o sossego do carro estar assegurado. Nunca houve uma conversa entre a Patricia e minha família: onde ela esclarece o que houve, sabe o que temos? Uma mensagem no WhatsApp que pode ser apagada a qualquer hora. Sempre pagamos o seguro com a maior satisfação, agora na hora que precisamos a ALLIANZ e sua funcionaria Patricia de ESPIRITO SANTO DO PINHAL-SP nos notificarem do que aconteceu nos deixaram na mão, o CANCELAMENTO DO SEGURO SEM AVISO PRÉVIO é considerado ilegal e abusivo, violando o Código de Defesa do Consumidor (CDC) e jurisprudência do STJ (Súmula 616), pois a seguradora deve notificar o segurado antes de suspender ou encerrar o contrato. A nova Lei de Seguros (15040/2024) reforça que é proibido o cancelamento automático por falta de pagamento sem notificação, exceto no não pagamento da primeira parcela ou de parcela única. A primeira parcela foi o paga. O maior problema de tudo isso foi a hostilidade da Patricia funcionaria da ALLIANZ, NÃO HOUVE CONTATO, NÃO HOUVE CONVERSA. HOUVE FALTA DE RESPEITO COMIGO E MEUS PAIS. Que se encontram num momento de total fragilidade pela saúde da minha mãe e toda chateação e perturbação, e todo constrangimento que se deu pelo comportamento malcriado, ofensivo, difamatório (ela afirmou que vimos a mensagem e não respondemos), humilhante, afrontoso e insolente de Patricia, funcionaria da Allianz. _x000D_
+_x000D_
+</t>
+  </si>
+  <si>
+    <t>95584900</t>
+  </si>
+  <si>
+    <t>240921965</t>
+  </si>
+  <si>
+    <t>17/02/2026 20:04</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Guincho</t>
+  </si>
+  <si>
+    <t>132258710</t>
+  </si>
+  <si>
+    <t>Negativa indevida de assistência em situação de risco  descumprimento contratual_x000D_
+_x000D_
+_x000D_
+Durante o feriado de Carnaval, eu estava em viagem ao Rio de Janeiro e, ao iniciar o deslocamento de retorno para São Paulo, identifiquei o estouro/furo de um dos pneus do veículo segurado. De imediato, estacionei o automóvel e realizei a substituição pelo estepe temporário, adotando as medidas mínimas de segurança._x000D_
+_x000D_
+_x000D_
+Na sequência, busquei atendimento em borracharias próximas. As duas primeiras estavam fechadas em razão do feriado prolongado. A terceira realizou a avaliação técnica e constatou que o pneu não possuía reparo, além de não haver disponibilidade de pneu compatível com o veículo. Continuei tentando outros estabelecimentos, sem sucesso, seja por estarem fechados, seja por ausência de estoque adequado._x000D_
+_x000D_
+_x000D_
+Ressalto que eu me encontrava em região de reconhecida periculosidade no Rio de Janeiro, não sendo razoável nem seguro permanecer com o veículo imobilizado por tempo indeterminado, tampouco circular aleatoriamente em busca de locais desconhecidos. Diante desse cenário, segui deslocamento mínimo apenas para sair da área de risco e acionei a seguradora Allianz, ciente de que não é permitido nem seguro realizar trajeto rodoviário superior a 400 km com estepe temporário, conforme orientação do fabricante e normas básicas de segurança veicular._x000D_
+_x000D_
+_x000D_
+Solicitei, então, remoção do veículo por guincho, seja para a cidade de São Paulo, seja para local onde fosse possível efetuar o reparo adequado. Contudo, a seguradora negou a abertura do atendimento, sob a justificativa de que o veículo possuía condição de rodar, desconsiderando que tal condição era precária, emergencial e insegura, além de incompatível com viagem de longa distância._x000D_
+_x000D_
+_x000D_
+A negativa se estendeu inclusive ao serviço de borracheiro, o que evidencia absoluta falta de razoabilidade e de avaliação do contexto fático apresentado. Registrei expressamente que não possuía condições seguras de seguir viagem, que não conhecia a região e que havia risco concreto à minha integridade física, mas tais argumentos foram ignorados._x000D_
+_x000D_
+_x000D_
+Foram realizadas duas ligações ao atendimento regular e uma ao SAC, sem que qualquer atendimento fosse aberto, solução apresentada ou alternativa oferecida. Em nenhum momento houve análise individualizada do risco, tampouco observância do dever de assistência ao segurado em situação emergencial._x000D_
+_x000D_
+_x000D_
+A conduta da seguradora caracteriza falha na prestação do serviço, em desacordo com os princípios da boa-fé objetiva, da função social do contrato e da proteção ao consumidor, conforme o Código de Defesa do Consumidor. A assistência 24h existe justamente para amparar o segurado em situações excepcionais, e não para se limitar a interpretações restritivas e automáticas que colocam o consumidor em risco._x000D_
+_x000D_
+_x000D_
+Diante do exposto, registro minha indignação com o descaso e a negativa indevida de assistência, esperando providências, esclarecimentos formais e reparação adequada pela falha ocorrida.</t>
+  </si>
+  <si>
+    <t>95578162</t>
+  </si>
+  <si>
+    <t>240901665</t>
+  </si>
+  <si>
+    <t>17/02/2026 14:19</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Condomínio ; Sinistro ; Indenização ; Litoral Norte SP ; RA ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Condomínio</t>
+  </si>
+  <si>
+    <t>Indenização</t>
+  </si>
+  <si>
+    <t>Litoral Norte SP</t>
+  </si>
+  <si>
+    <t>RA</t>
+  </si>
+  <si>
+    <t>274324875</t>
+  </si>
+  <si>
+    <t>Oi Allianz, boa tarde_x000D_
+_x000D_
+Como a empresa vai? Acredito que bem e fazendo sucesso com novos clientes. Entao.  passando aqui pra lembrar da tragedia em São Sebastião  no dia 19/2/2023 bem no carnaval. Pra Allianz pode nem fazer parte do memorial essa tragedia, mas pra mim sera sempre um trauma o que vivi la com a minha família  3 anos com a minha casa interditada pela defesa civil. Nao estou so com a minha casa interditada estou com minha vida tambem. Tenho um bem que nao posso usufruir. Que fui obrigada a pagar para fazer reparos para que o telhado nao caisse e fechar as paredes derrubadas pra evitar abrigo de animais . Duas cobras foram encontradas dentro da casa por estar sem paredes portas e janelas. Mas ai  o que a Allianz fez pelo cliente? NADA!  Ofereceu valores que nao condiz com o sinistro. E so tivemos uma opcao entrar com uma ação. Ai vc vai me falar como existe uma acao nao posso te responder. Entendo. Nao aceito, mas entendo. So pra lembrar meu marido quase morreu soterrado, ficou com sequela no ombro. Eu minha filha, minha nora e meu sobrinho tembem ficamos com sequela emocional. TRAUMA! Mas o que a Allianz tem que ver com isso ne? Nna verdade NADA. Mas poderia ter sido mais empatica em resolver um problema causado por uma tragedia ninca visto no Brasil mais de 600 milometros de agua e 66 mortes. O mundo soube! mas a Allianz virou de costas. Foi mais bacana colocar que enviou guinchos para retirar os veiculos que ficaram alagados do que arcar com idoneidade de uma empresa em pagar pelo sinistro no condominio em pelas casas destruidas._x000D_
+_x000D_
+O Residencial Flat Parque dos Colibris e um condominio horizontal e nossa apolice era Ampla total. Toda area do condominio mais as 40 unidades. Nosso condominio está td em ordem frente a prefeitura. Plantas, Hábits,  IPTU, taxas td certinho. Nosso seguro estava pago td conforme a lei diz. E a empresa Allianz so na negativa. _x000D_
+_x000D_
+Que pena! Gostaria de falar que vcs foram muito humanos com nos os atingidos pela tragédia, mas infelizmente nao e essa a minha realidade._x000D_
+_x000D_
+Tenham um bom feriado  de carnaval coisa que minha familia nao tem faz tempo_x000D_
+_x000D_
+_x000D_
+Myrian _x000D_
+_x000D_
+Unidade 32 _x000D_
+_x000D_
+Casa interditada pela Defesa Civil</t>
+  </si>
+  <si>
+    <t>95577019</t>
+  </si>
+  <si>
+    <t>240898287</t>
+  </si>
+  <si>
+    <t>17/02/2026 13:29</t>
+  </si>
+  <si>
+    <t>Allianz ; CPF/CNPJ ; Automóvel ; Canal de Atendimento ; Comercial ; 11 Não Cliente ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>CPF/CNPJ</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>11 Não Cliente</t>
+  </si>
+  <si>
+    <t>246309398</t>
+  </si>
+  <si>
+    <t>ESTOU TENTANDO FAZER UM CADASTRO DE MINHA EMPRESA COMO PRESTADOR DE ASSISTENCIA 24 HS . _x000D_
+_x000D_
+MAS NÃO ENCONTRO NOS SITES E LINKS DISPONIBILIZADOS A OPÇÃO PARA PRESTADOR DE SERVIÇOS GUINCHO 24HS, SO LOCALIZEI OFICINAS PARA CREDENCIAR; NÃO TEM UM CHAT, ZAP, EMAIL QUE POSSA FORMULAR A PERGUNTA PARA ;_x000D_
+_x000D_
+TENHO UM UMA PLATAFORMA GUINCHO PARA PRESTAR SERVIÇOS E GOSTARIA DE FAZER PARTE DOS PRESTADORES DA ALLIANZ ; MAS TA DIFICIL OBRIGADO</t>
+  </si>
+  <si>
+    <t>95569650</t>
+  </si>
+  <si>
+    <t>240877747</t>
+  </si>
+  <si>
+    <t>17/02/2026 08:28</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; 2 Terceiro do Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Análise Sinistro</t>
+  </si>
+  <si>
     <t>2 Terceiro do Sinistro</t>
   </si>
   <si>
-    <t>Apólice</t>
-  </si>
-  <si>
-    <t>Guincho</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Cancelamento ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Cancelamento</t>
-  </si>
-  <si>
-    <t>Prezados,_x000D_
-_x000D_
-Venho por meio deste solicitar o cancelamento do meu seguro automóvel, conforme dados abaixo:_x000D_
-_x000D_
-_x000D_
-Nome Completo: Ana Carolina Oliveira Pereira_x000D_
-_x000D_
-CPF: 484.177.528-54_x000D_
-_x000D_
-Data da Solicitação: 17/02/2026_x000D_
-_x000D_
-Marca e Modelo do Veículo: Fiat Argo_x000D_
-_x000D_
-Placa do Veículo: RFQ7E37_x000D_
-_x000D_
-Motivo do Cancelamento: Reorganização financeira em razão do encerramento do meu contrato de trabalho, sendo necessária a redução imediata de despesas._x000D_
-_x000D_
-_x000D_
-Informo que a parcela referente ao mês atual já foi paga pelo cartão de crédito. Solicito, portanto, a apuração de eventual valor proporcional a ser restituído, considerando o período não utilizado da cobertura._x000D_
-_x000D_
-_x000D_
-Caso haja devolução, os dados bancários para depósito são:_x000D_
-_x000D_
-_x000D_
-Banco: Banco do Brasil_x000D_
-_x000D_
-Agência: 5631-6_x000D_
-_x000D_
-Conta: 5949-8_x000D_
-_x000D_
-_x000D_
-Peço, por gentileza, a confirmação formal do cancelamento, bem como informação sobre prazo para efetivação e eventual multa contratual._x000D_
-_x000D_
-_x000D_
-Fico no aguardo do retorno._x000D_
-_x000D_
-_x000D_
-Atenciosamente,_x000D_
-_x000D_
-Ana Carolina Oliveira Pereira</t>
-  </si>
-  <si>
-    <t>Sou terceiro envolvido em um sinistro e estou com meu veículo aguardando reparo/ por responsabilidade do seguro Allianz (seguradora do condutor/segurado responsável)._x000D_
-_x000D_
-_x000D_
-No atendimento, fui orientado a aguardar do dia 20/01 até 12/02 para a chegada das peças necessárias. O prazo informado já venceu e, desde então, não recebo retorno objetivo, não me informam status das peças, nem nova previsão real de entrega e conclusão._x000D_
-_x000D_
-_x000D_
-Estou sendo prejudicado com o veículo parado/sem solução, arcando com transtornos e perdendo tempo com tentativas de contato sem respostas efetivas._x000D_
-_x000D_
-_x000D_
-Solicito com urgência:_x000D_
-_x000D_
-_x000D_
-Atualização formal do status das peças (se foram aprovadas, compradas, enviadas, se chegaram e onde estão)._x000D_
-_x000D_
-_x000D_
-Novo prazo real para chegada das peças e finalização do reparo, com datas._x000D_
-_x000D_
-_x000D_
-Caso não exista prazo viável, solução imediata alternativa, como:_x000D_
-_x000D_
-_x000D_
-mudança de fornecedor/peça equivalente disponível, ou_x000D_
-_x000D_
-_x000D_
-outra forma de resolução para não prolongar indefinidamente o conserto.</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; 1 Segurado ; Não ; Sim ; Sem Resposta - Dentro SLA ; Repasse Time MindBe</t>
-  </si>
-  <si>
-    <t>Demora para chegada do grincho</t>
-  </si>
-  <si>
-    <t>Abri um sinistro na área Sinistro Digital do site da Allianz. Escolhi uma oficina, agendei a vistoria e, depois, ao telefonar para a oficina para confirmar o serviço, fui informada que lá o tipo de serviço que preciso não é realizado. Entrei no site da Allianz para tentar cancelar o agendamento nesta oficina e marcar em outra, onde o serviço específico necessário é realizado. Não tem link para fazer isso. Entrei no fale com Analista, e nada, nenhuma resposta. Entrei no whatsapp e não fui atendida conforme arquivo anexado. Procurei de diferentes formas, sem sucesso, Site pouco amigável, com ausência de informações, atendimento inexistente. Nunca mais faço seguro com a Allianz, MAS AGORA PRECISO SER ATENDIDA NESTE SINISTRO.</t>
-  </si>
-  <si>
-    <t>Processado</t>
-  </si>
-  <si>
-    <t>Cadastro correto, processo: 26/0002532.</t>
-  </si>
-  <si>
-    <t>Cadastro correto, processo: 26/0002533.</t>
-  </si>
-  <si>
-    <t>Cadastro correto, processo: 26/0002534.</t>
+    <t>304440631</t>
+  </si>
+  <si>
+    <t>Estou abrindo essa reclamação porque já entrei em contato com Allianz tentando resolver a questão do valores do LC, referente ao meus 2 dias para por causa do acidente, Esse valor que me foi analisado pra mim não passa de esmola, querer me pagar 86 reais por dia, e desconta aí 40% de gasolina e manutenção não sabia que Allianz pagava minha gasolina, não vou aceitar esse valor o mínimo é 300 por dia tenho no anexo foto dos valores que faço por dia, 304440631 esse é o número do sinistro _x000D_
+_x000D_
+Espero que alguém desse empresa tenha ciência porque esse dois dias que não trabalhei me trouxe prejuízo</t>
+  </si>
+  <si>
+    <t>95567873</t>
+  </si>
+  <si>
+    <t>240872531</t>
+  </si>
+  <si>
+    <t>17/02/2026 01:06</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; 2 Terceiro do Sinistro ; SAC Aberto</t>
+  </si>
+  <si>
+    <t>135670704</t>
+  </si>
+  <si>
+    <t>Acionei o.seguro sobre protocolo 51431680 as 22:24 sendo que as 23:29 estavam procurando prestador maos ee 60 min além.de inúmeros ligacoes eu ja nervoso falei muito e ate usei palavras de baixo calão pelo desprezo pelo segurado que paga suas parcelas em.dia e no dia que precisa nao é  atendido irei entrar com ação na justiça pelo descaso com o segurado e removi meu veículo por meios  próprios pois a segurado se quiser teve a simpatia de oferecer pois estava em outra cidade</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -298,11 +440,6 @@
       <color rgb="FFFFFF00"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="5">
@@ -331,7 +468,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -365,26 +502,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -395,20 +517,14 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="22" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -744,7 +860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AA8803-373C-4E0C-ABA8-1F171C96DA02}">
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="3" bestFit="1" customWidth="1" collapsed="1"/>
@@ -850,308 +966,530 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AA1" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="409.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
-        <v>95565881</v>
-      </c>
-      <c r="B2" s="6">
-        <v>240866303</v>
-      </c>
-      <c r="C2" s="7">
-        <v>46069.909722222219</v>
-      </c>
-      <c r="D2" s="6" t="s">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="6" t="s">
+      <c r="Z2"/>
+      <c r="AA2"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="W2" s="6">
-        <v>136548341</v>
-      </c>
-      <c r="X2" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="326.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
-        <v>95560326</v>
-      </c>
-      <c r="B3" s="6">
-        <v>240849325</v>
-      </c>
-      <c r="C3" s="7">
-        <v>46069.704861111109</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="V3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="W3" s="6">
-        <v>304747530</v>
-      </c>
-      <c r="X3" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>53</v>
-      </c>
+      <c r="Z3"/>
+      <c r="AA3"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
-        <v>95556549</v>
-      </c>
-      <c r="B4" s="6">
-        <v>240838371</v>
-      </c>
-      <c r="C4" s="7">
-        <v>46069.601388888892</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="A4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="W4" s="6">
-        <v>136364103</v>
-      </c>
-      <c r="X4" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>54</v>
-      </c>
+      <c r="Z4"/>
+      <c r="AA4"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
-        <v>95553299</v>
-      </c>
-      <c r="B5" s="6">
-        <v>240828825</v>
-      </c>
-      <c r="C5" s="7">
-        <v>46069.517361111109</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="A5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="W5" s="6">
-        <v>305791854</v>
-      </c>
-      <c r="X5" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>51</v>
-      </c>
+      <c r="Z5"/>
       <c r="AA5"/>
     </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="X6" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z6"/>
+      <c r="AA6"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="X7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z7"/>
+      <c r="AA7"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="X8" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z8"/>
+      <c r="AA8"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="X9" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z9"/>
+      <c r="AA9"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN5" xr:uid="{D3AA8803-373C-4E0C-ABA8-1F171C96DA02}"/>
+  <autoFilter ref="A1:AN9" xr:uid="{D3AA8803-373C-4E0C-ABA8-1F171C96DA02}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Treinamento/GestaoReclamacao.xlsx
+++ b/Treinamento/GestaoReclamacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9E8668-D1BF-494D-B481-4BDDE8F7E3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489CEA6D-13C7-4854-9275-4779BF25EAD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B1A77FD5-2AD3-4458-ACB3-7F19D1A3340A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="116">
   <si>
     <t>Id HugMe</t>
   </si>
@@ -122,13 +122,13 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>95591799</t>
-  </si>
-  <si>
-    <t>240942843</t>
-  </si>
-  <si>
-    <t>18/02/2026 09:01</t>
+    <t>95628000</t>
+  </si>
+  <si>
+    <t>241043317</t>
+  </si>
+  <si>
+    <t>19/02/2026 07:20</t>
   </si>
   <si>
     <t>Não respondido</t>
@@ -137,7 +137,7 @@
     <t>Não</t>
   </si>
   <si>
-    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; 1 Segurado ; Assistência Residencial ; SAC Aberto ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Vidros - AutoGlass ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
     <t>Allianz</t>
@@ -152,62 +152,316 @@
     <t>Assistência Não Danos</t>
   </si>
   <si>
+    <t>Vidros - AutoGlass</t>
+  </si>
+  <si>
+    <t>1 Segurado</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Repasse Time MindBe</t>
+  </si>
+  <si>
+    <t>Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Juliana</t>
+  </si>
+  <si>
+    <t>133346487</t>
+  </si>
+  <si>
+    <t>Bom dia. Eu tenho um seguro com a Allianz e eu contactei porque um motoqueiro bateu na lâmpada traseira do meu carro e arranhou e soltou a lanterna! Isso já tinha acontecido do outro lado do veículo. As lanternas foram coladas. A companhia de seguros me mandou um link para bater as fotos , mas os exemplos para mostrar não identificaram o problema, eu pedi para fazer uma vistoria e levei o carro na companhia de vidros! O rapaz da vistoria me Informou que as lanternas estavam quebradas e que o seguro iria trocar, me deu um prazo de uma semana se tiverem a peça! No mesmo dia recebi uma ligação do seguro me informando que a lanterna não estava quebrada e que não iriam pagar porque era causas naturais!  Como pode ser natural se as outras não estão? O carro tem 9000 km vive parado dentro de uma garagem coberta! O carro levou um golpe de motoqueiro quando parou no sinal. E o seguro não se responsabiliza porque o golpe não quebrou o vidro!</t>
+  </si>
+  <si>
+    <t>95624925</t>
+  </si>
+  <si>
+    <t>241034067</t>
+  </si>
+  <si>
+    <t>18/02/2026 23:04</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; Reclamante em nome do Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Guincho</t>
+  </si>
+  <si>
+    <t>Reclamante em nome do Segurado</t>
+  </si>
+  <si>
+    <t>135077835</t>
+  </si>
+  <si>
+    <t>Empresa me deixou na mão com o carro quebrado em região de risco, tarde da noite, com uma criança de 9 anos (avisei a atendente). Deram previsão de chegada de 30 minutos, mas demorou quase 1:30h. Não fossem os amigos nos acolherem, teríamos corrido risco de assalto, etc.</t>
+  </si>
+  <si>
+    <t>95622154</t>
+  </si>
+  <si>
+    <t>241025395</t>
+  </si>
+  <si>
+    <t>18/02/2026 20:59</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Residência ; Apólice ; Renovação ; 1 Segurado ; SAC Aberto ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Residência</t>
+  </si>
+  <si>
+    <t>Renovação</t>
+  </si>
+  <si>
+    <t>SAC Aberto</t>
+  </si>
+  <si>
+    <t>135972802</t>
+  </si>
+  <si>
+    <t>ano passado contratei um seguro residencial junto ao banco Banrisul, com vigência e prazo determinados. O contrato foi integralmente cumprido, as parcelas foram quitadas e o seguro foi encerrado normalmente._x000D_
+_x000D_
+_x000D_
+Após o término, optei por NÃO renovar o seguro com esta instituição, inclusive contratando um novo seguro residencial em outro banco._x000D_
+_x000D_
+_x000D_
+Para minha surpresa, neste ano o seguro foi renovado automaticamente, sem qualquer solicitação, autorização ou aceite da minha parte. Não houve assinatura de novo contrato, concordância expressa, nem autorização para renovação ou cobrança._x000D_
+_x000D_
+_x000D_
+Além da renovação indevida, foi realizado débito diretamente em minha conta bancária, que estava inativa. Isso fez com que a conta ficasse negativa, gerando cobrança de juros e encargos financeiros, causando prejuízo material._x000D_
+_x000D_
+_x000D_
+Ressalto que:_x000D_
+_x000D_
+_x000D_
+Comunicação unilateral não configura autorização de renovação;_x000D_
+_x000D_
+_x000D_
+A cobrança sem consentimento viola o Código de Defesa do Consumidor;_x000D_
+_x000D_
+_x000D_
+A instituição não pode impor renovação automática com ônus financeiro sem manifestação expressa do cliente._x000D_
+_x000D_
+_x000D_
+Diante do ocorrido, solicito:_x000D_
+_x000D_
+_x000D_
+Cancelamento imediato desta renovação indevida;_x000D_
+_x000D_
+_x000D_
+Estorno integral do valor debitado;_x000D_
+_x000D_
+_x000D_
+Ressarcimento dos juros e encargos gerados pela negativação da conta;_x000D_
+_x000D_
+_x000D_
+Confirmação formal de encerramento definitivo do seguro;_x000D_
+_x000D_
+_x000D_
+Garantia de que não haverá novas renovações automáticas sem autorização expressa._x000D_
+_x000D_
+_x000D_
+Aguardo solução com urgência, uma vez que houve cobrança indevida e prejuízo financeiro. Caso não haja resolução, tomarei as medidas cabíveis junto aos órgãos de defesa do consumidor.</t>
+  </si>
+  <si>
+    <t>95620654</t>
+  </si>
+  <si>
+    <t>241020569</t>
+  </si>
+  <si>
+    <t>18/02/2026 20:02</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Condições Gerais ; 1 Segurado ; Não ; Sem Resposta - Dentro SLA ; Sim ; Repasse Time MindBe</t>
+  </si>
+  <si>
+    <t>Condições Gerais</t>
+  </si>
+  <si>
+    <t>112177680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olá, dia 2 de novembro de 2025 t minha esposa teve um sinistro de trânsito em colisão danificando aporta do meu veículo do lado do motorista a porta do passageiro. Fiz uma pesquisa se compensava arruma particular ou acionar o seguro em dezembro entrei em contato com o corretor para aciona o seguro  o corretor deu vários endereços para eu levar o veículo , levei na empresa Marques e Marques que fica na av. Santo Amaro mas não gostei da vistoria que fizeram e optei para fazer em outra oficina credenciada fui na oficina 400 que fica no socorro e lá fizeram a vistoria e depois iria entra em contato comigo  passou uma semana a  não entrou em contato liguei lá e me informaram que a vistoria não foi aprovada, retornei para o meu corretor para sabe o que tinha acontecido fui informado que o sinistro não tinha atingido a franquia do meu carro sendo que a franquia é 6.340 e fiz os orçamentos ficou em 7,750 feito pela Hyundai e tbm pela uma oficina aonde arrumei o carro   Aí fica a questão pagar o seguro e quando precisei não fui atendido  e gastei dinheiro mas do que a franquia  Resumindo só quero o meu dinheiro de volta que paguei  que paguei o seguro ou a seguradora Allianz me dá o dinheiro que gastei para arrumar o carro que foi 7.750 ._x000D_
+_x000D_
+</t>
+  </si>
+  <si>
+    <t>95619475</t>
+  </si>
+  <si>
+    <t>241017145</t>
+  </si>
+  <si>
+    <t>18/02/2026 19:23</t>
+  </si>
+  <si>
+    <t>Allianz ; Automóvel ; Assistência Não Danos ; Carro Reserva ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Apólice</t>
+  </si>
+  <si>
+    <t>Carro Reserva</t>
+  </si>
+  <si>
+    <t>132353368</t>
+  </si>
+  <si>
+    <t>Tive meu veículo (segurado pela Allianz) envolvido em acidente de trânsito no dia 22/01/26, sendo atingido por outro automóvel segurado pela Seguradora Yelum._x000D_
+_x000D_
+Após o cadastro do sinistro do terceiro, optei em fazer o serviço na concessionária Alpínia, por se tratar de veículo em período de garantia e pouco mais de 13 mil kms de uso._x000D_
+_x000D_
+Realizada a vistoria da seguradora na concessionária me foi enviado o orçamento (anexo) no valor de R$ 4.209,98, sendo informado pelo funcionário Paulo (funilaria da Alpínia) que o serviço duraria em média de 3 a 4 dias, coadunando assim com a previsão de quase 16 horas de serviço mencionadas no orçamento._x000D_
+_x000D_
+Verifiquei junto a minha corretora (VL Seguros) a possibilidade de concessão de carro reserva pela Allianz, ocasião em que me foi informado que conforme cláusula contratual, tal condição só poderia acontecer se o valor do reparo ultrapasse minha franquia, no caso R$ 4.901,01, conforme condições gerais de uso do seguro emitidas pela Allianz, item 13.6._x000D_
+_x000D_
+Nesse prisma compete salientar que minha apólice (anexa) tem previsão de acionamento de primeira franquia com desconto de 100% (sem pagamento de qualquer valor) e em caso de segundo acionamento o valor de R$ 4.901,01. Destaca-se que não houve nenhum acionamento do seguro desde a última renovação._x000D_
+_x000D_
+Ocorre que no dia 11/02/26, em contato com a funilaria da concessionária Alpínia Fiat, durante a realização do agendamento do serviço, o funcionário Ricardo, solicitou que o carro fosse levado no dia 23/02/26, e atualizou o prazo de entrega do veículo para entre 7 e 10 dias úteis e não mais 3 dias como anteriormente fora informado. Diante disso questionei sobre a divergência absurda para o quantitativo de horas de serviço previstos em orçamento (16h), sendo então informado que tal orçamento sofreria alteração de valor e aumento das horas (conforme print), ocasião em que seria solicitado um aditivo._x000D_
+_x000D_
+Posto isso, ainda sim solicitei a minha corretora VL Seguros que solicitasse o carro reserva, considerando que haveria aumento de vários dias de serviço e consequentemente ultrapassaria o valor de minha franquia, possibilitando o direito a concessão de carro reserva por 7 dias._x000D_
+_x000D_
+Entretanto conforme informou meu corretor, a Allianz condicionou a concessão a remessa de outro orçamento com o complemento previsto, mesmo que minha franquia para primeiro acionamento seja livre de custos e que seja iminente o aumento de valores que ultrapassarão os custos do segundo acionamento de franquia._x000D_
+_x000D_
+Porém para que seja elaborado tal complemento é necessário que seja iniciado o serviço e desmontado o veículo, a fim de que seja identificado corretamente quais seriam as demandas. Nessa lógica o expediente só poderá ser liberado dias após, ficando esse período sem carro reserva, considerando ainda o período de análise da documentação pela Allianz, o que na prática pode consumir todo o período de reparos e consequentemente perder a necessidade de um carro reserva._x000D_
+_x000D_
+Ou seja, se ao final os valores ultrapassarem a franquia, perderei um direito previsto em apólice por meras filigranas jurídicas da Allianz, ou ainda, pela correta análise do caso concreto._x000D_
+_x000D_
+Permaneço a disposição para eventuais esclarecimentos ou envio de mais documentos necessários.</t>
+  </si>
+  <si>
+    <t>95619163</t>
+  </si>
+  <si>
+    <t>241015919</t>
+  </si>
+  <si>
+    <t>18/02/2026 19:10</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Pagamento ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Pagamento</t>
+  </si>
+  <si>
+    <t>136724861</t>
+  </si>
+  <si>
+    <t>Boa noite, venho através desse canal alertar os consumidores para redobrar a atenção ao fazer seguro do deu patrimônio com essa seguradora, fechei um seguro para o meu veículo no valor de R$ 9.821,31 em 10 vezes no cartão de crédito, ocorre que a seguradora descontou em duplicidade o valor da primeira parcela, segundo informações da seguradora o valor seria extornado em 24 horas, já se passou uma semana e o extorno não aconteceu, acho que cai em uma silada, essa seguradora tem diversas reclamações no site reclame aqui sem resposta, sei que cometi um erro, deveria ter visto isso antes de fechar o seguro, mas infelizmente confiei no corretor e acabei fechando seguro com essa seguradora, a minha única alternativa de ser ouvido é abrir essa reclamação e levar sorte que respondam, Não façam negócio com essa seguradora, Diante da experiência não recomendo, é só olhar no site do reclame aqui e ver reclamação sem resposta por parte da seguradora.</t>
+  </si>
+  <si>
+    <t>95614712</t>
+  </si>
+  <si>
+    <t>241003047</t>
+  </si>
+  <si>
+    <t>18/02/2026 17:06</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Residência ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Assistência Não Danos ; Assistência Residencial</t>
+  </si>
+  <si>
     <t>Assistência Residencial</t>
   </si>
   <si>
-    <t>1 Segurado</t>
-  </si>
-  <si>
-    <t>SAC Aberto</t>
-  </si>
-  <si>
-    <t>Sim</t>
-  </si>
-  <si>
-    <t>Repasse Time MindBe</t>
-  </si>
-  <si>
-    <t>Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Juliana</t>
-  </si>
-  <si>
-    <t>135166100</t>
-  </si>
-  <si>
-    <t>No dia 26/01 foi encaminhado documentação para análise reembolso, porém até a data de hoje, o setor de assistência não analisou a o documento a documentação e muito menos realizou o reembolso. Fazendo com que até o momento eu ficasse sem o valor que o desembolse por uma ineficiência no sistema de assistência da Allianz.</t>
-  </si>
-  <si>
-    <t>95590747</t>
-  </si>
-  <si>
-    <t>240939947</t>
-  </si>
-  <si>
-    <t>18/02/2026 08:20</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Residência ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Sinistro ; Análise Sinistro</t>
+    <t>131130277</t>
+  </si>
+  <si>
+    <t>Prezados,_x000D_
+_x000D_
+_x000D_
+Venho por meio deste solicitar um parecer formal referente aos dois protocolos de reembolso, os quais foram devidamente liberados e autorizados pela própria central da Allianz._x000D_
+_x000D_
+_x000D_
+Trata-se de uma empresa de grande porte, que preza pela qualidade no atendimento. No entanto, já realizei diversos contatos e enviei inúmeros e-mails, todos sem retorno efetivo. Infelizmente, os analistas não têm apresentado resolutividade, demonstrando descaso com a segurada._x000D_
+_x000D_
+_x000D_
+Ressalto que foi criado um link para envio de documentação para análise, no qual consta o prazo de 2 a 5 dias para retorno. Contudo, esse prazo já foi ultrapassado há dias, sem qualquer posicionamento._x000D_
+_x000D_
+_x000D_
+O acúmulo de protocolos é falha interna da própria seguradora, e não da segurada, uma vez que os chamados foram abertos em datas distintas, assim como os serviços foram realizados em momentos diferentes._x000D_
+_x000D_
+_x000D_
+Além da demora no agendamento por falta de prestadores disponíveis, fui orientada pela própria central a realizar os serviços de forma particular. Após o envio correto de toda a documentação exigida, não houve retorno conclusivo. Os atendentes informam que o setor interno entrará em contato, porém não recebo e-mail nem ligação._x000D_
+_x000D_
+_x000D_
+Diante do exposto, exijo uma data conclusiva para o pagamento de ambos os reembolsos, considerando que todas as exigências foram devidamente cumpridas por minha parte._x000D_
+_x000D_
+PROTOCOLOS :_x000D_
+_x000D_
+- 51197183_x000D_
+_x000D_
+-51158633_x000D_
+_x000D_
+-51264749_x000D_
+_x000D_
+_x000D_
+Aguardo retorno com a máxima urgência._x000D_
+_x000D_
+_x000D_
+Atenciosamente,_x000D_
+_x000D_
+Valeska Souza</t>
+  </si>
+  <si>
+    <t>95614051</t>
+  </si>
+  <si>
+    <t>241000931</t>
+  </si>
+  <si>
+    <t>18/02/2026 16:49</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 2 Terceiro do Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
     <t>Sinistro</t>
   </si>
   <si>
-    <t>Residência</t>
-  </si>
-  <si>
     <t>Análise Sinistro</t>
   </si>
   <si>
-    <t>305042073</t>
-  </si>
-  <si>
-    <t>Abri um sinistro desde de o dia 13/01, envie todas as documentações e orçamento e ate agora não recebi._x000D_
-_x000D_
-Moro sozinha, estou sem motor do portão, sem as cameras._x000D_
-_x000D_
-Pagamos um seguro para ser RAPIDO, e ate agora não resolveram meu problema.</t>
+    <t>2 Terceiro do Sinistro</t>
+  </si>
+  <si>
+    <t>278260621</t>
+  </si>
+  <si>
+    <t>Em Julho de 2023, aconteceu uma colisão entre o meu carro e o carro de uma segurada da ALLIANZ. Na época, foi solicitado o seguro para terceiros, para arrumar o meu carro._x000D_
+_x000D_
+O carro foi levado na oficina que vocês escolheram, e foi arrumado. Agora, em 2026, estou colocando o carro a venda, e quando fui fazer a vistoria cautelar, para a minha surpresa o carro foi reprovado, e está com apontamentos. Entrei em contato com a seguradora, para verificarem a minha situação, e me disseram está tudo Ok. Pois bem, antes da batida e antes do conserto o meu carro não tinha laudo reprovado, então peço por favor que reavaliem essa situação para o devido conserto do carro. Para que ele seja aprovado na cautelar , para que eu possa dar andamento na venda do mesmo. _x000D_
+_x000D_
+Já pesquisei sobre a situação, e como é um vício oculto, que foi descoberto agora, a segurado não pode se negar a prestar o serviço. É um direito do consumidor. Não posso ficar nessa situação, aguardo um breve retorno.</t>
+  </si>
+  <si>
+    <t>95610102</t>
+  </si>
+  <si>
+    <t>240989455</t>
+  </si>
+  <si>
+    <t>18/02/2026 15:17</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; 11 Não Cliente ; Emissão ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Sinistro</t>
+  </si>
+  <si>
+    <t>Emissão</t>
+  </si>
+  <si>
+    <t>11 Não Cliente</t>
+  </si>
+  <si>
+    <t>133028853</t>
+  </si>
+  <si>
+    <t>Adquiri através d Freitas Leiloeiro em 12/12/2025 o véiculo Kia Stonic 2022, placas CSU8A82 cuja NF não me foi fornecida e até agora não consegui transferir o automével.Solicito providências.Obrigado-Cesar Rafael Soffredi</t>
   </si>
   <si>
     <t>95589312</t>
@@ -228,7 +482,7 @@
     <t>Corretor</t>
   </si>
   <si>
-    <t>Reclamante em nome do Segurado</t>
+    <t>Eliana</t>
   </si>
   <si>
     <t>134774861</t>
@@ -247,168 +501,6 @@
 Vocês violaram o código de defesa do consumidor, estava disposta a pagar o seguro até por boleto mesmo com juros altíssimos para termos o sossego do carro estar assegurado. Nunca houve uma conversa entre a Patricia e minha família: onde ela esclarece o que houve, sabe o que temos? Uma mensagem no WhatsApp que pode ser apagada a qualquer hora. Sempre pagamos o seguro com a maior satisfação, agora na hora que precisamos a ALLIANZ e sua funcionaria Patricia de ESPIRITO SANTO DO PINHAL-SP nos notificarem do que aconteceu nos deixaram na mão, o CANCELAMENTO DO SEGURO SEM AVISO PRÉVIO é considerado ilegal e abusivo, violando o Código de Defesa do Consumidor (CDC) e jurisprudência do STJ (Súmula 616), pois a seguradora deve notificar o segurado antes de suspender ou encerrar o contrato. A nova Lei de Seguros (15040/2024) reforça que é proibido o cancelamento automático por falta de pagamento sem notificação, exceto no não pagamento da primeira parcela ou de parcela única. A primeira parcela foi o paga. O maior problema de tudo isso foi a hostilidade da Patricia funcionaria da ALLIANZ, NÃO HOUVE CONTATO, NÃO HOUVE CONVERSA. HOUVE FALTA DE RESPEITO COMIGO E MEUS PAIS. Que se encontram num momento de total fragilidade pela saúde da minha mãe e toda chateação e perturbação, e todo constrangimento que se deu pelo comportamento malcriado, ofensivo, difamatório (ela afirmou que vimos a mensagem e não respondemos), humilhante, afrontoso e insolente de Patricia, funcionaria da Allianz. _x000D_
 _x000D_
 </t>
-  </si>
-  <si>
-    <t>95584900</t>
-  </si>
-  <si>
-    <t>240921965</t>
-  </si>
-  <si>
-    <t>17/02/2026 20:04</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Guincho</t>
-  </si>
-  <si>
-    <t>132258710</t>
-  </si>
-  <si>
-    <t>Negativa indevida de assistência em situação de risco  descumprimento contratual_x000D_
-_x000D_
-_x000D_
-Durante o feriado de Carnaval, eu estava em viagem ao Rio de Janeiro e, ao iniciar o deslocamento de retorno para São Paulo, identifiquei o estouro/furo de um dos pneus do veículo segurado. De imediato, estacionei o automóvel e realizei a substituição pelo estepe temporário, adotando as medidas mínimas de segurança._x000D_
-_x000D_
-_x000D_
-Na sequência, busquei atendimento em borracharias próximas. As duas primeiras estavam fechadas em razão do feriado prolongado. A terceira realizou a avaliação técnica e constatou que o pneu não possuía reparo, além de não haver disponibilidade de pneu compatível com o veículo. Continuei tentando outros estabelecimentos, sem sucesso, seja por estarem fechados, seja por ausência de estoque adequado._x000D_
-_x000D_
-_x000D_
-Ressalto que eu me encontrava em região de reconhecida periculosidade no Rio de Janeiro, não sendo razoável nem seguro permanecer com o veículo imobilizado por tempo indeterminado, tampouco circular aleatoriamente em busca de locais desconhecidos. Diante desse cenário, segui deslocamento mínimo apenas para sair da área de risco e acionei a seguradora Allianz, ciente de que não é permitido nem seguro realizar trajeto rodoviário superior a 400 km com estepe temporário, conforme orientação do fabricante e normas básicas de segurança veicular._x000D_
-_x000D_
-_x000D_
-Solicitei, então, remoção do veículo por guincho, seja para a cidade de São Paulo, seja para local onde fosse possível efetuar o reparo adequado. Contudo, a seguradora negou a abertura do atendimento, sob a justificativa de que o veículo possuía condição de rodar, desconsiderando que tal condição era precária, emergencial e insegura, além de incompatível com viagem de longa distância._x000D_
-_x000D_
-_x000D_
-A negativa se estendeu inclusive ao serviço de borracheiro, o que evidencia absoluta falta de razoabilidade e de avaliação do contexto fático apresentado. Registrei expressamente que não possuía condições seguras de seguir viagem, que não conhecia a região e que havia risco concreto à minha integridade física, mas tais argumentos foram ignorados._x000D_
-_x000D_
-_x000D_
-Foram realizadas duas ligações ao atendimento regular e uma ao SAC, sem que qualquer atendimento fosse aberto, solução apresentada ou alternativa oferecida. Em nenhum momento houve análise individualizada do risco, tampouco observância do dever de assistência ao segurado em situação emergencial._x000D_
-_x000D_
-_x000D_
-A conduta da seguradora caracteriza falha na prestação do serviço, em desacordo com os princípios da boa-fé objetiva, da função social do contrato e da proteção ao consumidor, conforme o Código de Defesa do Consumidor. A assistência 24h existe justamente para amparar o segurado em situações excepcionais, e não para se limitar a interpretações restritivas e automáticas que colocam o consumidor em risco._x000D_
-_x000D_
-_x000D_
-Diante do exposto, registro minha indignação com o descaso e a negativa indevida de assistência, esperando providências, esclarecimentos formais e reparação adequada pela falha ocorrida.</t>
-  </si>
-  <si>
-    <t>95578162</t>
-  </si>
-  <si>
-    <t>240901665</t>
-  </si>
-  <si>
-    <t>17/02/2026 14:19</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Condomínio ; Sinistro ; Indenização ; Litoral Norte SP ; RA ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Condomínio</t>
-  </si>
-  <si>
-    <t>Indenização</t>
-  </si>
-  <si>
-    <t>Litoral Norte SP</t>
-  </si>
-  <si>
-    <t>RA</t>
-  </si>
-  <si>
-    <t>274324875</t>
-  </si>
-  <si>
-    <t>Oi Allianz, boa tarde_x000D_
-_x000D_
-Como a empresa vai? Acredito que bem e fazendo sucesso com novos clientes. Entao.  passando aqui pra lembrar da tragedia em São Sebastião  no dia 19/2/2023 bem no carnaval. Pra Allianz pode nem fazer parte do memorial essa tragedia, mas pra mim sera sempre um trauma o que vivi la com a minha família  3 anos com a minha casa interditada pela defesa civil. Nao estou so com a minha casa interditada estou com minha vida tambem. Tenho um bem que nao posso usufruir. Que fui obrigada a pagar para fazer reparos para que o telhado nao caisse e fechar as paredes derrubadas pra evitar abrigo de animais . Duas cobras foram encontradas dentro da casa por estar sem paredes portas e janelas. Mas ai  o que a Allianz fez pelo cliente? NADA!  Ofereceu valores que nao condiz com o sinistro. E so tivemos uma opcao entrar com uma ação. Ai vc vai me falar como existe uma acao nao posso te responder. Entendo. Nao aceito, mas entendo. So pra lembrar meu marido quase morreu soterrado, ficou com sequela no ombro. Eu minha filha, minha nora e meu sobrinho tembem ficamos com sequela emocional. TRAUMA! Mas o que a Allianz tem que ver com isso ne? Nna verdade NADA. Mas poderia ter sido mais empatica em resolver um problema causado por uma tragedia ninca visto no Brasil mais de 600 milometros de agua e 66 mortes. O mundo soube! mas a Allianz virou de costas. Foi mais bacana colocar que enviou guinchos para retirar os veiculos que ficaram alagados do que arcar com idoneidade de uma empresa em pagar pelo sinistro no condominio em pelas casas destruidas._x000D_
-_x000D_
-O Residencial Flat Parque dos Colibris e um condominio horizontal e nossa apolice era Ampla total. Toda area do condominio mais as 40 unidades. Nosso condominio está td em ordem frente a prefeitura. Plantas, Hábits,  IPTU, taxas td certinho. Nosso seguro estava pago td conforme a lei diz. E a empresa Allianz so na negativa. _x000D_
-_x000D_
-Que pena! Gostaria de falar que vcs foram muito humanos com nos os atingidos pela tragédia, mas infelizmente nao e essa a minha realidade._x000D_
-_x000D_
-Tenham um bom feriado  de carnaval coisa que minha familia nao tem faz tempo_x000D_
-_x000D_
-_x000D_
-Myrian _x000D_
-_x000D_
-Unidade 32 _x000D_
-_x000D_
-Casa interditada pela Defesa Civil</t>
-  </si>
-  <si>
-    <t>95577019</t>
-  </si>
-  <si>
-    <t>240898287</t>
-  </si>
-  <si>
-    <t>17/02/2026 13:29</t>
-  </si>
-  <si>
-    <t>Allianz ; CPF/CNPJ ; Automóvel ; Canal de Atendimento ; Comercial ; 11 Não Cliente ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>CPF/CNPJ</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>11 Não Cliente</t>
-  </si>
-  <si>
-    <t>246309398</t>
-  </si>
-  <si>
-    <t>ESTOU TENTANDO FAZER UM CADASTRO DE MINHA EMPRESA COMO PRESTADOR DE ASSISTENCIA 24 HS . _x000D_
-_x000D_
-MAS NÃO ENCONTRO NOS SITES E LINKS DISPONIBILIZADOS A OPÇÃO PARA PRESTADOR DE SERVIÇOS GUINCHO 24HS, SO LOCALIZEI OFICINAS PARA CREDENCIAR; NÃO TEM UM CHAT, ZAP, EMAIL QUE POSSA FORMULAR A PERGUNTA PARA ;_x000D_
-_x000D_
-TENHO UM UMA PLATAFORMA GUINCHO PARA PRESTAR SERVIÇOS E GOSTARIA DE FAZER PARTE DOS PRESTADORES DA ALLIANZ ; MAS TA DIFICIL OBRIGADO</t>
-  </si>
-  <si>
-    <t>95569650</t>
-  </si>
-  <si>
-    <t>240877747</t>
-  </si>
-  <si>
-    <t>17/02/2026 08:28</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; 2 Terceiro do Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Análise Sinistro</t>
-  </si>
-  <si>
-    <t>2 Terceiro do Sinistro</t>
-  </si>
-  <si>
-    <t>304440631</t>
-  </si>
-  <si>
-    <t>Estou abrindo essa reclamação porque já entrei em contato com Allianz tentando resolver a questão do valores do LC, referente ao meus 2 dias para por causa do acidente, Esse valor que me foi analisado pra mim não passa de esmola, querer me pagar 86 reais por dia, e desconta aí 40% de gasolina e manutenção não sabia que Allianz pagava minha gasolina, não vou aceitar esse valor o mínimo é 300 por dia tenho no anexo foto dos valores que faço por dia, 304440631 esse é o número do sinistro _x000D_
-_x000D_
-Espero que alguém desse empresa tenha ciência porque esse dois dias que não trabalhei me trouxe prejuízo</t>
-  </si>
-  <si>
-    <t>95567873</t>
-  </si>
-  <si>
-    <t>240872531</t>
-  </si>
-  <si>
-    <t>17/02/2026 01:06</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; 2 Terceiro do Sinistro ; SAC Aberto</t>
-  </si>
-  <si>
-    <t>135670704</t>
-  </si>
-  <si>
-    <t>Acionei o.seguro sobre protocolo 51431680 as 22:24 sendo que as 23:29 estavam procurando prestador maos ee 60 min além.de inúmeros ligacoes eu ja nervoso falei muito e ate usei palavras de baixo calão pelo desprezo pelo segurado que paga suas parcelas em.dia e no dia que precisa nao é  atendido irei entrar com ação na justiça pelo descaso com o segurado e removi meu veículo por meios  próprios pois a segurado se quiser teve a simpatia de oferecer pois estava em outra cidade</t>
   </si>
 </sst>
 </file>
@@ -860,7 +952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AA8803-373C-4E0C-ABA8-1F171C96DA02}">
-  <dimension ref="A1:AA9"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="3" bestFit="1" customWidth="1" collapsed="1"/>
@@ -1014,25 +1106,25 @@
         <v>38</v>
       </c>
       <c r="M2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="W2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="Y2" s="3" t="s">
         <v>26</v>
@@ -1042,13 +1134,13 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>30</v>
@@ -1057,46 +1149,46 @@
         <v>31</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="M3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3" s="3" t="s">
+      <c r="X3" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="Y3" s="3" t="s">
         <v>26</v>
@@ -1106,13 +1198,13 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>30</v>
@@ -1121,7 +1213,7 @@
         <v>31</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>33</v>
@@ -1130,37 +1222,37 @@
         <v>34</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="N4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="X4" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="X4" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="Y4" s="3" t="s">
         <v>26</v>
@@ -1170,13 +1262,13 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>30</v>
@@ -1185,7 +1277,7 @@
         <v>31</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>33</v>
@@ -1197,10 +1289,10 @@
         <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>38</v>
@@ -1209,22 +1301,22 @@
         <v>31</v>
       </c>
       <c r="N5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="V5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="V5" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="W5" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="Y5" s="3" t="s">
         <v>26</v>
@@ -1234,13 +1326,13 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>30</v>
@@ -1249,46 +1341,46 @@
         <v>31</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="I6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="X6" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="V6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W6" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="X6" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="Y6" s="3" t="s">
         <v>26</v>
@@ -1298,13 +1390,13 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>30</v>
@@ -1313,46 +1405,46 @@
         <v>31</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="P7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P7" s="3" t="s">
+      <c r="V7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="V7" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="W7" s="4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="Y7" s="3" t="s">
         <v>26</v>
@@ -1362,13 +1454,13 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>30</v>
@@ -1377,46 +1469,46 @@
         <v>31</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O8" s="3" t="s">
+      <c r="P8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="V8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="W8" s="4" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>26</v>
@@ -1426,13 +1518,13 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>30</v>
@@ -1441,52 +1533,212 @@
         <v>31</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="N9" s="3" t="s">
+      <c r="O9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="P9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="V9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="W9" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>26</v>
       </c>
       <c r="Z9"/>
       <c r="AA9"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W10" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="X10" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="X11" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y11" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="W13" s="4"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="W14" s="4"/>
+      <c r="X14" s="4"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="W15" s="4"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="W16" s="4"/>
+      <c r="X16" s="4"/>
+    </row>
+    <row r="17" spans="23:24" x14ac:dyDescent="0.2">
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+    </row>
+    <row r="18" spans="23:24" x14ac:dyDescent="0.2">
+      <c r="W18" s="4"/>
+    </row>
+    <row r="19" spans="23:24" x14ac:dyDescent="0.2">
+      <c r="W19" s="4"/>
+      <c r="X19" s="4"/>
+    </row>
+    <row r="20" spans="23:24" x14ac:dyDescent="0.2">
+      <c r="W20" s="4"/>
+      <c r="X20" s="4"/>
+    </row>
+    <row r="21" spans="23:24" x14ac:dyDescent="0.2">
+      <c r="W21" s="4"/>
+    </row>
+    <row r="22" spans="23:24" x14ac:dyDescent="0.2">
+      <c r="W22" s="4"/>
+      <c r="X22" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AN9" xr:uid="{D3AA8803-373C-4E0C-ABA8-1F171C96DA02}"/>

--- a/Treinamento/GestaoReclamacao.xlsx
+++ b/Treinamento/GestaoReclamacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489CEA6D-13C7-4854-9275-4779BF25EAD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD532292-6319-4BA3-A304-B7C2A90585D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B1A77FD5-2AD3-4458-ACB3-7F19D1A3340A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="166">
   <si>
     <t>Id HugMe</t>
   </si>
@@ -122,13 +122,13 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>95628000</t>
-  </si>
-  <si>
-    <t>241043317</t>
-  </si>
-  <si>
-    <t>19/02/2026 07:20</t>
+    <t>95687865</t>
+  </si>
+  <si>
+    <t>241190583</t>
+  </si>
+  <si>
+    <t>20/02/2026 12:02</t>
   </si>
   <si>
     <t>Não respondido</t>
@@ -137,7 +137,7 @@
     <t>Não</t>
   </si>
   <si>
-    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Vidros - AutoGlass ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Chaveiro ; Reclamante em nome do Segurado ; SAC Aberto ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
     <t>Allianz</t>
@@ -152,355 +152,530 @@
     <t>Assistência Não Danos</t>
   </si>
   <si>
-    <t>Vidros - AutoGlass</t>
+    <t>Chaveiro</t>
+  </si>
+  <si>
+    <t>Reclamante em nome do Segurado</t>
+  </si>
+  <si>
+    <t>SAC Aberto</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Repasse Time MindBe</t>
+  </si>
+  <si>
+    <t>Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Juliana</t>
+  </si>
+  <si>
+    <t>132366013</t>
+  </si>
+  <si>
+    <t>minha esposa e cliente da Allianz seguros,solicitou um serviço de chaveiro da referida empresa na data 19/022026as 17:57 as 19:24; foi enformada que não avia nenhum prestador dia ponivel e orientaram que procurasse por conta própria que depois enviasse documentos para um possível reembolso .fiquei indiquinado pós após 90 minutos ela a margem de uma rodovia só vem essa resposta que pra min seria desumana se tratando de um mulher só as margens de uma rodovia .peguei meu carro rodei 35km com meu filho fui de encontro a ela ,deixei os dois no local e sai a procura de um chaveiro que encontrei .o mesmo acordo um valor e foi ao local cmg ,fazendo a abertura do veículo.a Allianz não teve nem um tipo de solidariedade ,podia enviar um guincho já que não tinha chaveiro para tirar ela do local que com o avancar das horas poderia ser perigoso para uma mulher só .mais não fizemos a abertura por volta das 22hs .aí ligaram dizendo que talvez um prestador chegaria às 23: 30 ,já estávamos em casa .agora fica a pergunta quando contratei achei que eles resolveria .passaram para nós depois eles fazer iam o reembolso pra min falta de compromisso com clientes primeiro protocolo 51457612</t>
+  </si>
+  <si>
+    <t>95677069</t>
+  </si>
+  <si>
+    <t>241160093</t>
+  </si>
+  <si>
+    <t>20/02/2026 07:40</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 2 Terceiro do Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Sinistro</t>
+  </si>
+  <si>
+    <t>Análise Sinistro</t>
+  </si>
+  <si>
+    <t>2 Terceiro do Sinistro</t>
+  </si>
+  <si>
+    <t>304126542</t>
+  </si>
+  <si>
+    <t>Realizamos o serviço referente ao sinistro citado, a empresa Allianz relatou que realizou o pagamento porém isso não aconteceu, entrei em contato e fui informado pela empresa que não tem previsão para realizar o pagamento</t>
+  </si>
+  <si>
+    <t>95667714</t>
+  </si>
+  <si>
+    <t>241143763</t>
+  </si>
+  <si>
+    <t>19/02/2026 21:32</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
     <t>1 Segurado</t>
   </si>
   <si>
-    <t>Sim</t>
-  </si>
-  <si>
-    <t>Repasse Time MindBe</t>
-  </si>
-  <si>
-    <t>Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Juliana</t>
-  </si>
-  <si>
-    <t>133346487</t>
-  </si>
-  <si>
-    <t>Bom dia. Eu tenho um seguro com a Allianz e eu contactei porque um motoqueiro bateu na lâmpada traseira do meu carro e arranhou e soltou a lanterna! Isso já tinha acontecido do outro lado do veículo. As lanternas foram coladas. A companhia de seguros me mandou um link para bater as fotos , mas os exemplos para mostrar não identificaram o problema, eu pedi para fazer uma vistoria e levei o carro na companhia de vidros! O rapaz da vistoria me Informou que as lanternas estavam quebradas e que o seguro iria trocar, me deu um prazo de uma semana se tiverem a peça! No mesmo dia recebi uma ligação do seguro me informando que a lanterna não estava quebrada e que não iriam pagar porque era causas naturais!  Como pode ser natural se as outras não estão? O carro tem 9000 km vive parado dentro de uma garagem coberta! O carro levou um golpe de motoqueiro quando parou no sinal. E o seguro não se responsabiliza porque o golpe não quebrou o vidro!</t>
-  </si>
-  <si>
-    <t>95624925</t>
-  </si>
-  <si>
-    <t>241034067</t>
-  </si>
-  <si>
-    <t>18/02/2026 23:04</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; Reclamante em nome do Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+    <t>305573609</t>
+  </si>
+  <si>
+    <t>Registrei esta reclamação em razão da falha grave e reiterada na prestação de serviço por parte da seguradora, referente ao sinistro ocorrido em 06/02._x000D_
+_x000D_
+_x000D_
+Mesmo agindo com boa-fé, educação e colaboração, não obtive solução até o momento._x000D_
+_x000D_
+_x000D_
+Resumo dos fatos_x000D_
+_x000D_
+_x000D_
+O acidente ocorreu em 06/02. Meu primeiro contato com a seguradora foi em 10/02, após aguardar, de forma razoável, que o terceiro envolvido arcasse com os prejuízos, o que não ocorreu. Em razão do impacto, passei a sentir dores na coluna e no pescoço, motivo pelo qual acionei o seguro._x000D_
+_x000D_
+_x000D_
+O veículo ficou totalmente impossibilitado de rodar, apresentando:_x000D_
+_x000D_
+_x000D_
+Amassamentos em toda a lateral esquerda;_x000D_
+_x000D_
+_x000D_
+Rodas do lado esquerdo arranhadas;_x000D_
+_x000D_
+_x000D_
+Estouro de dois pneus do lado direito;_x000D_
+_x000D_
+_x000D_
+Rodas do lado direito trincadas._x000D_
+_x000D_
+_x000D_
+Acionei o guincho, solicitando que o veículo fosse levado à residência de minha irmã, para não onerar a seguradora, já que meu endereço fica a aproximadamente 27 km._x000D_
+_x000D_
+_x000D_
+Posteriormente, solicitei novo guincho, conforme previsto na apólice (guincho ilimitado), pois o veículo seguia sem condições de circulação._x000D_
+_x000D_
+_x000D_
+Falhas no atendimento_x000D_
+_x000D_
+_x000D_
+Foi informado prazo de 24 horas, que não foi cumprido;_x000D_
+_x000D_
+_x000D_
+Disseram que o processo aguardava vistoria, porém o vistoriador não compareceu;_x000D_
+_x000D_
+_x000D_
+Informei mais de uma vez que não há ninguém fixo no local, solicitando agendamento prévio, o que foi ignorado;_x000D_
+_x000D_
+_x000D_
+Em 18/02, informaram que o guincho estava liberado, mas que não poderia ser acionado por processo interno;_x000D_
+_x000D_
+_x000D_
+Fui informado de que o veículo seria retirado em 19/02, permaneci aguardando até às 17h, arcando com custos de Uber e metrô, e ninguém compareceu._x000D_
+_x000D_
+_x000D_
+Em atendimento realizado pela Patrícia, gravei integralmente a conversa em vídeo, no qual constam as informações prestadas e os compromissos assumidos, que não foram cumpridos._x000D_
+_x000D_
+_x000D_
+Prejuízos_x000D_
+_x000D_
+_x000D_
+O veículo é instrumento de trabalho, e sua indisponibilidade está gerando prejuízos financeiros, despesas extras e grande transtorno. O seguro foi contratado justamente para evitar esse tipo de situação, o que não está ocorrendo._x000D_
+_x000D_
+_x000D_
+Solicitação_x000D_
+_x000D_
+_x000D_
+Solicito solução imediata, com a efetiva prestação do serviço contratado. Caso contrário, realizarei o reparo por conta própria e adotarei as medidas cabíveis, inclusive judiciais, para ressarcimento dos prejuízos, com lucros cessantes, já que dependo do veículo para minha renda._x000D_
+_x000D_
+_x000D_
+Aguardo retorno objetivo e urgente.</t>
+  </si>
+  <si>
+    <t>95665445</t>
+  </si>
+  <si>
+    <t>241138285</t>
+  </si>
+  <si>
+    <t>19/02/2026 20:29</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Residência</t>
+  </si>
+  <si>
+    <t>Assistência Residencial</t>
+  </si>
+  <si>
+    <t>135074012</t>
+  </si>
+  <si>
+    <t>Entrei em contato no dia 19 de fevereiro de 2026 Solicitando a troca de um bojo ou Cuba da minha da pia da cozinha. Fui informado que a minha apolice não contempla troca da Cuba, mesmo ela solta e vazando. Mesmo eu ja tendo a Cuba nova, me foi negado o atendimento para instalacao. Solicitei também a instalação de uma torneira e tb me foi negado o atendimento porque a torneira não está vazando. Que porcaria de prestacao de serviço hidráulico é isso? Ao oferecerem o seguro De prestação de serviços hidráulicos em nenhum momento foi informado sobre condições .estou totalmente Insatisfeito e não Concordo com esse tipo de de atendimento. Jamais renovarei esse seguro e ainda, irei acionar judicialmente essa seguradora.</t>
+  </si>
+  <si>
+    <t>95663397</t>
+  </si>
+  <si>
+    <t>241133053</t>
+  </si>
+  <si>
+    <t>19/02/2026 19:32</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
     <t>Guincho</t>
   </si>
   <si>
-    <t>Reclamante em nome do Segurado</t>
-  </si>
-  <si>
-    <t>135077835</t>
-  </si>
-  <si>
-    <t>Empresa me deixou na mão com o carro quebrado em região de risco, tarde da noite, com uma criança de 9 anos (avisei a atendente). Deram previsão de chegada de 30 minutos, mas demorou quase 1:30h. Não fossem os amigos nos acolherem, teríamos corrido risco de assalto, etc.</t>
-  </si>
-  <si>
-    <t>95622154</t>
-  </si>
-  <si>
-    <t>241025395</t>
-  </si>
-  <si>
-    <t>18/02/2026 20:59</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Residência ; Apólice ; Renovação ; 1 Segurado ; SAC Aberto ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Residência</t>
-  </si>
-  <si>
-    <t>Renovação</t>
-  </si>
-  <si>
-    <t>SAC Aberto</t>
-  </si>
-  <si>
-    <t>135972802</t>
-  </si>
-  <si>
-    <t>ano passado contratei um seguro residencial junto ao banco Banrisul, com vigência e prazo determinados. O contrato foi integralmente cumprido, as parcelas foram quitadas e o seguro foi encerrado normalmente._x000D_
-_x000D_
-_x000D_
-Após o término, optei por NÃO renovar o seguro com esta instituição, inclusive contratando um novo seguro residencial em outro banco._x000D_
-_x000D_
-_x000D_
-Para minha surpresa, neste ano o seguro foi renovado automaticamente, sem qualquer solicitação, autorização ou aceite da minha parte. Não houve assinatura de novo contrato, concordância expressa, nem autorização para renovação ou cobrança._x000D_
-_x000D_
-_x000D_
-Além da renovação indevida, foi realizado débito diretamente em minha conta bancária, que estava inativa. Isso fez com que a conta ficasse negativa, gerando cobrança de juros e encargos financeiros, causando prejuízo material._x000D_
-_x000D_
-_x000D_
-Ressalto que:_x000D_
-_x000D_
-_x000D_
-Comunicação unilateral não configura autorização de renovação;_x000D_
-_x000D_
-_x000D_
-A cobrança sem consentimento viola o Código de Defesa do Consumidor;_x000D_
-_x000D_
-_x000D_
-A instituição não pode impor renovação automática com ônus financeiro sem manifestação expressa do cliente._x000D_
-_x000D_
-_x000D_
-Diante do ocorrido, solicito:_x000D_
-_x000D_
-_x000D_
-Cancelamento imediato desta renovação indevida;_x000D_
-_x000D_
-_x000D_
-Estorno integral do valor debitado;_x000D_
-_x000D_
-_x000D_
-Ressarcimento dos juros e encargos gerados pela negativação da conta;_x000D_
-_x000D_
-_x000D_
-Confirmação formal de encerramento definitivo do seguro;_x000D_
-_x000D_
-_x000D_
-Garantia de que não haverá novas renovações automáticas sem autorização expressa._x000D_
-_x000D_
-_x000D_
-Aguardo solução com urgência, uma vez que houve cobrança indevida e prejuízo financeiro. Caso não haja resolução, tomarei as medidas cabíveis junto aos órgãos de defesa do consumidor.</t>
-  </si>
-  <si>
-    <t>95620654</t>
-  </si>
-  <si>
-    <t>241020569</t>
-  </si>
-  <si>
-    <t>18/02/2026 20:02</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Condições Gerais ; 1 Segurado ; Não ; Sem Resposta - Dentro SLA ; Sim ; Repasse Time MindBe</t>
+    <t>134788365</t>
+  </si>
+  <si>
+    <t>Contratei o seguro para minha moto e contempla assistência 24h._x000D_
+_x000D_
+Meu pneu furou, fui agendar para realizar a troca e nem o guincho para levar ao borracheira contempla. _x000D_
+_x000D_
+Na hora de fechar o plano contemplava várias coberturas, agr que preciso usar não tenho direito a nada. _x000D_
+_x000D_
+Sem contar no atendimento péssimo de IA, perdi o atendimento 3 vezes pq demorei 2/3 minutos para responder.</t>
+  </si>
+  <si>
+    <t>95658820</t>
+  </si>
+  <si>
+    <t>241123923</t>
+  </si>
+  <si>
+    <t>19/02/2026 18:03</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Assistência Não Danos ; Guincho ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>305752130</t>
+  </si>
+  <si>
+    <t>Meu carro quebrou em Abadiandia-GO, no dia 13 de fevereiro. Era para ter sido entregue na oficina para reparos no dia 18 de fevereiro, devido ao recesso de Carnaval. Hoje, dia 19, me falaram que o carro saiu da Base ao meio-dia. Até agora, às 18h, ainda não foi entregue. Onde está meu veículo?</t>
+  </si>
+  <si>
+    <t>95658526</t>
+  </si>
+  <si>
+    <t>241123151</t>
+  </si>
+  <si>
+    <t>19/02/2026 17:56</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Fornecimento de Peças ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Fornecimento de Peças</t>
+  </si>
+  <si>
+    <t>299773541</t>
+  </si>
+  <si>
+    <t>ano passado eu sofri um acidente de moto, quebrou algumas peças da minha suzuki e eu prontamente acionei seguro. Demorou um pouco mas minha moto tava concertada, mas duas peças o perito não viu e tinha arranhões do acidente. solicitei uma nova perícia, e o mesmo constou que não viu e iria solicitar as peças novamente. _x000D_
+_x000D_
+_x000D_
+Só que isso faz mais de 3 meses e eu estou esperando apenas um email desse perito para a concessionária comprar as peças. _x000D_
+_x000D_
+_x000D_
+Estou odiando a comunicação da allianz comigo e com a consecionária.Meu contrato com eles vai até esse ano, não renovarei</t>
+  </si>
+  <si>
+    <t>95658193</t>
+  </si>
+  <si>
+    <t>241122607</t>
+  </si>
+  <si>
+    <t>19/02/2026 17:51</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>304606640</t>
+  </si>
+  <si>
+    <t>Estou com processo de indenização de sinistro aguardando pagamento. A empresa sempre impõe obrigações a mim que deveriam ser dela, já que tem procuração com plenos poderes para administrar, conforme a sua vontade, o veículo sinistrado, cuja posse está com ela há mais de mês. Enfim, sempre dão um jeito de postergar o pagamento. Infelizmente, pensei que fosse uma seguradora segura.</t>
+  </si>
+  <si>
+    <t>95657407</t>
+  </si>
+  <si>
+    <t>241120987</t>
+  </si>
+  <si>
+    <t>19/02/2026 17:37</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Cancelamento ; 1 Segurado ; SAC Aberto ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Cancelamento</t>
+  </si>
+  <si>
+    <t>136718932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seguradora não estornou valor total cobrado_x000D_
+_x000D_
+Proposta enviada pela Minuto Seguro foi fechada junto a seguradora Allianz sem minha confirmação e autorização em 12/02/2026, nesta mesma data solicitei cancelamento na mesma ferramenta que estava sendo tratado o assunto WhatsApp, onde o atendente da Minuto afirmou que estava cancelando a apólice e que o valor estaria sento estornado em 48 horas._x000D_
+_x000D_
+Após as 48 horas (Devido ao feriado de Carnaval ficou estabelecido dia 18/02/26), voltei contato com a Minuto Seguro, pois embora recebido o cancelamento da apólice não identifiquei o estorno do valor cobrado no cartão. Neste momento fui informado que a responsabilidade deste estorno seria a seguradora Allianz._x000D_
+_x000D_
+Iniciado contato imediato com Seguradora Allianz, onde estabeleci dois protocolos: 2624535443(Ref. a estorno do pagamento) e 260002560(Ref. reclamação para devolução total do valor R$171,79 pago contra R$159,97 devolvido em até 3 dias mesmo já passado  48 horas._x000D_
+_x000D_
+Deixei explicito junto ao atendente é inadmissível não contratar algo e ser cobrado por este contrato e quando do esclarecimento e da solicitação da regularização tenha que pagar ainda como uma punição imposta, no qual jamais concordarei e exijo ser ressarcido antes que o erro das partes passe a ser crime._x000D_
+_x000D_
+</t>
+  </si>
+  <si>
+    <t>95650345</t>
+  </si>
+  <si>
+    <t>241107231</t>
+  </si>
+  <si>
+    <t>19/02/2026 15:48</t>
+  </si>
+  <si>
+    <t>Andreza</t>
+  </si>
+  <si>
+    <t>134909955</t>
+  </si>
+  <si>
+    <t>Acionei o reboque da Allianz para o meu veículo na noite da terça-feira (17/02) e, conforme contactado, o carro seria transportado para a oficina  na minha cidade. Fui direto para oficina próximo das 23 horas. Após meia-hora esperando, o motorista do reboque me deixou uma mensagem informando que o veículo seria encaminhado para a base deles. A entrega na minha cidade ficou para hoje (19/02). Perdi o dia de trabalho aguardando a chegada do veículo, que ninguém sabia informar quando sairia para o destino. Agora, no final do expediente, os atendentes da Allianz informam que o veículo não será entregue hoje, mas amanhã. Devo confiar? Como ficam meus compromissos? Terei que perder mais um dia de trabalho? _x000D_
+_x000D_
+Será que amanhã ocorre a entrega ou a seguradora irá negligenciar o atendimento ao segurado pela terceira vez em 4 dias?</t>
+  </si>
+  <si>
+    <t>95647022</t>
+  </si>
+  <si>
+    <t>241097771</t>
+  </si>
+  <si>
+    <t>19/02/2026 14:39</t>
+  </si>
+  <si>
+    <t>Allianz ; Residência ; Sinistro ; Assistência Não Danos ; Assistência Residencial ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>305488889</t>
+  </si>
+  <si>
+    <t>Solicitei um serviço de desentupimento pela Allianz no dia 07/02, protocolo 51355725. No dia 08/02 o profissional veio e executou o atendimento. O detalhe importante é que os ralos ficam em área externa, então o problema só aparece quando chove. O próprio prestador informou que, caso não resolvesse, seria necessário maquinário profissional (Roto-Rooter) e registrou essa observação no protocolo._x000D_
+_x000D_
+_x000D_
+No dia 16/02 choveu muito em São Paulo e os ralos encheram novamente. Ou seja, o serviço foi feito, mas não resolveu o problema, o que claramente deveria entrar como garantia do atendimento anterior._x000D_
+_x000D_
+_x000D_
+Entrei em contato no próprio dia 16/02 e agendei um novo atendimento com maquinário para o dia 18/02. Recebi SMS de confirmação, porém ninguém apareceu._x000D_
+_x000D_
+_x000D_
+Liguei novamente no dia 19/02, protocolo 51453536, para entender o ocorrido e fui informada de que o serviço havia sido desmarcado porque no laudo não constava a observação do prestador. Durante a própria ligação, a atendente identificou que vincularam em meu CPF um laudo de um endereço do Espírito Santo, sendo que moro em São Paulo. Ou seja, uma completa desorganização interna._x000D_
+_x000D_
+_x000D_
+Mesmo diante desse erro evidente, a solução apresentada foi absurda: eu deveria abrir um novo chamado e consumir mais uma utilização da apólice, sob a justificativa de que agora seria outro serviço por envolver maquinário. Expliquei várias vezes que não se trata de outro serviço, mas do mesmo desentupimento dos mesmos ralos, apenas com técnica diferente. Ainda assim, a atendente insistiu nessa lógica sem nenhum sentido._x000D_
+_x000D_
+_x000D_
+Questionei então se, em situações futuras, seria possível solicitar diretamente o atendimento com maquinário, e fui informada de que não, pois obrigatoriamente um técnico precisa tentar manualmente antes. Exatamente o que ocorreu no primeiro atendimento._x000D_
+_x000D_
+_x000D_
+Alegaram também que o prestador fez o serviço. Claro que fez. Não estava chovendo no dia e não havia como validar o resultado naquele momento. Justamente por isso a observação sobre eventual uso de maquinário foi registrada, mas simplesmente não localizaram por erro interno da própria Allianz._x000D_
+_x000D_
+_x000D_
+Exijo que esse novo atendimento não seja contabilizado como mais uma utilização da minha apólice. O problema é o mesmo, o erro foi da Allianz e o desgaste para resolver algo tão simples é completamente desnecessário._x000D_
+_x000D_
+_x000D_
+Vale dizer que, apesar de a situação não ser culpa direta da atendente, fui interrompida diversas vezes durante a ligação e não consegui sequer explicar o ocorrido de forma adequada.</t>
+  </si>
+  <si>
+    <t>95646219</t>
+  </si>
+  <si>
+    <t>241095575</t>
+  </si>
+  <si>
+    <t>19/02/2026 14:22</t>
+  </si>
+  <si>
+    <t>136068808</t>
+  </si>
+  <si>
+    <t>Agendei um atendimento técnico em minha residência para hoje, com janela de horário entre 13h e 18h. Por conta disso, deixei de ir trabalhar para poder aguardar o técnico dentro do período combinado._x000D_
+_x000D_
+_x000D_
+Para minha surpresa, às 14h  já dentro do horário agendado  recebi apenas a informação de que o atendimento havia sido remarcado, sem qualquer consulta prévia sobre minha disponibilidade ou autorização. Ou seja, alteraram um compromisso que eu organizei toda a minha rotina para cumprir, demonstrando total desrespeito com o consumidor._x000D_
+_x000D_
+_x000D_
+Esse tipo de conduta causa prejuízo e e transtorno, além de evidenciar falta de consideração com o tempo do cliente. Espero que a empresa reveja seus procedimentos e trate seus consumidores com o mínimo de respeito e responsabilidade. Eu que sou cliente ha anos, com certeza deixarei de ser, pois demonstrou ser uma empresa que visa qualquer coisa, menos a qualidade de atendimento ao cliente.</t>
+  </si>
+  <si>
+    <t>95645710</t>
+  </si>
+  <si>
+    <t>241094245</t>
+  </si>
+  <si>
+    <t>19/02/2026 14:13</t>
+  </si>
+  <si>
+    <t>303622971</t>
+  </si>
+  <si>
+    <t>Estou com meu carro parado desde o data do sinistro em 17/12/2026, uma demora absurda o atendimento e resolução das pendências, muita demora para avaliar e para enviarem as peças, quando chegou que montou o carro, foi verificado que precisava de revisão em mais algumas peças, e desde o dia 04/02/2026 que estamos solicitando as peças, ligando para o perito sem obter nenhuma resposta, várias fotos enviadas, laudos solicitados, e quando eu ligo para a central a atendente fala que não tem nada no sistema, para eu aguardar 24 horas, e depois de 24 horas a mesma conversa e pedem pra aguardar mais 24 horas, nunca me ligaram ou enviaram uma resposta, liguei ontem pela terceira vez, e como sempre, novamente me falaram que não tinha nenhuma solicitação nem nenhuma pendência no sistema, sendo que as fotos são feitas no aplicativo, com data, hora e local, tudo registrado._x000D_
+_x000D_
+Já é a terceira vez que eu ligo e não tem nada e nenhuma posição, aguardo uma resolução hoje, e vou entrar com meu advogado para ajudar a resolver essa pendência que nem vocês sabem dizer o que esta acontecendo, e espero que o Avaliador (Wendell) consiga responder, porque ele esta ciente de toda situação e não esta nos atendendo ou respondendo mais.</t>
+  </si>
+  <si>
+    <t>95644430</t>
+  </si>
+  <si>
+    <t>241090267</t>
+  </si>
+  <si>
+    <t>19/02/2026 13:45</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Análise Sinistro</t>
+  </si>
+  <si>
+    <t>304924451</t>
+  </si>
+  <si>
+    <t>SINISTRO 304924451_x000D_
+_x000D_
+Eu, Elaine da Silva Donizetti Gondim, segurada da Allianz Seguros (Apólice n 517720252N311047138, vigência a partir de 12/05/2025), comunico que sofri um sinistro de roubo n 304924451, ocorrido em 23/01/2026. Após orientação da seguradora, efetuei o pagamento do IPVA 2026 para prosseguimento do processo de indenização. Considerando o roubo, o valor devido correspondeu a 1/12 do imposto, no montante de R$ 337,38, pago em 05/02/2026 por meio de guias emitidas pela Secretaria de Estado da Fazenda do RJ. Entretanto, no relatório de indenização enviado pela seguradora, foi aplicado desconto indevido de R$ 4.035,28, alegadamente referente ao IPVA 2026. Desde então, eu e meu corretor solicitamos esclarecimentos e o ressarcimento do valor, porém a seguradora atribui a responsabilidade à Secretaria da Fazenda, a qual informa que recebeu apenas o valor efetivamente pago por mim, não havendo possibilidade de devolução adicional. Ressalto que a seguradora não apresentou qualquer comprovação de pagamento do valor descontado, o que caracteriza desconto indevido e possível apropriação indevida de valores. Por meio deste, concedo à Allianz a oportunidade de se manifestar formalmente e apresentar justificativas e comprovações cabíveis, antes da adoção das medidas judiciais pertinentes.</t>
+  </si>
+  <si>
+    <t>95644320</t>
+  </si>
+  <si>
+    <t>241090003</t>
+  </si>
+  <si>
+    <t>19/02/2026 13:43</t>
+  </si>
+  <si>
+    <t>305833393</t>
+  </si>
+  <si>
+    <t>Eu nunca precisei do seguro, mas a hora que a gente faz, é pra quando a gente precisar, né? Ter ali um suporte, no qual eu precisei e, assim, fui pessimamente atendida. Eu fiquei numa rodovia durante 4h00. A seguradora, assim, não deu nenhum suporte e, cada hora, era um que ligava. A gente ficou numa rodovia sem, sem banheiro, sem nada, lugar perigoso, né? A gente ficou num, em um pedágio abandonado. Cada hora era uma pessoa que ligava. A gente acionou o guincho e o táxi, porque eu estava em outro estado e o nosso seguro só cobria 500 km. Quando foi na hora de pagar a diferença, né, do excedente, todas as pessoas passaram um valor na hora de finalizar e liberar o guincheiro, que ficou por uma hora e meia no local, e o taxista ficou por 2h00 e eu, né, assegurada, fiquei por 4h00, com uma pet no meio, assim, do nada, e eles não liberavam, não liberavam o guincheiro nem o taxista pra estar saindo do local. E, na hora de finalizar, um passou um valor do excedente, o guincheiro passou o valor e a seguradora passou outro. E cada vez que você ligava pra seguradora, passava por uma pessoa diferente e você tinha que repetir tudo, todos os seus dados, tudo que tava acontecendo. E cada hora um falava uma coisa. E todos confirmavam o valor, né, o primeiro valor. E só uma pessoa que ligou pra gente falando que tinha cotado errado, só que daí o erro já não é nosso, né? Já cabe à seguradora está fazendo isso com a pessoa que errou, né? E, assim, eu achei um total descaso. Eu não recomendo pra ninguém. Resumindo, a gente ficou no local há mais de 4h00 e isso levou o dia todo. Eu, eu, eu parei lá e assinei o seguro às 9h00 da manhã e eu consegui chegar na minha casa às, à meia-noite 4h30 mais ou menos. Só foi o tempo de espera só pra eles aprovarem. E, assim, coisas que não aprovam, eu pago o seguro há anos e, assim, você só conhece a seguradora, minhas fãs, quando você precisa. E essa, eu vi que é péssima. Eu não recomendo a ninguém e, assim, tudo muito bagunçado. E o meu carro ele era pra estar vindo no no dia seguinte né por conta de tanta demora deles não ia ser o tempo suficiente pra chegar na cidade né aonde eu moro que é aonde ia ser entregue o carro e mesmo assim levou um dia todo pra eles resolver pra enviar o carro no outro dia ou seja o meu carro foi pra outro lugar e demorou dois dias pra chegar No na minha casa né no caso pra mim levar ele pro conserto já que a gente trabalha com o carro</t>
+  </si>
+  <si>
+    <t>95642933</t>
+  </si>
+  <si>
+    <t>241086141</t>
+  </si>
+  <si>
+    <t>19/02/2026 13:13</t>
+  </si>
+  <si>
+    <t>303819348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pessoal horrível de trabalho, estou a 2 meses sem minha moto após o acidente, nao tem comunicação na empresa, todo dia tem que entrar em contato para tentar agilizar o serviço, irresponsáveis, sem compromisso e desleal com o seu cliente._x000D_
+_x000D_
+</t>
+  </si>
+  <si>
+    <t>95635892</t>
+  </si>
+  <si>
+    <t>241065531</t>
+  </si>
+  <si>
+    <t>19/02/2026 10:53</t>
+  </si>
+  <si>
+    <t>Allianz ; CPF/CNPJ ; Automóvel ; Canal de Atendimento ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; 11 Não Cliente ; Comercial</t>
+  </si>
+  <si>
+    <t>CPF/CNPJ</t>
+  </si>
+  <si>
+    <t>Canal de Atendimento</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>11 Não Cliente</t>
+  </si>
+  <si>
+    <t>8468677701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assunto: Pedido de retirada de consultas ao CPF - afronta ao Código de Defesa do Consumidor_x000D_
+_x000D_
+_x000D_
+Tenho sido alvo de consultas indevidas em meu CPF junto ao Serasa, realizadas sem qualquer solicitação de crédito ou vínculo contratual vigente._x000D_
+_x000D_
+Essas consultas impactam negativamente meu score e afetam minha credibilidade financeira._x000D_
+_x000D_
+Nos termos do art. 43 do Código de Defesa do Consumidor, as informações do consumidor devem ser tratadas de forma legítima, correta e sem causar prejuízos indevidos. Da mesma forma, a Lei Geral de Proteção de Dados (Lei n 13.709/2018) estabelece que o tratamento de dados pessoais deve observar os princípios da finalidade, necessidade e adequação._x000D_
+_x000D_
+A realização de consultas reiteradas, sem autorização ou fundamento legal, viola a boa-fé objetiva e caracteriza uso abusivo de dados pessoais._x000D_
+_x000D_
+Diante disso, requer-se a exclusão imediata das consultas indevidas, a cessação de novas pesquisas não autorizadas e a regularização do histórico de crédito._x000D_
+_x000D_
+</t>
+  </si>
+  <si>
+    <t>95631331</t>
+  </si>
+  <si>
+    <t>241052775</t>
+  </si>
+  <si>
+    <t>19/02/2026 09:25</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Pagamento ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Pagamento</t>
+  </si>
+  <si>
+    <t>132837714</t>
+  </si>
+  <si>
+    <t>Houve uma uma inconsistência no sistema da Allianz que está alegando que eu não paguei a fatura deste mês, só que eu já paguei o meu cartão de crédito da Caixa Econômica Federal, já debitou já está lá. Já está lá como aprovado, já mandei print para meu corretor e para assistente do corretor e ainda alegam que não foi feito o pagamento, só que eu já paguei já mandei print e eu estou aqui agora utilizando esse recurso do reclame aqui para reclamar sobre essa inconsistência que a aliança está alegando para o meu corretor e para assistente do corretor que a cliente não pagou, só que eu já paguei a Caixa Econômica não disponibiliza em PDF ou comprovante da transação o que pode o que eu fiz foi criar foto da tela do celular da transação que foi feito do pagamento que já foi debitado no meu cartão o limite que tinha já foi já foi suprido pela pelo débito, né 215 alguma coisa e ali antes tá alegando.Que eu paguei tanto é que no aplicativo ainda consta que ainda está em atraso de pagamento, só que eu já paguei e a linha está com algum inconsistência no sistema que não quer reconhecer não quer reconhecer então na Caixa Econômica está tudo regularizado, está tudo pago. Inclusive a minha esposa que é a dona do cartão ligou para caixa econômica e a Caixa Econômica alegou que está tudo certo com esse débito, o débito foi compensado no sistema da Caixa, só que a aliena a gente não quer reconhecer e a menina da seguradora ela informou que a própria aliança mesmo recebendo a comprovação do print da foto da a foto da da tela do celular ainda assim não quis reconhecer. Aplicativo do Reclame Aqui não está me deixando anexar os comprovantes. Favor pedir por email ou conversa interna.</t>
+  </si>
+  <si>
+    <t>95629379</t>
+  </si>
+  <si>
+    <t>241047277</t>
+  </si>
+  <si>
+    <t>19/02/2026 08:32</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Vida / Acidentes Pessoais ; Apólice ; Condições Gerais ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Vida / Acidentes Pessoais</t>
   </si>
   <si>
     <t>Condições Gerais</t>
   </si>
   <si>
-    <t>112177680</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olá, dia 2 de novembro de 2025 t minha esposa teve um sinistro de trânsito em colisão danificando aporta do meu veículo do lado do motorista a porta do passageiro. Fiz uma pesquisa se compensava arruma particular ou acionar o seguro em dezembro entrei em contato com o corretor para aciona o seguro  o corretor deu vários endereços para eu levar o veículo , levei na empresa Marques e Marques que fica na av. Santo Amaro mas não gostei da vistoria que fizeram e optei para fazer em outra oficina credenciada fui na oficina 400 que fica no socorro e lá fizeram a vistoria e depois iria entra em contato comigo  passou uma semana a  não entrou em contato liguei lá e me informaram que a vistoria não foi aprovada, retornei para o meu corretor para sabe o que tinha acontecido fui informado que o sinistro não tinha atingido a franquia do meu carro sendo que a franquia é 6.340 e fiz os orçamentos ficou em 7,750 feito pela Hyundai e tbm pela uma oficina aonde arrumei o carro   Aí fica a questão pagar o seguro e quando precisei não fui atendido  e gastei dinheiro mas do que a franquia  Resumindo só quero o meu dinheiro de volta que paguei  que paguei o seguro ou a seguradora Allianz me dá o dinheiro que gastei para arrumar o carro que foi 7.750 ._x000D_
-_x000D_
-</t>
-  </si>
-  <si>
-    <t>95619475</t>
-  </si>
-  <si>
-    <t>241017145</t>
-  </si>
-  <si>
-    <t>18/02/2026 19:23</t>
-  </si>
-  <si>
-    <t>Allianz ; Automóvel ; Assistência Não Danos ; Carro Reserva ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Apólice</t>
-  </si>
-  <si>
-    <t>Carro Reserva</t>
-  </si>
-  <si>
-    <t>132353368</t>
-  </si>
-  <si>
-    <t>Tive meu veículo (segurado pela Allianz) envolvido em acidente de trânsito no dia 22/01/26, sendo atingido por outro automóvel segurado pela Seguradora Yelum._x000D_
-_x000D_
-Após o cadastro do sinistro do terceiro, optei em fazer o serviço na concessionária Alpínia, por se tratar de veículo em período de garantia e pouco mais de 13 mil kms de uso._x000D_
-_x000D_
-Realizada a vistoria da seguradora na concessionária me foi enviado o orçamento (anexo) no valor de R$ 4.209,98, sendo informado pelo funcionário Paulo (funilaria da Alpínia) que o serviço duraria em média de 3 a 4 dias, coadunando assim com a previsão de quase 16 horas de serviço mencionadas no orçamento._x000D_
-_x000D_
-Verifiquei junto a minha corretora (VL Seguros) a possibilidade de concessão de carro reserva pela Allianz, ocasião em que me foi informado que conforme cláusula contratual, tal condição só poderia acontecer se o valor do reparo ultrapasse minha franquia, no caso R$ 4.901,01, conforme condições gerais de uso do seguro emitidas pela Allianz, item 13.6._x000D_
-_x000D_
-Nesse prisma compete salientar que minha apólice (anexa) tem previsão de acionamento de primeira franquia com desconto de 100% (sem pagamento de qualquer valor) e em caso de segundo acionamento o valor de R$ 4.901,01. Destaca-se que não houve nenhum acionamento do seguro desde a última renovação._x000D_
-_x000D_
-Ocorre que no dia 11/02/26, em contato com a funilaria da concessionária Alpínia Fiat, durante a realização do agendamento do serviço, o funcionário Ricardo, solicitou que o carro fosse levado no dia 23/02/26, e atualizou o prazo de entrega do veículo para entre 7 e 10 dias úteis e não mais 3 dias como anteriormente fora informado. Diante disso questionei sobre a divergência absurda para o quantitativo de horas de serviço previstos em orçamento (16h), sendo então informado que tal orçamento sofreria alteração de valor e aumento das horas (conforme print), ocasião em que seria solicitado um aditivo._x000D_
-_x000D_
-Posto isso, ainda sim solicitei a minha corretora VL Seguros que solicitasse o carro reserva, considerando que haveria aumento de vários dias de serviço e consequentemente ultrapassaria o valor de minha franquia, possibilitando o direito a concessão de carro reserva por 7 dias._x000D_
-_x000D_
-Entretanto conforme informou meu corretor, a Allianz condicionou a concessão a remessa de outro orçamento com o complemento previsto, mesmo que minha franquia para primeiro acionamento seja livre de custos e que seja iminente o aumento de valores que ultrapassarão os custos do segundo acionamento de franquia._x000D_
-_x000D_
-Porém para que seja elaborado tal complemento é necessário que seja iniciado o serviço e desmontado o veículo, a fim de que seja identificado corretamente quais seriam as demandas. Nessa lógica o expediente só poderá ser liberado dias após, ficando esse período sem carro reserva, considerando ainda o período de análise da documentação pela Allianz, o que na prática pode consumir todo o período de reparos e consequentemente perder a necessidade de um carro reserva._x000D_
-_x000D_
-Ou seja, se ao final os valores ultrapassarem a franquia, perderei um direito previsto em apólice por meras filigranas jurídicas da Allianz, ou ainda, pela correta análise do caso concreto._x000D_
-_x000D_
-Permaneço a disposição para eventuais esclarecimentos ou envio de mais documentos necessários.</t>
-  </si>
-  <si>
-    <t>95619163</t>
-  </si>
-  <si>
-    <t>241015919</t>
-  </si>
-  <si>
-    <t>18/02/2026 19:10</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Pagamento ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Pagamento</t>
-  </si>
-  <si>
-    <t>136724861</t>
-  </si>
-  <si>
-    <t>Boa noite, venho através desse canal alertar os consumidores para redobrar a atenção ao fazer seguro do deu patrimônio com essa seguradora, fechei um seguro para o meu veículo no valor de R$ 9.821,31 em 10 vezes no cartão de crédito, ocorre que a seguradora descontou em duplicidade o valor da primeira parcela, segundo informações da seguradora o valor seria extornado em 24 horas, já se passou uma semana e o extorno não aconteceu, acho que cai em uma silada, essa seguradora tem diversas reclamações no site reclame aqui sem resposta, sei que cometi um erro, deveria ter visto isso antes de fechar o seguro, mas infelizmente confiei no corretor e acabei fechando seguro com essa seguradora, a minha única alternativa de ser ouvido é abrir essa reclamação e levar sorte que respondam, Não façam negócio com essa seguradora, Diante da experiência não recomendo, é só olhar no site do reclame aqui e ver reclamação sem resposta por parte da seguradora.</t>
-  </si>
-  <si>
-    <t>95614712</t>
-  </si>
-  <si>
-    <t>241003047</t>
-  </si>
-  <si>
-    <t>18/02/2026 17:06</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Residência ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Assistência Não Danos ; Assistência Residencial</t>
-  </si>
-  <si>
-    <t>Assistência Residencial</t>
-  </si>
-  <si>
-    <t>131130277</t>
-  </si>
-  <si>
-    <t>Prezados,_x000D_
-_x000D_
-_x000D_
-Venho por meio deste solicitar um parecer formal referente aos dois protocolos de reembolso, os quais foram devidamente liberados e autorizados pela própria central da Allianz._x000D_
-_x000D_
-_x000D_
-Trata-se de uma empresa de grande porte, que preza pela qualidade no atendimento. No entanto, já realizei diversos contatos e enviei inúmeros e-mails, todos sem retorno efetivo. Infelizmente, os analistas não têm apresentado resolutividade, demonstrando descaso com a segurada._x000D_
-_x000D_
-_x000D_
-Ressalto que foi criado um link para envio de documentação para análise, no qual consta o prazo de 2 a 5 dias para retorno. Contudo, esse prazo já foi ultrapassado há dias, sem qualquer posicionamento._x000D_
-_x000D_
-_x000D_
-O acúmulo de protocolos é falha interna da própria seguradora, e não da segurada, uma vez que os chamados foram abertos em datas distintas, assim como os serviços foram realizados em momentos diferentes._x000D_
-_x000D_
-_x000D_
-Além da demora no agendamento por falta de prestadores disponíveis, fui orientada pela própria central a realizar os serviços de forma particular. Após o envio correto de toda a documentação exigida, não houve retorno conclusivo. Os atendentes informam que o setor interno entrará em contato, porém não recebo e-mail nem ligação._x000D_
-_x000D_
-_x000D_
-Diante do exposto, exijo uma data conclusiva para o pagamento de ambos os reembolsos, considerando que todas as exigências foram devidamente cumpridas por minha parte._x000D_
-_x000D_
-PROTOCOLOS :_x000D_
-_x000D_
-- 51197183_x000D_
-_x000D_
--51158633_x000D_
-_x000D_
--51264749_x000D_
-_x000D_
-_x000D_
-Aguardo retorno com a máxima urgência._x000D_
-_x000D_
-_x000D_
-Atenciosamente,_x000D_
-_x000D_
-Valeska Souza</t>
-  </si>
-  <si>
-    <t>95614051</t>
-  </si>
-  <si>
-    <t>241000931</t>
-  </si>
-  <si>
-    <t>18/02/2026 16:49</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 2 Terceiro do Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Sinistro</t>
-  </si>
-  <si>
-    <t>Análise Sinistro</t>
-  </si>
-  <si>
-    <t>2 Terceiro do Sinistro</t>
-  </si>
-  <si>
-    <t>278260621</t>
-  </si>
-  <si>
-    <t>Em Julho de 2023, aconteceu uma colisão entre o meu carro e o carro de uma segurada da ALLIANZ. Na época, foi solicitado o seguro para terceiros, para arrumar o meu carro._x000D_
-_x000D_
-O carro foi levado na oficina que vocês escolheram, e foi arrumado. Agora, em 2026, estou colocando o carro a venda, e quando fui fazer a vistoria cautelar, para a minha surpresa o carro foi reprovado, e está com apontamentos. Entrei em contato com a seguradora, para verificarem a minha situação, e me disseram está tudo Ok. Pois bem, antes da batida e antes do conserto o meu carro não tinha laudo reprovado, então peço por favor que reavaliem essa situação para o devido conserto do carro. Para que ele seja aprovado na cautelar , para que eu possa dar andamento na venda do mesmo. _x000D_
-_x000D_
-Já pesquisei sobre a situação, e como é um vício oculto, que foi descoberto agora, a segurado não pode se negar a prestar o serviço. É um direito do consumidor. Não posso ficar nessa situação, aguardo um breve retorno.</t>
-  </si>
-  <si>
-    <t>95610102</t>
-  </si>
-  <si>
-    <t>240989455</t>
-  </si>
-  <si>
-    <t>18/02/2026 15:17</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; 11 Não Cliente ; Emissão ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Sinistro</t>
-  </si>
-  <si>
-    <t>Emissão</t>
-  </si>
-  <si>
-    <t>11 Não Cliente</t>
-  </si>
-  <si>
-    <t>133028853</t>
-  </si>
-  <si>
-    <t>Adquiri através d Freitas Leiloeiro em 12/12/2025 o véiculo Kia Stonic 2022, placas CSU8A82 cuja NF não me foi fornecida e até agora não consegui transferir o automével.Solicito providências.Obrigado-Cesar Rafael Soffredi</t>
-  </si>
-  <si>
-    <t>95589312</t>
-  </si>
-  <si>
-    <t>240935779</t>
-  </si>
-  <si>
-    <t>18/02/2026 03:32</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Canal de Atendimento ; Corretor ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Reclamante em nome do Segurado</t>
-  </si>
-  <si>
-    <t>Canal de Atendimento</t>
-  </si>
-  <si>
-    <t>Corretor</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>134774861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Espirito Santo do Pinhal.  13/02/2026_x000D_
-_x000D_
-Tenho Um Fox 2009 Modelo 2010. Desde que o  comprei eu tenho seguro, com uma vendedora chamada Patrícia aqui de Espirito Santo do Pinhal-SP. Não sei se ela sempre trabalhou pela Seguradora Allianz, se trabalhava para outra seguradora, o fato é que meu Pai Honorato **** da Costa, CPF 040.***.***-08  sempre foi fiel a essa vendedora Patricia, desde que compramos o carro confiamos nela sobre o seguro do Fox. _x000D_
-_x000D_
-No dia 23/jan/2026 tivemos um incidente e batemos num carro, quebrando o retrovisor deste, o dono nos contatou, ligamos para a Patricia que trabalha para a  Allianz responsável pelo seguro do nosso Fox no dia 26/jan/2026 ela pediu todos os dados, o que aconteceu, pediu o documento do carro, as fotos do nosso carro e do carro do terceiro mandamos para ela. No dia 30 de Janeiro de 2026 ela diz que o sinistro foi aberto e esta tudo encaminhado. Ficamos sossegados. _x000D_
-_x000D_
-06/FEV/2026 ficamos sabendo pelo terceiro, que houve um problema na cobertura do seguro, um problema no pagamento lá em novembro de 2025, FICAMOS SABENDO PELO TERECEIRO QUE NOSSO CARRO ESTAVA DESCOBERTO DE SEGURO. Pelo que nosso advogado orientou o que aconteceu foi ilegal e abusivo, liguei para a Patricia ela disse que mandou mensagem no WhatsApp de fato ela mandou, mas não vimos a mensagem em MOMENTO ALGUM houve uma conversa que o SEGURO HAVIA SIDO CANCELADO. Que falta de respeito é essa que um assunto num nível tão serio foi conversado de maneira tão indiferente para ser enviado via WhastApp? Desde outrubro do ano passado minha família vem enfrentando problemas de saúde (PROBLEMA EXCLUSIVO NOSSO, NINGUEM TEM NADA A VER COM ISSO) mas se não houve resposta no aplicativo de conversa e não regularizamos o pagamento, Patricia não nos contatou, nem no telefone fixo, ela alegou que não tem nosso telefone fixo, como alguém que é responsável pelo seguro do nosso carro há mais de dez anos não tem nosso telefone fixo? Durante a ligação Patricia  foi rude, hostil, grossa, disse que não tem como saber qual cliente esta doente ou não, uma grosseria, e um total constrangimento a nós clientes a mais de uma década. O modo como ela tratou minha mãe Terezinha de F***  L**** Costa foi um tom alterado, rude, totalmente constrangedor.  esse comportamento vai contra o Codigo de Defesa do Consumidor: Vendedor que constrange, (..)  expõe cliente ao ridículo viola o Código de Defesa do Consumidor (art. 42). E foi exatamente isso que a Patricia e seguradora Allianz  fez: expos meu Pai, minha mãe ao ridículo, por sabermos somente pelo terceiro que houve falha no pagamento e o carro estava descoberto. Não houve nenhum contato direto da Vendedora de Seguros da Allianz, Patricia com ninguém dessa família. Um assunto tão serio que envolve seguro de carro não devia ser tratado como conversa de aplicativo, Leu a mensagem, leu. Não Leu Paciencia É essa a mensagem e imagem que a seguradora Allianz transmite? Um assunto tão serio como fofoca de aplicativo? Ao ser questionada por que não ligou no telefone fixo onde era certeza encontrar alguém e conversar diretamente a resposta de Patricia foi: Não tenho o telefone fixo de voces uma década sendo a responsável pelo seguro do carro com todos os nossos dados ela não tem o fixo e nunca pensou em acrescentar no nosso cadastro. _x000D_
-_x000D_
-Que TOTAL FALTA DE RESPEITO SEGURADORA ALLIANZ. _x000D_
-_x000D_
-Vocês violaram o código de defesa do consumidor, estava disposta a pagar o seguro até por boleto mesmo com juros altíssimos para termos o sossego do carro estar assegurado. Nunca houve uma conversa entre a Patricia e minha família: onde ela esclarece o que houve, sabe o que temos? Uma mensagem no WhatsApp que pode ser apagada a qualquer hora. Sempre pagamos o seguro com a maior satisfação, agora na hora que precisamos a ALLIANZ e sua funcionaria Patricia de ESPIRITO SANTO DO PINHAL-SP nos notificarem do que aconteceu nos deixaram na mão, o CANCELAMENTO DO SEGURO SEM AVISO PRÉVIO é considerado ilegal e abusivo, violando o Código de Defesa do Consumidor (CDC) e jurisprudência do STJ (Súmula 616), pois a seguradora deve notificar o segurado antes de suspender ou encerrar o contrato. A nova Lei de Seguros (15040/2024) reforça que é proibido o cancelamento automático por falta de pagamento sem notificação, exceto no não pagamento da primeira parcela ou de parcela única. A primeira parcela foi o paga. O maior problema de tudo isso foi a hostilidade da Patricia funcionaria da ALLIANZ, NÃO HOUVE CONTATO, NÃO HOUVE CONVERSA. HOUVE FALTA DE RESPEITO COMIGO E MEUS PAIS. Que se encontram num momento de total fragilidade pela saúde da minha mãe e toda chateação e perturbação, e todo constrangimento que se deu pelo comportamento malcriado, ofensivo, difamatório (ela afirmou que vimos a mensagem e não respondemos), humilhante, afrontoso e insolente de Patricia, funcionaria da Allianz. _x000D_
-_x000D_
-</t>
+    <t>131386215</t>
+  </si>
+  <si>
+    <t>Foi gerado um boleto indevido no meu nome no valor de 164,13 e não consigo contato via telefone. Gostaria de que o boleto fosse cancelado pois não assinei nenhum seguro, desde já agradeço e aguardo contato.</t>
   </si>
 </sst>
 </file>
@@ -952,7 +1127,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AA8803-373C-4E0C-ABA8-1F171C96DA02}">
-  <dimension ref="A1:AA22"/>
+  <dimension ref="A1:AA20"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="3" bestFit="1" customWidth="1" collapsed="1"/>
@@ -1106,25 +1281,25 @@
         <v>38</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y2" s="3" t="s">
         <v>26</v>
@@ -1134,13 +1309,13 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>30</v>
@@ -1149,46 +1324,46 @@
         <v>31</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y3" s="3" t="s">
         <v>26</v>
@@ -1198,13 +1373,13 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>30</v>
@@ -1213,40 +1388,40 @@
         <v>31</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W4" s="4" t="s">
         <v>60</v>
@@ -1286,37 +1461,37 @@
         <v>34</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Y5" s="3" t="s">
         <v>26</v>
@@ -1326,13 +1501,13 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>30</v>
@@ -1341,7 +1516,7 @@
         <v>31</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>33</v>
@@ -1356,31 +1531,31 @@
         <v>36</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y6" s="3" t="s">
         <v>26</v>
@@ -1390,13 +1565,13 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>30</v>
@@ -1405,40 +1580,40 @@
         <v>31</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W7" s="4" t="s">
         <v>81</v>
@@ -1475,34 +1650,34 @@
         <v>33</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>87</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W8" s="4" t="s">
         <v>88</v>
@@ -1533,46 +1708,46 @@
         <v>31</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="W9" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="X9" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="W9" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="X9" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>26</v>
@@ -1582,13 +1757,13 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>30</v>
@@ -1597,46 +1772,46 @@
         <v>31</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>26</v>
@@ -1644,13 +1819,13 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>30</v>
@@ -1659,7 +1834,7 @@
         <v>31</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>33</v>
@@ -1671,74 +1846,596 @@
         <v>35</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="Y11" s="3" t="s">
         <v>26</v>
       </c>
     </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="X12" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W13" s="4"/>
+      <c r="A13" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V13" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="W13" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="X13" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y13" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
+      <c r="A14" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="W14" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="X14" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W15" s="4"/>
+      <c r="A15" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="W15" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="X15" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
+      <c r="A16" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="W16" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="X16" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y16" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="17" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="18" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W18" s="4"/>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="W18" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="X18" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="19" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W19" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="X19" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y19" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="20" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W20" s="4"/>
-      <c r="X20" s="4"/>
-    </row>
-    <row r="21" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W21" s="4"/>
-    </row>
-    <row r="22" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W22" s="4"/>
-      <c r="X22" s="4"/>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="W20" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="X20" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AN9" xr:uid="{D3AA8803-373C-4E0C-ABA8-1F171C96DA02}"/>

--- a/Treinamento/GestaoReclamacao.xlsx
+++ b/Treinamento/GestaoReclamacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D43C2A-B27E-4AB6-9CF3-A8A9217F056B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F417AB67-AE3D-4B4C-A09A-3660837AD69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B1A77FD5-2AD3-4458-ACB3-7F19D1A3340A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="124">
   <si>
     <t>Id HugMe</t>
   </si>
@@ -122,13 +122,13 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>95836290</t>
-  </si>
-  <si>
-    <t>241603093</t>
-  </si>
-  <si>
-    <t>24/02/2026 23:48</t>
+    <t>95872955</t>
+  </si>
+  <si>
+    <t>241709689</t>
+  </si>
+  <si>
+    <t>25/02/2026 22:29</t>
   </si>
   <si>
     <t>Não respondido</t>
@@ -137,292 +137,346 @@
     <t>Não</t>
   </si>
   <si>
-    <t>Allianz ; Apólice ; Automóvel ; Apólice ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Cancelamento</t>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 2 Terceiro do Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
     <t>Allianz</t>
   </si>
   <si>
+    <t>Sinistro</t>
+  </si>
+  <si>
+    <t>Automóvel</t>
+  </si>
+  <si>
+    <t>Análise Sinistro</t>
+  </si>
+  <si>
+    <t>2 Terceiro do Sinistro</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Repasse Time MindBe</t>
+  </si>
+  <si>
+    <t>Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Juliana</t>
+  </si>
+  <si>
+    <t>305688122</t>
+  </si>
+  <si>
+    <t>Quero resposta sobre o meu carro que to aguardando resposta para o conserto</t>
+  </si>
+  <si>
+    <t>95871846</t>
+  </si>
+  <si>
+    <t>241706183</t>
+  </si>
+  <si>
+    <t>25/02/2026 21:40</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Condomínio ; Sinistro ; Indenização ; Reclamante em nome do Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Condomínio</t>
+  </si>
+  <si>
+    <t>Indenização</t>
+  </si>
+  <si>
+    <t>Reclamante em nome do Segurado</t>
+  </si>
+  <si>
+    <t>301848864</t>
+  </si>
+  <si>
+    <t>_x000D_
+_x000D_
+_x000D_
+Olá, demos entrada no seguro em novembro, enviamos toda a documentação necessária, o prazo de análise já encerrou e até o momento não nos deram retorno acerca do início do pagamento. Teremos que esperar mais quanto tempo? Que absurdo!!</t>
+  </si>
+  <si>
+    <t>95866952</t>
+  </si>
+  <si>
+    <t>241691237</t>
+  </si>
+  <si>
+    <t>25/02/2026 18:48</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Reclamante em nome do Segurado ; Vistoria Prévia ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Con.GOV</t>
+  </si>
+  <si>
     <t>Apólice</t>
   </si>
   <si>
-    <t>Automóvel</t>
+    <t>Vistoria Prévia</t>
+  </si>
+  <si>
+    <t>Con.GOV</t>
+  </si>
+  <si>
+    <t>135415124</t>
+  </si>
+  <si>
+    <t>Título: Descaso da Allianz com idosa: Vistoria digital travada e resposta de 10 dias para um endosso urgente_x000D_
+_x000D_
+_x000D_
+Estou utilizando este canal para manifestar minha profunda indignação com o tratamento que a Allianz Seguros está dando à minha sogra, Joselita (Apólice: 517720252P312494882)._x000D_
+_x000D_
+_x000D_
+Ontem pela manhã (24/02/2026), foi ela realizado todo o procedimento de vistoria digital para substituição de veículo (endosso). O processo, que deveria ser ágil por ser feito via fotos, está travado em "análise" há mais de 24 horas. O resultado? Ela está com o carro praticamente na garagem, sem poder circular por falta de cobertura securitária, sendo impedida de exercer seu direito de ir e vir com segurança._x000D_
+_x000D_
+_x000D_
+Ao formalizar a reclamação na Ouvidoria esperando prioridade, a resposta da Allianz foi um completo desdém: um protocolo (OUV_587_2026) informando que o prazo de resposta é de até 10 dias._x000D_
+_x000D_
+_x000D_
+É inadmissível que uma seguradora desse porte peça 10 dias para analisar fotos de uma vistoria digital que deveria ser concluída em horas. Minha sogra é uma pessoa que cumpre com seus deveres e precisa do veículo para sua rotina. Deixá-la desamparada e sem previsão real de solução é uma falta de respeito com o consumidor._x000D_
+_x000D_
+_x000D_
+Pedimos:_x000D_
+_x000D_
+A análise imediata das fotos enviadas na vistoria digital;_x000D_
+_x000D_
+A formalização do endosso ainda hoje para que o veículo esteja devidamente coberto;_x000D_
+_x000D_
+Respeito ao cliente que opta pelos canais digitais em busca de eficiência, não de burocracia._x000D_
+_x000D_
+_x000D_
+Não aceitaremos o prazo de 10 dias para um problema causado pela própria lentidão da seguradora.</t>
+  </si>
+  <si>
+    <t>95865816</t>
+  </si>
+  <si>
+    <t>241687829</t>
+  </si>
+  <si>
+    <t>25/02/2026 18:15</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Vidros - AutoGlass ; 1 Segurado ; Assistência Não Danos ; Sim ; Repasse Time MindBe ; Com Resposta - Dentro SLA - Analista ; RA</t>
+  </si>
+  <si>
+    <t>Assistência Não Danos</t>
+  </si>
+  <si>
+    <t>Vidros - AutoGlass</t>
+  </si>
+  <si>
+    <t>1 Segurado</t>
+  </si>
+  <si>
+    <t>RA</t>
+  </si>
+  <si>
+    <t>Com Resposta - Dentro SLA - Analista</t>
+  </si>
+  <si>
+    <t>Carla</t>
+  </si>
+  <si>
+    <t>131336504</t>
+  </si>
+  <si>
+    <t>Estou esperando a mais de 1 mês para conserto do retrovisor e até agora nada resolvido. Não consigo nenhum retorno para resolver o assunto. Solicito que seja resolvido urgentemente</t>
+  </si>
+  <si>
+    <t>95858621</t>
+  </si>
+  <si>
+    <t>241667259</t>
+  </si>
+  <si>
+    <t>25/02/2026 15:21</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Pagamento ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Pagamento</t>
+  </si>
+  <si>
+    <t>136187068</t>
+  </si>
+  <si>
+    <t>Liguei no dia 18/02 para reclamar sobre cobrança em duplicidade no meu seguro._x000D_
+_x000D_
+Paguei com cartão de crédito no dia 09/02, mesmo assim no dia 18/02 fizeram a mesma cobrança em conta corrente._x000D_
+_x000D_
+_x000D_
+Foi me passado o protocolo 2624519115 dizendo que seria estornado automaticamente em até 7 dias._x000D_
+_x000D_
+_x000D_
+Ainda não houve esse estorno na minha conta.</t>
+  </si>
+  <si>
+    <t>95857199</t>
+  </si>
+  <si>
+    <t>241663299</t>
+  </si>
+  <si>
+    <t>25/02/2026 14:50</t>
+  </si>
+  <si>
+    <t>Allianz ; Residência ; 1 Segurado ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Não ; Não ; Sinistro ; Atraso na Análise ; Sinistro</t>
+  </si>
+  <si>
+    <t>Residência</t>
+  </si>
+  <si>
+    <t>Atraso na Análise</t>
+  </si>
+  <si>
+    <t>304858824</t>
+  </si>
+  <si>
+    <t>Tive um sinistro com a minha geladeira e tv ja foi ressarcido porém ninguém me responde se é a seguradora quem faz o descarte das coisas ou se eu posso descartar?_x000D_
+_x000D_
+Ligo na central para informações e ninguém sabe me informar e fala que vai pedir para o setor responsável entrar em contato e ate agora nada_x000D_
+_x000D_
+Preciso de uma resposta, péssimo atendimento não indico</t>
+  </si>
+  <si>
+    <t>95855542</t>
+  </si>
+  <si>
+    <t>241658625</t>
+  </si>
+  <si>
+    <t>25/02/2026 14:14</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Residência ; Apólice ; Assistência Residencial ; Reclamante em nome do Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Assistência Residencial</t>
+  </si>
+  <si>
+    <t>136716335</t>
+  </si>
+  <si>
+    <t>Temos um seguro residencial junto a Allianz seguradora e temos no pacote de assistencia 5 itens entre os diversos possiveis para utilizar. Precisamos solicitar a instalação de um chuveiro e a atendente não informou que era somente um acionamento para até 5 itens, ou seja, o prestador foi lá, instalou o chuveiro e agora precisamos acionar para colocar um suporte de TV, quadro e cortina e simplesmete não podemos mais utilizar por que alegam que já foi utilizado. Se a atendente, fosse competente e bem instruida, teria informado, Sra Tatiane, não quer aproveitar a ida do prestador para colocar o chuveiro e utilizar mais 4 itens? Porque ele só vai lá uma vez ppr vigência. Dessa forma saberiamos e ja teriamos pedido. Agora, não foi orientado e agora nos privam de utilizar? Não temos obrigação de decorar o manual de utilização,  a orientação precisa ser clara e precisa para não lesar os clientes. Conto com a colaboração da Allianz para resolver amigavelmente esse ocorrido.</t>
+  </si>
+  <si>
+    <t>95852622</t>
+  </si>
+  <si>
+    <t>241649611</t>
+  </si>
+  <si>
+    <t>25/02/2026 13:03</t>
+  </si>
+  <si>
+    <t>134637065</t>
+  </si>
+  <si>
+    <t>1) Apólice N.: 517720253U312080959_x000D_
+_x000D_
+Proposta N.: 134637065 _x000D_
+_x000D_
+Conforme renovaçao do seguro em tela, o seguro do meu veiculo  Citroen C3 deveria ser pago em 10 parcelas MENSAIS de 208,00 mensais ._x000D_
+_x000D_
+Ocorre que a parcela deste mes foi DEBITADA em meu cartão final 6094  DUAS VEZES _x000D_
+_x000D_
+Devendo ser devolvida UMA DELAS pela ALIANZ de pronto  em meu cartao credito, pena  de ENRIQUECIMENTO INDEVIDO ._x000D_
+_x000D_
+_x000D_
+2) No mais, referente a TRANSFERENCIA de MEU VEICULO anterior  PARA A ALIANZ , (que  já e de propriedade da seguradora) um UPP  2015 , CONSTAM DEBITOS DE IPVA NO ORGAO RESPECTIVO._x000D_
+_x000D_
+_x000D_
+3) iSTO FEITO SOLICITO :  a) a devolução em meu cartao de credito acima da parcela cobrada A MAIOR ; b) o pagamento dos IPVAs do UPPI 2015 preto indicado acima  , e o COMPROVANTE DE TRANSFERENCIA JUNTO AO ORGÃO COMPETENTE _x000D_
+_x000D_
+_x000D_
+Aguardo as providencias  em 48 horas ,_x000D_
+_x000D_
+att.</t>
+  </si>
+  <si>
+    <t>95846312</t>
+  </si>
+  <si>
+    <t>241631499</t>
+  </si>
+  <si>
+    <t>25/02/2026 10:50</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Análise Sinistro</t>
+  </si>
+  <si>
+    <t>304981479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sou segurado no meu veículo RVY 4j85 pagamento em dia tive um incidente _x000D_
+_x000D_
+O corretor comunicou o reparo foi autorizado o veículo foi para a oficina e dias depois a Allianz negou o conserto!_x000D_
+_x000D_
+</t>
+  </si>
+  <si>
+    <t>95845101</t>
+  </si>
+  <si>
+    <t>241627947</t>
+  </si>
+  <si>
+    <t>25/02/2026 10:25</t>
+  </si>
+  <si>
+    <t>305500658</t>
+  </si>
+  <si>
+    <t>Segurado de vocês bateu no meu veiculo, foi aberto o sinistro por telefone tantio da parte dela quanto da minha no local do acidente, no dia 09/02/2026, no dia 12 se bem me recordo foi feita a vistoria e estou ate hoje dia 25/02/2026 ainda sem liberação para execução do serviço. Não existe duvida quanto ao acidente,  a mesma relatou o acontecido ao telefone na abertura do sinistro assumindo total culpa pelo acontecido, tenho videos e fotos do local do acidente na hora, o acidente foi em frente ao posto da policia rodoviaria, onde tem cameras. Estou tentando contato pelo site, onde apos inserir todos os dados solicitados me apresenta o historico e optei a falar pelo chat pra entender melhor a situação, onde ja estou a quase 1 h aguaradando para ser atendido e esta tudo gravado._x000D_
+_x000D_
+è um descaso absurdo, sera que não pensam que hoje eu sou terceiro, mas posso um dia ter um seguro da Allianz se fosse bem atendido: Temos 5 carros aqui em casa, e essa possibilidade vai ficando cada dia mais impossivel pela qualidade do atendimento._x000D_
+_x000D_
+Eu não ando nem com carro sujo, e agora estou ha 16 dias andando com carro batido, isso é um absurdo!!!!</t>
+  </si>
+  <si>
+    <t>95843440</t>
+  </si>
+  <si>
+    <t>241623247</t>
+  </si>
+  <si>
+    <t>25/02/2026 09:51</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Residência ; Apólice ; Cancelamento ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
     <t>Cancelamento</t>
   </si>
   <si>
-    <t>1 Segurado</t>
-  </si>
-  <si>
-    <t>Sim</t>
-  </si>
-  <si>
-    <t>Repasse Time MindBe</t>
-  </si>
-  <si>
-    <t>Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Juliana</t>
-  </si>
-  <si>
-    <t>131369756</t>
-  </si>
-  <si>
-    <t>Cancelei um seguro de vida em 28/12/2025 e foram cobrados indevidamente na fatura do meu cartão de crédito duas parcelas, uma em 23/01 e 23/02/2026. Solicito o ressarcimento destas parcelas cobradas e pagas.</t>
-  </si>
-  <si>
-    <t>95834767</t>
-  </si>
-  <si>
-    <t>241598417</t>
-  </si>
-  <si>
-    <t>24/02/2026 22:23</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Residência</t>
-  </si>
-  <si>
-    <t>Assistência Não Danos</t>
-  </si>
-  <si>
-    <t>Assistência Residencial</t>
-  </si>
-  <si>
-    <t>132515255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sou segurado da Allianz seguro residencial apolice 5177202561140190648. Tive um incidente de vazamento de tubulação 22/12/25 em minha residência. Abri o sinistro, registrei com fotos e vídeos os danos. Devido ao período próximo ao Natal, os orçamentos foram prejudicados. No início do ano, fiz os orçamentos e os enviei. Sempre fui acionado pela empresa terceira SINISTROSRE. Pediram detalhamento dos orçamentos. Enviados. Após muitas cobranças por minha parte a empresa SINISTROSRE, em 23/02 entrou em contato comigo autorizando o sinistro porém, dizendo que a porta que empenou com a água e o caixilho, não seriam completamente pagos pois um TÉCNICO a distância, sem ter vindo até a minha casa achava não necessário trocar o caixilho que está estufado e estragado pela inundação! Além disto, em vários itens pediram DESCONTOS financeiros para pagar à vista (algo óbvio e contratual). Além do desconto da franquia de 10%!_x000D_
-_x000D_
-Enfim, um descaso total da Allianz! Querendo ganhar em cima do contratante, com uma empresa terceira SINSITROSRE que nitidamente tem metas de reduzir linearmente os valores!_x000D_
-_x000D_
-Encerram meu pedido e eu que me vire!_x000D_
-_x000D_
-Um descaso!_x000D_
-_x000D_
-Um absurdo!_x000D_
-_x000D_
-Fui completamente agredido moralmente dois meses depois da abertura do sinistro!_x000D_
-_x000D_
-Me sinto lesado financeiramente e moralmente!_x000D_
-_x000D_
-A Allianz, que terceirizou o serviço deveria avaliar esta situação. _x000D_
-_x000D_
-</t>
-  </si>
-  <si>
-    <t>95831367</t>
-  </si>
-  <si>
-    <t>241587773</t>
-  </si>
-  <si>
-    <t>24/02/2026 20:18</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Carro Reserva ; Assistência Não Danos ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Sinistro</t>
-  </si>
-  <si>
-    <t>Carro Reserva</t>
-  </si>
-  <si>
-    <t>303896774</t>
-  </si>
-  <si>
-    <t>A seguradora já está a 60 dias sem solução pois não consegue a peça pro concerto do carro, e me deu so 15 dias de carro reserva. Estou gastando muito e o prejuizo material e emocional tá enorme, os mesmos não tem previsão.</t>
-  </si>
-  <si>
-    <t>95816894</t>
-  </si>
-  <si>
-    <t>241544797</t>
-  </si>
-  <si>
-    <t>24/02/2026 14:05</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Análise Sinistro</t>
-  </si>
-  <si>
-    <t>304763276</t>
-  </si>
-  <si>
-    <t>No dia 20 de janeiro de 2026 meu veículo sofreu perda total (PT). O veículo é financiado pelo Itaú._x000D_
-_x000D_
-_x000D_
-Desde então, estou aguardando a quitação do saldo devedor por parte da seguradora, conforme previsto em contrato._x000D_
-_x000D_
-_x000D_
-Já enviei o boleto de quitação emitido pelo Itaú quatro vezes, sempre com todas as informações corretas. Em cada envio, surge uma nova alegação para postergar o pagamento._x000D_
-_x000D_
-_x000D_
-Agora, a justificativa apresentada foi de que o boleto não está em meu nome, mas sim no nome do Itaú  o que é absolutamente coerente, pois o veículo é financiado e o banco é o beneficiário até a quitação._x000D_
-_x000D_
-_x000D_
-Não existe possibilidade de o boleto constar em meu nome, já que o carro ainda não está quitado._x000D_
-_x000D_
-_x000D_
-Enquanto a seguradora posterga o pagamento:_x000D_
-_x000D_
-_x000D_
-O saldo devedor já aumentou mais de R$ 200_x000D_
-_x000D_
-_x000D_
-Juros e multa continuam correndo_x000D_
-_x000D_
-_x000D_
-Uma parcela regular venceu_x000D_
-_x000D_
-_x000D_
-Estou sofrendo prejuízo financeiro por responsabilidade exclusiva da seguradora_x000D_
-_x000D_
-_x000D_
-Estou registrando todas as ligações e protocolos._x000D_
-_x000D_
-_x000D_
-Solicito urgência na quitação do financiamento conforme contrato, bem como posicionamento formal sobre o ressarcimento dos valores acrescidos por atraso indevido.</t>
-  </si>
-  <si>
-    <t>95814209</t>
-  </si>
-  <si>
-    <t>241536913</t>
-  </si>
-  <si>
-    <t>24/02/2026 13:06</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Assistência Não Danos ; Carro Reserva</t>
-  </si>
-  <si>
-    <t>131176878</t>
-  </si>
-  <si>
-    <t>Envolvi em um acidente da data de 13/12/2025, somente foi aprovado deixar o carro na oficina no dia 29 de janeiro, a oficina solicitou peças complementares, com previsão de entrega no dia 16/02/2026, e hoje dia 24/02/2026 e as peças ainda não chegaram. Vão sempre adiando a entrega. Agora consta a previsão de entrega das peças somente em Março. Enquanto isso o carro permanece na oficina, parado e sem o conserto finalizado. Já se passaram quase 3 (três) meses desde o acidente. Sou segurada e tenho direito a 30 dias de carro reserva mas como a causadora do acidente foi uma terceira, também segurada Allianz, somente me forneceram 7 (sete) dias de carro reserva, mesmo eu sendo segurada com 30 dias de carro reserva. Pago o seguro e quando preciso não posso usar os 30 dias de carro reserva porque não fui a causadora do acidente. Um total descaso pois estou desde Dezembro de  2025 sem o carro.</t>
-  </si>
-  <si>
-    <t>95805741</t>
-  </si>
-  <si>
-    <t>241516221</t>
-  </si>
-  <si>
-    <t>24/02/2026 10:42</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Apólice Digital ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Apólice Digital</t>
-  </si>
-  <si>
-    <t>136796878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proposta 003450255040 via Autocompara -  apresenta pendencias, o portal nao identifica quais são e no atendimento todos são perdidos, empurram o problema para o dia seguinte. Fujam dessa empresa!_x000D_
-_x000D_
-</t>
-  </si>
-  <si>
-    <t>95804263</t>
-  </si>
-  <si>
-    <t>241512021</t>
-  </si>
-  <si>
-    <t>24/02/2026 10:14</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; Reclamante em nome do Segurado ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; SAC Aberto</t>
-  </si>
-  <si>
-    <t>Reclamante em nome do Segurado</t>
-  </si>
-  <si>
-    <t>SAC Aberto</t>
-  </si>
-  <si>
-    <t>303626176</t>
-  </si>
-  <si>
-    <t>Mais de 70 dias sem veículo  demora excessiva e suporte insuficiente_x000D_
-_x000D_
-_x000D_
-Acionei o seguro da Allianz em dezembro de 2025 e, até o momento, já se passaram 70 dias sem a conclusão do reparo do meu veículo._x000D_
-_x000D_
-_x000D_
-Logo após o acionamento, o carro foi rebocado para a oficina credenciada. Ainda em dezembro foi realizado o pedido das peças necessárias, porém elas somente chegaram em 10/02/2026, o que já demonstra uma demora muito superior ao razoável._x000D_
-_x000D_
-_x000D_
-Após a chegada das peças, fui informado de que o veículo seria entregue no prazo de 10 dias úteis. Aguardei o prazo informado e, ao entrar novamente em contato, fui surpreendido com a informação de que o carro sequer havia iniciado os reparos, sem qualquer explicação clara ou específica. Depois de muita insistência  inclusive sendo ignorado no WhatsApp  informaram que a nova previsão de entrega será somente até o dia 13/03/2026._x000D_
-_x000D_
-_x000D_
-Além da demora excessiva, a seguradora disponibilizou apenas dois vouchers no valor de R$ 825,00 cada para utilização na Uber. Ocorre que esses valores já foram totalmente consumidos, considerando que tenho um gasto médio diário de aproximadamente R$ 41,00 apenas para me deslocar ao trabalho durante a semana, local que fica distante de onde moro. A demora no reparo acabou tornando o benefício claramente insuficiente, e estou tendo que arcar com despesas adicionais por conta da morosidade do próprio processo._x000D_
-_x000D_
-_x000D_
-Estou há mais de dois meses sem veículo, enfrentando falta de transparência, prazos imprecisos e suporte limitado. Pago o seguro justamente para ter segurança e tranquilidade em momentos como esse, mas a experiência tem sido extremamente desgastante._x000D_
-_x000D_
-_x000D_
-Solicito um posicionamento formal da Allianz e uma solução definitiva e urgente para o meu caso, inclusive quanto à extensão do suporte de transporte até a efetiva entrega do veículo._x000D_
-_x000D_
-_x000D_
-O período de renovação da apólice está se aproximando e, diante de toda essa situação, já tomei a decisão de que não renovarei com esta seguradora._x000D_
-_x000D_
-_x000D_
-Aguardo providências.</t>
-  </si>
-  <si>
-    <t>95803854</t>
-  </si>
-  <si>
-    <t>241510997</t>
-  </si>
-  <si>
-    <t>24/02/2026 10:07</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Apólice ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Endosso</t>
-  </si>
-  <si>
-    <t>Endosso</t>
-  </si>
-  <si>
-    <t>133695459</t>
-  </si>
-  <si>
-    <t>Fiz endosso de veículos no início  de janeiro, porém a Allianz, ficou de devolver a diferença, meu seguro foi feito pelo cnpj a qual sou o responsável, para fazer os pagamentos  foi usado cartão de crédito  de terceiros, pra ser restituído informei minha conta particular  sendo eu o segurado, nesse período  foi feito alguns agendamentos para pagamento, e não se cumpriu. Sigo insatisfeito mais uma vez, tanto com Allianz quanto corretora Minutos, não endico ambas para ninguém,que mais uma vez deixa seu cliente descepicionado.</t>
-  </si>
-  <si>
-    <t>95799670</t>
-  </si>
-  <si>
-    <t>241499105</t>
-  </si>
-  <si>
-    <t>24/02/2026 08:27</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Assistência Não Danos ; Guincho ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Guincho</t>
-  </si>
-  <si>
-    <t>305763155</t>
-  </si>
-  <si>
-    <t>Rebocaram meu carro e não levaram a oficina na data marcada onde houve o agendamento da perícia. Pedem pra ficar ligando para diversos canais de atendimento um jogando pro outro e não resolvem o problema. Uma falta de respeito terrível com o consumidor. Quero registrar apenas para outras pessoas não sofrer o que estou sofrendo. Pois assim q terminar meu concerto estarei cancelando o seguro.</t>
+    <t>134403514</t>
+  </si>
+  <si>
+    <t>Quero cancelar meu seguro residencial porém não consigo não tem opção nem por ligação e nem pelo chat, aí fica difícil cancelar .</t>
+  </si>
+  <si>
+    <t>95841055</t>
+  </si>
+  <si>
+    <t>241617409</t>
+  </si>
+  <si>
+    <t>25/02/2026 09:02</t>
+  </si>
+  <si>
+    <t>302622497</t>
+  </si>
+  <si>
+    <t>Meu carro foi abaroado por um segurado da ALLINZ seguradora, ele me enviaram a oficina AIRBRUSCH FREGUESIA,  porém a oficina não fez um bom serviço, por que a ALLIANZ SEGURADORA, não mandou uma peça genuína que não encaixou perfeitamente no meu carro, fiz uma reclamação na oficina ele estão esperando a ALLIANZ SEGURADORA, mandar a peça para refazer o serviço, o sinistro foi registrado em 23/11/25 até hoje não conseguir resolver o problema,  quero deixar aqui a responsabilidade também da AIRBRUSH pq mesmo  sabendo que a peça não encaixaria fizeram o serviço mesmo assim, não respeitando a boa relação de profissionalismo.</t>
   </si>
 </sst>
 </file>
@@ -1083,13 +1137,13 @@
         <v>48</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>31</v>
@@ -1147,16 +1201,16 @@
         <v>35</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>58</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>38</v>
@@ -1171,10 +1225,10 @@
         <v>41</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y4" s="3" t="s">
         <v>26</v>
@@ -1184,13 +1238,13 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>30</v>
@@ -1199,7 +1253,7 @@
         <v>31</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>33</v>
@@ -1211,16 +1265,16 @@
         <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>38</v>
@@ -1229,16 +1283,16 @@
         <v>39</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="Y5" s="3" t="s">
         <v>26</v>
@@ -1248,13 +1302,13 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>30</v>
@@ -1263,7 +1317,7 @@
         <v>31</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>33</v>
@@ -1275,13 +1329,13 @@
         <v>35</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>31</v>
@@ -1299,10 +1353,10 @@
         <v>41</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="Y6" s="3" t="s">
         <v>26</v>
@@ -1312,13 +1366,13 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>30</v>
@@ -1327,7 +1381,7 @@
         <v>31</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>33</v>
@@ -1336,16 +1390,16 @@
         <v>34</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>34</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>31</v>
@@ -1360,13 +1414,13 @@
         <v>40</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="Y7" s="3" t="s">
         <v>26</v>
@@ -1376,13 +1430,13 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>30</v>
@@ -1391,7 +1445,7 @@
         <v>31</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>33</v>
@@ -1400,19 +1454,19 @@
         <v>57</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>57</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>38</v>
@@ -1427,10 +1481,10 @@
         <v>41</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>26</v>
@@ -1440,13 +1494,13 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>30</v>
@@ -1455,25 +1509,25 @@
         <v>31</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>31</v>
@@ -1491,10 +1545,10 @@
         <v>41</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>26</v>
@@ -1504,13 +1558,13 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>30</v>
@@ -1519,25 +1573,25 @@
         <v>31</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>31</v>
@@ -1555,20 +1609,200 @@
         <v>41</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="X11" s="4"/>
+      <c r="A11" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="X11" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y11" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W13" s="4"/>
+      <c r="A13" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="W13" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="X13" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y13" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="W14" s="4"/>

--- a/Treinamento/GestaoReclamacao.xlsx
+++ b/Treinamento/GestaoReclamacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F417AB67-AE3D-4B4C-A09A-3660837AD69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ED8832F-D120-49DB-85A9-7FD00F4E9538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B1A77FD5-2AD3-4458-ACB3-7F19D1A3340A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="114">
   <si>
     <t>Id HugMe</t>
   </si>
@@ -122,13 +122,13 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>95872955</t>
-  </si>
-  <si>
-    <t>241709689</t>
-  </si>
-  <si>
-    <t>25/02/2026 22:29</t>
+    <t>95920068</t>
+  </si>
+  <si>
+    <t>241806005</t>
+  </si>
+  <si>
+    <t>26/02/2026 20:20</t>
   </si>
   <si>
     <t>Não respondido</t>
@@ -137,346 +137,416 @@
     <t>Não</t>
   </si>
   <si>
+    <t>Allianz ; Apólice ; Automóvel ; 1 Segurado ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; SAC Aberto ; Canal de Atendimento ; Corretor</t>
+  </si>
+  <si>
+    <t>Allianz</t>
+  </si>
+  <si>
+    <t>Apólice</t>
+  </si>
+  <si>
+    <t>Automóvel</t>
+  </si>
+  <si>
+    <t>Canal de Atendimento</t>
+  </si>
+  <si>
+    <t>Corretor</t>
+  </si>
+  <si>
+    <t>1 Segurado</t>
+  </si>
+  <si>
+    <t>SAC Aberto</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Repasse Time MindBe</t>
+  </si>
+  <si>
+    <t>Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Juliana</t>
+  </si>
+  <si>
+    <t>136032711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O canal da OUVIDORIA da Allianz não funciona! _x000D_
+_x000D_
+Tentei hoje mais de 3 vezes e gera erro. Ao procurar por outra forma de contato formal, observei que desde 28/10/2024 outra pessoa relatou o mesmo problema._x000D_
+_x000D_
+_x000D_
+Cópia da carta endereçada (ERROR - não enviada). _x000D_
+_x000D_
+_x000D_
+À Allianz Seguros,_x000D_
+_x000D_
+_x000D_
+Venho por meio desta formalizar minha indignação e contestação referente à cobrança indevida do Seguro Automóvel, no valor de R$ 1.177,27, que consta em minha fatura de cartão de crédito, apesar de o referido contrato jamais ter sido devidamente firmado por mim._x000D_
+_x000D_
+_x000D_
+O cancelamento ocorreu porque não houve clareza na negociação, tampouco consentimento formal para contratação. O vendedor:_x000D_
+_x000D_
+_x000D_
+Preencheu a proposta com informações incorretas;_x000D_
+_x000D_
+_x000D_
+Antecipou a emissão da apólice sem minha assinatura;_x000D_
+_x000D_
+_x000D_
+Tentou debitar o valor do seguro antes da formalização contratual;_x000D_
+_x000D_
+_x000D_
+Não aguardou minha aprovação e assinatura digital, que possuem validade jurídica e registro de data e hora._x000D_
+_x000D_
+_x000D_
+Ao questioná-lo sobre a emissão da apólice sem minha assinatura, recebi como justificativa que o procedimento teria ocorrido com base na boa-fé. No entanto, a boa-fé deve ser bilateral  e ele se antecipou inclusive a data da renovação que poderia ter aguardado. _x000D_
+_x000D_
+_x000D_
+Na tentativa de corrigir os dados incorretos inseridos pelo próprio vendedor, fui informada de que haveria cobrança adicional no valor médio de R$ 300,00 para realizar a alteração. Não concordei, pois o erro não foi meu. Diante disso, solicitei o cancelamento, e novamente houve tentativa de cobrança._x000D_
+_x000D_
+_x000D_
+Ressalto que:_x000D_
+_x000D_
+_x000D_
+O seguro venceria em 28/12;_x000D_
+_x000D_
+_x000D_
+O débito foi realizado em 26/12, sem contrato assinado;_x000D_
+_x000D_
+_x000D_
+Eu não assinei a/qualquer proposta digital;_x000D_
+_x000D_
+_x000D_
+Eu não finalizei a contratação._x000D_
+_x000D_
+_x000D_
+Pergunto objetivamente: como é possível debitar o cartão de um cliente antes da formalização contratual válida?_x000D_
+_x000D_
+_x000D_
+Além disso, considero extremamente grave o fato de terem solicitado que eu assinasse um destrato e nele haveria um acordo para devolução parcial de valores, sendo que não houve contrato assinado. Como se pode rescindir algo que juridicamente nunca foi celebrado? Tal conduta reforça a sensação de prática abusiva e má-fé._x000D_
+_x000D_
+_x000D_
+Importante destacar que eu estava tranquila quanto à contestação, inclusive busquei regularizar minha situação junto ao Banco Santander, solicitando novo Seguro  inclusive pela própria Allianz , porém o pedido foi negado._x000D_
+_x000D_
+_x000D_
+Ressalto que eu ainda desejava contratar o seguro, e inclusive estaria disposta, em último caso, a renegociar pelo mesmo valor inicialmente apresentado. Entretanto, o fato de ter sido negada anteriormente, no mês de janeiro, causa preocupação e apreensão, pois me sinto penalizada por ter agido de forma correta e transparente._x000D_
+_x000D_
+_x000D_
+Tenho receio de que, ao tentar agir com justiça e questionar uma cobrança indevida, eu esteja sendo prejudicada como consumidora, como se minha postura firme e honesta fosse um fator negativo em futuras análises._x000D_
+_x000D_
+_x000D_
+Sinto-me lesada, injustiçada e desrespeitada. Agi com transparência, solicitei correções (por escrito) antes de qualquer assinatura e não autorizei a contratação sem as devidas alterações solicitadas.  Ainda assim, estou sendo cobrada por um serviço que não contratei formalmente e foi cancelado em 30/12/2025 (conhece o código de defesa do consumidor? Até 7 dias para cancelamentos para contratos online, etc;;?)._x000D_
+_x000D_
+_x000D_
+Dessa forma, EXIJO:_x000D_
+_x000D_
+_x000D_
+Cancelamento imediato da cobrança no valor de R$ 1.177,27;_x000D_
+_x000D_
+_x000D_
+Confirmação formal do cancelamento sem qualquer ônus;_x000D_
+_x000D_
+_x000D_
+Esclarecimentos formais sobre a negativa posterior de contratação;_x000D_
+_x000D_
+_x000D_
+Encerramento definitivo desta tentativa de cobrança indevida._x000D_
+_x000D_
+_x000D_
+Informo que já realizei nova contestação junto à administradora do cartão e, caso a cobrança não seja cancelada, registrarei Boletim de Ocorrência, formalizarei reclamação junto ao Procon e ingressarei com ação no Juizado Especial Cível, além de registro em plataformas digitais sobre o tipo de tratamento e venda feita pelos envolvidos para que outros consumidores não se sintam prejudicados como eu._x000D_
+_x000D_
+_x000D_
+Reitero que não aceitarei arcar com erro cometido pelo vendedor ou com procedimento interno o qual sinto ser irregular na empresa._x000D_
+_x000D_
+_x000D_
+Aguardo solução imediata._x000D_
+_x000D_
+_x000D_
+Atenciosamente,_x000D_
+_x000D_
+Ligia Duarte_x000D_
+_x000D_
+</t>
+  </si>
+  <si>
+    <t>95919035</t>
+  </si>
+  <si>
+    <t>241802939</t>
+  </si>
+  <si>
+    <t>26/02/2026 19:45</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Vidros - AutoGlass ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Assistência Não Danos</t>
+  </si>
+  <si>
+    <t>Vidros - AutoGlass</t>
+  </si>
+  <si>
+    <t>134924776</t>
+  </si>
+  <si>
+    <t>Hoje por volta de 03:00 da manhã  uma pessoa  quebrou os dois retrovisores  e o vidro da  porta  do motorista do meu caminhão  Iveco  dali  entrei em contato com aliainz seguros  que mim passou o contato  da auto  Glass que eles resolver  liguei  para os mesmo uma moça  mim atendeu falou que vandalismo não  cobre mas em algum  momento  quando contratei o seguro com todas coberturas não  mim falara esse detalhes ala está  escrito cobertura vidros  retrovisores  e quando  precisei tive que comprar  a partir</t>
+  </si>
+  <si>
+    <t>95918025</t>
+  </si>
+  <si>
+    <t>241799891</t>
+  </si>
+  <si>
+    <t>26/02/2026 19:08</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Reclamante em nome do Segurado ; SAC Aberto ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Endosso</t>
+  </si>
+  <si>
+    <t>Endosso</t>
+  </si>
+  <si>
+    <t>Reclamante em nome do Segurado</t>
+  </si>
+  <si>
+    <t>131714025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOA TARDE !!!_x000D_
+_x000D_
+Eu tinha o seguro no meu carro da Allianz há dois pois troquei de carro entrei encontato com o meu corretor pra fazer o cancelamento do seguro._x000D_
+_x000D_
+Pois mesmo falou que tinha realizado o cancelamento e a Allianz tinha que me devolver o valor da diferença de R$ 249,03 esse valor tinha que cair na minha conta em 7 dias úteis o cancelamento foi realizado no dia 07/02 entrei em contato com o sac da Allianz e com o corretor informado que esse valor não caiu em minha conta._x000D_
+_x000D_
+O Corretor Gilvan falou que tinha caído mandei o extrato e ele viu q não caiu._x000D_
+_x000D_
+Entrei em contato com a Allianz novamente abrindo uma reclamação sobre o valor pois a Luci atendente do sac falou que eu teria que ligar no número 4090-1110 pra mim abrir uma solicitação com o financeiro. _x000D_
+_x000D_
+Liguei e não tive sucesso pois eu não sou mais cliente dele então não tenho apólice então não da pra falar._x000D_
+_x000D_
+Então liguei novamente no sac falei com a Luci novamente ele ensistiu pra mim ligar no mesmo número falei que não ia ligar e queria abrir uma reclamação no sac aí a mesma falou q abriu uma reclamação com o número de protocolo 260003028 e informou que eu tenho que esperar 7 dias essa situação está assim quase um mês sem ninguém resolver nada._x000D_
+_x000D_
+</t>
+  </si>
+  <si>
+    <t>95915235</t>
+  </si>
+  <si>
+    <t>241794475</t>
+  </si>
+  <si>
+    <t>26/02/2026 18:09</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Renovação ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Renovação</t>
+  </si>
+  <si>
+    <t>131482229</t>
+  </si>
+  <si>
+    <t>Totalmente insatisfeito com o serviço da seguradora. _x000D_
+_x000D_
+Sou cliente há um tempo e na minha primeira vez renovando o seguro ocorreu tudo conforme e prático, sem quaisquer dor de cabeça. Agora novamente necessito da renovação como de praxe os meus dados estão corretos e já aparece em meu extrato a parcela do seguro e também a parte das assinaturas estão ok, entrei em contato com o corretor e eles abriram uma solicitação para ver a questão da demora, entrei em contato com a ALLIANZ e a mesma informou que demora 25 dias úteis?! Tenho que esperar praticamente 1 mês (perdido) para renovar?! Mesmo tendo urgência de viajar com o veículo?! _x000D_
+_x000D_
+_x000D_
+Isso é um descaso com o cliente, pura decepção</t>
+  </si>
+  <si>
+    <t>95914813</t>
+  </si>
+  <si>
+    <t>241793229</t>
+  </si>
+  <si>
+    <t>26/02/2026 17:57</t>
+  </si>
+  <si>
+    <t>136199822</t>
+  </si>
+  <si>
+    <t>Uma pessoa jogou pedra no meu parabrisa. Solicitei a troca no dia 30/01 . Estamos no eia 26/02 e estamos na segunda vez que remarcam a chegada do parabrisa. A primeira vez a desculpa foi a transportadora não poderia trazer pois iria coincidir com o Carnaval,  ok. Agora dizem que estão tentando contato com a transportadora porém nao sabem onde esta a peça , que me retornaram mo outro dia, de fato , me ligam todo dia para falar que vão retornar no outro dia. Estou tendo que alugar carro, muito tempo para chegar uma peça simples. Gostaria de uma solução</t>
+  </si>
+  <si>
+    <t>95910763</t>
+  </si>
+  <si>
+    <t>241785181</t>
+  </si>
+  <si>
+    <t>26/02/2026 16:43</t>
+  </si>
+  <si>
     <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 2 Terceiro do Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
-    <t>Allianz</t>
-  </si>
-  <si>
     <t>Sinistro</t>
   </si>
   <si>
-    <t>Automóvel</t>
-  </si>
-  <si>
     <t>Análise Sinistro</t>
   </si>
   <si>
     <t>2 Terceiro do Sinistro</t>
   </si>
   <si>
-    <t>Sim</t>
-  </si>
-  <si>
-    <t>Repasse Time MindBe</t>
-  </si>
-  <si>
-    <t>Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Juliana</t>
-  </si>
-  <si>
-    <t>305688122</t>
-  </si>
-  <si>
-    <t>Quero resposta sobre o meu carro que to aguardando resposta para o conserto</t>
-  </si>
-  <si>
-    <t>95871846</t>
-  </si>
-  <si>
-    <t>241706183</t>
-  </si>
-  <si>
-    <t>25/02/2026 21:40</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Condomínio ; Sinistro ; Indenização ; Reclamante em nome do Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Condomínio</t>
-  </si>
-  <si>
-    <t>Indenização</t>
-  </si>
-  <si>
-    <t>Reclamante em nome do Segurado</t>
-  </si>
-  <si>
-    <t>301848864</t>
-  </si>
-  <si>
-    <t>_x000D_
-_x000D_
-_x000D_
-Olá, demos entrada no seguro em novembro, enviamos toda a documentação necessária, o prazo de análise já encerrou e até o momento não nos deram retorno acerca do início do pagamento. Teremos que esperar mais quanto tempo? Que absurdo!!</t>
-  </si>
-  <si>
-    <t>95866952</t>
-  </si>
-  <si>
-    <t>241691237</t>
-  </si>
-  <si>
-    <t>25/02/2026 18:48</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Reclamante em nome do Segurado ; Vistoria Prévia ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Con.GOV</t>
-  </si>
-  <si>
-    <t>Apólice</t>
-  </si>
-  <si>
-    <t>Vistoria Prévia</t>
-  </si>
-  <si>
-    <t>Con.GOV</t>
-  </si>
-  <si>
-    <t>135415124</t>
-  </si>
-  <si>
-    <t>Título: Descaso da Allianz com idosa: Vistoria digital travada e resposta de 10 dias para um endosso urgente_x000D_
-_x000D_
-_x000D_
-Estou utilizando este canal para manifestar minha profunda indignação com o tratamento que a Allianz Seguros está dando à minha sogra, Joselita (Apólice: 517720252P312494882)._x000D_
-_x000D_
-_x000D_
-Ontem pela manhã (24/02/2026), foi ela realizado todo o procedimento de vistoria digital para substituição de veículo (endosso). O processo, que deveria ser ágil por ser feito via fotos, está travado em "análise" há mais de 24 horas. O resultado? Ela está com o carro praticamente na garagem, sem poder circular por falta de cobertura securitária, sendo impedida de exercer seu direito de ir e vir com segurança._x000D_
-_x000D_
-_x000D_
-Ao formalizar a reclamação na Ouvidoria esperando prioridade, a resposta da Allianz foi um completo desdém: um protocolo (OUV_587_2026) informando que o prazo de resposta é de até 10 dias._x000D_
-_x000D_
-_x000D_
-É inadmissível que uma seguradora desse porte peça 10 dias para analisar fotos de uma vistoria digital que deveria ser concluída em horas. Minha sogra é uma pessoa que cumpre com seus deveres e precisa do veículo para sua rotina. Deixá-la desamparada e sem previsão real de solução é uma falta de respeito com o consumidor._x000D_
-_x000D_
-_x000D_
-Pedimos:_x000D_
-_x000D_
-A análise imediata das fotos enviadas na vistoria digital;_x000D_
-_x000D_
-A formalização do endosso ainda hoje para que o veículo esteja devidamente coberto;_x000D_
-_x000D_
-Respeito ao cliente que opta pelos canais digitais em busca de eficiência, não de burocracia._x000D_
-_x000D_
-_x000D_
-Não aceitaremos o prazo de 10 dias para um problema causado pela própria lentidão da seguradora.</t>
-  </si>
-  <si>
-    <t>95865816</t>
-  </si>
-  <si>
-    <t>241687829</t>
-  </si>
-  <si>
-    <t>25/02/2026 18:15</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Vidros - AutoGlass ; 1 Segurado ; Assistência Não Danos ; Sim ; Repasse Time MindBe ; Com Resposta - Dentro SLA - Analista ; RA</t>
-  </si>
-  <si>
-    <t>Assistência Não Danos</t>
-  </si>
-  <si>
-    <t>Vidros - AutoGlass</t>
-  </si>
-  <si>
-    <t>1 Segurado</t>
-  </si>
-  <si>
-    <t>RA</t>
-  </si>
-  <si>
-    <t>Com Resposta - Dentro SLA - Analista</t>
-  </si>
-  <si>
-    <t>Carla</t>
-  </si>
-  <si>
-    <t>131336504</t>
-  </si>
-  <si>
-    <t>Estou esperando a mais de 1 mês para conserto do retrovisor e até agora nada resolvido. Não consigo nenhum retorno para resolver o assunto. Solicito que seja resolvido urgentemente</t>
-  </si>
-  <si>
-    <t>95858621</t>
-  </si>
-  <si>
-    <t>241667259</t>
-  </si>
-  <si>
-    <t>25/02/2026 15:21</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Pagamento ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Pagamento</t>
-  </si>
-  <si>
-    <t>136187068</t>
-  </si>
-  <si>
-    <t>Liguei no dia 18/02 para reclamar sobre cobrança em duplicidade no meu seguro._x000D_
-_x000D_
-Paguei com cartão de crédito no dia 09/02, mesmo assim no dia 18/02 fizeram a mesma cobrança em conta corrente._x000D_
-_x000D_
-_x000D_
-Foi me passado o protocolo 2624519115 dizendo que seria estornado automaticamente em até 7 dias._x000D_
-_x000D_
-_x000D_
-Ainda não houve esse estorno na minha conta.</t>
-  </si>
-  <si>
-    <t>95857199</t>
-  </si>
-  <si>
-    <t>241663299</t>
-  </si>
-  <si>
-    <t>25/02/2026 14:50</t>
-  </si>
-  <si>
-    <t>Allianz ; Residência ; 1 Segurado ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Não ; Não ; Sinistro ; Atraso na Análise ; Sinistro</t>
+    <t>303946115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Após o sinistro ocorrido em 27/12/2025, a Allianz reconheceu a perda total do meu veículo Chevrolet Spin 2012/2013 e apresentou proposta de indenização no valor de R$ 51.000,00, com base na tabela FIPE._x000D_
+_x000D_
+Ocorre que o veículo foi adquirido por financiamento integral, sem entrada, e o valor atualmente necessário para quitação é de R$ 58.597,47. Assim, a quantia ofertada não é suficiente para liquidar a obrigação contratual vinculada ao bem sinistrado, resultando em diferença financeira significativa. A aceitação da proposta nos termos apresentados implicaria desembolso adicional para quitação do financiamento, além da perda definitiva do veículo._x000D_
+_x000D_
+Ressalte-se que, mesmo após o sinistro, continuaram sendo pagas parcelas do financiamento, o veículo permaneceu indisponível por aproximadamente dois meses, não houve disponibilização de carro reserva e foram suportadas despesas adicionais de transporte._x000D_
+_x000D_
+Diante desse cenário, busca-se solução adequada que efetivamente recomponha o prejuízo material experimentado, evitando a necessidade de adoção de medidas administrativas ou judiciais para discussão da suficiência da indenização e da extensão do dano._x000D_
+_x000D_
+Aguardamos posicionamento formal da empresa para encaminhamento da questão._x000D_
+_x000D_
+</t>
+  </si>
+  <si>
+    <t>95910466</t>
+  </si>
+  <si>
+    <t>241784413</t>
+  </si>
+  <si>
+    <t>26/02/2026 16:36</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Fornecimento de Peças ; 2 Terceiro do Sinistro ; SAC Aberto ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Fornecimento de Peças</t>
+  </si>
+  <si>
+    <t>Andreza</t>
+  </si>
+  <si>
+    <t>303987534</t>
+  </si>
+  <si>
+    <t>Sofri um acidente na data 30/12/25,  onde o responsavel acionou o seu seguro (Allianz), e foi autorizado a oficina para autorização do reparo, no dia 02/01/26 deixei o carro na oficina para passar por todo processo de avaliação, com orçamento fechado dia 05/01/26 e no dia 07/01/26 as peças  entraram em rota de envio para poderem ser entregue, sendo que as ultimas peças eram para ser entregues 19/01/26, prazo esse que nao foi cumprido, e deram um novo prazo de algumas peças para 04/02 e 06/02, onde teve um novo atraso, e eu ja vinha comunicando esse atraso a seguradora, e o restante das peças chegaram 19/02,  Porem em um novo contato, essas peças que chegaram foram as que vieram da concessionaria, ainda faltam as peças que vem diretamente da oficina, entrei em contato com a oficina 26/02/26 e comunicaram que as mesmas nao teriam prazo para chegada, de imediato comuniquei a central de sinistro da Aliianz que entraram em contato com a oficina e tambem não deram um prazo, a central pediu para que eu aguardasse até a segunda feira (02/03/26), ou seja nao foi resolvido, tambem entrei em contato com o SAC da seguradora mas sem resolução. Percebe-se que tal situação fere o codigo de defesa do consumidor, nao possuindo prazo para entrega, diversos atrasos, e quase 60 dias para nao resolução do sinsitro, sendo que o mercado possui peças.  Eu preciso saber o que realmente está havendo,  Ou se é somente descaso da empresa?? Estarei tomando medidas judiciais contra a seguradora. Não posso ficar sem trabalhar, quem vai cobrir meus prejuízos financeiros?? Se a seguradora nao trazer uma resolução e entrega do meu veiculo em tempo habil, irei ingressar com processo de indenização por danos materiais e morais.</t>
+  </si>
+  <si>
+    <t>95901163</t>
+  </si>
+  <si>
+    <t>241767059</t>
+  </si>
+  <si>
+    <t>26/02/2026 14:11</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; OUV ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>OUV</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>304058510</t>
+  </si>
+  <si>
+    <t>Título: Sinistro n 304058510  Veículo parado há mais de dois meses sem solução definitiva pela seguradora_x000D_
+_x000D_
+_x000D_
+No dia 24 de dezembro de 2025, meu veículo Nissan Kicks, placa IUH929, chassi 94DECAP15MB412528, fabricação 2020, modelo 2021, foi envolvido em uma colisão._x000D_
+_x000D_
+_x000D_
+O sinistro n 304058510 foi aberto junto à Allianz, e o veículo foi encaminhado à oficina Ferrino Reparo Automotiva no dia 29 de dezembro de 2025. A vistoria foi realizada em 5 de janeiro de 2026._x000D_
+_x000D_
+_x000D_
+Desde então, foram solicitadas as seguintes peças para reparo:_x000D_
+_x000D_
+  Farol esquerdo  código 260605RF4A_x000D_
+_x000D_
+  Lanterna traseira esquerda  código 265555RF0A_x000D_
+_x000D_
+  Eixo traseiro  BEAM COMPL RR SUSP  código 555015RROC_x000D_
+_x000D_
+_x000D_
+Contudo, até a presente data, essas peças não foram disponibilizadas, impedindo a conclusão do conserto. O veículo permanece parado há mais de dois meses, sem previsão concreta de finalização._x000D_
+_x000D_
+_x000D_
+Independentemente da eventual indisponibilidade de peças junto à montadora, é responsabilidade da seguradora garantir a adequada prestação do serviço contratado, assegurando a solução do sinistro dentro de prazo razoável e sem prejuízo excessivo ao segurado._x000D_
+_x000D_
+_x000D_
+Estou há mais de dois meses sem meu veículo e sem uma definição objetiva sobre qual medida será adotada._x000D_
+_x000D_
+_x000D_
+Diante disso, questiono formalmente:_x000D_
+_x000D_
+  Qual é a providência concreta que a Allianz adotará para resolver o sinistro?_x000D_
+_x000D_
+  Haverá indenização integral do veículo diante da impossibilidade de reparo em prazo razoável?_x000D_
+_x000D_
+  Será garantido veículo reserva até a efetiva solução do caso?_x000D_
+_x000D_
+  Qual é o prazo real e definitivo para encerramento do sinistro?_x000D_
+_x000D_
+_x000D_
+O consumidor não pode arcar com os prejuízos decorrentes da demora na cadeia de fornecimento ou na gestão do processo de reparo. Necessito de uma posição clara, formal e imediata, com definição objetiva sobre como a seguradora irá reparar os danos já suportados e assegurar meus direitos contratuais._x000D_
+_x000D_
+_x000D_
+Aguardo providências urgentes.</t>
+  </si>
+  <si>
+    <t>95896259</t>
+  </si>
+  <si>
+    <t>241760411</t>
+  </si>
+  <si>
+    <t>26/02/2026 13:16</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Residência ; Apólice ; Condições Gerais ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
     <t>Residência</t>
   </si>
   <si>
-    <t>Atraso na Análise</t>
-  </si>
-  <si>
-    <t>304858824</t>
-  </si>
-  <si>
-    <t>Tive um sinistro com a minha geladeira e tv ja foi ressarcido porém ninguém me responde se é a seguradora quem faz o descarte das coisas ou se eu posso descartar?_x000D_
-_x000D_
-Ligo na central para informações e ninguém sabe me informar e fala que vai pedir para o setor responsável entrar em contato e ate agora nada_x000D_
-_x000D_
-Preciso de uma resposta, péssimo atendimento não indico</t>
-  </si>
-  <si>
-    <t>95855542</t>
-  </si>
-  <si>
-    <t>241658625</t>
-  </si>
-  <si>
-    <t>25/02/2026 14:14</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Residência ; Apólice ; Assistência Residencial ; Reclamante em nome do Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Assistência Residencial</t>
-  </si>
-  <si>
-    <t>136716335</t>
-  </si>
-  <si>
-    <t>Temos um seguro residencial junto a Allianz seguradora e temos no pacote de assistencia 5 itens entre os diversos possiveis para utilizar. Precisamos solicitar a instalação de um chuveiro e a atendente não informou que era somente um acionamento para até 5 itens, ou seja, o prestador foi lá, instalou o chuveiro e agora precisamos acionar para colocar um suporte de TV, quadro e cortina e simplesmete não podemos mais utilizar por que alegam que já foi utilizado. Se a atendente, fosse competente e bem instruida, teria informado, Sra Tatiane, não quer aproveitar a ida do prestador para colocar o chuveiro e utilizar mais 4 itens? Porque ele só vai lá uma vez ppr vigência. Dessa forma saberiamos e ja teriamos pedido. Agora, não foi orientado e agora nos privam de utilizar? Não temos obrigação de decorar o manual de utilização,  a orientação precisa ser clara e precisa para não lesar os clientes. Conto com a colaboração da Allianz para resolver amigavelmente esse ocorrido.</t>
-  </si>
-  <si>
-    <t>95852622</t>
-  </si>
-  <si>
-    <t>241649611</t>
-  </si>
-  <si>
-    <t>25/02/2026 13:03</t>
-  </si>
-  <si>
-    <t>134637065</t>
-  </si>
-  <si>
-    <t>1) Apólice N.: 517720253U312080959_x000D_
-_x000D_
-Proposta N.: 134637065 _x000D_
-_x000D_
-Conforme renovaçao do seguro em tela, o seguro do meu veiculo  Citroen C3 deveria ser pago em 10 parcelas MENSAIS de 208,00 mensais ._x000D_
-_x000D_
-Ocorre que a parcela deste mes foi DEBITADA em meu cartão final 6094  DUAS VEZES _x000D_
-_x000D_
-Devendo ser devolvida UMA DELAS pela ALIANZ de pronto  em meu cartao credito, pena  de ENRIQUECIMENTO INDEVIDO ._x000D_
-_x000D_
-_x000D_
-2) No mais, referente a TRANSFERENCIA de MEU VEICULO anterior  PARA A ALIANZ , (que  já e de propriedade da seguradora) um UPP  2015 , CONSTAM DEBITOS DE IPVA NO ORGAO RESPECTIVO._x000D_
-_x000D_
-_x000D_
-3) iSTO FEITO SOLICITO :  a) a devolução em meu cartao de credito acima da parcela cobrada A MAIOR ; b) o pagamento dos IPVAs do UPPI 2015 preto indicado acima  , e o COMPROVANTE DE TRANSFERENCIA JUNTO AO ORGÃO COMPETENTE _x000D_
-_x000D_
-_x000D_
-Aguardo as providencias  em 48 horas ,_x000D_
-_x000D_
-att.</t>
-  </si>
-  <si>
-    <t>95846312</t>
-  </si>
-  <si>
-    <t>241631499</t>
-  </si>
-  <si>
-    <t>25/02/2026 10:50</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Análise Sinistro</t>
-  </si>
-  <si>
-    <t>304981479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sou segurado no meu veículo RVY 4j85 pagamento em dia tive um incidente _x000D_
-_x000D_
-O corretor comunicou o reparo foi autorizado o veículo foi para a oficina e dias depois a Allianz negou o conserto!_x000D_
-_x000D_
-</t>
-  </si>
-  <si>
-    <t>95845101</t>
-  </si>
-  <si>
-    <t>241627947</t>
-  </si>
-  <si>
-    <t>25/02/2026 10:25</t>
-  </si>
-  <si>
-    <t>305500658</t>
-  </si>
-  <si>
-    <t>Segurado de vocês bateu no meu veiculo, foi aberto o sinistro por telefone tantio da parte dela quanto da minha no local do acidente, no dia 09/02/2026, no dia 12 se bem me recordo foi feita a vistoria e estou ate hoje dia 25/02/2026 ainda sem liberação para execução do serviço. Não existe duvida quanto ao acidente,  a mesma relatou o acontecido ao telefone na abertura do sinistro assumindo total culpa pelo acontecido, tenho videos e fotos do local do acidente na hora, o acidente foi em frente ao posto da policia rodoviaria, onde tem cameras. Estou tentando contato pelo site, onde apos inserir todos os dados solicitados me apresenta o historico e optei a falar pelo chat pra entender melhor a situação, onde ja estou a quase 1 h aguaradando para ser atendido e esta tudo gravado._x000D_
-_x000D_
-è um descaso absurdo, sera que não pensam que hoje eu sou terceiro, mas posso um dia ter um seguro da Allianz se fosse bem atendido: Temos 5 carros aqui em casa, e essa possibilidade vai ficando cada dia mais impossivel pela qualidade do atendimento._x000D_
-_x000D_
-Eu não ando nem com carro sujo, e agora estou ha 16 dias andando com carro batido, isso é um absurdo!!!!</t>
-  </si>
-  <si>
-    <t>95843440</t>
-  </si>
-  <si>
-    <t>241623247</t>
-  </si>
-  <si>
-    <t>25/02/2026 09:51</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Residência ; Apólice ; Cancelamento ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Cancelamento</t>
-  </si>
-  <si>
-    <t>134403514</t>
-  </si>
-  <si>
-    <t>Quero cancelar meu seguro residencial porém não consigo não tem opção nem por ligação e nem pelo chat, aí fica difícil cancelar .</t>
-  </si>
-  <si>
-    <t>95841055</t>
-  </si>
-  <si>
-    <t>241617409</t>
-  </si>
-  <si>
-    <t>25/02/2026 09:02</t>
-  </si>
-  <si>
-    <t>302622497</t>
-  </si>
-  <si>
-    <t>Meu carro foi abaroado por um segurado da ALLINZ seguradora, ele me enviaram a oficina AIRBRUSCH FREGUESIA,  porém a oficina não fez um bom serviço, por que a ALLIANZ SEGURADORA, não mandou uma peça genuína que não encaixou perfeitamente no meu carro, fiz uma reclamação na oficina ele estão esperando a ALLIANZ SEGURADORA, mandar a peça para refazer o serviço, o sinistro foi registrado em 23/11/25 até hoje não conseguir resolver o problema,  quero deixar aqui a responsabilidade também da AIRBRUSH pq mesmo  sabendo que a peça não encaixaria fizeram o serviço mesmo assim, não respeitando a boa relação de profissionalismo.</t>
+    <t>Condições Gerais</t>
+  </si>
+  <si>
+    <t>134200614</t>
+  </si>
+  <si>
+    <t>Solicitei a seguradora informações detalhadas referente aos serviços disponíveis em minha apólice, não me passam Naao consta no site e nem na minha apólice, todo serviço que solicito informo que estrapolou minha apólice. Preciso do documento completo para consulta. Tentei fazer pelo zap, telefone e email e nada.</t>
+  </si>
+  <si>
+    <t>95884369</t>
+  </si>
+  <si>
+    <t>241740993</t>
+  </si>
+  <si>
+    <t>26/02/2026 10:49</t>
+  </si>
+  <si>
+    <t>Allianz ; Automóvel ; Apólice ; Assistência Não Danos ; Vidros - AutoGlass ; 1 Segurado ; Sac Enc ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Sac Enc</t>
+  </si>
+  <si>
+    <t>134719113</t>
+  </si>
+  <si>
+    <t>Fiz a abertura de uma reclamação no SAC da Allianz protocolo 26/0002173 solicitando reembolso de um serviço que foi prejudicado devido a uma credenciada da Allians e também solicitar que a nova troca do meu parabrisa seja feita em uma outra oficina sem ser a Fenix Auto vidros em juiz de fora, pois já é a terceira vez que tenho que ir lá reparar um péssimo serviço realizado em meu carro.  A Allianz me retornou apenas que eu posso ir até a credenciada realizar um novo serviço, nao se importando com as 02 solicitações que fiz junto ao sac. Preciso da solução deste tema!! nao adianta eu ir pela terceira na mesma oficina fazer o mesmo serviço, já está provado que a credenciada nao tem qualidade para isto.</t>
   </si>
 </sst>
 </file>
@@ -1073,34 +1143,34 @@
         <v>35</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Y2" s="3" t="s">
         <v>26</v>
@@ -1110,13 +1180,13 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>30</v>
@@ -1125,7 +1195,7 @@
         <v>31</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>33</v>
@@ -1134,37 +1204,37 @@
         <v>34</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y3" s="3" t="s">
         <v>26</v>
@@ -1174,13 +1244,13 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>30</v>
@@ -1189,40 +1259,40 @@
         <v>31</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>58</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="W4" s="4" t="s">
         <v>60</v>
@@ -1259,40 +1329,40 @@
         <v>33</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W5" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="X5" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="X5" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="Y5" s="3" t="s">
         <v>26</v>
@@ -1302,13 +1372,13 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>30</v>
@@ -1317,46 +1387,46 @@
         <v>31</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="Y6" s="3" t="s">
         <v>26</v>
@@ -1366,13 +1436,13 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>30</v>
@@ -1381,46 +1451,46 @@
         <v>31</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="Y7" s="3" t="s">
         <v>26</v>
@@ -1430,13 +1500,13 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>30</v>
@@ -1445,46 +1515,46 @@
         <v>31</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>26</v>
@@ -1494,13 +1564,13 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>30</v>
@@ -1509,46 +1579,46 @@
         <v>31</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>26</v>
@@ -1558,13 +1628,13 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>30</v>
@@ -1573,7 +1643,7 @@
         <v>31</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>33</v>
@@ -1582,31 +1652,31 @@
         <v>34</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>34</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="W10" s="4" t="s">
         <v>105</v>
@@ -1635,7 +1705,7 @@
         <v>31</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>33</v>
@@ -1647,162 +1717,41 @@
         <v>35</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>31</v>
+        <v>111</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Y11" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y12" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="V13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="W13" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="X13" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y13" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="W13" s="4"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="W14" s="4"/>

--- a/Treinamento/GestaoReclamacao.xlsx
+++ b/Treinamento/GestaoReclamacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ED8832F-D120-49DB-85A9-7FD00F4E9538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD68C8EA-A77B-48C1-B38D-32214A1FD9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B1A77FD5-2AD3-4458-ACB3-7F19D1A3340A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="160">
   <si>
     <t>Id HugMe</t>
   </si>
@@ -122,13 +122,13 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>95920068</t>
-  </si>
-  <si>
-    <t>241806005</t>
-  </si>
-  <si>
-    <t>26/02/2026 20:20</t>
+    <t>96050078</t>
+  </si>
+  <si>
+    <t>242016639</t>
+  </si>
+  <si>
+    <t>01/03/2026 20:49</t>
   </si>
   <si>
     <t>Não respondido</t>
@@ -137,7 +137,7 @@
     <t>Não</t>
   </si>
   <si>
-    <t>Allianz ; Apólice ; Automóvel ; 1 Segurado ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; SAC Aberto ; Canal de Atendimento ; Corretor</t>
+    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; Reclamante em nome do Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
     <t>Allianz</t>
@@ -146,407 +146,589 @@
     <t>Apólice</t>
   </si>
   <si>
+    <t>Residência</t>
+  </si>
+  <si>
+    <t>Assistência Não Danos</t>
+  </si>
+  <si>
+    <t>Assistência Residencial</t>
+  </si>
+  <si>
+    <t>Reclamante em nome do Segurado</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Repasse Time MindBe</t>
+  </si>
+  <si>
+    <t>Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Juliana</t>
+  </si>
+  <si>
+    <t>133533043</t>
+  </si>
+  <si>
+    <t>Acionei a Allianz hoje, 01/03/2026, protocolo 51537834, para uma assistência residencial urgente, devido a um curto-circuito na casa de meu pai. O eletricista chegaria em 60 minutos._x000D_
+_x000D_
+_x000D_
+Minha prima ficou aguardando durante cinco horas e nada. Verifiquei e haviam remarcado o atendimento para amanhã. Como é urgente, liguei pedindo para que o atendimento fosse hoje, pois amanhã não haverá outra pessoa de plantão (a pessoa ficou de plantão HOJE). A funcionária me atendeu super bem, cancelou a visita de amanhã e remarcou com outro terceirizado para hoje._x000D_
+_x000D_
+_x000D_
+Porém, até agora não apareceram. Fui verificar e novamente remarcaram, arbitrariamente, para amanhã._x000D_
+_x000D_
+_x000D_
+Muito descaso com o consumidor. Seguro custa caro, não estamos pedindo nenhum favor, mas exercendo o direito à assistência que consta na apólice._x000D_
+_x000D_
+_x000D_
+Aguardo providências e agradeço desde já.</t>
+  </si>
+  <si>
+    <t>96040732</t>
+  </si>
+  <si>
+    <t>241987555</t>
+  </si>
+  <si>
+    <t>01/03/2026 10:57</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Sinistro</t>
+  </si>
+  <si>
     <t>Automóvel</t>
   </si>
   <si>
-    <t>Canal de Atendimento</t>
-  </si>
-  <si>
-    <t>Corretor</t>
+    <t>Análise Sinistro</t>
   </si>
   <si>
     <t>1 Segurado</t>
   </si>
   <si>
-    <t>SAC Aberto</t>
-  </si>
-  <si>
-    <t>Sim</t>
-  </si>
-  <si>
-    <t>Repasse Time MindBe</t>
-  </si>
-  <si>
-    <t>Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Juliana</t>
-  </si>
-  <si>
-    <t>136032711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O canal da OUVIDORIA da Allianz não funciona! _x000D_
-_x000D_
-Tentei hoje mais de 3 vezes e gera erro. Ao procurar por outra forma de contato formal, observei que desde 28/10/2024 outra pessoa relatou o mesmo problema._x000D_
-_x000D_
-_x000D_
-Cópia da carta endereçada (ERROR - não enviada). _x000D_
-_x000D_
-_x000D_
-À Allianz Seguros,_x000D_
-_x000D_
-_x000D_
-Venho por meio desta formalizar minha indignação e contestação referente à cobrança indevida do Seguro Automóvel, no valor de R$ 1.177,27, que consta em minha fatura de cartão de crédito, apesar de o referido contrato jamais ter sido devidamente firmado por mim._x000D_
-_x000D_
-_x000D_
-O cancelamento ocorreu porque não houve clareza na negociação, tampouco consentimento formal para contratação. O vendedor:_x000D_
-_x000D_
-_x000D_
-Preencheu a proposta com informações incorretas;_x000D_
-_x000D_
-_x000D_
-Antecipou a emissão da apólice sem minha assinatura;_x000D_
-_x000D_
-_x000D_
-Tentou debitar o valor do seguro antes da formalização contratual;_x000D_
-_x000D_
-_x000D_
-Não aguardou minha aprovação e assinatura digital, que possuem validade jurídica e registro de data e hora._x000D_
-_x000D_
-_x000D_
-Ao questioná-lo sobre a emissão da apólice sem minha assinatura, recebi como justificativa que o procedimento teria ocorrido com base na boa-fé. No entanto, a boa-fé deve ser bilateral  e ele se antecipou inclusive a data da renovação que poderia ter aguardado. _x000D_
-_x000D_
-_x000D_
-Na tentativa de corrigir os dados incorretos inseridos pelo próprio vendedor, fui informada de que haveria cobrança adicional no valor médio de R$ 300,00 para realizar a alteração. Não concordei, pois o erro não foi meu. Diante disso, solicitei o cancelamento, e novamente houve tentativa de cobrança._x000D_
-_x000D_
-_x000D_
-Ressalto que:_x000D_
-_x000D_
-_x000D_
-O seguro venceria em 28/12;_x000D_
-_x000D_
-_x000D_
-O débito foi realizado em 26/12, sem contrato assinado;_x000D_
-_x000D_
-_x000D_
-Eu não assinei a/qualquer proposta digital;_x000D_
-_x000D_
-_x000D_
-Eu não finalizei a contratação._x000D_
-_x000D_
-_x000D_
-Pergunto objetivamente: como é possível debitar o cartão de um cliente antes da formalização contratual válida?_x000D_
-_x000D_
-_x000D_
-Além disso, considero extremamente grave o fato de terem solicitado que eu assinasse um destrato e nele haveria um acordo para devolução parcial de valores, sendo que não houve contrato assinado. Como se pode rescindir algo que juridicamente nunca foi celebrado? Tal conduta reforça a sensação de prática abusiva e má-fé._x000D_
-_x000D_
-_x000D_
-Importante destacar que eu estava tranquila quanto à contestação, inclusive busquei regularizar minha situação junto ao Banco Santander, solicitando novo Seguro  inclusive pela própria Allianz , porém o pedido foi negado._x000D_
-_x000D_
-_x000D_
-Ressalto que eu ainda desejava contratar o seguro, e inclusive estaria disposta, em último caso, a renegociar pelo mesmo valor inicialmente apresentado. Entretanto, o fato de ter sido negada anteriormente, no mês de janeiro, causa preocupação e apreensão, pois me sinto penalizada por ter agido de forma correta e transparente._x000D_
-_x000D_
-_x000D_
-Tenho receio de que, ao tentar agir com justiça e questionar uma cobrança indevida, eu esteja sendo prejudicada como consumidora, como se minha postura firme e honesta fosse um fator negativo em futuras análises._x000D_
-_x000D_
-_x000D_
-Sinto-me lesada, injustiçada e desrespeitada. Agi com transparência, solicitei correções (por escrito) antes de qualquer assinatura e não autorizei a contratação sem as devidas alterações solicitadas.  Ainda assim, estou sendo cobrada por um serviço que não contratei formalmente e foi cancelado em 30/12/2025 (conhece o código de defesa do consumidor? Até 7 dias para cancelamentos para contratos online, etc;;?)._x000D_
-_x000D_
-_x000D_
-Dessa forma, EXIJO:_x000D_
-_x000D_
-_x000D_
-Cancelamento imediato da cobrança no valor de R$ 1.177,27;_x000D_
-_x000D_
-_x000D_
-Confirmação formal do cancelamento sem qualquer ônus;_x000D_
-_x000D_
-_x000D_
-Esclarecimentos formais sobre a negativa posterior de contratação;_x000D_
-_x000D_
-_x000D_
-Encerramento definitivo desta tentativa de cobrança indevida._x000D_
-_x000D_
-_x000D_
-Informo que já realizei nova contestação junto à administradora do cartão e, caso a cobrança não seja cancelada, registrarei Boletim de Ocorrência, formalizarei reclamação junto ao Procon e ingressarei com ação no Juizado Especial Cível, além de registro em plataformas digitais sobre o tipo de tratamento e venda feita pelos envolvidos para que outros consumidores não se sintam prejudicados como eu._x000D_
-_x000D_
-_x000D_
-Reitero que não aceitarei arcar com erro cometido pelo vendedor ou com procedimento interno o qual sinto ser irregular na empresa._x000D_
-_x000D_
-_x000D_
-Aguardo solução imediata._x000D_
-_x000D_
-_x000D_
-Atenciosamente,_x000D_
-_x000D_
-Ligia Duarte_x000D_
+    <t>301489502</t>
+  </si>
+  <si>
+    <t>Sou segurada Alianz, sofri um acidente dia 19/10/2025, até o momento estou sem meu veículo! Se não sou ir na concessionária atrás, ficar ligando, não tenho retorno algum. Agora depois de fazer a troca de oficina, pedi pra fazer um acordo e resolver a situação, me pediram 2 dias úteis, já se passaram 6 dias e nada! Hoje dia 27/02/2026 sigo sem minha moto e sem respostas , sem resolução, não recomendo essa empresa!</t>
+  </si>
+  <si>
+    <t>96038557</t>
+  </si>
+  <si>
+    <t>241980911</t>
+  </si>
+  <si>
+    <t>01/03/2026 08:12</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Residência ; Assistência Residencial ; 1 Segurado ; Sac Enc ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Assistência Danos</t>
+  </si>
+  <si>
+    <t>Assistência Danos</t>
+  </si>
+  <si>
+    <t>Sac Enc</t>
+  </si>
+  <si>
+    <t>134391558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prezados,_x000D_
+_x000D_
+Sou segurado da Allianz (apólice residencial VIP N 517720252N140400459, vigência até 11/09/2026) e acionei a assistência 24h para instalação de um espelho retangular jateado 90x70 cm com LED. O serviço foi agendado para 06/02/2026 (protocolo 51293317), entre 9h e 12h. O prestador compareceu, instalou o espelho na parede do banheiro e deixou laudo assinado (anexo), descrevendo apenas "Fixação de 1 espelho na parede" e "Feito e instalação de 1 espelho na solicitação", sem qualquer menção a defeito no produto, descolamento de silicone, risco de quebra ou peso excessivo._x000D_
+_x000D_
+Minutos após a saída do prestador, o espelho descolou da própria estrutura (o suporte/parafusos ficaram firmes na parede  fotos anexas) e caiu, espatifando no chão. Como consequência direta, a pia de mármore cortada sob medida rachou gravemente (foto anexa, fissura na base da torneira/cuba), exigindo substituição total. Obtive orçamento preliminar da Marmoraria SI Ltda (anexo, data 28/02/2026, R$ 1.530,00 à vista para pia Branco Prime extra 1,0 x 0,50 m, com 1/2 boleado), mas este é incompleto: falta incluir visita prévia para medição, troca da cuba da pia quebrada para a nova, fretes de retirada e entrega, além do orçamento da mão-de-obra do marceneiro (que instalou a pia original em 2021). O prejuízo total será maior e será complementado em breve._x000D_
+_x000D_
+Relatei imediatamente via WhatsApp da Allianz Assistência 24h (transcrição completa anexa). Eles abriram "manifestação de danos", mas alegaram que o prestador "informou a pessoa no local" sobre defeito (descolamento de silicone e risco de quebra). No entanto, eu não estava presente (quem recebeu foi um faxineiro eventual), e nada disso consta no laudo assinado. Cobro o status dessa manifestação desde 06/02/2026 (conversas em 07/02, 22/02 e 28/02), mas sempre dizem "em análise" ou "aguarde SMS/retorno", sem resolução até hoje._x000D_
+_x000D_
+Minha corretora também abriu reclamação (protocolo 26/0002158), mas a Allianz negou qualquer indenização (e-mail anexo de 27/02/2026), alegando que "o descolamento não está relacionado à falha de execução", que o suporte plástico é "apenas proteção" e que o prestador "relatou ter alertado sobre peso elevado". Isso é contraditório e sem provas: se havia risco, por que instalaram? E por que não registraram no laudo? A apólice inclui Assistência 24h VIP com "Pacote de Serviços Domiciliares (instalações e fixações)" e cobertura para Quebra de Vidros/Mármores/Granitos (até R$ 13.500,00), o que abrange o dano causado._x000D_
+_x000D_
+Ademais, tenho 59 anos (nascido em 17/07/1966) e, desde uma trombose na perna direita em 2010, sofro com úlceras venosas recorrentes (tratando uma há mais de um ano no calcanhar direito). O incidente gerou alto risco: se eu estivesse no banheiro (ex.: sentado no vaso) no momento da queda, os cacos poderiam causar cortes que, agravados pela minha condição clínica, levariam a complicações graves e difíceis de mensurar, como infecções ou piora da circulação._x000D_
+_x000D_
+Pelo Código de Defesa do Consumidor (art. 14), a Allianz responde objetivamente por danos causados por serviço defeituoso. Exijo:_x000D_
+_x000D_
+ Indenização pela substituição da pia de mármore rachada (orçamento preliminar R$ 1.530,00 anexo, mas faltam itens como visita para medição, troca de cuba, fretes e mão-de-obra, a ser complementado) + mão de obra_x000D_
+_x000D_
+ Indenização por danos morais pelo transtorno, risco de acidente (cacos no banheiro) e agravamento potencial à minha saúde (compatível com a gravidade do caso)_x000D_
+_x000D_
+Anexo: fotos do suporte intacto, espelho espatifado, mecanismo falho, pia rachada; laudo da instalação; orçamento preliminar da marmoraria; apólice completa; transcrição completa do WhatsApp; e-mail da corretora com negativa da Allianz._x000D_
+_x000D_
+Aguardo solução urgente em até 5 dias úteis, sob pena de escalar para Procon-RJ, SUSEP e Juizado Especial Cível._x000D_
+_x000D_
+Fabio Coelho Martins_x000D_
 _x000D_
 </t>
   </si>
   <si>
-    <t>95919035</t>
-  </si>
-  <si>
-    <t>241802939</t>
-  </si>
-  <si>
-    <t>26/02/2026 19:45</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Vidros - AutoGlass ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Assistência Não Danos</t>
-  </si>
-  <si>
-    <t>Vidros - AutoGlass</t>
-  </si>
-  <si>
-    <t>134924776</t>
-  </si>
-  <si>
-    <t>Hoje por volta de 03:00 da manhã  uma pessoa  quebrou os dois retrovisores  e o vidro da  porta  do motorista do meu caminhão  Iveco  dali  entrei em contato com aliainz seguros  que mim passou o contato  da auto  Glass que eles resolver  liguei  para os mesmo uma moça  mim atendeu falou que vandalismo não  cobre mas em algum  momento  quando contratei o seguro com todas coberturas não  mim falara esse detalhes ala está  escrito cobertura vidros  retrovisores  e quando  precisei tive que comprar  a partir</t>
-  </si>
-  <si>
-    <t>95918025</t>
-  </si>
-  <si>
-    <t>241799891</t>
-  </si>
-  <si>
-    <t>26/02/2026 19:08</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Reclamante em nome do Segurado ; SAC Aberto ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA ; Endosso</t>
-  </si>
-  <si>
-    <t>Endosso</t>
-  </si>
-  <si>
-    <t>Reclamante em nome do Segurado</t>
-  </si>
-  <si>
-    <t>131714025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOA TARDE !!!_x000D_
-_x000D_
-Eu tinha o seguro no meu carro da Allianz há dois pois troquei de carro entrei encontato com o meu corretor pra fazer o cancelamento do seguro._x000D_
-_x000D_
-Pois mesmo falou que tinha realizado o cancelamento e a Allianz tinha que me devolver o valor da diferença de R$ 249,03 esse valor tinha que cair na minha conta em 7 dias úteis o cancelamento foi realizado no dia 07/02 entrei em contato com o sac da Allianz e com o corretor informado que esse valor não caiu em minha conta._x000D_
-_x000D_
-O Corretor Gilvan falou que tinha caído mandei o extrato e ele viu q não caiu._x000D_
-_x000D_
-Entrei em contato com a Allianz novamente abrindo uma reclamação sobre o valor pois a Luci atendente do sac falou que eu teria que ligar no número 4090-1110 pra mim abrir uma solicitação com o financeiro. _x000D_
-_x000D_
-Liguei e não tive sucesso pois eu não sou mais cliente dele então não tenho apólice então não da pra falar._x000D_
-_x000D_
-Então liguei novamente no sac falei com a Luci novamente ele ensistiu pra mim ligar no mesmo número falei que não ia ligar e queria abrir uma reclamação no sac aí a mesma falou q abriu uma reclamação com o número de protocolo 260003028 e informou que eu tenho que esperar 7 dias essa situação está assim quase um mês sem ninguém resolver nada._x000D_
+    <t>96002080</t>
+  </si>
+  <si>
+    <t>241912793</t>
+  </si>
+  <si>
+    <t>27/02/2026 22:24</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Guincho</t>
+  </si>
+  <si>
+    <t>132545229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assistência 24 horas muito demorada, hoje, 27/02, fiz uma solicitação de assistência ao meu veículo pelo wattsapp da Allians, o numero de protocolo 51528834 tinha um compromisso urgente e me decepcionei com o ocorreu logo em seguida:_x000D_
+_x000D_
+_x000D_
+1 o app dizia que chegaria um sms para acompanhamento do prestador e previsao de chegada. ESPEREI O SMS POR 10 MIN e nao chegou. pelo proprio watts solicitei esclarescimento e apareceu uma msg automatica dando previsao de chegada as 20h45. _x000D_
+_x000D_
+_x000D_
+nao chegou o prestador, as 21h12 liguei para central pois nao haviam chegado e me disseram que o prestador estava a caminho na radial leste (perto da minha casa), e que ele atrasou porque estava indo de carro (Normalmente para casos de bateria eles vem de moto), um absurdocomo cliente l, agora sao 22h18 quase duas horas apos a solicitação e ninguem sequer apareceu, mesmo eu ligando 3 x para central, e ninguem resolve o problema. Tenho um seguro do meu outro carro na porto seguro, e j precisei algumas vezes e esse carro tambem ja foi da porto e isso nunca aconteceu, é o primeiro ano que uso a allians.. Experiência péssima no atendimento 24 horas  protocolo do atendimento 51528834. tive prejuizo, perdi meu compromisso. Na teoria é uma boa companhia, mas no atendimento pratico são péssimos_x000D_
 _x000D_
 </t>
   </si>
   <si>
-    <t>95915235</t>
-  </si>
-  <si>
-    <t>241794475</t>
-  </si>
-  <si>
-    <t>26/02/2026 18:09</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Renovação ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Renovação</t>
-  </si>
-  <si>
-    <t>131482229</t>
-  </si>
-  <si>
-    <t>Totalmente insatisfeito com o serviço da seguradora. _x000D_
-_x000D_
-Sou cliente há um tempo e na minha primeira vez renovando o seguro ocorreu tudo conforme e prático, sem quaisquer dor de cabeça. Agora novamente necessito da renovação como de praxe os meus dados estão corretos e já aparece em meu extrato a parcela do seguro e também a parte das assinaturas estão ok, entrei em contato com o corretor e eles abriram uma solicitação para ver a questão da demora, entrei em contato com a ALLIANZ e a mesma informou que demora 25 dias úteis?! Tenho que esperar praticamente 1 mês (perdido) para renovar?! Mesmo tendo urgência de viajar com o veículo?! _x000D_
-_x000D_
-_x000D_
-Isso é um descaso com o cliente, pura decepção</t>
-  </si>
-  <si>
-    <t>95914813</t>
-  </si>
-  <si>
-    <t>241793229</t>
-  </si>
-  <si>
-    <t>26/02/2026 17:57</t>
-  </si>
-  <si>
-    <t>136199822</t>
-  </si>
-  <si>
-    <t>Uma pessoa jogou pedra no meu parabrisa. Solicitei a troca no dia 30/01 . Estamos no eia 26/02 e estamos na segunda vez que remarcam a chegada do parabrisa. A primeira vez a desculpa foi a transportadora não poderia trazer pois iria coincidir com o Carnaval,  ok. Agora dizem que estão tentando contato com a transportadora porém nao sabem onde esta a peça , que me retornaram mo outro dia, de fato , me ligam todo dia para falar que vão retornar no outro dia. Estou tendo que alugar carro, muito tempo para chegar uma peça simples. Gostaria de uma solução</t>
-  </si>
-  <si>
-    <t>95910763</t>
-  </si>
-  <si>
-    <t>241785181</t>
-  </si>
-  <si>
-    <t>26/02/2026 16:43</t>
+    <t>95997812</t>
+  </si>
+  <si>
+    <t>241909099</t>
+  </si>
+  <si>
+    <t>27/02/2026 21:21</t>
+  </si>
+  <si>
+    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; OUV ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>OUV</t>
+  </si>
+  <si>
+    <t>304558646</t>
+  </si>
+  <si>
+    <t>Assunto: Reclamação formal por demora excessiva, falha na prestação do serviço, informações divergentes e ausência de suporte adequado ao consumidor idoso  Sinistro n 304558646_x000D_
+_x000D_
+_x000D_
+Venho, por meio desta, formalizar reclamação contra a seguradora Allianz Seguros S/A, em razão da demora excessiva na conclusão do reparo do veículo, falhas reiteradas na condução do sinistro, prestação de informações divergentes, ausência de suporte adequado ao consumidor idoso e evidente falha na prestação do serviço._x000D_
+_x000D_
+_x000D_
+A apólice do seguro está em nome de Alda Márcia Gomes Ferreira Areas, pessoa idosa, com 66 anos de idade. O sinistro n 304558646 foi acionado em 15/01, ocasião em que o veículo de placa RBG7J47 foi rebocado pela seguradora e encaminhado para oficina credenciada._x000D_
+_x000D_
+_x000D_
+Desde então, já se passaram mais de 46 dias corridos sem a entrega do veículo, prazo manifestamente abusivo e incompatível com os princípios da razoabilidade, eficiência e boa-fé objetiva que regem as relações de consumo e a prestação de serviços securitários._x000D_
+_x000D_
+_x000D_
+Durante todo o período, foram registradas diversas falhas operacionais graves, tais como:_x000D_
+_x000D_
+- Atraso injustificado na entrega de peças;_x000D_
+_x000D_
+- Envio de peça incorreta, gerando novo atraso no reparo;_x000D_
+_x000D_
+- Necessidade de substituição da peça equivocada;_x000D_
+_x000D_
+- Identificação tardia de novos problemas apenas após longo período de imobilização do veículo;_x000D_
+_x000D_
+- Falta de previsibilidade e ausência de informações claras sobre o prazo real de conclusão._x000D_
+_x000D_
+_x000D_
+Adicionalmente, houve prestação de informações divergentes ao consumidor, incluindo a afirmação de que o veículo já teria sido indenizado, informação esta inverídica e extremamente grave, pois gerou insegurança, desinformação e demonstra clara falha na comunicação e transparência por parte da seguradora e/ou seus prestadores credenciados._x000D_
+_x000D_
+_x000D_
+Importante destacar que a segurada, Alda Márcia Gomes Ferreira Areas, possui 66 anos de idade, e seu esposo apresenta problemas no joelho, necessitando de locomoção adequada para atividades essenciais, consultas médicas e compromissos diários. A retenção prolongada do veículo, bem essencial à mobilidade, tem causado impactos diretos na qualidade de vida, dignidade e rotina familiar._x000D_
+_x000D_
+_x000D_
+Ressalta-se ainda que a apólice contratada contemplava o benefício de carro reserva, o qual foi disponibilizado apenas pelo período contratual de 15 dias. Contudo, mesmo diante da demora excessiva superior a 46 dias, da falha operacional da própria seguradora/oficina credenciada, da condição de pessoa idosa da segurada e da limitação física do esposo, em nenhum momento foi oferecida extensão do carro reserva ou solução alternativa de mobilidade, o que evidencia descaso com o consumidor e afronta aos princípios da boa-fé e da função social do contrato._x000D_
+_x000D_
+_x000D_
+Nos termos dos arts. 6, 14 e 20 do Código de Defesa do Consumidor, a responsabilidade da seguradora é objetiva, respondendo integralmente pela falha na prestação do serviço, inclusive por atos de oficinas credenciadas e problemas logísticos internos, não podendo o consumidor ser penalizado por erros operacionais, atraso de peças ou falhas técnicas de terceiros._x000D_
+_x000D_
+_x000D_
+A situação narrada caracteriza:_x000D_
+_x000D_
+- Falha grave na prestação do serviço;_x000D_
+_x000D_
+- Demora abusiva e desarrazoada no reparo do veículo;_x000D_
+_x000D_
+- Retenção indevida de bem essencial por período excessivo;_x000D_
+_x000D_
+- Falha na transparência e comunicação (informação incorreta sobre indenização);_x000D_
+_x000D_
+- Ausência de suporte adequado ao consumidor idoso;_x000D_
+_x000D_
+- Potencial dano material e moral decorrente dos transtornos e da limitação de mobilidade._x000D_
+_x000D_
+_x000D_
+Diante do exposto, requer-se formalmente:_x000D_
+_x000D_
+1) Definição imediata, formal e definitiva do prazo para conclusão do reparo e entrega do veículo placa RBG7J47;_x000D_
+_x000D_
+2) Esclarecimento oficial sobre a informação equivocada de suposta indenização do veículo;_x000D_
+_x000D_
+3) Relatório detalhado e cronológico de todo o andamento do sinistro n 304558646 desde 15/01;_x000D_
+_x000D_
+4) Avaliação de compensação pelos prejuízos e transtornos causados pela demora superior a 46 dias;_x000D_
+_x000D_
+5) Análise quanto à extensão do benefício de carro reserva ou indenização substitutiva pela ausência de mobilidade durante o período excedente;_x000D_
+_x000D_
+6) Apuração interna das falhas na condução do sinistro e na comunicação com o consumidor._x000D_
+_x000D_
+_x000D_
+Registra-se que a presente reclamação busca solução administrativa célere e proporcional, especialmente considerando tratar-se de segurada idosa (66 anos), com necessidade real de mobilidade familiar e diante de uma demora excessiva causada por falhas operacionais da própria cadeia de prestação do serviço securitário._x000D_
+_x000D_
+_x000D_
+Na ausência de solução imediata e efetiva, serão adotadas as medidas cabíveis junto aos órgãos reguladores, de defesa do consumidor e, se necessário, na esfera judicial, inclusive para reparação por danos materiais e morais decorrentes da falha na prestação do serviço e do prolongado período de indisponibilidade do veículo.</t>
+  </si>
+  <si>
+    <t>95996694</t>
+  </si>
+  <si>
+    <t>241908011</t>
+  </si>
+  <si>
+    <t>27/02/2026 21:05</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Assistência Não Danos ; Guincho ; Reclamante em nome do Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>135481749</t>
+  </si>
+  <si>
+    <t>Hoje o meu carro quebrou as 18hrs ? Assinoei  o seguro 18:30 , para rebocar o carro, eles pediram para aguarda que dentro de 1hrs eles chegariam, pois bem as 20:30 , entrei em contato com eles . E foi nformada que nao teria reboque para o.meu carro e tive que pagar um particular , então.pra que seguro se na hora que precisa nao ajuda</t>
+  </si>
+  <si>
+    <t>95988072</t>
+  </si>
+  <si>
+    <t>241899527</t>
+  </si>
+  <si>
+    <t>27/02/2026 19:06</t>
+  </si>
+  <si>
+    <t>131420181</t>
+  </si>
+  <si>
+    <t>Precisei do reboque da seguradora porém estou a quase 5 horas aguardando e sem previsão da chegada do prestador de serviços e segundo a central de atendimentos não tem previsão para chegada, estou sozinho, no escuro e em uma br movimentada correndo risco de vida. INADIMICIVEL !!!</t>
+  </si>
+  <si>
+    <t>95977105</t>
+  </si>
+  <si>
+    <t>241887545</t>
+  </si>
+  <si>
+    <t>27/02/2026 16:54</t>
   </si>
   <si>
     <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 2 Terceiro do Sinistro ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
   </si>
   <si>
-    <t>Sinistro</t>
-  </si>
-  <si>
-    <t>Análise Sinistro</t>
-  </si>
-  <si>
     <t>2 Terceiro do Sinistro</t>
   </si>
   <si>
-    <t>303946115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Após o sinistro ocorrido em 27/12/2025, a Allianz reconheceu a perda total do meu veículo Chevrolet Spin 2012/2013 e apresentou proposta de indenização no valor de R$ 51.000,00, com base na tabela FIPE._x000D_
-_x000D_
-Ocorre que o veículo foi adquirido por financiamento integral, sem entrada, e o valor atualmente necessário para quitação é de R$ 58.597,47. Assim, a quantia ofertada não é suficiente para liquidar a obrigação contratual vinculada ao bem sinistrado, resultando em diferença financeira significativa. A aceitação da proposta nos termos apresentados implicaria desembolso adicional para quitação do financiamento, além da perda definitiva do veículo._x000D_
-_x000D_
-Ressalte-se que, mesmo após o sinistro, continuaram sendo pagas parcelas do financiamento, o veículo permaneceu indisponível por aproximadamente dois meses, não houve disponibilização de carro reserva e foram suportadas despesas adicionais de transporte._x000D_
-_x000D_
-Diante desse cenário, busca-se solução adequada que efetivamente recomponha o prejuízo material experimentado, evitando a necessidade de adoção de medidas administrativas ou judiciais para discussão da suficiência da indenização e da extensão do dano._x000D_
-_x000D_
-Aguardamos posicionamento formal da empresa para encaminhamento da questão._x000D_
+    <t>304449613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mês dia 11/01, bateram no meu carro e depois de enviar documentação e vistoria, foi agendado para dia 02/02 para deixar meu carro na oficina parceira. Neste mesmo dia tive acesso ao orçamento, no qual constava reparo das portas onde haviam sido batidas, no mesmo dia entrei em contato com o corretor e informei que queria a troca da porta, pois devido o estrago, já imaginava que seria impossível o reparo ficar bom mas o corretor por sua fez me garantiu que não seria necessário a troca e me garantiu que o reparo ficaria perfeito. Mas no dia em que fui buscar meu carro (19/02), assim que me aproximei do carro já vi que a porta não ficou perfeita conforme o corretor se comprometeu comigo. No mesmo momento, antes de sair d em oficina, tentei contato com o corretor da Allianz várias vezes e o mesmo não me atendeu. Então, fiz contato com o 0800 da Allianz, na qual a mesma abriu minha reclamação e segundo fui informada, eles tinham o prazo de 1 dia útil para entrar em contato comigo, o qual até agora não aconteceu._x000D_
+_x000D_
+O corretor também está me enrolando, uma hora pede para eu abrir novamente outra reclamação na seguradora onde ELE representa, eu informei que não iria fazer, pois já tinha feito e depois de uns 2 dias cobrei uma posição do mesmo, que ficou de verificar e me informar_x000D_
+_x000D_
+*Descaso total. Estou me sentindo lesada materialmente e fisicamente falando.*_x000D_
+_x000D_
 _x000D_
 </t>
   </si>
   <si>
-    <t>95910466</t>
-  </si>
-  <si>
-    <t>241784413</t>
-  </si>
-  <si>
-    <t>26/02/2026 16:36</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Fornecimento de Peças ; 2 Terceiro do Sinistro ; SAC Aberto ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Fornecimento de Peças</t>
-  </si>
-  <si>
-    <t>Andreza</t>
-  </si>
-  <si>
-    <t>303987534</t>
-  </si>
-  <si>
-    <t>Sofri um acidente na data 30/12/25,  onde o responsavel acionou o seu seguro (Allianz), e foi autorizado a oficina para autorização do reparo, no dia 02/01/26 deixei o carro na oficina para passar por todo processo de avaliação, com orçamento fechado dia 05/01/26 e no dia 07/01/26 as peças  entraram em rota de envio para poderem ser entregue, sendo que as ultimas peças eram para ser entregues 19/01/26, prazo esse que nao foi cumprido, e deram um novo prazo de algumas peças para 04/02 e 06/02, onde teve um novo atraso, e eu ja vinha comunicando esse atraso a seguradora, e o restante das peças chegaram 19/02,  Porem em um novo contato, essas peças que chegaram foram as que vieram da concessionaria, ainda faltam as peças que vem diretamente da oficina, entrei em contato com a oficina 26/02/26 e comunicaram que as mesmas nao teriam prazo para chegada, de imediato comuniquei a central de sinistro da Aliianz que entraram em contato com a oficina e tambem não deram um prazo, a central pediu para que eu aguardasse até a segunda feira (02/03/26), ou seja nao foi resolvido, tambem entrei em contato com o SAC da seguradora mas sem resolução. Percebe-se que tal situação fere o codigo de defesa do consumidor, nao possuindo prazo para entrega, diversos atrasos, e quase 60 dias para nao resolução do sinsitro, sendo que o mercado possui peças.  Eu preciso saber o que realmente está havendo,  Ou se é somente descaso da empresa?? Estarei tomando medidas judiciais contra a seguradora. Não posso ficar sem trabalhar, quem vai cobrir meus prejuízos financeiros?? Se a seguradora nao trazer uma resolução e entrega do meu veiculo em tempo habil, irei ingressar com processo de indenização por danos materiais e morais.</t>
-  </si>
-  <si>
-    <t>95901163</t>
-  </si>
-  <si>
-    <t>241767059</t>
-  </si>
-  <si>
-    <t>26/02/2026 14:11</t>
-  </si>
-  <si>
-    <t>Allianz ; Sinistro ; Automóvel ; Sinistro ; Análise Sinistro ; 1 Segurado ; OUV ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>OUV</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>304058510</t>
-  </si>
-  <si>
-    <t>Título: Sinistro n 304058510  Veículo parado há mais de dois meses sem solução definitiva pela seguradora_x000D_
-_x000D_
-_x000D_
-No dia 24 de dezembro de 2025, meu veículo Nissan Kicks, placa IUH929, chassi 94DECAP15MB412528, fabricação 2020, modelo 2021, foi envolvido em uma colisão._x000D_
-_x000D_
-_x000D_
-O sinistro n 304058510 foi aberto junto à Allianz, e o veículo foi encaminhado à oficina Ferrino Reparo Automotiva no dia 29 de dezembro de 2025. A vistoria foi realizada em 5 de janeiro de 2026._x000D_
-_x000D_
-_x000D_
-Desde então, foram solicitadas as seguintes peças para reparo:_x000D_
-_x000D_
-  Farol esquerdo  código 260605RF4A_x000D_
-_x000D_
-  Lanterna traseira esquerda  código 265555RF0A_x000D_
-_x000D_
-  Eixo traseiro  BEAM COMPL RR SUSP  código 555015RROC_x000D_
-_x000D_
-_x000D_
-Contudo, até a presente data, essas peças não foram disponibilizadas, impedindo a conclusão do conserto. O veículo permanece parado há mais de dois meses, sem previsão concreta de finalização._x000D_
-_x000D_
-_x000D_
-Independentemente da eventual indisponibilidade de peças junto à montadora, é responsabilidade da seguradora garantir a adequada prestação do serviço contratado, assegurando a solução do sinistro dentro de prazo razoável e sem prejuízo excessivo ao segurado._x000D_
-_x000D_
-_x000D_
-Estou há mais de dois meses sem meu veículo e sem uma definição objetiva sobre qual medida será adotada._x000D_
-_x000D_
-_x000D_
-Diante disso, questiono formalmente:_x000D_
-_x000D_
-  Qual é a providência concreta que a Allianz adotará para resolver o sinistro?_x000D_
-_x000D_
-  Haverá indenização integral do veículo diante da impossibilidade de reparo em prazo razoável?_x000D_
-_x000D_
-  Será garantido veículo reserva até a efetiva solução do caso?_x000D_
-_x000D_
-  Qual é o prazo real e definitivo para encerramento do sinistro?_x000D_
-_x000D_
-_x000D_
-O consumidor não pode arcar com os prejuízos decorrentes da demora na cadeia de fornecimento ou na gestão do processo de reparo. Necessito de uma posição clara, formal e imediata, com definição objetiva sobre como a seguradora irá reparar os danos já suportados e assegurar meus direitos contratuais._x000D_
-_x000D_
-_x000D_
-Aguardo providências urgentes.</t>
-  </si>
-  <si>
-    <t>95896259</t>
-  </si>
-  <si>
-    <t>241760411</t>
-  </si>
-  <si>
-    <t>26/02/2026 13:16</t>
-  </si>
-  <si>
-    <t>Allianz ; Apólice ; Residência ; Apólice ; Condições Gerais ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Residência</t>
-  </si>
-  <si>
-    <t>Condições Gerais</t>
-  </si>
-  <si>
-    <t>134200614</t>
-  </si>
-  <si>
-    <t>Solicitei a seguradora informações detalhadas referente aos serviços disponíveis em minha apólice, não me passam Naao consta no site e nem na minha apólice, todo serviço que solicito informo que estrapolou minha apólice. Preciso do documento completo para consulta. Tentei fazer pelo zap, telefone e email e nada.</t>
-  </si>
-  <si>
-    <t>95884369</t>
-  </si>
-  <si>
-    <t>241740993</t>
-  </si>
-  <si>
-    <t>26/02/2026 10:49</t>
-  </si>
-  <si>
-    <t>Allianz ; Automóvel ; Apólice ; Assistência Não Danos ; Vidros - AutoGlass ; 1 Segurado ; Sac Enc ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
-  </si>
-  <si>
-    <t>Sac Enc</t>
-  </si>
-  <si>
-    <t>134719113</t>
-  </si>
-  <si>
-    <t>Fiz a abertura de uma reclamação no SAC da Allianz protocolo 26/0002173 solicitando reembolso de um serviço que foi prejudicado devido a uma credenciada da Allians e também solicitar que a nova troca do meu parabrisa seja feita em uma outra oficina sem ser a Fenix Auto vidros em juiz de fora, pois já é a terceira vez que tenho que ir lá reparar um péssimo serviço realizado em meu carro.  A Allianz me retornou apenas que eu posso ir até a credenciada realizar um novo serviço, nao se importando com as 02 solicitações que fiz junto ao sac. Preciso da solução deste tema!! nao adianta eu ir pela terceira na mesma oficina fazer o mesmo serviço, já está provado que a credenciada nao tem qualidade para isto.</t>
+    <t>95975194</t>
+  </si>
+  <si>
+    <t>241885255</t>
+  </si>
+  <si>
+    <t>27/02/2026 16:33</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Residência ; Assistência Não Danos ; Assistência Residencial ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>133246663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiz o agendamento para duas assistências (fixação de quadros/fixação de rede e dedetização) e ambas foram agendadas para o dia 27/02 no período matutino. Uma das assistências o prestador chegou no período da tarde, e o outro sequer apareceu._x000D_
+_x000D_
+Mesmo o que apareceu, totalmente despreparado para o serviço que foi realizar. Instalar um suporte de rede e quadros na parede. Simplesmente não conseguiu executar nada, não tinha broca para furar a pedra onde deixou apenas um lado furado, serviço inacabado, horrível, medonho, para a fixar o quadro sequer levou escada. Pergunto: Como a seguradora envia um prestador de serviço sem equipamentos básicos como broca e escada? _x000D_
+_x000D_
+Um total descaso com o cliente. Alterei toda a minha agenda, tirei animal de estimação de casa por conta da dedetização, alterei o dia da limpeza pois não pode limpar no mesmo dia após dedetizar, peguei folga no trabalho para esperar os prestadores e nenhum dos agendamentos foram concretizados._x000D_
+_x000D_
+Reclamei no atendimento via whats, ficaram de me dar um retorno em 30 minutos, já se passaram quase 30 horas e estou esperando até agora. Como fica o serviço inexecutado, os furos feitos nas paredes sem conclusão do serviço da rede, sem a fixação dos quadros e sem a dedetização realizada? O pagamento está em dia, quem arcará com tudo isso?_x000D_
+_x000D_
+Protocolos:  51487704 e 51487752_x000D_
+_x000D_
+</t>
+  </si>
+  <si>
+    <t>95974190</t>
+  </si>
+  <si>
+    <t>241884033</t>
+  </si>
+  <si>
+    <t>27/02/2026 16:21</t>
+  </si>
+  <si>
+    <t>304523429</t>
+  </si>
+  <si>
+    <t>Venho por meio deste registrar minha insatisfação com a conduta da seguradora Allianz, em razão de desconto indevido do IPVA e do licenciamento no pagamento de indenização referente a sinistro com perda total._x000D_
+_x000D_
+_x000D_
+Ressalto, desde já, que não sou o contratante do seguro, mas sim terceiro prejudicado, tendo direito a receber a indenização de forma integral, justa e proporcional, sem abatimentos indevidos._x000D_
+_x000D_
+_x000D_
+O sinistro ocorreu em 05 de janeiro de 2026, em seguida, pela própria seguradora, o veículo foi declarado perda total. No entanto, ao efetuar o pagamento da indenização, a seguradora descontou integralmente (12/12) o valor do IPVA e do licenciamento, o que considero abusivo, desproporcional e injustificável._x000D_
+_x000D_
+_x000D_
+O veículo existiu e esteve em minha posse por apenas 5 dias no exercício de 2026, não sendo razoável que recaia sobre mim  terceiro e vítima do sinistro  o pagamento integral de um imposto anual. O critério correto, justo e proporcional é o desconto de apenas 1/12 do IPVA, correspondente ao mês de janeiro, com a restituição dos 11/12 restantes, bem como do valor do licenciamento indevidamente abatido da indenização._x000D_
+_x000D_
+_x000D_
+A seguradora não pode transferir ao terceiro prejudicado um ônus tributário que não lhe compete, ainda mais em um caso de perda total ocorrida no início do ano, sob pena de violação aos princípios da boa-fé, razoabilidade e proporcionalidade, além de caracterizar prática abusiva contra o consumidor._x000D_
+_x000D_
+_x000D_
+Diante do exposto, exijo a devolução imediata dos valores correspondentes a 11/12 do IPVA e do licenciamento, devidamente corrigidos. Caso a situação não seja resolvida de forma administrativa e amigável, não me restará alternativa senão ingressar com ação no Juizado Especial Cível (Pequenas Causas) para garantir meus direitos._x000D_
+_x000D_
+_x000D_
+Aguardo uma solução rápida e definitiva.</t>
+  </si>
+  <si>
+    <t>95969519</t>
+  </si>
+  <si>
+    <t>241878201</t>
+  </si>
+  <si>
+    <t>27/02/2026 15:30</t>
+  </si>
+  <si>
+    <t>305506590</t>
+  </si>
+  <si>
+    <t>Desde o dia 09/02/2026 aguardando aprovação para realização do conserto do meu carro e até agora, dia 27/02/2026, quase 20 dias sem retorno. A concessionária já passou 2 orçamentos, ja desmontaram todo o motor e até agora não deram retorno sobre a realização do serviço. _x000D_
+_x000D_
+_x000D_
+Estou tendo que alugar carro por conta própria e nem o carro reserva eles disponibilizaram. Um absurdo total. _x000D_
+_x000D_
+_x000D_
+Quero retorno URGENTE!</t>
+  </si>
+  <si>
+    <t>95968568</t>
+  </si>
+  <si>
+    <t>241876841</t>
+  </si>
+  <si>
+    <t>27/02/2026 15:19</t>
+  </si>
+  <si>
+    <t>299387048</t>
+  </si>
+  <si>
+    <t>Descaso, falta de qualidade no serviço prestado e péssimo atendimento, isso é o que respondo quando me pedem um resumo do meu sentimento como cliente da Allianz como prestadora de seguros._x000D_
+_x000D_
+_x000D_
+Sou do RS, cliente da Allianz e estou muito insatisfeito com o atendimento e a qualidade do serviço que disponibilizam,  pois estou desde agosto de 2025 com problemas e ainda não tive minha solicitação concluída, mesmo com dois corretores de seguros distintos tentando me apoiar, o problemas nunca é resolvido._x000D_
+_x000D_
+_x000D_
+No dia 16/08/2025 tive um sinistro no meu carro, uma HAVAL H6, nesse dia em questão os problemas de atendimento começaram, pois a Allianz foi acionado e o guincho foi solicitado porém fiquei aguardando por quase duas horas, mas o guincho nunca chegou, ao ligar novamente fiquei sabendo que haviam cancelado o guincho pois meu carro era hibrido e nao tinham equipamento correto para rebocar um carro eletrico na empresa que haviam acionado e na regiao tb nao havia nenhuma guincho conveniado, POREM EU SO FIQUEI SABENDO DESSA SITUAÇÃO POIS LIGUEI, se nao ficaria eternamente aguardando um guincho que nao chegaria e em nenhum momento houve uma tentativa de me contatar para avisar essa situação._x000D_
+_x000D_
+_x000D_
+Mas o pior nao é isso e sim, que até hoje, 27/02/2026 o CARRO CONTINUA NO MEU NOME, mesmo tendo feito a assinatura de transferencia do veiculo e enviado para a Allianz e seu respectivo despachante, a empresa NÃO TRANSFERIU o veiculo. Apos quase 8 meses da batida fui inclusive ver que estava com pendencias do IPVA de um veiculo que teve perda total e nem era para estar mais em meu nome._x000D_
+_x000D_
+_x000D_
+É um absurdo, pois a empresa ainda insiste que transferiu, sendo que mandei fotos da pagina do Detran e do app da carteira de motorista mostrando que está no meu nome e que inclusive haviam pendencias nos documentos NO MEU NOME. _x000D_
+_x000D_
+_x000D_
+Allianz, o minimo que gostaria é um pouco de respeito com o seu cliente, assuma que errou e resolva as pendencias URGENTEMENTE. Estou cansado de ter que ficar explicando e explicando para os atendentes a situação e nada ser resolvido.</t>
+  </si>
+  <si>
+    <t>95965871</t>
+  </si>
+  <si>
+    <t>241873113</t>
+  </si>
+  <si>
+    <t>27/02/2026 14:48</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Cancelamento ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Cancelamento</t>
+  </si>
+  <si>
+    <t>136866625</t>
+  </si>
+  <si>
+    <t>Recebi hoje um e-mail de renovação de contrato de seguro, porém eu tenho o número do protocolo de atendimento onde eu fiz o cancelamento porque eu vendi o veículo e o veículo está na concessionária já e renovar o automático sem autorização ._x000D_
+_x000D_
+mesmo tendo ligado no início de Fevereiro para fazer o cancelamento e avisado que eu não iria fazer a renovação. Gostaria que fizesse o cancelamento desse seguro que fizeram sem autorização._x000D_
+_x000D_
+Segue o número do Protocolo 2624484748 cancelamento de seguro da Sportage</t>
+  </si>
+  <si>
+    <t>95956316</t>
+  </si>
+  <si>
+    <t>241861261</t>
+  </si>
+  <si>
+    <t>27/02/2026 13:01</t>
+  </si>
+  <si>
+    <t>Allianz ; CPF/CNPJ ; Automóvel ; Assistência Não Danos ; Guincho ; 11 Não Cliente ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>CPF/CNPJ</t>
+  </si>
+  <si>
+    <t>11 Não Cliente</t>
+  </si>
+  <si>
+    <t>5469156710</t>
+  </si>
+  <si>
+    <t>Olha que absurdo! Por isso a humanidade está doente com excesso de barulho e perturbação e o planeta se acabando com o efeito estufa. Esse caminhão veio atender um cliente na minha rua (demorou horas por sinal) e desde que ele chegou aqui o CAMINHÃO ESTÁ LIGADO. Já fui à janela várias vezes. Não tem ngm tentando colocar pra cima ou fzr qq movimento que justifique. Tem pelo menos 1h que está ligado a toa. Um barulho insuportável!!! Eu com autista em casa! E mesmo se não tivesse! De onde as pessoas tiram a ideia de que eh liberado incomodar as outras assim? Gastando combustível e jogando direto a poluição no ar; incomodando com barulho excessivo na porta dos outros! E tudo isso A TOA!!! Que ridículo! Patético! Desrespeitoso! Absurdo! Essa empresa NUNCA entrará na minha lista de opções. E olha q tenho carro há mtos anos.</t>
+  </si>
+  <si>
+    <t>95954584</t>
+  </si>
+  <si>
+    <t>241858937</t>
+  </si>
+  <si>
+    <t>27/02/2026 12:40</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Pagamento ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Pagamento</t>
+  </si>
+  <si>
+    <t>136228562</t>
+  </si>
+  <si>
+    <t>Minha reclamação neste momento é exclusivamente sobre a Allianz, e não sobre a corretora Interweg. Fui cliente da Porto por 10 anos e, neste ano, optei por migrar para a Allianz. Entretanto, estou bastante arrependido dessa escolha._x000D_
+_x000D_
+_x000D_
+Escolhi como forma de pagamento o cartão de crédito, que possui limite disponível. Ainda assim, nos três/dois meses em que sou cliente, recebi emails de cobrança solicitando pagamento via boleto. Além disso, ao consultar o autoatendimento da Allianz, o sistema indica inadimplência referente ao mês de dezembro, informação que não procede. Ressalto que, especificamente em dezembro, a contratação já havia apresentado diversas dificuldades, o que pode ter contribuído para alguma falha no processo._x000D_
+_x000D_
+_x000D_
+Diante disso, solicito:_x000D_
+_x000D_
+_x000D_
+Que não sejam enviados novos emails de cobrança via boleto, uma vez que essa não foi a forma de pagamento escolhida._x000D_
+_x000D_
+_x000D_
+A exclusão da inadimplência indevida referente ao mês de dezembro, especialmente considerando que o próprio sistema não permite emissão de boleto para esse período._x000D_
+_x000D_
+_x000D_
+Finalizo registrando minha preocupação de que a seguradora esteja adotando esse procedimento para evitar o pagamento das taxas do cartão de crédito, e informo desde já que será encerrada a relação com a Allianz assim que ocorrer término do contrato.</t>
+  </si>
+  <si>
+    <t>95952918</t>
+  </si>
+  <si>
+    <t>241857047</t>
+  </si>
+  <si>
+    <t>27/02/2026 12:24</t>
+  </si>
+  <si>
+    <t>305568852</t>
+  </si>
+  <si>
+    <t>Meu veículo encontra-se com um sinistro em aberto, está parado dentro da concessionária sem solução devido uma pancada na roda lado direto, os peritos foram 2x na loja, já foi identificado pelo gerente da oficina o que precisa ser trocado de peças e eles reprovam _x000D_
+_x000D_
+_x000D_
+Infelizmente o profissionalismo esta nota 0 _x000D_
+_x000D_
+Estou disposto a pagar franquia _x000D_
+_x000D_
+Necessito do meu veículo _x000D_
+_x000D_
+Estou á pé!!!_x000D_
+_x000D_
+_x000D_
+Quero a solução imediata!!</t>
+  </si>
+  <si>
+    <t>95942380</t>
+  </si>
+  <si>
+    <t>241845831</t>
+  </si>
+  <si>
+    <t>27/02/2026 10:56</t>
+  </si>
+  <si>
+    <t>Allianz ; Apólice ; Automóvel ; Apólice ; Emissão ; 1 Segurado ; Não ; Sim ; Repasse Time MindBe ; Sem Resposta - Dentro SLA</t>
+  </si>
+  <si>
+    <t>Emissão</t>
+  </si>
+  <si>
+    <t>133764760</t>
+  </si>
+  <si>
+    <t>A Allianz Auto vem adotando uma postura inadequada em relação aos seus segurados, realizando cobranças que considero indevidas._x000D_
+_x000D_
+_x000D_
+Há cerca de um mês, mudei de estado e trouxe comigo o veículo segurado. Assim que cheguei ao novo destino, comuniquei imediatamente a seguradora sobre a alteração de endereço. Nas primeiras semanas, permaneci em uma moradia temporária e, agora, após me estabelecer de forma definitiva, estou informando meu novo endereço residencial._x000D_
+_x000D_
+_x000D_
+No entanto, a empresa está tentando cobrar novamente uma taxa de alteração cadastral, mesmo já tendo sido comunicada anteriormente sobre a mudança. Ressalto, inclusive, que o novo endereço está localizado na avenida principal do bairro Ponta Negra, área turística de Natal e considerada ainda mais segura do que a anterior._x000D_
+_x000D_
+_x000D_
+Entendo que essa nova cobrança é indevida e representa uma prática abusiva, aproveitando-se do poder de cobrança da empresa e da vulnerabilidade do consumidor.</t>
+  </si>
+  <si>
+    <t>95941342</t>
+  </si>
+  <si>
+    <t>241845465</t>
+  </si>
+  <si>
+    <t>27/02/2026 10:53</t>
+  </si>
+  <si>
+    <t>134106321</t>
+  </si>
+  <si>
+    <t>Cancelei essa porcaria logo depois do pagamento e mesma assim lançaram na minha fatura paguei e agora o vendedor falou que não tem reembolso!!! Vou ter a acionar o Procon!!! Paguei um mês de graça sem fala que o meu veículo não está  mais no seguro!!! Quero o meu reembolso</t>
+  </si>
+  <si>
+    <t>95932685</t>
+  </si>
+  <si>
+    <t>241840137</t>
+  </si>
+  <si>
+    <t>27/02/2026 10:13</t>
+  </si>
+  <si>
+    <t>134225296</t>
+  </si>
+  <si>
+    <t>Ficam mandando mensagem de parcela atrasada que foi paga no dia  do vencimento através de débito automático bancário, o suporte é uma merda, o aplicativo não funciona, os atendimentos de chat são hipócritas e no 0800 da ouvidoria a Rosana além de imbecil que é ser respeitada mas não tem educação, nem sabe o que se faz na ouvidoria</t>
   </si>
 </sst>
 </file>
@@ -1152,25 +1334,25 @@
         <v>38</v>
       </c>
       <c r="M2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="W2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="Y2" s="3" t="s">
         <v>26</v>
@@ -1180,13 +1362,13 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>30</v>
@@ -1195,46 +1377,46 @@
         <v>31</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>51</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="V3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="V3" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="W3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Y3" s="3" t="s">
         <v>26</v>
@@ -1244,13 +1426,13 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>30</v>
@@ -1259,7 +1441,7 @@
         <v>31</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>33</v>
@@ -1271,34 +1453,34 @@
         <v>35</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="M4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="V4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="V4" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="W4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Y4" s="3" t="s">
         <v>26</v>
@@ -1308,13 +1490,13 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>30</v>
@@ -1323,7 +1505,7 @@
         <v>31</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>33</v>
@@ -1332,37 +1514,37 @@
         <v>34</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="V5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="V5" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="W5" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Y5" s="3" t="s">
         <v>26</v>
@@ -1372,13 +1554,13 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>30</v>
@@ -1387,46 +1569,46 @@
         <v>31</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>51</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="N6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O6" s="3" t="s">
+      <c r="P6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="3" t="s">
+      <c r="V6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="V6" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="W6" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="Y6" s="3" t="s">
         <v>26</v>
@@ -1436,13 +1618,13 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>30</v>
@@ -1451,40 +1633,40 @@
         <v>31</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="P7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P7" s="3" t="s">
+      <c r="V7" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="V7" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="W7" s="4" t="s">
         <v>81</v>
@@ -1515,46 +1697,46 @@
         <v>31</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="K8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="X8" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="W8" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="X8" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>26</v>
@@ -1564,13 +1746,13 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>30</v>
@@ -1579,46 +1761,46 @@
         <v>31</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="N9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="P9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="V9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="W9" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>26</v>
@@ -1628,13 +1810,13 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>30</v>
@@ -1643,7 +1825,7 @@
         <v>31</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>33</v>
@@ -1652,37 +1834,37 @@
         <v>34</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>104</v>
+        <v>37</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="N10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O10" s="3" t="s">
+      <c r="P10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P10" s="3" t="s">
+      <c r="V10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="W10" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="Y10" s="3" t="s">
         <v>26</v>
@@ -1690,13 +1872,13 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>30</v>
@@ -1705,84 +1887,613 @@
         <v>31</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>51</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>111</v>
+        <v>31</v>
       </c>
       <c r="N11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="O11" s="3" t="s">
+      <c r="P11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P11" s="3" t="s">
+      <c r="V11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="V11" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="W11" s="3" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Y11" s="3" t="s">
         <v>26</v>
       </c>
     </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="X12" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W13" s="4"/>
+      <c r="A13" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W13" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="X13" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y13" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
+      <c r="A14" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W14" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="X14" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W15" s="4"/>
+      <c r="A15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W15" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
+      <c r="A16" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W16" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="X16" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y16" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="17" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="18" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W18" s="4"/>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W18" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="X18" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="19" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W19" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="X19" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y19" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="20" spans="23:24" x14ac:dyDescent="0.2">
-      <c r="W20" s="4"/>
-      <c r="X20" s="4"/>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W20" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="X20" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="21" spans="23:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="W21" s="4"/>
     </row>
-    <row r="22" spans="23:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="W22" s="4"/>
       <c r="X22" s="4"/>
     </row>
